--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1024,62 +1024,62 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>997.15</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>925.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13091194606.6</t>
+          <t>12964522972.0</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14155319682.02</t>
+          <t>14209168625.62</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-44367517.39</v>
+        <v>-273240924.16</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,37 +1177,37 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO2" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-3.9</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>1002.3</t>
+          <t>997.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>916.24</t>
+          <t>920.92</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>11321413068.4</t>
+          <t>13091194606.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>13994353884.38</t>
+          <t>14155319682.02</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-516496615.28</v>
+        <v>-44367517.39</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,37 +1608,37 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO3" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-4.59</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,77 +1871,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1005.15</t>
+          <t>1002.3</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>911.3</t>
+          <t>916.24</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,27 +1961,27 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>11246965605.2</t>
+          <t>11321413068.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>13940555876.02</t>
+          <t>13994353884.38</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
@@ -1991,11 +1991,11 @@
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-374411751.64</v>
+        <v>-516496615.28</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,37 +2039,37 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO4" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2129,17 +2129,17 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11380.761</t>
+          <t>14451.354</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.42</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,42 +2302,42 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
@@ -2347,32 +2347,32 @@
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>1005.15</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>906.14</t>
+          <t>911.3</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>792.68</t>
+          <t>798.52</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-51.60</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>11237820653.0</t>
+          <t>13958553198.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>11891933198.2</t>
+          <t>11246965605.2</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15361285967.4</t>
+          <t>15377407355.7</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13790744516.9</t>
+          <t>13940555876.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-19367696.47659796</t>
+          <t>-73989858.81012851</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-503578481.4</v>
+        <v>-374411751.64</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,27 +2470,27 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO5" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
@@ -2500,7 +2500,7 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11544.121</t>
+          <t>11380.761</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.51</t>
+          <t>-6.11</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>973.4</t>
+          <t>972.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1009.3</t>
+          <t>1006.4</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>901.1</t>
+          <t>906.14</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>786.78</t>
+          <t>792.68</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-43.71</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-45.98</t>
+          <t>-51.60</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11343128112.0</t>
+          <t>11237820653.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13403862876.8</t>
+          <t>11891933198.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15214887680.6</t>
+          <t>15361285967.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13806820609.68</t>
+          <t>13790744516.9</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-1811024803</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>68670628.05428252</t>
+          <t>-19367696.47659796</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-378610376.88</v>
+        <v>-503578481.4</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>159.79</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,37 +2901,37 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO6" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>968.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>9673.113</t>
+          <t>11544.121</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-7.21</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,12 +3143,12 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>973.6</t>
+          <t>973.4</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1009.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>895.16</t>
+          <t>901.1</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>780.68</t>
+          <t>786.78</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.05</t>
+          <t>-43.71</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-45.98</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9333835091.0</t>
+          <t>11343128112.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>14406527688.6</t>
+          <t>13403862876.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15631820791.9</t>
+          <t>15214887680.6</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13722429318.62</t>
+          <t>13806820609.68</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1225293103</t>
+          <t>-1811024803</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>149994447.1341497</t>
+          <t>68670628.05428252</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-197845656.16</v>
+        <v>-378610376.88</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>155.29</t>
+          <t>159.79</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,27 +3332,27 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO7" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>956.0</t>
+          <t>968.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>10520.332</t>
+          <t>9673.113</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-6.07</t>
+          <t>-5.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>36.40</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,17 +3595,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3615,57 +3615,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>979.6</t>
+          <t>973.6</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1010.95</t>
+          <t>1010.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>889.38</t>
+          <t>895.16</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>774.52</t>
+          <t>780.68</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-38.15</t>
+          <t>-43.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-33.63</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10361490972.0</t>
+          <t>9333835091.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>16745332011.6</t>
+          <t>14406527688.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15236738765.8</t>
+          <t>15631820791.9</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13669578091.4</t>
+          <t>13722429318.62</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1508593245</t>
+          <t>-1225293103</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>213238102.2782578</t>
+          <t>149994447.1341497</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>282736970.56</v>
+        <v>-197845656.16</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>158.73</t>
+          <t>155.29</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,22 +3763,22 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO8" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP8" t="inlineStr">
@@ -3793,7 +3793,7 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>960.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>977.0</t>
+          <t>956.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>18127.318</t>
+          <t>10520.332</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-4.88</t>
+          <t>-6.77</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>36.40</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>986.0</t>
+          <t>979.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1011.4</t>
+          <t>1010.95</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>883.1</t>
+          <t>889.38</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>768.34</t>
+          <t>774.52</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-35.01</t>
+          <t>-38.15</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-27.30</t>
+          <t>-33.63</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>17183391163.0</t>
+          <t>10361490972.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>19507849106.2</t>
+          <t>16745332011.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14790780132.1</t>
+          <t>15236738765.8</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13601884471.72</t>
+          <t>13669578091.4</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1508593245</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>200601944.4081775</t>
+          <t>213238102.2782578</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>849079843.97</v>
+        <v>282736970.56</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>158.73</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,37 +4194,37 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO9" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18976.367</t>
+          <t>18127.318</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.75</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,12 +4457,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>986.0</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1011.4</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>876.72</t>
+          <t>883.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>762.28</t>
+          <t>768.34</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-35.01</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>51.24</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-27.30</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,27 +4547,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18797469046.0</t>
+          <t>17183391163.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>18830638736.6</t>
+          <t>19507849106.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13888309324.8</t>
+          <t>14790780132.1</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13500272781.74</t>
+          <t>13601884471.72</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4577,11 +4577,11 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>82696871.76092552</t>
+          <t>200601944.4081775</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>896898933.9400001</v>
+        <v>849079843.97</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>157.94</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,27 +4625,27 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO10" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>16545.187</t>
+          <t>18976.367</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>983.0</t>
+          <t>975.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.62</t>
+          <t>-6.44</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>65.66</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4903,62 +4903,62 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1024.6</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1006.1</t>
+          <t>1010.15</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>869.72</t>
+          <t>876.72</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>755.73</t>
+          <t>762.28</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>54.95</t>
+          <t>51.24</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-15.21</t>
+          <t>-20.93</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>16356452171.0</t>
+          <t>18797469046.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>17025912484.4</t>
+          <t>18830638736.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13248435709.6</t>
+          <t>13888309324.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13488520531.46</t>
+          <t>13500272781.74</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-65339866.81703715</t>
+          <t>82696871.76092552</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>760242898.79</v>
+        <v>896898933.9400001</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>160.05</t>
+          <t>157.94</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,27 +5056,27 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO11" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>992.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>1010.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>975.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>983.0</t>
+          <t>975.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.5</t>
+          <t>-1.21</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>21049.86</t>
+          <t>16545.187</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>995.0</t>
+          <t>983.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.0</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>30.50</t>
+          <t>28.51</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-1.97</t>
+          <t>-3.15</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>72.83</t>
+          <t>57.24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-2.14</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1,717</t>
+          <t>1,350</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>19610</t>
+          <t>11523</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>31.58</t>
+          <t>4.82</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.51</t>
+          <t>-4.06</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>4.15</t>
+          <t>1.84</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15.9</t>
+          <t>15.68</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.24</t>
+          <t>15.08</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1042.0</t>
+          <t>1024.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1000.5</t>
+          <t>1006.1</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>863.28</t>
+          <t>869.72</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>749.09</t>
+          <t>755.73</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-15.99</t>
+          <t>-22.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>48.78</t>
+          <t>42.48</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>58.07</t>
+          <t>54.95</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-10.40</t>
+          <t>-15.21</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6305605424.954414</t>
+          <t>6319708097.618497</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>21027856706.0</t>
+          <t>16356452171.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>16857113895.2</t>
+          <t>17025912484.4</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12917790221.2</t>
+          <t>13248435709.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13350361228.88</t>
+          <t>13488520531.46</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-215445824.2009059</t>
+          <t>-65339866.81703715</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>799405981.67</v>
+        <v>760242898.79</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>163.23</t>
+          <t>160.05</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,27 +5487,27 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>5.424847321536705</t>
+          <t>0.5656582232900037</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
         <is>
-          <t>26.71354526726619</t>
+          <t>47.83155119056676</t>
         </is>
       </c>
       <c r="BO12" t="inlineStr">
         <is>
-          <t>24.59143450787822</t>
+          <t>30.3369714889051</t>
         </is>
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>10.74</t>
+          <t>10.61</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>47.95</t>
+          <t>47.63</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>34.89</t>
+          <t>33.74</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2394935</t>
+          <t>2379349</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>1000.0</t>
+          <t>992.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>1015.0</t>
+          <t>1005.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>990.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>995.0</t>
+          <t>983.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>111.96</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>100.52</t>
+          <t>101.12</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3862957422.0</t>
+          <t>3985238440.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>7171595467.56</t>
+          <t>7220968787.64</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-379050437.08</v>
+        <v>-376123979.93</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,22 +5918,22 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO13" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP13" t="inlineStr">
@@ -5948,12 +5948,12 @@
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-10.72</t>
+          <t>-3.31</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,17 +6181,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>111.96</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>99.87</t>
+          <t>100.52</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3003565305.2</t>
+          <t>3862957422.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>7070679471.22</t>
+          <t>7171595467.56</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-731529321.58</v>
+        <v>-379050437.08</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,42 +6349,42 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO14" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-14.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,77 +6612,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>112.52</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>99.87</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>2923123432.4</t>
+          <t>3003565305.2</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>7004676232.68</t>
+          <t>7070679471.22</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-962313517.74</v>
+        <v>-731529321.58</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,42 +6780,42 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO15" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>20206.638</t>
+          <t>13178.714</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-29.70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>82.71</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-54.62</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-50.96</t>
+          <t>-56.85</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2119964809.0</t>
+          <t>1385646995.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3628117837.4</t>
+          <t>2923123432.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4590922523.2</t>
+          <t>4157974302.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>7037581985.4</t>
+          <t>7004676232.68</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-962804685</t>
+          <t>-1234850870</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-603815707.0069512</t>
+          <t>-658969216.3510649</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-863458529.16</v>
+        <v>-962313517.74</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,42 +7211,42 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO16" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,12 +7296,12 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
@@ -7311,7 +7311,7 @@
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32158.04</t>
+          <t>20206.638</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,12 +7474,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7489,62 +7489,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>110.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>112.7</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>97.59</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>81.99</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-48.86</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-50.96</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3377995788.0</t>
+          <t>2119964809.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3972870766.6</t>
+          <t>3628117837.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4754290282.0</t>
+          <t>4590922523.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>7089210465.74</t>
+          <t>7037581985.4</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-781419515</t>
+          <t>-962804685</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-556607921.1607085</t>
+          <t>-603815707.0069512</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-770076220.9299999</v>
+        <v>-863458529.16</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>88.97</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,27 +7642,27 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO17" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
@@ -7672,12 +7672,12 @@
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>28070.898</t>
+          <t>32158.04</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-9.22</t>
+          <t>-9.73</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-17.83</t>
+          <t>-16.44</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7925,57 +7925,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>110.4</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>112.88</t>
+          <t>112.7</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>97.59</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>80.55</t>
+          <t>81.27</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-44.97</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3069573936.0</t>
+          <t>3377995788.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>4159914695.6</t>
+          <t>3972870766.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>5062324469.3</t>
+          <t>4754290282.0</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7212241390.94</t>
+          <t>7089210465.74</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-902409773</t>
+          <t>-781419515</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-517795503.0207172</t>
+          <t>-556607921.1607085</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-743959234.75</v>
+        <v>-770076220.9299999</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>97.11</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,27 +8073,27 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO18" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>41008.816</t>
+          <t>28070.898</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.73</t>
+          <t>-12.84</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-17.83</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,17 +8336,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>16.53</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>112.95</t>
+          <t>112.88</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>80.55</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-25.10</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-34.84</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>4662435634.0</t>
+          <t>3069573936.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>5212568091.8</t>
+          <t>4159914695.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5086668589.6</t>
+          <t>5062324469.3</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>7342838422.34</t>
+          <t>7212241390.94</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>125899502</t>
+          <t>-902409773</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-476674824.5251145</t>
+          <t>-517795503.0207172</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-647034083.39</v>
+        <v>-743959234.75</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>103.44</t>
+          <t>97.11</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,27 +8504,27 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO19" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>44759.042</t>
+          <t>41008.816</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-11.22</t>
+          <t>-16.46</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,77 +8767,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>114.6</t>
+          <t>113.8</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>112.98</t>
+          <t>112.95</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>95.26</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>78.96</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-25.10</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-34.84</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4910619020.0</t>
+          <t>4662435634.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>5392825172.8</t>
+          <t>5212568091.8</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>5284409444.9</t>
+          <t>5086668589.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>7480816542.68</t>
+          <t>7342838422.34</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>108415727</t>
+          <t>125899502</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-445700413.8232446</t>
+          <t>-476674824.5251145</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-656124974.6799999</v>
+        <v>-647034083.39</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>103.44</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,27 +8935,27 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO20" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
           <t>112.0</t>
         </is>
       </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>33574.452</t>
+          <t>44759.042</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.73</t>
+          <t>-14.91</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9213,62 +9213,62 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>115.3</t>
+          <t>114.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.98</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>94.32</t>
+          <t>95.26</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>78.15</t>
+          <t>78.96</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-26.83</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3843729455.0</t>
+          <t>4910619020.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>5553727209.0</t>
+          <t>5392825172.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>6725058126.2</t>
+          <t>5284409444.9</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7456405170.48</t>
+          <t>7480816542.68</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1171330917</t>
+          <t>108415727</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-407441402.7588964</t>
+          <t>-445700413.8232446</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-672270004.5</v>
+        <v>-656124974.6799999</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>105.24</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,42 +9366,42 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO21" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>37105.11</t>
+          <t>33574.452</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-15.73</t>
+          <t>-17.49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-23.00</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>19.91</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>115.8</t>
+          <t>115.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>113.15</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>93.21</t>
+          <t>94.32</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>78.15</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-14.10</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-26.83</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4313215433.0</t>
+          <t>3843729455.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5535709797.4</t>
+          <t>5553727209.0</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>7188909240.3</t>
+          <t>6725058126.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7405586314.02</t>
+          <t>7456405170.48</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1653199442</t>
+          <t>-1171330917</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-359290747.8971783</t>
+          <t>-407441402.7588964</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-557015093.55</v>
+        <v>-672270004.5</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>105.24</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,27 +9797,27 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO22" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>70734.341</t>
+          <t>37105.11</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-19.57</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.83</t>
+          <t>-4.23</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.58</t>
+          <t>-23.00</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>12.02</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-10-31</t>
+          <t>2025-11-03</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>21.37</t>
+          <t>11.21</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.55</t>
+          <t>-1.28</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>1,462</t>
+          <t>484</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>72776</t>
+          <t>40908</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>50.0</t>
+          <t>66.67</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>57.94</t>
+          <t>62.7</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>0.69</t>
+          <t>-0.26</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.75</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>22.32</t>
+          <t>21.39</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>20.41</t>
+          <t>20.56</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>115.7</t>
+          <t>115.8</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>112.6</t>
+          <t>113.15</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>92.06</t>
+          <t>93.21</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>76.45</t>
+          <t>77.32</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-12.36</t>
+          <t>-14.10</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.51</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>7.84</t>
+          <t>7.58</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-23.62</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1850297997.719565</t>
+          <t>1856280346.958032</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>8332840917.0</t>
+          <t>4313215433.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>5964734243.0</t>
+          <t>5535709797.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>7237379106.9</t>
+          <t>7188909240.3</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7342423166.74</t>
+          <t>7405586314.02</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1272644863</t>
+          <t>-1653199442</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-323340866.8700235</t>
+          <t>-359290747.8971783</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-422773893.63</v>
+        <v>-557015093.55</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>110.67</t>
+          <t>108.86</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,27 +10228,27 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.7</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>-4.706727542950304</t>
+          <t>-4.506561377619261</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
         <is>
-          <t>3.929846696802713</t>
+          <t>17.0797647787938</t>
         </is>
       </c>
       <c r="BO23" t="inlineStr">
         <is>
-          <t>3.190012340264129</t>
+          <t>5.983401519253764</t>
         </is>
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.11</t>
+          <t>3.09</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.2</t>
+          <t>2.28</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>43.39</t>
+          <t>42.0</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>41.46</t>
+          <t>41.37</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>237169</t>
+          <t>229564</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10318,17 +10318,17 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>121.5</t>
+          <t>118.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>114.5</t>
+          <t>114.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>116.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>987.15</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>925.54</t>
+          <t>929.9</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>12964522972.0</t>
+          <t>13187701378.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14209168625.62</t>
+          <t>14292572173.18</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-273240924.16</v>
+        <v>-303325579.84</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>-2.0</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
           <t>-0.66</t>
         </is>
       </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-1.07</t>
-        </is>
-      </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1455,62 +1455,62 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>997.15</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>925.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13091194606.6</t>
+          <t>12964522972.0</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>14155319682.02</t>
+          <t>14209168625.62</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-44367517.39</v>
+        <v>-273240924.16</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-4.59</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>1002.3</t>
+          <t>997.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>916.24</t>
+          <t>920.92</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>11321413068.4</t>
+          <t>13091194606.6</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>13994353884.38</t>
+          <t>14155319682.02</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-516496615.28</v>
+        <v>-44367517.39</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.68</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,77 +2302,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1005.15</t>
+          <t>1002.3</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>911.3</t>
+          <t>916.24</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,27 +2392,27 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>11246965605.2</t>
+          <t>11321413068.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13940555876.02</t>
+          <t>13994353884.38</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
@@ -2422,11 +2422,11 @@
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-374411751.64</v>
+        <v>-516496615.28</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2560,17 +2560,17 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11380.761</t>
+          <t>14451.354</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-6.11</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,42 +2733,42 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
@@ -2778,32 +2778,32 @@
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>1005.15</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>906.14</t>
+          <t>911.3</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>792.68</t>
+          <t>798.52</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-51.60</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,27 +2823,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>11237820653.0</t>
+          <t>13958553198.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11891933198.2</t>
+          <t>11246965605.2</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15361285967.4</t>
+          <t>15377407355.7</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13790744516.9</t>
+          <t>13940555876.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-19367696.47659796</t>
+          <t>-73989858.81012851</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-503578481.4</v>
+        <v>-374411751.64</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,7 +2921,7 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11544.121</t>
+          <t>11380.761</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-7.21</t>
+          <t>-8.24</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>973.4</t>
+          <t>972.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1009.3</t>
+          <t>1006.4</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>901.1</t>
+          <t>906.14</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>786.78</t>
+          <t>792.68</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-43.71</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-45.98</t>
+          <t>-51.60</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,41 +3254,41 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11343128112.0</t>
+          <t>11237820653.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13403862876.8</t>
+          <t>11891933198.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15214887680.6</t>
+          <t>15361285967.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13806820609.68</t>
+          <t>13790744516.9</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-1811024803</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>68670628.05428252</t>
+          <t>-19367696.47659796</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-378610376.88</v>
+        <v>-503578481.4</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>159.79</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>968.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>9673.113</t>
+          <t>11544.121</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-5.35</t>
+          <t>-9.35</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,12 +3574,12 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>973.6</t>
+          <t>973.4</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1009.3</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>895.16</t>
+          <t>901.1</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>780.68</t>
+          <t>786.78</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-43.05</t>
+          <t>-43.71</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-45.98</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>9333835091.0</t>
+          <t>11343128112.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>14406527688.6</t>
+          <t>13403862876.8</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15631820791.9</t>
+          <t>15214887680.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13722429318.62</t>
+          <t>13806820609.68</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1225293103</t>
+          <t>-1811024803</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>149994447.1341497</t>
+          <t>68670628.05428252</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-197845656.16</v>
+        <v>-378610376.88</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>155.29</t>
+          <t>159.79</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>956.0</t>
+          <t>968.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>10520.332</t>
+          <t>9673.113</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-6.77</t>
+          <t>-7.46</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>36.40</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,17 +4026,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4046,57 +4046,57 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>979.6</t>
+          <t>973.6</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1010.95</t>
+          <t>1010.15</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>889.38</t>
+          <t>895.16</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>774.52</t>
+          <t>780.68</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-38.15</t>
+          <t>-43.05</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-33.63</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10361490972.0</t>
+          <t>9333835091.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>16745332011.6</t>
+          <t>14406527688.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15236738765.8</t>
+          <t>15631820791.9</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13669578091.4</t>
+          <t>13722429318.62</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1508593245</t>
+          <t>-1225293103</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>213238102.2782578</t>
+          <t>149994447.1341497</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>282736970.56</v>
+        <v>-197845656.16</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>158.73</t>
+          <t>155.29</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4224,12 +4224,12 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>960.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>977.0</t>
+          <t>956.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>18127.318</t>
+          <t>10520.332</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-8.91</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>36.40</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>986.0</t>
+          <t>979.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1011.4</t>
+          <t>1010.95</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>883.1</t>
+          <t>889.38</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>768.34</t>
+          <t>774.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-35.01</t>
+          <t>-38.15</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-27.30</t>
+          <t>-33.63</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>17183391163.0</t>
+          <t>10361490972.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>19507849106.2</t>
+          <t>16745332011.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14790780132.1</t>
+          <t>15236738765.8</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13601884471.72</t>
+          <t>13669578091.4</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1508593245</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>200601944.4081775</t>
+          <t>213238102.2782578</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>849079843.97</v>
+        <v>282736970.56</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>158.73</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18976.367</t>
+          <t>18127.318</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.44</t>
+          <t>-7.68</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,12 +4888,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>986.0</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1011.4</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>876.72</t>
+          <t>883.1</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>762.28</t>
+          <t>768.34</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-35.01</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>51.24</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-27.30</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,27 +4978,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18797469046.0</t>
+          <t>17183391163.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>18830638736.6</t>
+          <t>19507849106.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13888309324.8</t>
+          <t>14790780132.1</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13500272781.74</t>
+          <t>13601884471.72</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5008,11 +5008,11 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>82696871.76092552</t>
+          <t>200601944.4081775</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>896898933.9400001</v>
+        <v>849079843.97</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>157.94</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.82</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>16545.187</t>
+          <t>18976.367</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>983.0</t>
+          <t>975.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-8.57</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>28.51</t>
+          <t>35.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.15</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>57.24</t>
+          <t>65.66</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.14</t>
+          <t>-3.59</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1,350</t>
+          <t>861</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11523</t>
+          <t>13615</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,62 +5334,62 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>4.82</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-4.06</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>1.84</t>
+          <t>-0.55</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15.68</t>
+          <t>15.22</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.08</t>
+          <t>15.01</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1024.6</t>
+          <t>1004.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1006.1</t>
+          <t>1010.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>869.72</t>
+          <t>876.72</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>755.73</t>
+          <t>762.28</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-22.69</t>
+          <t>-28.92</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>42.48</t>
+          <t>36.42</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>54.95</t>
+          <t>51.24</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-15.21</t>
+          <t>-20.93</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6319708097.618497</t>
+          <t>6337328387.560606</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>16356452171.0</t>
+          <t>18797469046.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>17025912484.4</t>
+          <t>18830638736.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13248435709.6</t>
+          <t>13888309324.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13488520531.46</t>
+          <t>13500272781.74</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-65339866.81703715</t>
+          <t>82696871.76092552</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>760242898.79</v>
+        <v>896898933.9400001</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>160.05</t>
+          <t>157.94</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.29</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>10.61</t>
+          <t>10.52</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.78</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>47.63</t>
+          <t>46.7</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>33.74</t>
+          <t>33.39</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2379349</t>
+          <t>2332594</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>992.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>1005.0</t>
+          <t>1010.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>975.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>983.0</t>
+          <t>975.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5765,62 +5765,62 @@
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>111.34</t>
+          <t>110.06</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>101.66</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3985238440.6</t>
+          <t>4175037440.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>7220968787.64</t>
+          <t>7265450343.64</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-376123979.93</v>
+        <v>-433705440.9</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-3.31</t>
+          <t>-2.99</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>111.96</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>100.52</t>
+          <t>101.12</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3862957422.0</t>
+          <t>3985238440.6</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>7171595467.56</t>
+          <t>7220968787.64</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-379050437.08</v>
+        <v>-376123979.93</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6379,12 +6379,12 @@
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-14.39</t>
+          <t>-6.4</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,17 +6612,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6632,57 +6632,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>111.96</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>99.87</t>
+          <t>100.52</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3003565305.2</t>
+          <t>3862957422.0</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>7070679471.22</t>
+          <t>7171595467.56</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-731529321.58</v>
+        <v>-379050437.08</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-17.8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,77 +7043,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>112.52</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>99.87</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>2923123432.4</t>
+          <t>3003565305.2</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>7004676232.68</t>
+          <t>7070679471.22</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-962313517.74</v>
+        <v>-731529321.58</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>20206.638</t>
+          <t>13178.714</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-29.70</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>82.71</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-54.62</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-50.96</t>
+          <t>-56.85</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2119964809.0</t>
+          <t>1385646995.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3628117837.4</t>
+          <t>2923123432.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4590922523.2</t>
+          <t>4157974302.6</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>7037581985.4</t>
+          <t>7004676232.68</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-962804685</t>
+          <t>-1234850870</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-603815707.0069512</t>
+          <t>-658969216.3510649</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-863458529.16</v>
+        <v>-962313517.74</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,12 +7727,12 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
@@ -7742,7 +7742,7 @@
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32158.04</t>
+          <t>20206.638</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-9.73</t>
+          <t>-11.41</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,12 +7905,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7920,62 +7920,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>110.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>112.7</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>97.59</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>81.99</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-48.86</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-50.96</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3377995788.0</t>
+          <t>2119964809.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3972870766.6</t>
+          <t>3628117837.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4754290282.0</t>
+          <t>4590922523.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7089210465.74</t>
+          <t>7037581985.4</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-781419515</t>
+          <t>-962804685</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-556607921.1607085</t>
+          <t>-603815707.0069512</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-770076220.9299999</v>
+        <v>-863458529.16</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>88.97</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,7 +8093,7 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
@@ -8103,12 +8103,12 @@
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>28070.898</t>
+          <t>32158.04</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.84</t>
+          <t>-13.01</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-17.83</t>
+          <t>-16.44</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8356,57 +8356,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>110.4</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>112.88</t>
+          <t>112.7</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>97.59</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>80.55</t>
+          <t>81.27</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-44.97</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3069573936.0</t>
+          <t>3377995788.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>4159914695.6</t>
+          <t>3972870766.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>5062324469.3</t>
+          <t>4754290282.0</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>7212241390.94</t>
+          <t>7089210465.74</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-902409773</t>
+          <t>-781419515</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-517795503.0207172</t>
+          <t>-556607921.1607085</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-743959234.75</v>
+        <v>-770076220.9299999</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>97.11</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>41008.816</t>
+          <t>28070.898</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-16.46</t>
+          <t>-16.2</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-17.83</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,17 +8767,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>16.53</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>112.95</t>
+          <t>112.88</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>80.55</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-25.10</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-34.84</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>4662435634.0</t>
+          <t>3069573936.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>5212568091.8</t>
+          <t>4159914695.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>5086668589.6</t>
+          <t>5062324469.3</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>7342838422.34</t>
+          <t>7212241390.94</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>125899502</t>
+          <t>-902409773</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-476674824.5251145</t>
+          <t>-517795503.0207172</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-647034083.39</v>
+        <v>-743959234.75</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>103.44</t>
+          <t>97.11</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>44759.042</t>
+          <t>41008.816</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.91</t>
+          <t>-19.94</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,77 +9198,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>114.6</t>
+          <t>113.8</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>112.98</t>
+          <t>112.95</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>95.26</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>78.96</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-25.10</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-34.84</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>4910619020.0</t>
+          <t>4662435634.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>5392825172.8</t>
+          <t>5212568091.8</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>5284409444.9</t>
+          <t>5086668589.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7480816542.68</t>
+          <t>7342838422.34</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>108415727</t>
+          <t>125899502</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-445700413.8232446</t>
+          <t>-476674824.5251145</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-656124974.6799999</v>
+        <v>-647034083.39</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>103.44</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
           <t>112.0</t>
         </is>
       </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>33574.452</t>
+          <t>44759.042</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-17.49</t>
+          <t>-18.34</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,12 +9629,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9644,62 +9644,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>115.3</t>
+          <t>114.6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.98</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>94.32</t>
+          <t>95.26</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>78.15</t>
+          <t>78.96</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-26.83</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>3843729455.0</t>
+          <t>4910619020.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5553727209.0</t>
+          <t>5392825172.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>6725058126.2</t>
+          <t>5284409444.9</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7456405170.48</t>
+          <t>7480816542.68</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1171330917</t>
+          <t>108415727</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-407441402.7588964</t>
+          <t>-445700413.8232446</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-672270004.5</v>
+        <v>-656124974.6799999</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>105.24</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>37105.11</t>
+          <t>33574.452</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-19.57</t>
+          <t>-21.0</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.23</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-23.00</t>
+          <t>-17.42</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>9.13</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-03</t>
+          <t>2025-11-04</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>11.21</t>
+          <t>10.14</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.28</t>
+          <t>-2.18</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>484</t>
+          <t>429</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>40908</t>
+          <t>32133</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>66.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>62.7</t>
+          <t>38.89</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-0.26</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>21.39</t>
+          <t>19.91</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>20.56</t>
+          <t>20.69</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>115.8</t>
+          <t>115.3</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>113.15</t>
+          <t>113.1</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>93.21</t>
+          <t>94.32</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>77.32</t>
+          <t>78.15</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-14.10</t>
+          <t>-17.52</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>6.51</t>
+          <t>5.99</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>7.58</t>
+          <t>7.26</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-23.62</t>
+          <t>-26.83</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1856280346.958032</t>
+          <t>1860250230.433526</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4313215433.0</t>
+          <t>3843729455.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>5535709797.4</t>
+          <t>5553727209.0</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>7188909240.3</t>
+          <t>6725058126.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7405586314.02</t>
+          <t>7456405170.48</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1653199442</t>
+          <t>-1171330917</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-359290747.8971783</t>
+          <t>-407441402.7588964</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-557015093.55</v>
+        <v>-672270004.5</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>108.86</t>
+          <t>105.24</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|暮星</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.09</t>
+          <t>3.03</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.28</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>42.0</t>
+          <t>40.78</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>41.37</t>
+          <t>40.07</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>229564</t>
+          <t>222910</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>117.0</t>
+          <t>116.0</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>118.5</t>
+          <t>117.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>114.0</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,12 +1009,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,57 +1029,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>987.15</t>
+          <t>980.85</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>929.9</t>
+          <t>933.96</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13187701378.4</t>
+          <t>12590700418.8</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14292572173.18</t>
+          <t>14368721493.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-303325579.84</v>
+        <v>-420314020.7</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,17 +1197,17 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-2.0</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>987.15</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>925.54</t>
+          <t>929.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>12964522972.0</t>
+          <t>13187701378.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>14209168625.62</t>
+          <t>14292572173.18</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-273240924.16</v>
+        <v>-303325579.84</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,17 +1628,17 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-2.46</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1886,62 +1886,62 @@
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>997.15</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>925.54</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13091194606.6</t>
+          <t>12964522972.0</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14155319682.02</t>
+          <t>14209168625.62</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-44367517.39</v>
+        <v>-273240924.16</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,17 +2059,17 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-6.68</t>
+          <t>-3.13</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>1002.3</t>
+          <t>997.15</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>916.24</t>
+          <t>920.92</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>11321413068.4</t>
+          <t>13091194606.6</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>13994353884.38</t>
+          <t>14155319682.02</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-516496615.28</v>
+        <v>-44367517.39</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,17 +2490,17 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-7.16</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,77 +2733,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1005.15</t>
+          <t>1002.3</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>911.3</t>
+          <t>916.24</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,27 +2823,27 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11246965605.2</t>
+          <t>11321413068.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13940555876.02</t>
+          <t>13994353884.38</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
@@ -2853,11 +2853,11 @@
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-374411751.64</v>
+        <v>-516496615.28</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,17 +2921,17 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2991,17 +2991,17 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11380.761</t>
+          <t>14451.354</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.24</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,42 +3164,42 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
@@ -3209,32 +3209,32 @@
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>1005.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>906.14</t>
+          <t>911.3</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>792.68</t>
+          <t>798.52</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-51.60</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>11237820653.0</t>
+          <t>13958553198.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>11891933198.2</t>
+          <t>11246965605.2</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15361285967.4</t>
+          <t>15377407355.7</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13790744516.9</t>
+          <t>13940555876.02</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-19367696.47659796</t>
+          <t>-73989858.81012851</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-503578481.4</v>
+        <v>-374411751.64</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,7 +3352,7 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
@@ -3362,7 +3362,7 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3417,22 +3417,22 @@
       </c>
       <c r="CC7" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11544.121</t>
+          <t>11380.761</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-9.35</t>
+          <t>-8.72</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,77 +3595,77 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>973.4</t>
+          <t>972.8</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1009.3</t>
+          <t>1006.4</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>901.1</t>
+          <t>906.14</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>786.78</t>
+          <t>792.68</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-43.71</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-45.98</t>
+          <t>-51.60</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,41 +3685,41 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11343128112.0</t>
+          <t>11237820653.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>13403862876.8</t>
+          <t>11891933198.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15214887680.6</t>
+          <t>15361285967.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13806820609.68</t>
+          <t>13790744516.9</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-1811024803</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>68670628.05428252</t>
+          <t>-19367696.47659796</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-378610376.88</v>
+        <v>-503578481.4</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>159.79</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,17 +3783,17 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>968.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>9673.113</t>
+          <t>11544.121</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.46</t>
+          <t>-9.84</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,12 +4005,12 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>973.6</t>
+          <t>973.4</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1009.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>895.16</t>
+          <t>901.1</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>780.68</t>
+          <t>786.78</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-43.05</t>
+          <t>-43.71</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-45.98</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>9333835091.0</t>
+          <t>11343128112.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>14406527688.6</t>
+          <t>13403862876.8</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15631820791.9</t>
+          <t>15214887680.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13722429318.62</t>
+          <t>13806820609.68</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1225293103</t>
+          <t>-1811024803</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>149994447.1341497</t>
+          <t>68670628.05428252</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-197845656.16</v>
+        <v>-378610376.88</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>155.29</t>
+          <t>159.79</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
@@ -4224,7 +4224,7 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>956.0</t>
+          <t>968.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>10520.332</t>
+          <t>9673.113</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.91</t>
+          <t>-7.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,17 +4436,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>36.40</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4457,17 +4457,17 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
@@ -4477,57 +4477,57 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>979.6</t>
+          <t>973.6</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1010.95</t>
+          <t>1010.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>889.38</t>
+          <t>895.16</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>774.52</t>
+          <t>780.68</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-38.15</t>
+          <t>-43.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-33.63</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10361490972.0</t>
+          <t>9333835091.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>16745332011.6</t>
+          <t>14406527688.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15236738765.8</t>
+          <t>15631820791.9</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13669578091.4</t>
+          <t>13722429318.62</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1508593245</t>
+          <t>-1225293103</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>213238102.2782578</t>
+          <t>149994447.1341497</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>282736970.56</v>
+        <v>-197845656.16</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>158.73</t>
+          <t>155.29</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4655,7 +4655,7 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>960.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>977.0</t>
+          <t>956.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>18127.318</t>
+          <t>10520.332</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-7.68</t>
+          <t>-9.4</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>36.40</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,77 +4888,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>986.0</t>
+          <t>979.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1011.4</t>
+          <t>1010.95</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>883.1</t>
+          <t>889.38</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>768.34</t>
+          <t>774.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-35.01</t>
+          <t>-38.15</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-27.30</t>
+          <t>-33.63</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>17183391163.0</t>
+          <t>10361490972.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>19507849106.2</t>
+          <t>16745332011.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14790780132.1</t>
+          <t>15236738765.8</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13601884471.72</t>
+          <t>13669578091.4</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1508593245</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>200601944.4081775</t>
+          <t>213238102.2782578</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>849079843.97</v>
+        <v>282736970.56</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>158.73</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5076,7 +5076,7 @@
       </c>
       <c r="BP11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ11" t="inlineStr">
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.82</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18976.367</t>
+          <t>18127.318</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.57</t>
+          <t>-8.17</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>35.59</t>
+          <t>31.89</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>65.66</t>
+          <t>62.72</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.59</t>
+          <t>3.46</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,12 +5319,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>861</t>
+          <t>716</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>13615</t>
+          <t>12209</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5339,57 +5339,57 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-1.93</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-0.55</t>
+          <t>-2.51</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>15.22</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>15.01</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>1004.6</t>
+          <t>986.0</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1011.4</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>876.72</t>
+          <t>883.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>762.28</t>
+          <t>768.34</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-28.92</t>
+          <t>-35.01</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>36.42</t>
+          <t>30.62</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>51.24</t>
+          <t>47.12</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-20.93</t>
+          <t>-27.30</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,27 +5409,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6337328387.560606</t>
+          <t>6351914834.552594</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18797469046.0</t>
+          <t>17183391163.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>18830638736.6</t>
+          <t>19507849106.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13888309324.8</t>
+          <t>14790780132.1</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13500272781.74</t>
+          <t>13601884471.72</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5439,11 +5439,11 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>82696871.76092552</t>
+          <t>200601944.4081775</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>896898933.9400001</v>
+        <v>849079843.97</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>157.94</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;衝高回落&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,7 +5517,7 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>10.52</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>46.7</t>
+          <t>46.49</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>33.39</t>
+          <t>32.95</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2332594</t>
+          <t>2322203</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>1010.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>975.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32132.941</t>
+          <t>29839.894</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,12 +5750,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5770,57 +5770,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>98.74</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>110.06</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>101.66</t>
+          <t>102.19</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>85.35</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-161.08</t>
+          <t>-283.53</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-81.65</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4175037440.4</t>
+          <t>4453509900.0</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3901577638.9</t>
+          <t>3688316666.2</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>7265450343.64</t>
+          <t>7280178623.2</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>273459801</t>
+          <t>765193233</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-563422943.5374118</t>
+          <t>-551356508.5589601</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-433705440.9</v>
+        <v>-484991116.18</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-2.99</t>
+          <t>-0.86</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6196,62 +6196,62 @@
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>111.34</t>
+          <t>110.06</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>101.66</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3985238440.6</t>
+          <t>4175037440.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>7220968787.64</t>
+          <t>7265450343.64</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-376123979.93</v>
+        <v>-433705440.9</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.4</t>
+          <t>-3.87</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>111.96</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>100.52</t>
+          <t>101.12</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3862957422.0</t>
+          <t>3985238440.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>7171595467.56</t>
+          <t>7220968787.64</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-379050437.08</v>
+        <v>-376123979.93</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6810,12 +6810,12 @@
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-17.8</t>
+          <t>-7.31</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,17 +7043,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7063,57 +7063,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>111.96</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>99.87</t>
+          <t>100.52</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3003565305.2</t>
+          <t>3862957422.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>7070679471.22</t>
+          <t>7171595467.56</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-731529321.58</v>
+        <v>-379050437.08</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7231,22 +7231,22 @@
       </c>
       <c r="BP16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-18.82</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,77 +7474,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>112.52</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>99.87</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>2923123432.4</t>
+          <t>3003565305.2</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>7004676232.68</t>
+          <t>7070679471.22</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-962313517.74</v>
+        <v>-731529321.58</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>20206.638</t>
+          <t>13178.714</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-11.41</t>
+          <t>-13.98</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-29.70</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>82.71</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-54.62</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-50.96</t>
+          <t>-56.85</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2119964809.0</t>
+          <t>1385646995.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3628117837.4</t>
+          <t>2923123432.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4590922523.2</t>
+          <t>4157974302.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7037581985.4</t>
+          <t>7004676232.68</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-962804685</t>
+          <t>-1234850870</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-603815707.0069512</t>
+          <t>-658969216.3510649</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-863458529.16</v>
+        <v>-962313517.74</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,12 +8158,12 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
@@ -8173,7 +8173,7 @@
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>32158.04</t>
+          <t>20206.638</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-13.01</t>
+          <t>-12.37</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,12 +8336,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8351,62 +8351,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>110.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>112.7</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>97.59</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>81.99</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-48.86</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-50.96</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3377995788.0</t>
+          <t>2119964809.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3972870766.6</t>
+          <t>3628117837.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4754290282.0</t>
+          <t>4590922523.2</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>7089210465.74</t>
+          <t>7037581985.4</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-781419515</t>
+          <t>-962804685</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-556607921.1607085</t>
+          <t>-603815707.0069512</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-770076220.9299999</v>
+        <v>-863458529.16</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>88.97</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,7 +8524,7 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
@@ -8534,12 +8534,12 @@
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,22 +8589,22 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>28070.898</t>
+          <t>32158.04</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-16.2</t>
+          <t>-13.98</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-17.83</t>
+          <t>-16.44</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8787,57 +8787,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>110.4</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>112.88</t>
+          <t>112.7</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>97.59</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>80.55</t>
+          <t>81.27</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-44.97</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3069573936.0</t>
+          <t>3377995788.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>4159914695.6</t>
+          <t>3972870766.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>5062324469.3</t>
+          <t>4754290282.0</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>7212241390.94</t>
+          <t>7089210465.74</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-902409773</t>
+          <t>-781419515</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-517795503.0207172</t>
+          <t>-556607921.1607085</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-743959234.75</v>
+        <v>-770076220.9299999</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>97.11</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>41008.816</t>
+          <t>28070.898</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-19.94</t>
+          <t>-17.2</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-17.83</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,17 +9198,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>16.53</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>112.95</t>
+          <t>112.88</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>80.55</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-25.10</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-34.84</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>4662435634.0</t>
+          <t>3069573936.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>5212568091.8</t>
+          <t>4159914695.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>5086668589.6</t>
+          <t>5062324469.3</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7342838422.34</t>
+          <t>7212241390.94</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>125899502</t>
+          <t>-902409773</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-476674824.5251145</t>
+          <t>-517795503.0207172</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-647034083.39</v>
+        <v>-743959234.75</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>103.44</t>
+          <t>97.11</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,22 +9386,22 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>44759.042</t>
+          <t>41008.816</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-18.34</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,77 +9629,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>114.6</t>
+          <t>113.8</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>112.98</t>
+          <t>112.95</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>95.26</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>78.96</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-25.10</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-34.84</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4910619020.0</t>
+          <t>4662435634.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5392825172.8</t>
+          <t>5212568091.8</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>5284409444.9</t>
+          <t>5086668589.6</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7480816542.68</t>
+          <t>7342838422.34</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>108415727</t>
+          <t>125899502</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-445700413.8232446</t>
+          <t>-476674824.5251145</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-656124974.6799999</v>
+        <v>-647034083.39</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>103.44</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
           <t>112.0</t>
         </is>
       </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>-2.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>33574.452</t>
+          <t>44759.042</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-21.0</t>
+          <t>-19.35</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-5.2</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.42</t>
+          <t>2.05</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>9.13</t>
+          <t>6.73</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-04</t>
+          <t>2025-11-05</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>10.14</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.18</t>
+          <t>2.84</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,12 +10060,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>429</t>
+          <t>259</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>32133</t>
+          <t>29840</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10075,62 +10075,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>38.89</t>
+          <t>22.22</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-3.14</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>19.91</t>
+          <t>18.59</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>20.69</t>
+          <t>20.65</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>115.3</t>
+          <t>114.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>113.1</t>
+          <t>112.98</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>94.32</t>
+          <t>95.26</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>78.15</t>
+          <t>78.96</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-17.52</t>
+          <t>-22.68</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>5.99</t>
+          <t>5.31</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>7.26</t>
+          <t>6.87</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-26.83</t>
+          <t>-30.75</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1860250230.433526</t>
+          <t>1863578893.794373</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3843729455.0</t>
+          <t>4910619020.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>5553727209.0</t>
+          <t>5392825172.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>6725058126.2</t>
+          <t>5284409444.9</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7456405170.48</t>
+          <t>7480816542.68</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1171330917</t>
+          <t>108415727</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-407441402.7588964</t>
+          <t>-445700413.8232446</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-672270004.5</v>
+        <v>-656124974.6799999</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>105.24</t>
+          <t>100.72</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>3.03</t>
+          <t>2.97</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>40.78</t>
+          <t>40.43</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>40.07</t>
+          <t>40.19</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>222910</t>
+          <t>221009</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>117.5</t>
+          <t>112.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>111.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -878,12 +878,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -893,7 +893,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -908,12 +908,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -978,7 +978,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -988,17 +988,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1009,77 +1009,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>980.85</t>
+          <t>977.55</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>933.96</t>
+          <t>938.52</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1089,7 +1089,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1099,41 +1099,41 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>12590700418.8</t>
+          <t>13620510362.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14368721493.28</t>
+          <t>14466055493.78</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC2" t="n">
-        <v>-420314020.7</v>
+        <v>-123505858.33</v>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
@@ -1152,7 +1152,7 @@
       </c>
       <c r="BG2" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BH2" t="inlineStr">
@@ -1177,7 +1177,7 @@
       </c>
       <c r="BL2" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM2" t="inlineStr">
@@ -1197,22 +1197,22 @@
       </c>
       <c r="BP2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1222,7 +1222,7 @@
       </c>
       <c r="BU2" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV2" t="inlineStr">
@@ -1237,12 +1237,12 @@
       </c>
       <c r="BX2" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
@@ -1262,22 +1262,22 @@
       </c>
       <c r="CC2" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
@@ -1309,12 +1309,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1324,7 +1324,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1334,17 +1334,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.29</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1409,7 +1409,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1419,17 +1419,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1440,12 +1440,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1460,57 +1460,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>987.15</t>
+          <t>980.85</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>929.9</t>
+          <t>933.96</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,41 +1530,41 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13187701378.4</t>
+          <t>12590700418.8</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>14292572173.18</t>
+          <t>14368721493.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC3" t="n">
-        <v>-303325579.84</v>
+        <v>-420314020.7</v>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
@@ -1583,7 +1583,7 @@
       </c>
       <c r="BG3" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BH3" t="inlineStr">
@@ -1608,7 +1608,7 @@
       </c>
       <c r="BL3" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM3" t="inlineStr">
@@ -1628,22 +1628,22 @@
       </c>
       <c r="BP3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1653,7 +1653,7 @@
       </c>
       <c r="BU3" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV3" t="inlineStr">
@@ -1668,12 +1668,12 @@
       </c>
       <c r="BX3" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
@@ -1693,22 +1693,22 @@
       </c>
       <c r="CC3" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
@@ -1740,12 +1740,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1755,7 +1755,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1765,17 +1765,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-2.46</t>
+          <t>5.87</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1840,7 +1840,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1850,17 +1850,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1871,12 +1871,12 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
@@ -1891,57 +1891,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>987.15</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>925.54</t>
+          <t>929.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1951,7 +1951,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1961,41 +1961,41 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>12964522972.0</t>
+          <t>13187701378.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14209168625.62</t>
+          <t>14292572173.18</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC4" t="n">
-        <v>-273240924.16</v>
+        <v>-303325579.84</v>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
@@ -2014,7 +2014,7 @@
       </c>
       <c r="BG4" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BH4" t="inlineStr">
@@ -2039,7 +2039,7 @@
       </c>
       <c r="BL4" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM4" t="inlineStr">
@@ -2059,22 +2059,22 @@
       </c>
       <c r="BP4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2084,7 +2084,7 @@
       </c>
       <c r="BU4" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV4" t="inlineStr">
@@ -2099,12 +2099,12 @@
       </c>
       <c r="BX4" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
@@ -2124,22 +2124,22 @@
       </c>
       <c r="CC4" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
@@ -2171,12 +2171,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2186,7 +2186,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2196,17 +2196,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-3.13</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2271,7 +2271,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2281,17 +2281,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2302,12 +2302,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2317,62 +2317,62 @@
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>997.15</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>925.54</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2382,7 +2382,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2392,41 +2392,41 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13091194606.6</t>
+          <t>12964522972.0</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>14155319682.02</t>
+          <t>14209168625.62</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC5" t="n">
-        <v>-44367517.39</v>
+        <v>-273240924.16</v>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
@@ -2445,7 +2445,7 @@
       </c>
       <c r="BG5" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BH5" t="inlineStr">
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BL5" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM5" t="inlineStr">
@@ -2490,22 +2490,22 @@
       </c>
       <c r="BP5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2515,7 +2515,7 @@
       </c>
       <c r="BU5" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV5" t="inlineStr">
@@ -2530,12 +2530,12 @@
       </c>
       <c r="BX5" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
@@ -2555,22 +2555,22 @@
       </c>
       <c r="CC5" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
@@ -2602,12 +2602,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2617,7 +2617,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2627,17 +2627,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-7.16</t>
+          <t>3.35</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2702,7 +2702,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2712,17 +2712,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2733,12 +2733,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2748,62 +2748,62 @@
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>1002.3</t>
+          <t>997.15</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>916.24</t>
+          <t>920.92</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2813,7 +2813,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2823,41 +2823,41 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>11321413068.4</t>
+          <t>13091194606.6</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>13994353884.38</t>
+          <t>14155319682.02</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC6" t="n">
-        <v>-516496615.28</v>
+        <v>-44367517.39</v>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BG6" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BH6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BL6" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BP6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BU6" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BX6" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CC6" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,77 +3164,77 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>1005.15</t>
+          <t>1002.3</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>911.3</t>
+          <t>916.24</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3244,7 +3244,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3254,27 +3254,27 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>11246965605.2</t>
+          <t>11321413068.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>13940555876.02</t>
+          <t>13994353884.38</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
@@ -3284,11 +3284,11 @@
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC7" t="n">
-        <v>-374411751.64</v>
+        <v>-516496615.28</v>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
@@ -3307,7 +3307,7 @@
       </c>
       <c r="BG7" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BH7" t="inlineStr">
@@ -3332,7 +3332,7 @@
       </c>
       <c r="BL7" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM7" t="inlineStr">
@@ -3352,22 +3352,22 @@
       </c>
       <c r="BP7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3377,7 +3377,7 @@
       </c>
       <c r="BU7" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV7" t="inlineStr">
@@ -3392,12 +3392,12 @@
       </c>
       <c r="BX7" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
@@ -3422,17 +3422,17 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
@@ -3464,12 +3464,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11380.761</t>
+          <t>14451.354</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3479,7 +3479,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3489,17 +3489,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-8.72</t>
+          <t>-1.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3564,7 +3564,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3574,17 +3574,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3595,42 +3595,42 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
@@ -3640,32 +3640,32 @@
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>1005.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>906.14</t>
+          <t>911.3</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>792.68</t>
+          <t>798.52</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3675,7 +3675,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-51.60</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3685,27 +3685,27 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>11237820653.0</t>
+          <t>13958553198.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>11891933198.2</t>
+          <t>11246965605.2</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>15361285967.4</t>
+          <t>15377407355.7</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13790744516.9</t>
+          <t>13940555876.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
@@ -3715,11 +3715,11 @@
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-19367696.47659796</t>
+          <t>-73989858.81012851</t>
         </is>
       </c>
       <c r="BC8" t="n">
-        <v>-503578481.4</v>
+        <v>-374411751.64</v>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
@@ -3738,7 +3738,7 @@
       </c>
       <c r="BG8" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BH8" t="inlineStr">
@@ -3763,7 +3763,7 @@
       </c>
       <c r="BL8" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM8" t="inlineStr">
@@ -3783,7 +3783,7 @@
       </c>
       <c r="BP8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ8" t="inlineStr">
@@ -3793,12 +3793,12 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3808,7 +3808,7 @@
       </c>
       <c r="BU8" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV8" t="inlineStr">
@@ -3823,12 +3823,12 @@
       </c>
       <c r="BX8" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
@@ -3848,22 +3848,22 @@
       </c>
       <c r="CC8" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
@@ -3895,12 +3895,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11544.121</t>
+          <t>11380.761</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3910,7 +3910,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3920,17 +3920,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-9.84</t>
+          <t>-1.89</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3995,7 +3995,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4005,17 +4005,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4026,77 +4026,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>973.4</t>
+          <t>972.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1009.3</t>
+          <t>1006.4</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>901.1</t>
+          <t>906.14</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>786.78</t>
+          <t>792.68</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-43.71</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4106,7 +4106,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-45.98</t>
+          <t>-51.60</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4116,41 +4116,41 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>11343128112.0</t>
+          <t>11237820653.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>13403862876.8</t>
+          <t>11891933198.2</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15214887680.6</t>
+          <t>15361285967.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13806820609.68</t>
+          <t>13790744516.9</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-1811024803</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>68670628.05428252</t>
+          <t>-19367696.47659796</t>
         </is>
       </c>
       <c r="BC9" t="n">
-        <v>-378610376.88</v>
+        <v>-503578481.4</v>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
@@ -4169,7 +4169,7 @@
       </c>
       <c r="BG9" t="inlineStr">
         <is>
-          <t>159.79</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="BH9" t="inlineStr">
@@ -4194,7 +4194,7 @@
       </c>
       <c r="BL9" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM9" t="inlineStr">
@@ -4214,22 +4214,22 @@
       </c>
       <c r="BP9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BU9" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV9" t="inlineStr">
@@ -4254,12 +4254,12 @@
       </c>
       <c r="BX9" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
@@ -4279,22 +4279,22 @@
       </c>
       <c r="CC9" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>968.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
@@ -4326,12 +4326,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>9673.113</t>
+          <t>11544.121</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4341,7 +4341,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4351,17 +4351,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-7.94</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4426,7 +4426,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4436,12 +4436,12 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
@@ -4457,77 +4457,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>973.6</t>
+          <t>973.4</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1009.3</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>895.16</t>
+          <t>901.1</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>780.68</t>
+          <t>786.78</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-43.05</t>
+          <t>-43.71</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4537,7 +4537,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-45.98</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4547,41 +4547,41 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>9333835091.0</t>
+          <t>11343128112.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>14406527688.6</t>
+          <t>13403862876.8</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15631820791.9</t>
+          <t>15214887680.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13722429318.62</t>
+          <t>13806820609.68</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-1225293103</t>
+          <t>-1811024803</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>149994447.1341497</t>
+          <t>68670628.05428252</t>
         </is>
       </c>
       <c r="BC10" t="n">
-        <v>-197845656.16</v>
+        <v>-378610376.88</v>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
@@ -4600,7 +4600,7 @@
       </c>
       <c r="BG10" t="inlineStr">
         <is>
-          <t>155.29</t>
+          <t>159.79</t>
         </is>
       </c>
       <c r="BH10" t="inlineStr">
@@ -4625,7 +4625,7 @@
       </c>
       <c r="BL10" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM10" t="inlineStr">
@@ -4645,7 +4645,7 @@
       </c>
       <c r="BP10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ10" t="inlineStr">
@@ -4655,12 +4655,12 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4670,7 +4670,7 @@
       </c>
       <c r="BU10" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV10" t="inlineStr">
@@ -4685,12 +4685,12 @@
       </c>
       <c r="BX10" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
@@ -4710,22 +4710,22 @@
       </c>
       <c r="CC10" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>956.0</t>
+          <t>968.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
@@ -4757,12 +4757,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.12</t>
+          <t>-1.35</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>10520.332</t>
+          <t>9673.113</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4772,7 +4772,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4782,17 +4782,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.4</t>
+          <t>-1.15</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>9.90</t>
+          <t>-7.84</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4857,7 +4857,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.65</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4867,17 +4867,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>36.40</t>
+          <t>33.47</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.53</t>
+          <t>0.22</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4888,17 +4888,17 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>10.19</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
@@ -4908,57 +4908,57 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>-0.88</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.10</t>
+          <t>-3.62</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>12.85</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.66</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>979.6</t>
+          <t>973.6</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1010.95</t>
+          <t>1010.15</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>889.38</t>
+          <t>895.16</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>774.52</t>
+          <t>780.68</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-38.15</t>
+          <t>-43.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>26.61</t>
+          <t>22.12</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>43.02</t>
+          <t>38.84</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4968,7 +4968,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-33.63</t>
+          <t>-40.07</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4978,41 +4978,41 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10361490972.0</t>
+          <t>9333835091.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>16745332011.6</t>
+          <t>14406527688.6</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15236738765.8</t>
+          <t>15631820791.9</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13669578091.4</t>
+          <t>13722429318.62</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>1508593245</t>
+          <t>-1225293103</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>213238102.2782578</t>
+          <t>149994447.1341497</t>
         </is>
       </c>
       <c r="BC11" t="n">
-        <v>282736970.56</v>
+        <v>-197845656.16</v>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
@@ -5031,7 +5031,7 @@
       </c>
       <c r="BG11" t="inlineStr">
         <is>
-          <t>158.73</t>
+          <t>155.29</t>
         </is>
       </c>
       <c r="BH11" t="inlineStr">
@@ -5056,7 +5056,7 @@
       </c>
       <c r="BL11" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM11" t="inlineStr">
@@ -5086,12 +5086,12 @@
       </c>
       <c r="BR11" t="inlineStr">
         <is>
-          <t>10.55</t>
+          <t>10.41</t>
         </is>
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5101,7 +5101,7 @@
       </c>
       <c r="BU11" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV11" t="inlineStr">
@@ -5116,12 +5116,12 @@
       </c>
       <c r="BX11" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
@@ -5141,22 +5141,22 @@
       </c>
       <c r="CC11" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>960.0</t>
         </is>
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>977.0</t>
+          <t>956.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
@@ -5188,12 +5188,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>1.12</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>18127.318</t>
+          <t>10520.332</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5203,7 +5203,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5213,17 +5213,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-8.17</t>
+          <t>-2.52</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>31.89</t>
+          <t>9.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5288,7 +5288,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-3.65</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5298,17 +5298,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>62.72</t>
+          <t>36.40</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>3.46</t>
+          <t>-1.53</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5319,77 +5319,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>716</t>
+          <t>998</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>12209</t>
+          <t>16670</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>10.19</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.93</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-2.51</t>
+          <t>-3.10</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>986.0</t>
+          <t>979.6</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1011.4</t>
+          <t>1010.95</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>883.1</t>
+          <t>889.38</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>768.34</t>
+          <t>774.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-35.01</t>
+          <t>-38.15</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>30.62</t>
+          <t>26.61</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>47.12</t>
+          <t>43.02</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5399,7 +5399,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-27.30</t>
+          <t>-33.63</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5409,41 +5409,41 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6351914834.552594</t>
+          <t>6377054765.738849</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>17183391163.0</t>
+          <t>10361490972.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>19507849106.2</t>
+          <t>16745332011.6</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14790780132.1</t>
+          <t>15236738765.8</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13601884471.72</t>
+          <t>13669578091.4</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>1508593245</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>200601944.4081775</t>
+          <t>213238102.2782578</t>
         </is>
       </c>
       <c r="BC12" t="n">
-        <v>849079843.97</v>
+        <v>282736970.56</v>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
@@ -5462,7 +5462,7 @@
       </c>
       <c r="BG12" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>158.73</t>
         </is>
       </c>
       <c r="BH12" t="inlineStr">
@@ -5487,7 +5487,7 @@
       </c>
       <c r="BL12" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="BM12" t="inlineStr">
@@ -5507,7 +5507,7 @@
       </c>
       <c r="BP12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ12" t="inlineStr">
@@ -5517,12 +5517,12 @@
       </c>
       <c r="BR12" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.55</t>
         </is>
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5532,7 +5532,7 @@
       </c>
       <c r="BU12" t="inlineStr">
         <is>
-          <t>46.49</t>
+          <t>49.61</t>
         </is>
       </c>
       <c r="BV12" t="inlineStr">
@@ -5547,12 +5547,12 @@
       </c>
       <c r="BX12" t="inlineStr">
         <is>
-          <t>32.95</t>
+          <t>33.81</t>
         </is>
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>2322203</t>
+          <t>2478056</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
@@ -5572,22 +5572,22 @@
       </c>
       <c r="CC12" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>977.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
@@ -5619,12 +5619,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>29839.894</t>
+          <t>31967.753</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5634,7 +5634,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5649,12 +5649,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5664,7 +5664,7 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
@@ -5719,7 +5719,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5729,17 +5729,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5750,77 +5750,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>95.85999999999999</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>108.02</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>102.19</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-283.53</t>
+          <t>-712.58</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5830,7 +5830,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5840,41 +5840,41 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4453509900.0</t>
+          <t>4058514408.6</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3688316666.2</t>
+          <t>3531039856.9</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>7280178623.2</t>
+          <t>7317342463.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>765193233</t>
+          <t>527474551</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-551356508.5589601</t>
+          <t>-541208113.7606318</t>
         </is>
       </c>
       <c r="BC13" t="n">
-        <v>-484991116.18</v>
+        <v>-485391942.37</v>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
@@ -5893,7 +5893,7 @@
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
@@ -5918,7 +5918,7 @@
       </c>
       <c r="BL13" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM13" t="inlineStr">
@@ -5938,22 +5938,22 @@
       </c>
       <c r="BP13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
@@ -5963,7 +5963,7 @@
       </c>
       <c r="BU13" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV13" t="inlineStr">
@@ -5978,12 +5978,12 @@
       </c>
       <c r="BX13" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
@@ -6050,12 +6050,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32132.941</t>
+          <t>29839.894</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6065,7 +6065,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6075,17 +6075,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-0.86</t>
+          <t>3.23</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6095,7 +6095,7 @@
       </c>
       <c r="L14" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M14" t="inlineStr">
@@ -6150,7 +6150,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6160,17 +6160,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6181,12 +6181,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6201,57 +6201,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>98.74</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>110.06</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>101.66</t>
+          <t>102.19</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>85.35</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-161.08</t>
+          <t>-283.53</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6261,7 +6261,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-81.65</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6271,41 +6271,41 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>4175037440.4</t>
+          <t>4453509900.0</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3901577638.9</t>
+          <t>3688316666.2</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>7265450343.64</t>
+          <t>7280178623.2</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>273459801</t>
+          <t>765193233</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-563422943.5374118</t>
+          <t>-551356508.5589601</t>
         </is>
       </c>
       <c r="BC14" t="n">
-        <v>-433705440.9</v>
+        <v>-484991116.18</v>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
@@ -6324,7 +6324,7 @@
       </c>
       <c r="BG14" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="BH14" t="inlineStr">
@@ -6349,7 +6349,7 @@
       </c>
       <c r="BL14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM14" t="inlineStr">
@@ -6369,22 +6369,22 @@
       </c>
       <c r="BP14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BU14" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV14" t="inlineStr">
@@ -6409,12 +6409,12 @@
       </c>
       <c r="BX14" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
@@ -6434,22 +6434,22 @@
       </c>
       <c r="CC14" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
@@ -6481,12 +6481,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6496,7 +6496,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6506,17 +6506,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.87</t>
+          <t>2.39</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6526,7 +6526,7 @@
       </c>
       <c r="L15" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M15" t="inlineStr">
@@ -6581,7 +6581,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6591,17 +6591,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6612,12 +6612,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6627,62 +6627,62 @@
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>111.34</t>
+          <t>110.06</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>101.66</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6692,7 +6692,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6702,41 +6702,41 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3985238440.6</t>
+          <t>4175037440.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>7220968787.64</t>
+          <t>7265450343.64</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC15" t="n">
-        <v>-376123979.93</v>
+        <v>-433705440.9</v>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
@@ -6755,7 +6755,7 @@
       </c>
       <c r="BG15" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BH15" t="inlineStr">
@@ -6780,7 +6780,7 @@
       </c>
       <c r="BL15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM15" t="inlineStr">
@@ -6800,22 +6800,22 @@
       </c>
       <c r="BP15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
@@ -6825,7 +6825,7 @@
       </c>
       <c r="BU15" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV15" t="inlineStr">
@@ -6840,12 +6840,12 @@
       </c>
       <c r="BX15" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
@@ -6865,22 +6865,22 @@
       </c>
       <c r="CC15" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
@@ -6912,12 +6912,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6927,7 +6927,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6937,17 +6937,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-7.31</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -6957,7 +6957,7 @@
       </c>
       <c r="L16" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M16" t="inlineStr">
@@ -7012,7 +7012,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7022,17 +7022,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7043,12 +7043,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7058,62 +7058,62 @@
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>111.96</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>100.52</t>
+          <t>101.12</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7123,7 +7123,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7133,41 +7133,41 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>3862957422.0</t>
+          <t>3985238440.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>7171595467.56</t>
+          <t>7220968787.64</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC16" t="n">
-        <v>-379050437.08</v>
+        <v>-376123979.93</v>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
@@ -7186,7 +7186,7 @@
       </c>
       <c r="BG16" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BH16" t="inlineStr">
@@ -7211,7 +7211,7 @@
       </c>
       <c r="BL16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM16" t="inlineStr">
@@ -7241,12 +7241,12 @@
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
@@ -7256,7 +7256,7 @@
       </c>
       <c r="BU16" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV16" t="inlineStr">
@@ -7271,12 +7271,12 @@
       </c>
       <c r="BX16" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
@@ -7296,22 +7296,22 @@
       </c>
       <c r="CC16" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
@@ -7343,12 +7343,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7358,7 +7358,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7368,17 +7368,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-18.82</t>
+          <t>-3.85</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7388,7 +7388,7 @@
       </c>
       <c r="L17" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M17" t="inlineStr">
@@ -7443,7 +7443,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7453,17 +7453,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7474,17 +7474,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7494,57 +7494,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>111.96</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>99.87</t>
+          <t>100.52</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7554,7 +7554,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7564,41 +7564,41 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3003565305.2</t>
+          <t>3862957422.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>7070679471.22</t>
+          <t>7171595467.56</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC17" t="n">
-        <v>-731529321.58</v>
+        <v>-379050437.08</v>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
@@ -7617,7 +7617,7 @@
       </c>
       <c r="BG17" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BH17" t="inlineStr">
@@ -7642,7 +7642,7 @@
       </c>
       <c r="BL17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM17" t="inlineStr">
@@ -7662,22 +7662,22 @@
       </c>
       <c r="BP17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
@@ -7687,7 +7687,7 @@
       </c>
       <c r="BU17" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV17" t="inlineStr">
@@ -7702,12 +7702,12 @@
       </c>
       <c r="BX17" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
@@ -7727,22 +7727,22 @@
       </c>
       <c r="CC17" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
@@ -7774,12 +7774,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7789,7 +7789,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7799,17 +7799,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-13.98</t>
+          <t>-14.98</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7819,7 +7819,7 @@
       </c>
       <c r="L18" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7905,77 +7905,77 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>112.52</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>99.87</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7985,7 +7985,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7995,41 +7995,41 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>2923123432.4</t>
+          <t>3003565305.2</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7004676232.68</t>
+          <t>7070679471.22</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC18" t="n">
-        <v>-962313517.74</v>
+        <v>-731529321.58</v>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
@@ -8048,7 +8048,7 @@
       </c>
       <c r="BG18" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BH18" t="inlineStr">
@@ -8073,7 +8073,7 @@
       </c>
       <c r="BL18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM18" t="inlineStr">
@@ -8093,22 +8093,22 @@
       </c>
       <c r="BP18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
@@ -8118,7 +8118,7 @@
       </c>
       <c r="BU18" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV18" t="inlineStr">
@@ -8133,12 +8133,12 @@
       </c>
       <c r="BX18" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
@@ -8158,22 +8158,22 @@
       </c>
       <c r="CC18" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
@@ -8205,12 +8205,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>20206.638</t>
+          <t>13178.714</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8220,7 +8220,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8230,17 +8230,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-12.37</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-29.70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8250,7 +8250,7 @@
       </c>
       <c r="L19" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M19" t="inlineStr">
@@ -8305,7 +8305,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8315,17 +8315,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8336,77 +8336,77 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>82.71</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-54.62</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8416,7 +8416,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-50.96</t>
+          <t>-56.85</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8426,41 +8426,41 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2119964809.0</t>
+          <t>1385646995.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3628117837.4</t>
+          <t>2923123432.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4590922523.2</t>
+          <t>4157974302.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>7037581985.4</t>
+          <t>7004676232.68</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-962804685</t>
+          <t>-1234850870</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-603815707.0069512</t>
+          <t>-658969216.3510649</t>
         </is>
       </c>
       <c r="BC19" t="n">
-        <v>-863458529.16</v>
+        <v>-962313517.74</v>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
@@ -8479,7 +8479,7 @@
       </c>
       <c r="BG19" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH19" t="inlineStr">
@@ -8504,7 +8504,7 @@
       </c>
       <c r="BL19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM19" t="inlineStr">
@@ -8524,22 +8524,22 @@
       </c>
       <c r="BP19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
@@ -8549,7 +8549,7 @@
       </c>
       <c r="BU19" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV19" t="inlineStr">
@@ -8564,12 +8564,12 @@
       </c>
       <c r="BX19" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
@@ -8589,12 +8589,12 @@
       </c>
       <c r="CC19" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
@@ -8604,7 +8604,7 @@
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
@@ -8636,12 +8636,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32158.04</t>
+          <t>20206.638</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8651,7 +8651,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8661,17 +8661,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-13.98</t>
+          <t>-8.74</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8681,7 +8681,7 @@
       </c>
       <c r="L20" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M20" t="inlineStr">
@@ -8736,7 +8736,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8746,17 +8746,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8767,12 +8767,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8782,62 +8782,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>110.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>112.7</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>97.59</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>81.99</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-48.86</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8847,7 +8847,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-50.96</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8857,41 +8857,41 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3377995788.0</t>
+          <t>2119964809.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>3972870766.6</t>
+          <t>3628117837.4</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4754290282.0</t>
+          <t>4590922523.2</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>7089210465.74</t>
+          <t>7037581985.4</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-781419515</t>
+          <t>-962804685</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-556607921.1607085</t>
+          <t>-603815707.0069512</t>
         </is>
       </c>
       <c r="BC20" t="n">
-        <v>-770076220.9299999</v>
+        <v>-863458529.16</v>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
@@ -8910,7 +8910,7 @@
       </c>
       <c r="BG20" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>88.97</t>
         </is>
       </c>
       <c r="BH20" t="inlineStr">
@@ -8935,7 +8935,7 @@
       </c>
       <c r="BL20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM20" t="inlineStr">
@@ -8955,7 +8955,7 @@
       </c>
       <c r="BP20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ20" t="inlineStr">
@@ -8965,12 +8965,12 @@
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
@@ -8980,7 +8980,7 @@
       </c>
       <c r="BU20" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV20" t="inlineStr">
@@ -8995,12 +8995,12 @@
       </c>
       <c r="BX20" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
@@ -9020,22 +9020,22 @@
       </c>
       <c r="CC20" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
@@ -9067,12 +9067,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>28070.898</t>
+          <t>32158.04</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9082,7 +9082,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9092,17 +9092,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-17.2</t>
+          <t>-10.3</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-17.83</t>
+          <t>-16.44</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9112,7 +9112,7 @@
       </c>
       <c r="L21" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M21" t="inlineStr">
@@ -9167,7 +9167,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9177,17 +9177,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9198,12 +9198,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9218,57 +9218,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>110.4</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>112.88</t>
+          <t>112.7</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>97.59</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>80.55</t>
+          <t>81.27</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9278,7 +9278,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-44.97</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9288,41 +9288,41 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3069573936.0</t>
+          <t>3377995788.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>4159914695.6</t>
+          <t>3972870766.6</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>5062324469.3</t>
+          <t>4754290282.0</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7212241390.94</t>
+          <t>7089210465.74</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-902409773</t>
+          <t>-781419515</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-517795503.0207172</t>
+          <t>-556607921.1607085</t>
         </is>
       </c>
       <c r="BC21" t="n">
-        <v>-743959234.75</v>
+        <v>-770076220.9299999</v>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
@@ -9341,7 +9341,7 @@
       </c>
       <c r="BG21" t="inlineStr">
         <is>
-          <t>97.11</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BH21" t="inlineStr">
@@ -9366,7 +9366,7 @@
       </c>
       <c r="BL21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM21" t="inlineStr">
@@ -9386,7 +9386,7 @@
       </c>
       <c r="BP21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BQ21" t="inlineStr">
@@ -9396,12 +9396,12 @@
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
@@ -9411,7 +9411,7 @@
       </c>
       <c r="BU21" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV21" t="inlineStr">
@@ -9426,12 +9426,12 @@
       </c>
       <c r="BX21" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
@@ -9451,22 +9451,22 @@
       </c>
       <c r="CC21" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
@@ -9498,12 +9498,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.3</t>
+          <t>-3.17</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>41008.816</t>
+          <t>28070.898</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9513,7 +9513,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9523,17 +9523,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-13.42</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>-17.83</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9543,7 +9543,7 @@
       </c>
       <c r="L22" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M22" t="inlineStr">
@@ -9598,7 +9598,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>8.17</t>
+          <t>4.81</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9608,17 +9608,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-06</t>
+          <t>2025-11-07</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>12.39</t>
+          <t>8.48</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-2.66</t>
+          <t>-2.29</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9629,17 +9629,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>27.27</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9649,57 +9649,57 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.14</t>
+          <t>-2.94</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>-0.51</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>17.46</t>
+          <t>16.53</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>20.54</t>
+          <t>20.25</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>113.8</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>112.95</t>
+          <t>112.88</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>96.16</t>
+          <t>96.86</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>79.78</t>
+          <t>80.55</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-25.10</t>
+          <t>-31.01</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>4.84</t>
+          <t>4.14</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>6.46</t>
+          <t>6.00</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9709,7 +9709,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-34.84</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9719,41 +9719,41 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>4662435634.0</t>
+          <t>3069573936.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>5212568091.8</t>
+          <t>4159914695.6</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>5086668589.6</t>
+          <t>5062324469.3</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7342838422.34</t>
+          <t>7212241390.94</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>125899502</t>
+          <t>-902409773</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-476674824.5251145</t>
+          <t>-517795503.0207172</t>
         </is>
       </c>
       <c r="BC22" t="n">
-        <v>-647034083.39</v>
+        <v>-743959234.75</v>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
@@ -9772,7 +9772,7 @@
       </c>
       <c r="BG22" t="inlineStr">
         <is>
-          <t>103.44</t>
+          <t>97.11</t>
         </is>
       </c>
       <c r="BH22" t="inlineStr">
@@ -9797,7 +9797,7 @@
       </c>
       <c r="BL22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM22" t="inlineStr">
@@ -9817,7 +9817,7 @@
       </c>
       <c r="BP22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ22" t="inlineStr">
@@ -9827,12 +9827,12 @@
       </c>
       <c r="BR22" t="inlineStr">
         <is>
-          <t>3.01</t>
+          <t>2.91</t>
         </is>
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
@@ -9842,7 +9842,7 @@
       </c>
       <c r="BU22" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV22" t="inlineStr">
@@ -9857,12 +9857,12 @@
       </c>
       <c r="BX22" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
@@ -9882,22 +9882,22 @@
       </c>
       <c r="CC22" t="inlineStr">
         <is>
-          <t>115.5</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>116.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>112.0</t>
+          <t>108.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
@@ -9929,12 +9929,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.3</t>
+          <t>1.3</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>44759.042</t>
+          <t>41008.816</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9944,7 +9944,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9954,17 +9954,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-19.35</t>
+          <t>-17.07</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.2</t>
+          <t>-1.09</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>2.05</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -9974,7 +9974,7 @@
       </c>
       <c r="L23" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="M23" t="inlineStr">
@@ -10029,7 +10029,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>6.73</t>
+          <t>8.17</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10039,17 +10039,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-05</t>
+          <t>2025-11-06</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.39</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.84</t>
+          <t>-2.66</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10060,77 +10060,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>259</t>
+          <t>268</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>29840</t>
+          <t>31968</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>27.27</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>22.22</t>
+          <t>9.09</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.14</t>
+          <t>-1.14</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>18.59</t>
+          <t>17.46</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>20.65</t>
+          <t>20.54</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>114.6</t>
+          <t>113.8</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>112.98</t>
+          <t>112.95</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>95.26</t>
+          <t>96.16</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>78.96</t>
+          <t>79.78</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-22.68</t>
+          <t>-25.10</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>5.31</t>
+          <t>4.84</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6.87</t>
+          <t>6.46</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10140,7 +10140,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-30.75</t>
+          <t>-34.84</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10150,41 +10150,41 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1863578893.794373</t>
+          <t>1867571577.393372</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>4910619020.0</t>
+          <t>4662435634.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>5392825172.8</t>
+          <t>5212568091.8</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>5284409444.9</t>
+          <t>5086668589.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7480816542.68</t>
+          <t>7342838422.34</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>108415727</t>
+          <t>125899502</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-445700413.8232446</t>
+          <t>-476674824.5251145</t>
         </is>
       </c>
       <c r="BC23" t="n">
-        <v>-656124974.6799999</v>
+        <v>-647034083.39</v>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
@@ -10203,7 +10203,7 @@
       </c>
       <c r="BG23" t="inlineStr">
         <is>
-          <t>100.72</t>
+          <t>103.44</t>
         </is>
       </c>
       <c r="BH23" t="inlineStr">
@@ -10228,7 +10228,7 @@
       </c>
       <c r="BL23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.73</t>
         </is>
       </c>
       <c r="BM23" t="inlineStr">
@@ -10248,7 +10248,7 @@
       </c>
       <c r="BP23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,多頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BQ23" t="inlineStr">
@@ -10258,12 +10258,12 @@
       </c>
       <c r="BR23" t="inlineStr">
         <is>
-          <t>2.97</t>
+          <t>3.01</t>
         </is>
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.29</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
@@ -10273,7 +10273,7 @@
       </c>
       <c r="BU23" t="inlineStr">
         <is>
-          <t>40.43</t>
+          <t>41.78</t>
         </is>
       </c>
       <c r="BV23" t="inlineStr">
@@ -10288,12 +10288,12 @@
       </c>
       <c r="BX23" t="inlineStr">
         <is>
-          <t>40.19</t>
+          <t>40.81</t>
         </is>
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>221009</t>
+          <t>228376</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
@@ -10313,22 +10313,22 @@
       </c>
       <c r="CC23" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>115.5</t>
         </is>
       </c>
       <c r="CD23" t="inlineStr">
         <is>
+          <t>116.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
           <t>112.0</t>
         </is>
       </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>107.0</t>
-        </is>
-      </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>111.0</t>
+          <t>112.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,17 +1014,17 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
@@ -1034,57 +1034,57 @@
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>971.8</t>
+          <t>962.95</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>941.9</t>
+          <t>944.08</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13146559354.4</t>
+          <t>14386844246.4</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14614553602.28</t>
+          <t>14618581897.64</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>15812987742</v>
+        <v>16911194399</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1217,7 +1217,7 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-6.59</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>977.55</t>
+          <t>971.8</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>938.52</t>
+          <t>941.9</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13620510362.4</t>
+          <t>13146559354.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>14466055493.78</t>
+          <t>14614553602.28</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>15882778006</v>
+        <v>15812987742</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1648,12 +1648,12 @@
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>-6.83</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>980.85</t>
+          <t>977.55</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>933.96</t>
+          <t>938.52</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>12590700418.8</t>
+          <t>13620510362.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14368721493.28</t>
+          <t>14466055493.78</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>10973548400</v>
+        <v>15882778006</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2079,17 +2079,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.34</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,12 +2322,12 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
@@ -2342,57 +2342,57 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>987.15</t>
+          <t>980.85</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>929.9</t>
+          <t>933.96</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13187701378.4</t>
+          <t>12590700418.8</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>14292572173.18</t>
+          <t>14368721493.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>12353712685</v>
+        <v>10973548400</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2515,17 +2515,17 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-0.56</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>987.15</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>925.54</t>
+          <t>929.9</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>12964522972.0</t>
+          <t>13187701378.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>14209168625.62</t>
+          <t>14292572173.18</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-273240924.15588</t>
+          <t>-303325579.8395176</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>10709769939</v>
+        <v>12353712685</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,17 +2951,17 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-2.58</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3209,62 +3209,62 @@
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>997.15</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>925.54</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13091194606.6</t>
+          <t>12964522972.0</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>14155319682.02</t>
+          <t>14209168625.62</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-44367517.38797188</t>
+          <t>-273240924.15588</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>18182742782</v>
+        <v>10709769939</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,17 +3387,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-7.04</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>1002.3</t>
+          <t>997.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>916.24</t>
+          <t>920.92</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>11321413068.4</t>
+          <t>13091194606.6</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>13994353884.38</t>
+          <t>14155319682.02</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-516496615.2771072</t>
+          <t>-44367517.38797188</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>10733728288</v>
+        <v>18182742782</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,17 +3823,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-8.04</t>
+          <t>-7.28</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,77 +4066,77 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1005.15</t>
+          <t>1002.3</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>911.3</t>
+          <t>916.24</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,27 +4156,27 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>11246965605.2</t>
+          <t>11321413068.4</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13940555876.02</t>
+          <t>13994353884.38</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
@@ -4186,16 +4186,16 @@
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-374411751.6445465</t>
+          <t>-516496615.2771072</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>13958553198</v>
+        <v>10733728288</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,17 +4259,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4329,17 +4329,17 @@
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11380.761</t>
+          <t>14451.354</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.6</t>
+          <t>-8.29</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,42 +4502,42 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
@@ -4547,32 +4547,32 @@
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>1005.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>906.14</t>
+          <t>911.3</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>792.68</t>
+          <t>798.52</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-51.60</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>11237820653.0</t>
+          <t>13958553198.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>11891933198.2</t>
+          <t>11246965605.2</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15361285967.4</t>
+          <t>15377407355.7</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13790744516.9</t>
+          <t>13940555876.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-19367696.47659796</t>
+          <t>-73989858.81012851</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-503578481.3964405</t>
+          <t>-374411751.6445465</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>11237820653</v>
+        <v>13958553198</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,7 +4705,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11544.121</t>
+          <t>11380.761</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-9.72</t>
+          <t>-8.85</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>973.4</t>
+          <t>972.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1009.3</t>
+          <t>1006.4</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>901.1</t>
+          <t>906.14</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>786.78</t>
+          <t>792.68</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-43.71</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-45.98</t>
+          <t>-51.60</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,46 +5028,46 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11343128112.0</t>
+          <t>11237820653.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>13403862876.8</t>
+          <t>11891933198.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15214887680.6</t>
+          <t>15361285967.4</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13806820609.68</t>
+          <t>13790744516.9</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-1811024803</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>68670628.05428252</t>
+          <t>-19367696.47659796</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-378610376.8849869</t>
+          <t>-503578481.3964405</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>11343128112</v>
+        <v>11237820653</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>159.79</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,7 +5141,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>968.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.35</t>
+          <t>1.73</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>9673.113</t>
+          <t>11544.121</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-7.82</t>
+          <t>-9.97</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-1.21</t>
+          <t>-0.74</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-7.84</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-3.25</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,12 +5353,12 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>33.47</t>
+          <t>39.94</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>1,477</t>
+          <t>304</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>17544</t>
+          <t>18856</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.89</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>9.36</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.88</t>
+          <t>0.88</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.62</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.85</t>
+          <t>12.01</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.66</t>
+          <t>14.53</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>973.6</t>
+          <t>973.4</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1010.15</t>
+          <t>1009.3</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>895.16</t>
+          <t>901.1</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>780.68</t>
+          <t>786.78</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-43.05</t>
+          <t>-43.71</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>22.12</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>38.84</t>
+          <t>35.01</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-40.07</t>
+          <t>-45.98</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6401972045.691811</t>
+          <t>6429181255.954088</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>9333835091.0</t>
+          <t>11343128112.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>14406527688.6</t>
+          <t>13403862876.8</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15631820791.9</t>
+          <t>15214887680.6</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13722429318.62</t>
+          <t>13806820609.68</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1225293103</t>
+          <t>-1811024803</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>149994447.1341497</t>
+          <t>68670628.05428252</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-197845656.1584454</t>
+          <t>-378610376.8849869</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>9333835091</v>
+        <v>11343128112</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>155.29</t>
+          <t>159.79</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.29</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,7 +5577,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>10.41</t>
+          <t>10.60</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>46.54</t>
+          <t>46.44</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.63</t>
+          <t>32.66</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2324801</t>
+          <t>2319606</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>960.0</t>
+          <t>980.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>994.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>956.0</t>
+          <t>968.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>982.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>32684.421</t>
+          <t>124181.065</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.80</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.56</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>106.92</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.41</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-939.09</t>
+          <t>-272.55</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>3191641823.4</t>
+          <t>4696916791.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3527299622.7</t>
+          <t>4341077616.0</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>7285669264.58</t>
+          <t>7241408797.74</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-335657799</t>
+          <t>355839175</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-531460699.0544155</t>
+          <t>-422675044.3923899</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-477849918.1702256</t>
+          <t>175646056.2487507</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>3032171594</v>
+        <v>11515775721</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>31967.753</t>
+          <t>32684.421</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,17 +6246,17 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
@@ -6266,57 +6266,57 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.80</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>95.85999999999999</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>108.02</t>
+          <t>106.92</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-712.58</t>
+          <t>-939.09</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>4058514408.6</t>
+          <t>3191641823.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3531039856.9</t>
+          <t>3527299622.7</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>7317342463.3</t>
+          <t>7285669264.58</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>527474551</t>
+          <t>-335657799</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-541208113.7606318</t>
+          <t>-531460699.0544155</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-485391942.3698263</t>
+          <t>-477849918.1702256</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>3089667541</v>
+        <v>3032171594</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>29839.894</t>
+          <t>31967.753</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.09</t>
+          <t>-3.44</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>95.85999999999999</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>108.02</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.19</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-283.53</t>
+          <t>-712.58</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>4453509900.0</t>
+          <t>4058514408.6</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3688316666.2</t>
+          <t>3531039856.9</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>7280178623.2</t>
+          <t>7317342463.3</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>765193233</t>
+          <t>527474551</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-551356508.5589601</t>
+          <t>-541208113.7606318</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-484991116.1774759</t>
+          <t>-485391942.3698263</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>2778009293</v>
+        <v>3089667541</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32132.941</t>
+          <t>29839.894</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-1.96</t>
+          <t>-0.11</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,12 +7118,12 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>98.74</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>110.06</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>101.66</t>
+          <t>102.19</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>85.35</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-161.08</t>
+          <t>-283.53</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-81.65</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>4175037440.4</t>
+          <t>4453509900.0</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3901577638.9</t>
+          <t>3688316666.2</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>7265450343.64</t>
+          <t>7280178623.2</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>273459801</t>
+          <t>765193233</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-563422943.5374118</t>
+          <t>-551356508.5589601</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-433705440.8963513</t>
+          <t>-484991116.1774759</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>3068959808</v>
+        <v>2778009293</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.0</t>
+          <t>-0.97</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7569,62 +7569,62 @@
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>111.34</t>
+          <t>110.06</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>101.66</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>3985238440.6</t>
+          <t>4175037440.4</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>7220968787.64</t>
+          <t>7265450343.64</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-376123979.9270172</t>
+          <t>-433705440.8963513</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>3989400881</v>
+        <v>3068959808</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.48</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>111.96</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>100.52</t>
+          <t>101.12</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3862957422.0</t>
+          <t>3985238440.6</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7171595467.56</t>
+          <t>7220968787.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-379050437.0805759</t>
+          <t>-376123979.9270172</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>7366534520</v>
+        <v>3989400881</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-20.11</t>
+          <t>-7.43</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,17 +8426,17 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
@@ -8446,57 +8446,57 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>111.96</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>99.87</t>
+          <t>100.52</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3003565305.2</t>
+          <t>3862957422.0</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>7070679471.22</t>
+          <t>7171595467.56</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-731529321.5827818</t>
+          <t>-379050437.0805759</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>5064644998</v>
+        <v>7366534520</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-18.95</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,77 +8862,77 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>112.52</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>99.87</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>2923123432.4</t>
+          <t>3003565305.2</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>7004676232.68</t>
+          <t>7070679471.22</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-962313517.7436905</t>
+          <t>-731529321.5827818</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>1385646995</v>
+        <v>5064644998</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>20206.638</t>
+          <t>13178.714</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-13.59</t>
+          <t>-14.1</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-29.70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>82.71</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-54.62</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-50.96</t>
+          <t>-56.85</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>2119964809.0</t>
+          <t>1385646995.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>3628117837.4</t>
+          <t>2923123432.4</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4590922523.2</t>
+          <t>4157974302.6</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7037581985.4</t>
+          <t>7004676232.68</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-962804685</t>
+          <t>-1234850870</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-603815707.0069512</t>
+          <t>-658969216.3510649</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-863458529.1612859</t>
+          <t>-962313517.7436905</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>2119964809</v>
+        <v>1385646995</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,12 +9556,12 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
@@ -9571,7 +9571,7 @@
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>32158.04</t>
+          <t>20206.638</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-15.22</t>
+          <t>-12.49</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,12 +9734,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9749,62 +9749,62 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>110.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>112.7</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>97.59</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>81.99</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-48.86</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-50.96</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>3377995788.0</t>
+          <t>2119964809.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>3972870766.6</t>
+          <t>3628117837.4</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>4754290282.0</t>
+          <t>4590922523.2</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7089210465.74</t>
+          <t>7037581985.4</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-781419515</t>
+          <t>-962804685</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-556607921.1607085</t>
+          <t>-603815707.0069512</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-770076220.9306612</t>
+          <t>-863458529.1612859</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>3377995788</v>
+        <v>2119964809</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>88.97</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-3.17</t>
+          <t>-2.76</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>28070.898</t>
+          <t>32158.04</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-18.48</t>
+          <t>-14.1</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-5.22</t>
+          <t>-4.36</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-17.83</t>
+          <t>-16.44</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>4.81</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-07</t>
+          <t>2025-11-10</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>8.48</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-2.29</t>
+          <t>0.08</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>286</t>
+          <t>9,313</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>32684</t>
+          <t>124181</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10190,57 +10190,57 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-2.94</t>
+          <t>-3.99</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-0.51</t>
+          <t>-2.04</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>16.53</t>
+          <t>15.49</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>20.25</t>
+          <t>20.07</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>110.4</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>112.88</t>
+          <t>112.7</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>96.86</t>
+          <t>97.59</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>80.55</t>
+          <t>81.27</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-31.01</t>
+          <t>-39.53</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>4.14</t>
+          <t>3.30</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>6.00</t>
+          <t>5.46</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-44.97</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1871428679.283453</t>
+          <t>1893558327.131465</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3069573936.0</t>
+          <t>3377995788.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>4159914695.6</t>
+          <t>3972870766.6</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>5062324469.3</t>
+          <t>4754290282.0</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7212241390.94</t>
+          <t>7089210465.74</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-902409773</t>
+          <t>-781419515</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-517795503.0207172</t>
+          <t>-556607921.1607085</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-743959234.7465324</t>
+          <t>-770076220.9306612</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>3069573936</v>
+        <v>3377995788</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>97.11</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.73</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.91</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.39</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>40.0</t>
+          <t>40.39</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>39.72</t>
+          <t>40.13</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>218632</t>
+          <t>220771</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>108.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>112.5</t>
+          <t>109.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>108.0</t>
+          <t>103.0</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>18856.003</t>
+          <t>10504.174</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>65.24</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>909.2</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>962.95</t>
+          <t>954.7</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>944.08</t>
+          <t>945.54</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>838.41</t>
+          <t>843.16</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-940.86</t>
+          <t>-265.70</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-102.03</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>14386844246.4</t>
+          <t>13831910429.6</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13675683609.2</t>
+          <t>13509805904.0</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14618581897.64</t>
+          <t>14413977761.06</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>711160637</t>
+          <t>322104525</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-83739087.18903175</t>
+          <t>-85354428.47894374</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>306359263.681345</t>
+          <t>-94238805.57345963</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>16911194399</v>
+        <v>9579043601</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>136.24</t>
+          <t>140.74</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>904.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>909.0</t>
+          <t>926.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>899.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.87</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,17 +1450,17 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
@@ -1470,57 +1470,57 @@
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>971.8</t>
+          <t>962.95</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>941.9</t>
+          <t>944.08</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>13146559354.4</t>
+          <t>14386844246.4</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>14614553602.28</t>
+          <t>14618581897.64</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>15812987742</v>
+        <v>16911194399</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1653,12 +1653,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-6.83</t>
+          <t>1.65</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,77 +1886,77 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>977.55</t>
+          <t>971.8</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>938.52</t>
+          <t>941.9</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13620510362.4</t>
+          <t>13146559354.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14466055493.78</t>
+          <t>14614553602.28</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>15882778006</v>
+        <v>15812987742</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2084,17 +2084,17 @@
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-4.84</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>980.85</t>
+          <t>977.55</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>933.96</t>
+          <t>938.52</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>12590700418.8</t>
+          <t>13620510362.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>14368721493.28</t>
+          <t>14466055493.78</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>10973548400</v>
+        <v>15882778006</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2515,22 +2515,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.56</t>
+          <t>1.76</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,12 +2758,12 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
@@ -2778,57 +2778,57 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>987.15</t>
+          <t>980.85</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>929.9</t>
+          <t>933.96</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>13187701378.4</t>
+          <t>12590700418.8</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>14292572173.18</t>
+          <t>14368721493.28</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>12353712685</v>
+        <v>10973548400</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-2.58</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>987.15</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>925.54</t>
+          <t>929.9</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>12964522972.0</t>
+          <t>13187701378.4</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>14209168625.62</t>
+          <t>14292572173.18</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-273240924.15588</t>
+          <t>-303325579.8395176</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>10709769939</v>
+        <v>12353712685</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-0.66</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3645,62 +3645,62 @@
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>997.15</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>925.54</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>13091194606.6</t>
+          <t>12964522972.0</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>14155319682.02</t>
+          <t>14209168625.62</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-44367517.38797188</t>
+          <t>-273240924.15588</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>18182742782</v>
+        <v>10709769939</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-7.28</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>1002.3</t>
+          <t>997.15</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>916.24</t>
+          <t>920.92</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>11321413068.4</t>
+          <t>13091194606.6</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>13994353884.38</t>
+          <t>14155319682.02</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-516496615.2771072</t>
+          <t>-44367517.38797188</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>10733728288</v>
+        <v>18182742782</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-8.29</t>
+          <t>-5.27</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,77 +4502,77 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1005.15</t>
+          <t>1002.3</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>911.3</t>
+          <t>916.24</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,27 +4592,27 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>11246965605.2</t>
+          <t>11321413068.4</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13940555876.02</t>
+          <t>13994353884.38</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
@@ -4622,16 +4622,16 @@
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-374411751.6445465</t>
+          <t>-516496615.2771072</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>13958553198</v>
+        <v>10733728288</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4695,7 +4695,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4705,12 +4705,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4765,17 +4765,17 @@
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11380.761</t>
+          <t>14451.354</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-8.85</t>
+          <t>-6.26</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,42 +4938,42 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
@@ -4983,32 +4983,32 @@
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>1005.15</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>906.14</t>
+          <t>911.3</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>792.68</t>
+          <t>798.52</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-51.60</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>11237820653.0</t>
+          <t>13958553198.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>11891933198.2</t>
+          <t>11246965605.2</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15361285967.4</t>
+          <t>15377407355.7</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13790744516.9</t>
+          <t>13940555876.02</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-19367696.47659796</t>
+          <t>-73989858.81012851</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-503578481.3964405</t>
+          <t>-374411751.6445465</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>11237820653</v>
+        <v>13958553198</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5196,22 +5196,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>1.73</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11544.121</t>
+          <t>11380.761</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-9.97</t>
+          <t>-6.81</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.74</t>
+          <t>-0.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-22.59</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-3.25</t>
+          <t>-4.24</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>39.94</t>
+          <t>39.38</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>0.22</t>
+          <t>-2.67</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,77 +5374,77 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>304</t>
+          <t>294</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>18856</t>
+          <t>10504</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>17.89</t>
+          <t>15.56</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>9.36</t>
+          <t>11.15</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>0.88</t>
+          <t>-0.08</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>12.01</t>
+          <t>11.06</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.53</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>973.4</t>
+          <t>972.8</t>
         </is>
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1009.3</t>
+          <t>1006.4</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>901.1</t>
+          <t>906.14</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>786.78</t>
+          <t>792.68</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-43.71</t>
+          <t>-46.45</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>16.80</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>35.01</t>
+          <t>31.37</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-45.98</t>
+          <t>-51.60</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,46 +5464,46 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6429181255.954088</t>
+          <t>6440555731.807306</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11343128112.0</t>
+          <t>11237820653.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>13403862876.8</t>
+          <t>11891933198.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15214887680.6</t>
+          <t>15361285967.4</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13806820609.68</t>
+          <t>13790744516.9</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-1811024803</t>
+          <t>-2147483648</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>68670628.05428252</t>
+          <t>-19367696.47659796</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-378610376.8849869</t>
+          <t>-503578481.3964405</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>11343128112</v>
+        <v>11237820653</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>159.79</t>
+          <t>157.14</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>10.60</t>
+          <t>10.49</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.78</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>46.44</t>
+          <t>47.32</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>32.66</t>
+          <t>33.24</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2319606</t>
+          <t>2363764</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>980.0</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>994.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>968.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>982.0</t>
+          <t>972.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>124181.065</t>
+          <t>52066.846</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-14.90</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,77 +5810,77 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>93.56</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>105.81</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>103.41</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-272.55</t>
+          <t>-161.95</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-108.99</t>
+          <t>-115.11</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>4696916791.4</t>
+          <t>5019578044.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4341077616.0</t>
+          <t>4597307742.4</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>7241408797.74</t>
+          <t>7180754379.14</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>355839175</t>
+          <t>422270302</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-422675044.3923899</t>
+          <t>-339772904.7418968</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>175646056.2487507</t>
+          <t>116188863.3358154</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>11515775721</v>
+        <v>4682266073</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>32684.421</t>
+          <t>124181.065</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.80</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.56</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>106.92</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.41</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-939.09</t>
+          <t>-272.55</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>3191641823.4</t>
+          <t>4696916791.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3527299622.7</t>
+          <t>4341077616.0</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>7285669264.58</t>
+          <t>7241408797.74</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-335657799</t>
+          <t>355839175</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-531460699.0544155</t>
+          <t>-422675044.3923899</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-477849918.1702256</t>
+          <t>175646056.2487507</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>3032171594</v>
+        <v>11515775721</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>31967.753</t>
+          <t>32684.421</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.44</t>
+          <t>-3.95</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,17 +6682,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6702,57 +6702,57 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.80</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>95.85999999999999</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>108.02</t>
+          <t>106.92</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-712.58</t>
+          <t>-939.09</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>4058514408.6</t>
+          <t>3191641823.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3531039856.9</t>
+          <t>3527299622.7</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>7317342463.3</t>
+          <t>7285669264.58</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>527474551</t>
+          <t>-335657799</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-541208113.7606318</t>
+          <t>-531460699.0544155</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-485391942.3698263</t>
+          <t>-477849918.1702256</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>3089667541</v>
+        <v>3032171594</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>29839.894</t>
+          <t>31967.753</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-0.11</t>
+          <t>-8.59</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,77 +7118,77 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>95.85999999999999</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>108.02</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>102.19</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-283.53</t>
+          <t>-712.58</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>4453509900.0</t>
+          <t>4058514408.6</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3688316666.2</t>
+          <t>3531039856.9</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>7280178623.2</t>
+          <t>7317342463.3</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>765193233</t>
+          <t>527474551</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-551356508.5589601</t>
+          <t>-541208113.7606318</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-484991116.1774759</t>
+          <t>-485391942.3698263</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>2778009293</v>
+        <v>3089667541</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,24 +7311,24 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
           <t>2.49</t>
         </is>
       </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
       <c r="BU16" t="inlineStr">
         <is>
           <t>6.21</t>
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32132.941</t>
+          <t>29839.894</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.97</t>
+          <t>-5.08</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,12 +7554,12 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
@@ -7574,57 +7574,57 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>98.74</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>110.06</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>101.66</t>
+          <t>102.19</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>85.35</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-161.08</t>
+          <t>-283.53</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-81.65</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>4175037440.4</t>
+          <t>4453509900.0</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3901577638.9</t>
+          <t>3688316666.2</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>7265450343.64</t>
+          <t>7280178623.2</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>273459801</t>
+          <t>765193233</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-563422943.5374118</t>
+          <t>-551356508.5589601</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-433705440.8963513</t>
+          <t>-484991116.1774759</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>3068959808</v>
+        <v>2778009293</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-5.99</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8005,62 +8005,62 @@
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>111.34</t>
+          <t>110.06</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>101.66</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>3985238440.6</t>
+          <t>4175037440.4</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7220968787.64</t>
+          <t>7265450343.64</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-376123979.9270172</t>
+          <t>-433705440.8963513</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>3989400881</v>
+        <v>3068959808</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.43</t>
+          <t>-9.15</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>111.96</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>100.52</t>
+          <t>101.12</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3862957422.0</t>
+          <t>3985238440.6</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>7171595467.56</t>
+          <t>7220968787.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-379050437.0805759</t>
+          <t>-376123979.9270172</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>7366534520</v>
+        <v>3989400881</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8629,12 +8629,12 @@
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-18.95</t>
+          <t>-12.77</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,17 +8862,17 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
@@ -8882,57 +8882,57 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>111.96</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>99.87</t>
+          <t>100.52</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>3003565305.2</t>
+          <t>3862957422.0</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>7070679471.22</t>
+          <t>7171595467.56</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-731529321.5827818</t>
+          <t>-379050437.0805759</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>5064644998</v>
+        <v>7366534520</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9055,22 +9055,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.1</t>
+          <t>-24.86</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,77 +9298,77 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>112.52</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>99.87</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>2923123432.4</t>
+          <t>3003565305.2</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7004676232.68</t>
+          <t>7070679471.22</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-962313517.7436905</t>
+          <t>-731529321.5827818</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>1385646995</v>
+        <v>5064644998</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>20206.638</t>
+          <t>13178.714</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-12.49</t>
+          <t>-19.77</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-29.70</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,217 +9734,217 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>82.71</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-54.62</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
+          <t>1.94</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>4.28</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-56.85</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>1900918213.476327</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>1385646995.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="inlineStr">
+        <is>
+          <t>2923123432.4</t>
+        </is>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>4157974302.6</t>
+        </is>
+      </c>
+      <c r="AZ22" t="inlineStr">
+        <is>
+          <t>7004676232.68</t>
+        </is>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>-1234850870</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-658969216.3510649</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-962313517.7436905</t>
+        </is>
+      </c>
+      <c r="BD22" t="n">
+        <v>1385646995</v>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>91.68</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ22" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK22" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL22" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM22" t="inlineStr">
+        <is>
+          <t>0.75</t>
+        </is>
+      </c>
+      <c r="BN22" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO22" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP22" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>2.83</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
           <t>2.49</t>
         </is>
       </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>4.86</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-50.96</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>1893558327.131465</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>2119964809.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>3628117837.4</t>
-        </is>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>4590922523.2</t>
-        </is>
-      </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>7037581985.4</t>
-        </is>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>-962804685</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-603815707.0069512</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>-863458529.1612859</t>
-        </is>
-      </c>
-      <c r="BD22" t="n">
-        <v>2119964809</v>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>88.97</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.76</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>2.79</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
       <c r="BU22" t="inlineStr">
         <is>
           <t>6.21</t>
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,12 +9992,12 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
@@ -10007,7 +10007,7 @@
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.76</t>
+          <t>-1.4</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>32158.04</t>
+          <t>20206.638</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-14.1</t>
+          <t>-18.08</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.36</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-16.44</t>
+          <t>-20.97</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>0.48</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-10</t>
+          <t>2025-11-11</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>6.10</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>0.08</t>
+          <t>-1.90</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,12 +10170,12 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>9,313</t>
+          <t>689</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>124181</t>
+          <t>52067</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
@@ -10185,62 +10185,62 @@
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>9.09</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.99</t>
+          <t>-3.78</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-2.04</t>
+          <t>-3.29</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>15.49</t>
+          <t>14.28</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>20.07</t>
+          <t>19.86</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>110.4</t>
+          <t>108.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>112.7</t>
+          <t>112.3</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>97.59</t>
+          <t>98.27</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>81.27</t>
+          <t>81.99</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-39.53</t>
+          <t>-48.86</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>3.30</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>5.46</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-44.97</t>
+          <t>-50.96</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1893558327.131465</t>
+          <t>1900918213.476327</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>3377995788.0</t>
+          <t>2119964809.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>3972870766.6</t>
+          <t>3628117837.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>4754290282.0</t>
+          <t>4590922523.2</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7089210465.74</t>
+          <t>7037581985.4</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-781419515</t>
+          <t>-962804685</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-556607921.1607085</t>
+          <t>-603815707.0069512</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-770076220.9306612</t>
+          <t>-863458529.1612859</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>3377995788</v>
+        <v>2119964809</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>88.97</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.79</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>40.39</t>
+          <t>38.48</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.13</t>
+          <t>40.55</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>220771</t>
+          <t>210315</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,22 +10428,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>108.5</t>
+          <t>107.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>109.0</t>
+          <t>107.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>103.0</t>
+          <t>103.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>10504.174</t>
+          <t>11426.896</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>39.54</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,77 +1014,77 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>909.2</t>
+          <t>919.4</t>
         </is>
       </c>
       <c r="AM2" t="inlineStr">
         <is>
-          <t>954.7</t>
+          <t>948.95</t>
         </is>
       </c>
       <c r="AN2" t="inlineStr">
         <is>
-          <t>945.54</t>
+          <t>947.82</t>
         </is>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>843.16</t>
+          <t>847.89</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-265.70</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1094,7 +1094,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-108.52</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1104,46 +1104,46 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="AX2" t="inlineStr">
         <is>
-          <t>13831910429.6</t>
+          <t>13777681330.2</t>
         </is>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13509805904.0</t>
+          <t>13184190874.5</t>
         </is>
       </c>
       <c r="AZ2" t="inlineStr">
         <is>
-          <t>14413977761.06</t>
+          <t>14165986897.28</t>
         </is>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>322104525</t>
+          <t>593490455</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-85354428.47894374</t>
+          <t>-116538291.2148735</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-94238805.57345963</t>
+          <t>-288049536.2624874</t>
         </is>
       </c>
       <c r="BD2" t="n">
-        <v>9579043601</v>
+        <v>10702402903</v>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1162,7 +1162,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>140.74</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1187,7 +1187,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1207,22 +1207,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1232,7 +1232,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1247,12 +1247,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1272,22 +1272,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>926.0</t>
+          <t>950.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>899.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1319,12 +1319,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>18856.003</t>
+          <t>10504.174</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1334,7 +1334,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1344,17 +1344,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.87</t>
+          <t>3.7</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1419,7 +1419,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1429,17 +1429,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>65.24</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1450,77 +1450,77 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>909.2</t>
         </is>
       </c>
       <c r="AM3" t="inlineStr">
         <is>
-          <t>962.95</t>
+          <t>954.7</t>
         </is>
       </c>
       <c r="AN3" t="inlineStr">
         <is>
-          <t>944.08</t>
+          <t>945.54</t>
         </is>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>838.41</t>
+          <t>843.16</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-940.86</t>
+          <t>-265.70</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1530,7 +1530,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-102.03</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1540,46 +1540,46 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="AX3" t="inlineStr">
         <is>
-          <t>14386844246.4</t>
+          <t>13831910429.6</t>
         </is>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13675683609.2</t>
+          <t>13509805904.0</t>
         </is>
       </c>
       <c r="AZ3" t="inlineStr">
         <is>
-          <t>14618581897.64</t>
+          <t>14413977761.06</t>
         </is>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>711160637</t>
+          <t>322104525</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-83739087.18903175</t>
+          <t>-85354428.47894374</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>306359263.681345</t>
+          <t>-94238805.57345963</t>
         </is>
       </c>
       <c r="BD3" t="n">
-        <v>16911194399</v>
+        <v>9579043601</v>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1598,7 +1598,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>136.24</t>
+          <t>140.74</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1623,7 +1623,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1643,22 +1643,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1668,7 +1668,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1683,12 +1683,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1708,22 +1708,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>904.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>909.0</t>
+          <t>926.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>899.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1755,12 +1755,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1770,7 +1770,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1780,17 +1780,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>1.65</t>
+          <t>5.5</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1855,7 +1855,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1865,17 +1865,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1886,17 +1886,17 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
@@ -1906,57 +1906,57 @@
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM4" t="inlineStr">
         <is>
-          <t>971.8</t>
+          <t>962.95</t>
         </is>
       </c>
       <c r="AN4" t="inlineStr">
         <is>
-          <t>941.9</t>
+          <t>944.08</t>
         </is>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1966,7 +1966,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1976,46 +1976,46 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX4" t="inlineStr">
         <is>
-          <t>13146559354.4</t>
+          <t>14386844246.4</t>
         </is>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ4" t="inlineStr">
         <is>
-          <t>14614553602.28</t>
+          <t>14618581897.64</t>
         </is>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD4" t="n">
-        <v>15812987742</v>
+        <v>16911194399</v>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2034,7 +2034,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2059,7 +2059,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2089,12 +2089,12 @@
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2104,7 +2104,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2119,12 +2119,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2144,22 +2144,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2191,12 +2191,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2206,7 +2206,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2216,17 +2216,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>-4.84</t>
+          <t>5.29</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2291,7 +2291,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2301,17 +2301,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2322,77 +2322,77 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM5" t="inlineStr">
         <is>
-          <t>977.55</t>
+          <t>971.8</t>
         </is>
       </c>
       <c r="AN5" t="inlineStr">
         <is>
-          <t>938.52</t>
+          <t>941.9</t>
         </is>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2402,7 +2402,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2412,46 +2412,46 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX5" t="inlineStr">
         <is>
-          <t>13620510362.4</t>
+          <t>13146559354.4</t>
         </is>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ5" t="inlineStr">
         <is>
-          <t>14466055493.78</t>
+          <t>14614553602.28</t>
         </is>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD5" t="n">
-        <v>15882778006</v>
+        <v>15812987742</v>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2470,7 +2470,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2495,7 +2495,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2520,17 +2520,17 @@
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2540,7 +2540,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2555,12 +2555,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2580,22 +2580,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2627,12 +2627,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2642,7 +2642,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2652,17 +2652,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>1.76</t>
+          <t>-0.95</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2727,7 +2727,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2737,17 +2737,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2758,77 +2758,77 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM6" t="inlineStr">
         <is>
-          <t>980.85</t>
+          <t>977.55</t>
         </is>
       </c>
       <c r="AN6" t="inlineStr">
         <is>
-          <t>933.96</t>
+          <t>938.52</t>
         </is>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2838,7 +2838,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2848,46 +2848,46 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX6" t="inlineStr">
         <is>
-          <t>12590700418.8</t>
+          <t>13620510362.4</t>
         </is>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ6" t="inlineStr">
         <is>
-          <t>14368721493.28</t>
+          <t>14466055493.78</t>
         </is>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD6" t="n">
-        <v>10973548400</v>
+        <v>15882778006</v>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -2906,7 +2906,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,7 +2931,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2951,22 +2951,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2976,7 +2976,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2991,12 +2991,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -3016,22 +3016,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3063,12 +3063,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3078,7 +3078,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3088,17 +3088,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>5.4</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3163,7 +3163,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3173,17 +3173,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3194,12 +3194,12 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
@@ -3214,57 +3214,57 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM7" t="inlineStr">
         <is>
-          <t>987.15</t>
+          <t>980.85</t>
         </is>
       </c>
       <c r="AN7" t="inlineStr">
         <is>
-          <t>929.9</t>
+          <t>933.96</t>
         </is>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3274,7 +3274,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3284,46 +3284,46 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX7" t="inlineStr">
         <is>
-          <t>13187701378.4</t>
+          <t>12590700418.8</t>
         </is>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ7" t="inlineStr">
         <is>
-          <t>14292572173.18</t>
+          <t>14368721493.28</t>
         </is>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD7" t="n">
-        <v>12353712685</v>
+        <v>10973548400</v>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3342,7 +3342,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3367,7 +3367,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3387,22 +3387,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3412,7 +3412,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3427,12 +3427,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3452,22 +3452,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3499,12 +3499,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3514,7 +3514,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3524,17 +3524,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-0.66</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3599,7 +3599,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3609,17 +3609,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3630,12 +3630,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3650,57 +3650,57 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM8" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>987.15</t>
         </is>
       </c>
       <c r="AN8" t="inlineStr">
         <is>
-          <t>925.54</t>
+          <t>929.9</t>
         </is>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3710,7 +3710,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3720,46 +3720,46 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX8" t="inlineStr">
         <is>
-          <t>12964522972.0</t>
+          <t>13187701378.4</t>
         </is>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ8" t="inlineStr">
         <is>
-          <t>14209168625.62</t>
+          <t>14292572173.18</t>
         </is>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-273240924.15588</t>
+          <t>-303325579.8395176</t>
         </is>
       </c>
       <c r="BD8" t="n">
-        <v>10709769939</v>
+        <v>12353712685</v>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3778,7 +3778,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3803,7 +3803,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3823,22 +3823,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3848,7 +3848,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3863,12 +3863,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3888,22 +3888,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3935,12 +3935,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3950,7 +3950,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3960,17 +3960,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>3.07</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -4035,7 +4035,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4045,17 +4045,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4066,12 +4066,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4081,62 +4081,62 @@
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM9" t="inlineStr">
         <is>
-          <t>997.15</t>
+          <t>993.0</t>
         </is>
       </c>
       <c r="AN9" t="inlineStr">
         <is>
-          <t>920.92</t>
+          <t>925.54</t>
         </is>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4146,7 +4146,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4156,46 +4156,46 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX9" t="inlineStr">
         <is>
-          <t>13091194606.6</t>
+          <t>12964522972.0</t>
         </is>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ9" t="inlineStr">
         <is>
-          <t>14155319682.02</t>
+          <t>14209168625.62</t>
         </is>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-44367517.38797188</t>
+          <t>-273240924.15588</t>
         </is>
       </c>
       <c r="BD9" t="n">
-        <v>18182742782</v>
+        <v>10709769939</v>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4214,7 +4214,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4239,7 +4239,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4259,22 +4259,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4284,7 +4284,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4299,12 +4299,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4324,22 +4324,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4371,12 +4371,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4386,7 +4386,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4396,17 +4396,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>-5.27</t>
+          <t>2.43</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4471,7 +4471,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4481,17 +4481,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4502,12 +4502,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4517,62 +4517,62 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM10" t="inlineStr">
         <is>
-          <t>1002.3</t>
+          <t>997.15</t>
         </is>
       </c>
       <c r="AN10" t="inlineStr">
         <is>
-          <t>916.24</t>
+          <t>920.92</t>
         </is>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4582,7 +4582,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4592,46 +4592,46 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX10" t="inlineStr">
         <is>
-          <t>11321413068.4</t>
+          <t>13091194606.6</t>
         </is>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ10" t="inlineStr">
         <is>
-          <t>13994353884.38</t>
+          <t>14155319682.02</t>
         </is>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-516496615.2771072</t>
+          <t>-44367517.38797188</t>
         </is>
       </c>
       <c r="BD10" t="n">
-        <v>10733728288</v>
+        <v>18182742782</v>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4650,7 +4650,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4675,7 +4675,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4695,22 +4695,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4720,7 +4720,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4735,12 +4735,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4760,22 +4760,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4807,12 +4807,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4822,7 +4822,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4832,17 +4832,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-6.26</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4907,7 +4907,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4917,17 +4917,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4938,77 +4938,77 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM11" t="inlineStr">
         <is>
-          <t>1005.15</t>
+          <t>1002.3</t>
         </is>
       </c>
       <c r="AN11" t="inlineStr">
         <is>
-          <t>911.3</t>
+          <t>916.24</t>
         </is>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -5018,7 +5018,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -5028,27 +5028,27 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX11" t="inlineStr">
         <is>
-          <t>11246965605.2</t>
+          <t>11321413068.4</t>
         </is>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ11" t="inlineStr">
         <is>
-          <t>13940555876.02</t>
+          <t>13994353884.38</t>
         </is>
       </c>
       <c r="BA11" t="inlineStr">
@@ -5058,16 +5058,16 @@
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-374411751.6445465</t>
+          <t>-516496615.2771072</t>
         </is>
       </c>
       <c r="BD11" t="n">
-        <v>13958553198</v>
+        <v>10733728288</v>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5086,7 +5086,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5111,7 +5111,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5131,7 +5131,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5141,12 +5141,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5156,7 +5156,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5171,12 +5171,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5201,17 +5201,17 @@
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5243,12 +5243,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-0.52</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11380.761</t>
+          <t>14451.354</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5258,7 +5258,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5268,17 +5268,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-6.81</t>
+          <t>-2.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.78</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-22.59</t>
+          <t>-26.86</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5343,7 +5343,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.24</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5353,17 +5353,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>39.38</t>
+          <t>50.00</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.67</t>
+          <t>-0.09</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5374,42 +5374,42 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>294</t>
+          <t>455</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>10504</t>
+          <t>11427</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>15.56</t>
+          <t>6.67</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>11.15</t>
+          <t>13.37</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.08</t>
+          <t>-0.60</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.22</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>11.06</t>
+          <t>10.3</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>14.12</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
@@ -5419,32 +5419,32 @@
       </c>
       <c r="AM12" t="inlineStr">
         <is>
-          <t>1006.4</t>
+          <t>1005.15</t>
         </is>
       </c>
       <c r="AN12" t="inlineStr">
         <is>
-          <t>906.14</t>
+          <t>911.3</t>
         </is>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>792.68</t>
+          <t>798.52</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-46.45</t>
+          <t>-50.05</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>16.80</t>
+          <t>13.93</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>31.37</t>
+          <t>27.88</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5454,7 +5454,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-51.60</t>
+          <t>-56.98</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5464,27 +5464,27 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6440555731.807306</t>
+          <t>6454308304.944206</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>11237820653.0</t>
+          <t>13958553198.0</t>
         </is>
       </c>
       <c r="AX12" t="inlineStr">
         <is>
-          <t>11891933198.2</t>
+          <t>11246965605.2</t>
         </is>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15361285967.4</t>
+          <t>15377407355.7</t>
         </is>
       </c>
       <c r="AZ12" t="inlineStr">
         <is>
-          <t>13790744516.9</t>
+          <t>13940555876.02</t>
         </is>
       </c>
       <c r="BA12" t="inlineStr">
@@ -5494,16 +5494,16 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-19367696.47659796</t>
+          <t>-73989858.81012851</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-503578481.3964405</t>
+          <t>-374411751.6445465</t>
         </is>
       </c>
       <c r="BD12" t="n">
-        <v>11237820653</v>
+        <v>13958553198</v>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5522,7 +5522,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>157.14</t>
+          <t>155.82</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5547,7 +5547,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.32</t>
+          <t>1.31</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5567,7 +5567,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5577,12 +5577,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>10.49</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.77</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5592,7 +5592,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>47.32</t>
+          <t>49.14</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5607,12 +5607,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33.24</t>
+          <t>33.62</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2363764</t>
+          <t>2454678</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5632,22 +5632,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>993.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>981.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>972.0</t>
+          <t>967.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5679,12 +5679,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>52066.846</t>
+          <t>30647.12</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5694,7 +5694,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5709,12 +5709,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5779,7 +5779,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.90</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5789,17 +5789,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5810,12 +5810,12 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
@@ -5830,57 +5830,57 @@
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="AM13" t="inlineStr">
         <is>
-          <t>104.44</t>
+          <t>103.07</t>
         </is>
       </c>
       <c r="AN13" t="inlineStr">
         <is>
-          <t>103.43</t>
+          <t>103.31</t>
         </is>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-161.95</t>
+          <t>-113.22</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5890,7 +5890,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-115.11</t>
+          <t>-121.07</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5900,46 +5900,46 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>4682266073.0</t>
+          <t>2683545818.0</t>
         </is>
       </c>
       <c r="AX13" t="inlineStr">
         <is>
-          <t>5019578044.4</t>
+          <t>5000685349.4</t>
         </is>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4597307742.4</t>
+          <t>4727097624.7</t>
         </is>
       </c>
       <c r="AZ13" t="inlineStr">
         <is>
-          <t>7180754379.14</t>
+          <t>6863428946.3</t>
         </is>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>422270302</t>
+          <t>273587724</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-339772904.7418968</t>
+          <t>-299537059.7680103</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>116188863.3358154</t>
+          <t>-78239912.41163445</t>
         </is>
       </c>
       <c r="BD13" t="n">
-        <v>4682266073</v>
+        <v>2683545818</v>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -5958,7 +5958,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5983,7 +5983,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -6003,22 +6003,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -6028,7 +6028,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -6068,22 +6068,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6115,12 +6115,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>124181.065</t>
+          <t>52066.846</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6130,7 +6130,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6140,17 +6140,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6215,7 +6215,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-14.90</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6225,17 +6225,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6246,77 +6246,77 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>93.56</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AM14" t="inlineStr">
         <is>
-          <t>105.81</t>
+          <t>104.44</t>
         </is>
       </c>
       <c r="AN14" t="inlineStr">
         <is>
-          <t>103.41</t>
+          <t>103.43</t>
         </is>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-272.55</t>
+          <t>-161.95</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6326,7 +6326,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-108.99</t>
+          <t>-115.11</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6336,46 +6336,46 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="AX14" t="inlineStr">
         <is>
-          <t>4696916791.4</t>
+          <t>5019578044.4</t>
         </is>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4341077616.0</t>
+          <t>4597307742.4</t>
         </is>
       </c>
       <c r="AZ14" t="inlineStr">
         <is>
-          <t>7241408797.74</t>
+          <t>7180754379.14</t>
         </is>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>355839175</t>
+          <t>422270302</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-422675044.3923899</t>
+          <t>-339772904.7418968</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>175646056.2487507</t>
+          <t>116188863.3358154</t>
         </is>
       </c>
       <c r="BD14" t="n">
-        <v>11515775721</v>
+        <v>4682266073</v>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6394,7 +6394,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6419,7 +6419,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6439,22 +6439,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6464,7 +6464,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6479,12 +6479,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6504,22 +6504,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6551,12 +6551,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>32684.421</t>
+          <t>124181.065</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6566,7 +6566,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6576,17 +6576,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-3.95</t>
+          <t>-6.54</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6651,7 +6651,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6661,17 +6661,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6682,77 +6682,77 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.80</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.56</t>
         </is>
       </c>
       <c r="AM15" t="inlineStr">
         <is>
-          <t>106.92</t>
+          <t>105.81</t>
         </is>
       </c>
       <c r="AN15" t="inlineStr">
         <is>
-          <t>103.14</t>
+          <t>103.41</t>
         </is>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-939.09</t>
+          <t>-272.55</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6762,7 +6762,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6772,46 +6772,46 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="AX15" t="inlineStr">
         <is>
-          <t>3191641823.4</t>
+          <t>4696916791.4</t>
         </is>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3527299622.7</t>
+          <t>4341077616.0</t>
         </is>
       </c>
       <c r="AZ15" t="inlineStr">
         <is>
-          <t>7285669264.58</t>
+          <t>7241408797.74</t>
         </is>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>-335657799</t>
+          <t>355839175</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-531460699.0544155</t>
+          <t>-422675044.3923899</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-477849918.1702256</t>
+          <t>175646056.2487507</t>
         </is>
       </c>
       <c r="BD15" t="n">
-        <v>3032171594</v>
+        <v>11515775721</v>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6830,7 +6830,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6855,7 +6855,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6875,22 +6875,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6900,7 +6900,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6915,12 +6915,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6940,22 +6940,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6987,12 +6987,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>31967.753</t>
+          <t>32684.421</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -7002,7 +7002,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -7012,17 +7012,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-8.59</t>
+          <t>-5.5</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7087,7 +7087,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7097,17 +7097,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7118,17 +7118,17 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
@@ -7138,57 +7138,57 @@
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.80</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>95.85999999999999</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AM16" t="inlineStr">
         <is>
-          <t>108.02</t>
+          <t>106.92</t>
         </is>
       </c>
       <c r="AN16" t="inlineStr">
         <is>
-          <t>102.75</t>
+          <t>103.14</t>
         </is>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-712.58</t>
+          <t>-939.09</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7198,7 +7198,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7208,46 +7208,46 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="AX16" t="inlineStr">
         <is>
-          <t>4058514408.6</t>
+          <t>3191641823.4</t>
         </is>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3531039856.9</t>
+          <t>3527299622.7</t>
         </is>
       </c>
       <c r="AZ16" t="inlineStr">
         <is>
-          <t>7317342463.3</t>
+          <t>7285669264.58</t>
         </is>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>527474551</t>
+          <t>-335657799</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-541208113.7606318</t>
+          <t>-531460699.0544155</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-485391942.3698263</t>
+          <t>-477849918.1702256</t>
         </is>
       </c>
       <c r="BD16" t="n">
-        <v>3089667541</v>
+        <v>3032171594</v>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7266,7 +7266,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7291,7 +7291,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7311,22 +7311,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7336,7 +7336,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7351,12 +7351,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7376,22 +7376,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7423,12 +7423,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>29839.894</t>
+          <t>31967.753</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7438,7 +7438,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7448,17 +7448,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-5.08</t>
+          <t>-10.21</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7523,7 +7523,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7533,17 +7533,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7554,77 +7554,77 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>95.85999999999999</t>
         </is>
       </c>
       <c r="AM17" t="inlineStr">
         <is>
-          <t>109.04</t>
+          <t>108.02</t>
         </is>
       </c>
       <c r="AN17" t="inlineStr">
         <is>
-          <t>102.19</t>
+          <t>102.75</t>
         </is>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-283.53</t>
+          <t>-712.58</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7634,7 +7634,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7644,46 +7644,46 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="AX17" t="inlineStr">
         <is>
-          <t>4453509900.0</t>
+          <t>4058514408.6</t>
         </is>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3688316666.2</t>
+          <t>3531039856.9</t>
         </is>
       </c>
       <c r="AZ17" t="inlineStr">
         <is>
-          <t>7280178623.2</t>
+          <t>7317342463.3</t>
         </is>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>765193233</t>
+          <t>527474551</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-551356508.5589601</t>
+          <t>-541208113.7606318</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-484991116.1774759</t>
+          <t>-485391942.3698263</t>
         </is>
       </c>
       <c r="BD17" t="n">
-        <v>2778009293</v>
+        <v>3089667541</v>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7702,7 +7702,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7727,7 +7727,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7747,22 +7747,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7772,7 +7772,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7787,12 +7787,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7812,22 +7812,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7859,12 +7859,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>32132.941</t>
+          <t>29839.894</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7874,7 +7874,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7884,17 +7884,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-5.99</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7959,7 +7959,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7969,17 +7969,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7990,12 +7990,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -8010,57 +8010,57 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>98.74</t>
         </is>
       </c>
       <c r="AM18" t="inlineStr">
         <is>
-          <t>110.06</t>
+          <t>109.04</t>
         </is>
       </c>
       <c r="AN18" t="inlineStr">
         <is>
-          <t>101.66</t>
+          <t>102.19</t>
         </is>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>85.35</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-161.08</t>
+          <t>-283.53</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -8070,7 +8070,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-81.65</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -8080,46 +8080,46 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="AX18" t="inlineStr">
         <is>
-          <t>4175037440.4</t>
+          <t>4453509900.0</t>
         </is>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3901577638.9</t>
+          <t>3688316666.2</t>
         </is>
       </c>
       <c r="AZ18" t="inlineStr">
         <is>
-          <t>7265450343.64</t>
+          <t>7280178623.2</t>
         </is>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>273459801</t>
+          <t>765193233</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-563422943.5374118</t>
+          <t>-551356508.5589601</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-433705440.8963513</t>
+          <t>-484991116.1774759</t>
         </is>
       </c>
       <c r="BD18" t="n">
-        <v>3068959808</v>
+        <v>2778009293</v>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8138,7 +8138,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8163,7 +8163,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8183,22 +8183,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8223,12 +8223,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8248,22 +8248,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8295,12 +8295,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8310,7 +8310,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8320,17 +8320,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-9.15</t>
+          <t>-7.57</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8395,7 +8395,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8405,17 +8405,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8426,12 +8426,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8441,62 +8441,62 @@
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM19" t="inlineStr">
         <is>
-          <t>111.34</t>
+          <t>110.06</t>
         </is>
       </c>
       <c r="AN19" t="inlineStr">
         <is>
-          <t>101.12</t>
+          <t>101.66</t>
         </is>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8506,7 +8506,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8516,46 +8516,46 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX19" t="inlineStr">
         <is>
-          <t>3985238440.6</t>
+          <t>4175037440.4</t>
         </is>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ19" t="inlineStr">
         <is>
-          <t>7220968787.64</t>
+          <t>7265450343.64</t>
         </is>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-376123979.9270172</t>
+          <t>-433705440.8963513</t>
         </is>
       </c>
       <c r="BD19" t="n">
-        <v>3989400881</v>
+        <v>3068959808</v>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8574,7 +8574,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8599,7 +8599,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8619,22 +8619,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8644,7 +8644,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8659,12 +8659,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8684,22 +8684,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8731,12 +8731,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8746,7 +8746,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8756,17 +8756,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-12.77</t>
+          <t>-10.78</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8831,7 +8831,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8841,17 +8841,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8862,12 +8862,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8877,62 +8877,62 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM20" t="inlineStr">
         <is>
-          <t>111.96</t>
+          <t>111.34</t>
         </is>
       </c>
       <c r="AN20" t="inlineStr">
         <is>
-          <t>100.52</t>
+          <t>101.12</t>
         </is>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8942,7 +8942,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8952,46 +8952,46 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX20" t="inlineStr">
         <is>
-          <t>3862957422.0</t>
+          <t>3985238440.6</t>
         </is>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ20" t="inlineStr">
         <is>
-          <t>7171595467.56</t>
+          <t>7220968787.64</t>
         </is>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-379050437.0805759</t>
+          <t>-376123979.9270172</t>
         </is>
       </c>
       <c r="BD20" t="n">
-        <v>7366534520</v>
+        <v>3989400881</v>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9010,7 +9010,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -9035,7 +9035,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -9065,12 +9065,12 @@
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -9080,7 +9080,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -9095,12 +9095,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9120,22 +9120,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9167,12 +9167,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9182,7 +9182,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9192,17 +9192,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-24.86</t>
+          <t>-14.45</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9267,7 +9267,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9277,17 +9277,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9298,17 +9298,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9318,57 +9318,57 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM21" t="inlineStr">
         <is>
-          <t>112.52</t>
+          <t>111.96</t>
         </is>
       </c>
       <c r="AN21" t="inlineStr">
         <is>
-          <t>99.87</t>
+          <t>100.52</t>
         </is>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9378,7 +9378,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9388,46 +9388,46 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX21" t="inlineStr">
         <is>
-          <t>3003565305.2</t>
+          <t>3862957422.0</t>
         </is>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ21" t="inlineStr">
         <is>
-          <t>7070679471.22</t>
+          <t>7171595467.56</t>
         </is>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-731529321.5827818</t>
+          <t>-379050437.0805759</t>
         </is>
       </c>
       <c r="BD21" t="n">
-        <v>5064644998</v>
+        <v>7366534520</v>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9446,7 +9446,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9471,7 +9471,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9491,22 +9491,22 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9516,7 +9516,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9531,12 +9531,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9556,22 +9556,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9603,12 +9603,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9618,7 +9618,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9628,17 +9628,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-19.77</t>
+          <t>-26.72</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9703,7 +9703,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9713,17 +9713,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9734,77 +9734,77 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM22" t="inlineStr">
         <is>
-          <t>112.4</t>
+          <t>112.52</t>
         </is>
       </c>
       <c r="AN22" t="inlineStr">
         <is>
-          <t>99.02</t>
+          <t>99.87</t>
         </is>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9814,7 +9814,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9824,46 +9824,46 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX22" t="inlineStr">
         <is>
-          <t>2923123432.4</t>
+          <t>3003565305.2</t>
         </is>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ22" t="inlineStr">
         <is>
-          <t>7004676232.68</t>
+          <t>7070679471.22</t>
         </is>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-962313517.7436905</t>
+          <t>-731529321.5827818</t>
         </is>
       </c>
       <c r="BD22" t="n">
-        <v>1385646995</v>
+        <v>5064644998</v>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -9882,7 +9882,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9907,7 +9907,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9927,7 +9927,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9937,12 +9937,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9952,7 +9952,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9967,12 +9967,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9992,22 +9992,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -10039,12 +10039,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-1.4</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>20206.638</t>
+          <t>13178.714</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -10054,7 +10054,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -10064,17 +10064,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-18.08</t>
+          <t>-21.56</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-4.94</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-20.97</t>
+          <t>-29.70</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10139,7 +10139,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>0.48</t>
+          <t>1.92</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10149,17 +10149,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-11</t>
+          <t>2025-11-12</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>6.10</t>
+          <t>3.98</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>-1.90</t>
+          <t>2.42</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10170,77 +10170,77 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>689</t>
+          <t>345</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>52067</t>
+          <t>30647</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>12.5</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.17</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-3.78</t>
+          <t>-1.49</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-3.29</t>
+          <t>-4.27</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>14.28</t>
+          <t>13.52</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>19.86</t>
+          <t>19.71</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>108.6</t>
+          <t>107.6</t>
         </is>
       </c>
       <c r="AM23" t="inlineStr">
         <is>
-          <t>112.3</t>
+          <t>112.4</t>
         </is>
       </c>
       <c r="AN23" t="inlineStr">
         <is>
-          <t>98.27</t>
+          <t>99.02</t>
         </is>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>81.99</t>
+          <t>82.71</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-48.86</t>
+          <t>-54.62</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>1.94</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>4.28</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10250,7 +10250,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-50.96</t>
+          <t>-56.85</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10260,46 +10260,46 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1900918213.476327</t>
+          <t>1903961767.22063</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>2119964809.0</t>
+          <t>1385646995.0</t>
         </is>
       </c>
       <c r="AX23" t="inlineStr">
         <is>
-          <t>3628117837.4</t>
+          <t>2923123432.4</t>
         </is>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>4590922523.2</t>
+          <t>4157974302.6</t>
         </is>
       </c>
       <c r="AZ23" t="inlineStr">
         <is>
-          <t>7037581985.4</t>
+          <t>7004676232.68</t>
         </is>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-962804685</t>
+          <t>-1234850870</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-603815707.0069512</t>
+          <t>-658969216.3510649</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-863458529.1612859</t>
+          <t>-962313517.7436905</t>
         </is>
       </c>
       <c r="BD23" t="n">
-        <v>2119964809</v>
+        <v>1385646995</v>
       </c>
       <c r="BE23" t="inlineStr">
         <is>
@@ -10318,7 +10318,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>88.97</t>
+          <t>91.68</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10343,7 +10343,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.74</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10363,7 +10363,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10373,12 +10373,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.79</t>
+          <t>2.83</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.52</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10388,7 +10388,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>38.48</t>
+          <t>37.91</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10403,12 +10403,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>40.55</t>
+          <t>41.32</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>210315</t>
+          <t>207226</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10428,12 +10428,12 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>107.0</t>
+          <t>104.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>107.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
@@ -10443,7 +10443,7 @@
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.0</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -1057,15 +1057,11 @@
           <t>919.4</t>
         </is>
       </c>
-      <c r="AM2" t="inlineStr">
-        <is>
-          <t>948.95</t>
-        </is>
-      </c>
-      <c r="AN2" t="inlineStr">
-        <is>
-          <t>947.82</t>
-        </is>
+      <c r="AM2" t="n">
+        <v>948.95</v>
+      </c>
+      <c r="AN2" t="n">
+        <v>947.8200000000001</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
@@ -1112,20 +1108,16 @@
           <t>10702402903.0</t>
         </is>
       </c>
-      <c r="AX2" t="inlineStr">
-        <is>
-          <t>13777681330.2</t>
-        </is>
+      <c r="AX2" t="n">
+        <v>13777681330.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
           <t>13184190874.5</t>
         </is>
       </c>
-      <c r="AZ2" t="inlineStr">
-        <is>
-          <t>14165986897.28</t>
-        </is>
+      <c r="AZ2" t="n">
+        <v>14165986897.28</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
@@ -1142,8 +1134,10 @@
           <t>-288049536.2624874</t>
         </is>
       </c>
-      <c r="BD2" t="n">
-        <v>10702402903</v>
+      <c r="BD2" t="inlineStr">
+        <is>
+          <t>10702402903.0</t>
+        </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
@@ -1309,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1493,15 +1487,11 @@
           <t>909.2</t>
         </is>
       </c>
-      <c r="AM3" t="inlineStr">
-        <is>
-          <t>954.7</t>
-        </is>
-      </c>
-      <c r="AN3" t="inlineStr">
-        <is>
-          <t>945.54</t>
-        </is>
+      <c r="AM3" t="n">
+        <v>954.7</v>
+      </c>
+      <c r="AN3" t="n">
+        <v>945.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
@@ -1548,20 +1538,16 @@
           <t>9579043601.0</t>
         </is>
       </c>
-      <c r="AX3" t="inlineStr">
-        <is>
-          <t>13831910429.6</t>
-        </is>
+      <c r="AX3" t="n">
+        <v>13831910429.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
           <t>13509805904.0</t>
         </is>
       </c>
-      <c r="AZ3" t="inlineStr">
-        <is>
-          <t>14413977761.06</t>
-        </is>
+      <c r="AZ3" t="n">
+        <v>14413977761.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
@@ -1578,8 +1564,10 @@
           <t>-94238805.57345963</t>
         </is>
       </c>
-      <c r="BD3" t="n">
-        <v>9579043601</v>
+      <c r="BD3" t="inlineStr">
+        <is>
+          <t>9579043601.0</t>
+        </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
@@ -1745,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1929,15 +1917,11 @@
           <t>906.8</t>
         </is>
       </c>
-      <c r="AM4" t="inlineStr">
-        <is>
-          <t>962.95</t>
-        </is>
-      </c>
-      <c r="AN4" t="inlineStr">
-        <is>
-          <t>944.08</t>
-        </is>
+      <c r="AM4" t="n">
+        <v>962.95</v>
+      </c>
+      <c r="AN4" t="n">
+        <v>944.08</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
@@ -1984,20 +1968,16 @@
           <t>16911194399.0</t>
         </is>
       </c>
-      <c r="AX4" t="inlineStr">
-        <is>
-          <t>14386844246.4</t>
-        </is>
+      <c r="AX4" t="n">
+        <v>14386844246.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
           <t>13675683609.2</t>
         </is>
       </c>
-      <c r="AZ4" t="inlineStr">
-        <is>
-          <t>14618581897.64</t>
-        </is>
+      <c r="AZ4" t="n">
+        <v>14618581897.64</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
@@ -2014,8 +1994,10 @@
           <t>306359263.681345</t>
         </is>
       </c>
-      <c r="BD4" t="n">
-        <v>16911194399</v>
+      <c r="BD4" t="inlineStr">
+        <is>
+          <t>16911194399.0</t>
+        </is>
       </c>
       <c r="BE4" t="inlineStr">
         <is>
@@ -2181,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2365,15 +2347,11 @@
           <t>911.4</t>
         </is>
       </c>
-      <c r="AM5" t="inlineStr">
-        <is>
-          <t>971.8</t>
-        </is>
-      </c>
-      <c r="AN5" t="inlineStr">
-        <is>
-          <t>941.9</t>
-        </is>
+      <c r="AM5" t="n">
+        <v>971.8</v>
+      </c>
+      <c r="AN5" t="n">
+        <v>941.9</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
@@ -2420,20 +2398,16 @@
           <t>15812987742.0</t>
         </is>
       </c>
-      <c r="AX5" t="inlineStr">
-        <is>
-          <t>13146559354.4</t>
-        </is>
+      <c r="AX5" t="n">
+        <v>13146559354.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
           <t>13118876980.5</t>
         </is>
       </c>
-      <c r="AZ5" t="inlineStr">
-        <is>
-          <t>14614553602.28</t>
-        </is>
+      <c r="AZ5" t="n">
+        <v>14614553602.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
@@ -2450,8 +2424,10 @@
           <t>82113231.98530579</t>
         </is>
       </c>
-      <c r="BD5" t="n">
-        <v>15812987742</v>
+      <c r="BD5" t="inlineStr">
+        <is>
+          <t>15812987742.0</t>
+        </is>
       </c>
       <c r="BE5" t="inlineStr">
         <is>
@@ -2617,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2801,15 +2777,11 @@
           <t>916.8</t>
         </is>
       </c>
-      <c r="AM6" t="inlineStr">
-        <is>
-          <t>977.55</t>
-        </is>
-      </c>
-      <c r="AN6" t="inlineStr">
-        <is>
-          <t>938.52</t>
-        </is>
+      <c r="AM6" t="n">
+        <v>977.55</v>
+      </c>
+      <c r="AN6" t="n">
+        <v>938.52</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
@@ -2856,20 +2828,16 @@
           <t>15882778006.0</t>
         </is>
       </c>
-      <c r="AX6" t="inlineStr">
-        <is>
-          <t>13620510362.4</t>
-        </is>
+      <c r="AX6" t="n">
+        <v>13620510362.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
           <t>12470961715.4</t>
         </is>
       </c>
-      <c r="AZ6" t="inlineStr">
-        <is>
-          <t>14466055493.78</t>
-        </is>
+      <c r="AZ6" t="n">
+        <v>14466055493.78</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
@@ -2886,8 +2854,10 @@
           <t>-123505858.3299389</t>
         </is>
       </c>
-      <c r="BD6" t="n">
-        <v>15882778006</v>
+      <c r="BD6" t="inlineStr">
+        <is>
+          <t>15882778006.0</t>
+        </is>
       </c>
       <c r="BE6" t="inlineStr">
         <is>
@@ -3053,7 +3023,7 @@
     <row r="7">
       <c r="A7" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B7" t="inlineStr">
@@ -3237,15 +3207,11 @@
           <t>917.6</t>
         </is>
       </c>
-      <c r="AM7" t="inlineStr">
-        <is>
-          <t>980.85</t>
-        </is>
-      </c>
-      <c r="AN7" t="inlineStr">
-        <is>
-          <t>933.96</t>
-        </is>
+      <c r="AM7" t="n">
+        <v>980.85</v>
+      </c>
+      <c r="AN7" t="n">
+        <v>933.96</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
@@ -3292,20 +3258,16 @@
           <t>10973548400.0</t>
         </is>
       </c>
-      <c r="AX7" t="inlineStr">
-        <is>
-          <t>12590700418.8</t>
-        </is>
+      <c r="AX7" t="n">
+        <v>12590700418.8</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
           <t>11918833012.0</t>
         </is>
       </c>
-      <c r="AZ7" t="inlineStr">
-        <is>
-          <t>14368721493.28</t>
-        </is>
+      <c r="AZ7" t="n">
+        <v>14368721493.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
@@ -3322,8 +3284,10 @@
           <t>-420314020.6970749</t>
         </is>
       </c>
-      <c r="BD7" t="n">
-        <v>10973548400</v>
+      <c r="BD7" t="inlineStr">
+        <is>
+          <t>10973548400.0</t>
+        </is>
       </c>
       <c r="BE7" t="inlineStr">
         <is>
@@ -3489,7 +3453,7 @@
     <row r="8">
       <c r="A8" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B8" t="inlineStr">
@@ -3673,15 +3637,11 @@
           <t>932.2</t>
         </is>
       </c>
-      <c r="AM8" t="inlineStr">
-        <is>
-          <t>987.15</t>
-        </is>
-      </c>
-      <c r="AN8" t="inlineStr">
-        <is>
-          <t>929.9</t>
-        </is>
+      <c r="AM8" t="n">
+        <v>987.15</v>
+      </c>
+      <c r="AN8" t="n">
+        <v>929.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
@@ -3728,20 +3688,16 @@
           <t>12353712685.0</t>
         </is>
       </c>
-      <c r="AX8" t="inlineStr">
-        <is>
-          <t>13187701378.4</t>
-        </is>
+      <c r="AX8" t="n">
+        <v>13187701378.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
           <t>12539817288.3</t>
         </is>
       </c>
-      <c r="AZ8" t="inlineStr">
-        <is>
-          <t>14292572173.18</t>
-        </is>
+      <c r="AZ8" t="n">
+        <v>14292572173.18</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
@@ -3758,8 +3714,10 @@
           <t>-303325579.8395176</t>
         </is>
       </c>
-      <c r="BD8" t="n">
-        <v>12353712685</v>
+      <c r="BD8" t="inlineStr">
+        <is>
+          <t>12353712685.0</t>
+        </is>
       </c>
       <c r="BE8" t="inlineStr">
         <is>
@@ -3925,7 +3883,7 @@
     <row r="9">
       <c r="A9" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B9" t="inlineStr">
@@ -4109,15 +4067,11 @@
           <t>947.0</t>
         </is>
       </c>
-      <c r="AM9" t="inlineStr">
-        <is>
-          <t>993.0</t>
-        </is>
-      </c>
-      <c r="AN9" t="inlineStr">
-        <is>
-          <t>925.54</t>
-        </is>
+      <c r="AM9" t="n">
+        <v>993</v>
+      </c>
+      <c r="AN9" t="n">
+        <v>925.54</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
@@ -4164,20 +4118,16 @@
           <t>10709769939.0</t>
         </is>
       </c>
-      <c r="AX9" t="inlineStr">
-        <is>
-          <t>12964522972.0</t>
-        </is>
+      <c r="AX9" t="n">
+        <v>12964522972</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
           <t>13184192924.4</t>
         </is>
       </c>
-      <c r="AZ9" t="inlineStr">
-        <is>
-          <t>14209168625.62</t>
-        </is>
+      <c r="AZ9" t="n">
+        <v>14209168625.62</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
@@ -4194,8 +4144,10 @@
           <t>-273240924.15588</t>
         </is>
       </c>
-      <c r="BD9" t="n">
-        <v>10709769939</v>
+      <c r="BD9" t="inlineStr">
+        <is>
+          <t>10709769939.0</t>
+        </is>
       </c>
       <c r="BE9" t="inlineStr">
         <is>
@@ -4361,7 +4313,7 @@
     <row r="10">
       <c r="A10" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B10" t="inlineStr">
@@ -4545,15 +4497,11 @@
           <t>960.2</t>
         </is>
       </c>
-      <c r="AM10" t="inlineStr">
-        <is>
-          <t>997.15</t>
-        </is>
-      </c>
-      <c r="AN10" t="inlineStr">
-        <is>
-          <t>920.92</t>
-        </is>
+      <c r="AM10" t="n">
+        <v>997.15</v>
+      </c>
+      <c r="AN10" t="n">
+        <v>920.92</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
@@ -4600,20 +4548,16 @@
           <t>18182742782.0</t>
         </is>
       </c>
-      <c r="AX10" t="inlineStr">
-        <is>
-          <t>13091194606.6</t>
-        </is>
+      <c r="AX10" t="n">
+        <v>13091194606.6</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
           <t>13748861147.6</t>
         </is>
       </c>
-      <c r="AZ10" t="inlineStr">
-        <is>
-          <t>14155319682.02</t>
-        </is>
+      <c r="AZ10" t="n">
+        <v>14155319682.02</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
@@ -4630,8 +4574,10 @@
           <t>-44367517.38797188</t>
         </is>
       </c>
-      <c r="BD10" t="n">
-        <v>18182742782</v>
+      <c r="BD10" t="inlineStr">
+        <is>
+          <t>18182742782.0</t>
+        </is>
       </c>
       <c r="BE10" t="inlineStr">
         <is>
@@ -4797,7 +4743,7 @@
     <row r="11">
       <c r="A11" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B11" t="inlineStr">
@@ -4981,15 +4927,11 @@
           <t>968.8</t>
         </is>
       </c>
-      <c r="AM11" t="inlineStr">
-        <is>
-          <t>1002.3</t>
-        </is>
-      </c>
-      <c r="AN11" t="inlineStr">
-        <is>
-          <t>916.24</t>
-        </is>
+      <c r="AM11" t="n">
+        <v>1002.3</v>
+      </c>
+      <c r="AN11" t="n">
+        <v>916.24</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
@@ -5036,20 +4978,16 @@
           <t>10733728288.0</t>
         </is>
       </c>
-      <c r="AX11" t="inlineStr">
-        <is>
-          <t>11321413068.4</t>
-        </is>
+      <c r="AX11" t="n">
+        <v>11321413068.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
           <t>14033372540.0</t>
         </is>
       </c>
-      <c r="AZ11" t="inlineStr">
-        <is>
-          <t>13994353884.38</t>
-        </is>
+      <c r="AZ11" t="n">
+        <v>13994353884.38</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
@@ -5066,8 +5004,10 @@
           <t>-516496615.2771072</t>
         </is>
       </c>
-      <c r="BD11" t="n">
-        <v>10733728288</v>
+      <c r="BD11" t="inlineStr">
+        <is>
+          <t>10733728288.0</t>
+        </is>
       </c>
       <c r="BE11" t="inlineStr">
         <is>
@@ -5233,7 +5173,7 @@
     <row r="12">
       <c r="A12" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B12" t="inlineStr">
@@ -5417,15 +5357,11 @@
           <t>972.8</t>
         </is>
       </c>
-      <c r="AM12" t="inlineStr">
-        <is>
-          <t>1005.15</t>
-        </is>
-      </c>
-      <c r="AN12" t="inlineStr">
-        <is>
-          <t>911.3</t>
-        </is>
+      <c r="AM12" t="n">
+        <v>1005.15</v>
+      </c>
+      <c r="AN12" t="n">
+        <v>911.3</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
@@ -5472,20 +5408,16 @@
           <t>13958553198.0</t>
         </is>
       </c>
-      <c r="AX12" t="inlineStr">
-        <is>
-          <t>11246965605.2</t>
-        </is>
+      <c r="AX12" t="n">
+        <v>11246965605.2</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
           <t>15377407355.7</t>
         </is>
       </c>
-      <c r="AZ12" t="inlineStr">
-        <is>
-          <t>13940555876.02</t>
-        </is>
+      <c r="AZ12" t="n">
+        <v>13940555876.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5502,8 +5434,10 @@
           <t>-374411751.6445465</t>
         </is>
       </c>
-      <c r="BD12" t="n">
-        <v>13958553198</v>
+      <c r="BD12" t="inlineStr">
+        <is>
+          <t>13958553198.0</t>
+        </is>
       </c>
       <c r="BE12" t="inlineStr">
         <is>
@@ -5669,7 +5603,7 @@
     <row r="13">
       <c r="A13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B13" t="inlineStr">
@@ -5853,15 +5787,11 @@
           <t>91.34</t>
         </is>
       </c>
-      <c r="AM13" t="inlineStr">
-        <is>
-          <t>103.07</t>
-        </is>
-      </c>
-      <c r="AN13" t="inlineStr">
-        <is>
-          <t>103.31</t>
-        </is>
+      <c r="AM13" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>103.31</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
@@ -5908,20 +5838,16 @@
           <t>2683545818.0</t>
         </is>
       </c>
-      <c r="AX13" t="inlineStr">
-        <is>
-          <t>5000685349.4</t>
-        </is>
+      <c r="AX13" t="n">
+        <v>5000685349.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
           <t>4727097624.7</t>
         </is>
       </c>
-      <c r="AZ13" t="inlineStr">
-        <is>
-          <t>6863428946.3</t>
-        </is>
+      <c r="AZ13" t="n">
+        <v>6863428946.3</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
@@ -5938,8 +5864,10 @@
           <t>-78239912.41163445</t>
         </is>
       </c>
-      <c r="BD13" t="n">
-        <v>2683545818</v>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
       </c>
       <c r="BE13" t="inlineStr">
         <is>
@@ -6105,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6289,15 +6217,11 @@
           <t>92.5</t>
         </is>
       </c>
-      <c r="AM14" t="inlineStr">
-        <is>
-          <t>104.44</t>
-        </is>
-      </c>
-      <c r="AN14" t="inlineStr">
-        <is>
-          <t>103.43</t>
-        </is>
+      <c r="AM14" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>103.43</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
@@ -6344,20 +6268,16 @@
           <t>4682266073.0</t>
         </is>
       </c>
-      <c r="AX14" t="inlineStr">
-        <is>
-          <t>5019578044.4</t>
-        </is>
+      <c r="AX14" t="n">
+        <v>5019578044.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
           <t>4597307742.4</t>
         </is>
       </c>
-      <c r="AZ14" t="inlineStr">
-        <is>
-          <t>7180754379.14</t>
-        </is>
+      <c r="AZ14" t="n">
+        <v>7180754379.14</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
@@ -6374,8 +6294,10 @@
           <t>116188863.3358154</t>
         </is>
       </c>
-      <c r="BD14" t="n">
-        <v>4682266073</v>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
       </c>
       <c r="BE14" t="inlineStr">
         <is>
@@ -6541,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6725,15 +6647,11 @@
           <t>93.56</t>
         </is>
       </c>
-      <c r="AM15" t="inlineStr">
-        <is>
-          <t>105.81</t>
-        </is>
-      </c>
-      <c r="AN15" t="inlineStr">
-        <is>
-          <t>103.41</t>
-        </is>
+      <c r="AM15" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>103.41</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
@@ -6780,20 +6698,16 @@
           <t>11515775721.0</t>
         </is>
       </c>
-      <c r="AX15" t="inlineStr">
-        <is>
-          <t>4696916791.4</t>
-        </is>
+      <c r="AX15" t="n">
+        <v>4696916791.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
           <t>4341077616.0</t>
         </is>
       </c>
-      <c r="AZ15" t="inlineStr">
-        <is>
-          <t>7241408797.74</t>
-        </is>
+      <c r="AZ15" t="n">
+        <v>7241408797.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
@@ -6810,8 +6724,10 @@
           <t>175646056.2487507</t>
         </is>
       </c>
-      <c r="BD15" t="n">
-        <v>11515775721</v>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
       </c>
       <c r="BE15" t="inlineStr">
         <is>
@@ -6977,7 +6893,7 @@
     <row r="16">
       <c r="A16" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B16" t="inlineStr">
@@ -7161,15 +7077,11 @@
           <t>94.3</t>
         </is>
       </c>
-      <c r="AM16" t="inlineStr">
-        <is>
-          <t>106.92</t>
-        </is>
-      </c>
-      <c r="AN16" t="inlineStr">
-        <is>
-          <t>103.14</t>
-        </is>
+      <c r="AM16" t="n">
+        <v>106.92</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>103.14</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
@@ -7216,20 +7128,16 @@
           <t>3032171594.0</t>
         </is>
       </c>
-      <c r="AX16" t="inlineStr">
-        <is>
-          <t>3191641823.4</t>
-        </is>
+      <c r="AX16" t="n">
+        <v>3191641823.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
           <t>3527299622.7</t>
         </is>
       </c>
-      <c r="AZ16" t="inlineStr">
-        <is>
-          <t>7285669264.58</t>
-        </is>
+      <c r="AZ16" t="n">
+        <v>7285669264.58</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
@@ -7246,8 +7154,10 @@
           <t>-477849918.1702256</t>
         </is>
       </c>
-      <c r="BD16" t="n">
-        <v>3032171594</v>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
       </c>
       <c r="BE16" t="inlineStr">
         <is>
@@ -7413,7 +7323,7 @@
     <row r="17">
       <c r="A17" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B17" t="inlineStr">
@@ -7597,15 +7507,11 @@
           <t>95.85999999999999</t>
         </is>
       </c>
-      <c r="AM17" t="inlineStr">
-        <is>
-          <t>108.02</t>
-        </is>
-      </c>
-      <c r="AN17" t="inlineStr">
-        <is>
-          <t>102.75</t>
-        </is>
+      <c r="AM17" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>102.75</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
@@ -7652,20 +7558,16 @@
           <t>3089667541.0</t>
         </is>
       </c>
-      <c r="AX17" t="inlineStr">
-        <is>
-          <t>4058514408.6</t>
-        </is>
+      <c r="AX17" t="n">
+        <v>4058514408.6</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
           <t>3531039856.9</t>
         </is>
       </c>
-      <c r="AZ17" t="inlineStr">
-        <is>
-          <t>7317342463.3</t>
-        </is>
+      <c r="AZ17" t="n">
+        <v>7317342463.3</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
@@ -7682,8 +7584,10 @@
           <t>-485391942.3698263</t>
         </is>
       </c>
-      <c r="BD17" t="n">
-        <v>3089667541</v>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
       </c>
       <c r="BE17" t="inlineStr">
         <is>
@@ -7849,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -8033,15 +7937,11 @@
           <t>98.74</t>
         </is>
       </c>
-      <c r="AM18" t="inlineStr">
-        <is>
-          <t>109.04</t>
-        </is>
-      </c>
-      <c r="AN18" t="inlineStr">
-        <is>
-          <t>102.19</t>
-        </is>
+      <c r="AM18" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>102.19</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
@@ -8088,20 +7988,16 @@
           <t>2778009293.0</t>
         </is>
       </c>
-      <c r="AX18" t="inlineStr">
-        <is>
-          <t>4453509900.0</t>
-        </is>
+      <c r="AX18" t="n">
+        <v>4453509900</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
           <t>3688316666.2</t>
         </is>
       </c>
-      <c r="AZ18" t="inlineStr">
-        <is>
-          <t>7280178623.2</t>
-        </is>
+      <c r="AZ18" t="n">
+        <v>7280178623.2</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
@@ -8118,8 +8014,10 @@
           <t>-484991116.1774759</t>
         </is>
       </c>
-      <c r="BD18" t="n">
-        <v>2778009293</v>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
       </c>
       <c r="BE18" t="inlineStr">
         <is>
@@ -8285,7 +8183,7 @@
     <row r="19">
       <c r="A19" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B19" t="inlineStr">
@@ -8469,15 +8367,11 @@
           <t>101.34</t>
         </is>
       </c>
-      <c r="AM19" t="inlineStr">
-        <is>
-          <t>110.06</t>
-        </is>
-      </c>
-      <c r="AN19" t="inlineStr">
-        <is>
-          <t>101.66</t>
-        </is>
+      <c r="AM19" t="n">
+        <v>110.06</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>101.66</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
@@ -8524,20 +8418,16 @@
           <t>3068959808.0</t>
         </is>
       </c>
-      <c r="AX19" t="inlineStr">
-        <is>
-          <t>4175037440.4</t>
-        </is>
+      <c r="AX19" t="n">
+        <v>4175037440.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
           <t>3901577638.9</t>
         </is>
       </c>
-      <c r="AZ19" t="inlineStr">
-        <is>
-          <t>7265450343.64</t>
-        </is>
+      <c r="AZ19" t="n">
+        <v>7265450343.64</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
@@ -8554,8 +8444,10 @@
           <t>-433705440.8963513</t>
         </is>
       </c>
-      <c r="BD19" t="n">
-        <v>3068959808</v>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
       </c>
       <c r="BE19" t="inlineStr">
         <is>
@@ -8721,7 +8613,7 @@
     <row r="20">
       <c r="A20" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B20" t="inlineStr">
@@ -8905,15 +8797,11 @@
           <t>103.48</t>
         </is>
       </c>
-      <c r="AM20" t="inlineStr">
-        <is>
-          <t>111.34</t>
-        </is>
-      </c>
-      <c r="AN20" t="inlineStr">
-        <is>
-          <t>101.12</t>
-        </is>
+      <c r="AM20" t="n">
+        <v>111.34</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>101.12</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
@@ -8960,20 +8848,16 @@
           <t>3989400881.0</t>
         </is>
       </c>
-      <c r="AX20" t="inlineStr">
-        <is>
-          <t>3985238440.6</t>
-        </is>
+      <c r="AX20" t="n">
+        <v>3985238440.6</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
           <t>3979054603.6</t>
         </is>
       </c>
-      <c r="AZ20" t="inlineStr">
-        <is>
-          <t>7220968787.64</t>
-        </is>
+      <c r="AZ20" t="n">
+        <v>7220968787.64</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
@@ -8990,8 +8874,10 @@
           <t>-376123979.9270172</t>
         </is>
       </c>
-      <c r="BD20" t="n">
-        <v>3989400881</v>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>3989400881.0</t>
+        </is>
       </c>
       <c r="BE20" t="inlineStr">
         <is>
@@ -9157,7 +9043,7 @@
     <row r="21">
       <c r="A21" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B21" t="inlineStr">
@@ -9341,15 +9227,11 @@
           <t>105.36</t>
         </is>
       </c>
-      <c r="AM21" t="inlineStr">
-        <is>
-          <t>111.96</t>
-        </is>
-      </c>
-      <c r="AN21" t="inlineStr">
-        <is>
-          <t>100.52</t>
-        </is>
+      <c r="AM21" t="n">
+        <v>111.96</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>100.52</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
@@ -9396,20 +9278,16 @@
           <t>7366534520.0</t>
         </is>
       </c>
-      <c r="AX21" t="inlineStr">
-        <is>
-          <t>3862957422.0</t>
-        </is>
+      <c r="AX21" t="n">
+        <v>3862957422</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
           <t>4011436058.8</t>
         </is>
       </c>
-      <c r="AZ21" t="inlineStr">
-        <is>
-          <t>7171595467.56</t>
-        </is>
+      <c r="AZ21" t="n">
+        <v>7171595467.56</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
@@ -9426,8 +9304,10 @@
           <t>-379050437.0805759</t>
         </is>
       </c>
-      <c r="BD21" t="n">
-        <v>7366534520</v>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>7366534520.0</t>
+        </is>
       </c>
       <c r="BE21" t="inlineStr">
         <is>
@@ -9593,7 +9473,7 @@
     <row r="22">
       <c r="A22" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B22" t="inlineStr">
@@ -9777,15 +9657,11 @@
           <t>107.2</t>
         </is>
       </c>
-      <c r="AM22" t="inlineStr">
-        <is>
-          <t>112.52</t>
-        </is>
-      </c>
-      <c r="AN22" t="inlineStr">
-        <is>
-          <t>99.87</t>
-        </is>
+      <c r="AM22" t="n">
+        <v>112.52</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>99.87</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
@@ -9832,20 +9708,16 @@
           <t>5064644998.0</t>
         </is>
       </c>
-      <c r="AX22" t="inlineStr">
-        <is>
-          <t>3003565305.2</t>
-        </is>
+      <c r="AX22" t="n">
+        <v>3003565305.2</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
           <t>4108066698.5</t>
         </is>
       </c>
-      <c r="AZ22" t="inlineStr">
-        <is>
-          <t>7070679471.22</t>
-        </is>
+      <c r="AZ22" t="n">
+        <v>7070679471.22</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
@@ -9862,8 +9734,10 @@
           <t>-731529321.5827818</t>
         </is>
       </c>
-      <c r="BD22" t="n">
-        <v>5064644998</v>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>5064644998.0</t>
+        </is>
       </c>
       <c r="BE22" t="inlineStr">
         <is>
@@ -10029,7 +9903,7 @@
     <row r="23">
       <c r="A23" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>【c】</t>
         </is>
       </c>
       <c r="B23" t="inlineStr">
@@ -10213,15 +10087,11 @@
           <t>107.6</t>
         </is>
       </c>
-      <c r="AM23" t="inlineStr">
-        <is>
-          <t>112.4</t>
-        </is>
-      </c>
-      <c r="AN23" t="inlineStr">
-        <is>
-          <t>99.02</t>
-        </is>
+      <c r="AM23" t="n">
+        <v>112.4</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>99.02</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
@@ -10268,20 +10138,16 @@
           <t>1385646995.0</t>
         </is>
       </c>
-      <c r="AX23" t="inlineStr">
-        <is>
-          <t>2923123432.4</t>
-        </is>
+      <c r="AX23" t="n">
+        <v>2923123432.4</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
           <t>4157974302.6</t>
         </is>
       </c>
-      <c r="AZ23" t="inlineStr">
-        <is>
-          <t>7004676232.68</t>
-        </is>
+      <c r="AZ23" t="n">
+        <v>7004676232.68</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
@@ -10298,8 +10164,10 @@
           <t>-962313517.7436905</t>
         </is>
       </c>
-      <c r="BD23" t="n">
-        <v>1385646995</v>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>1385646995.0</t>
+        </is>
       </c>
       <c r="BE23" t="inlineStr">
         <is>

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>11426.896</t>
+          <t>8820.259</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>39.54</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>85.25</t>
+          <t>80.33</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>63.91</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>919.4</t>
+          <t>917.0</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>948.95</v>
+        <v>945.55</v>
       </c>
       <c r="AN2" t="n">
-        <v>947.8200000000001</v>
+        <v>949.92</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>847.89</t>
+          <t>852.31</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-56.69</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.52</t>
+          <t>-109.92</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>13777681330.2</v>
+        <v>12272712875.4</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13184190874.5</t>
+          <t>12946611618.9</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>14165986897.28</v>
+        <v>13990667425.04</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>593490455</t>
+          <t>-673898743</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-116538291.2148735</t>
+          <t>-189740222.8992386</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-288049536.2624874</t>
+          <t>-592350847.1632462</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>149.21</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,17 +1201,17 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>955.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>950.0</t>
+          <t>959.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>10504.174</t>
+          <t>11426.896</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>3.7</t>
+          <t>-0.32</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>39.54</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>909.2</t>
+          <t>919.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>954.7</v>
+        <v>948.95</v>
       </c>
       <c r="AN3" t="n">
-        <v>945.54</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>843.16</t>
+          <t>847.89</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-265.70</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-108.52</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>13831910429.6</v>
+        <v>13777681330.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13509805904.0</t>
+          <t>13184190874.5</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>14413977761.06</v>
+        <v>14165986897.28</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>322104525</t>
+          <t>593490455</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-85354428.47894374</t>
+          <t>-116538291.2148735</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-94238805.57345963</t>
+          <t>-288049536.2624874</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>140.74</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,17 +1631,17 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>926.0</t>
+          <t>950.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>899.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>18856.003</t>
+          <t>10504.174</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.5</t>
+          <t>3.4</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>65.24</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>909.2</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>962.95</v>
+        <v>954.7</v>
       </c>
       <c r="AN4" t="n">
-        <v>944.08</v>
+        <v>945.54</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>838.41</t>
+          <t>843.16</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-940.86</t>
+          <t>-265.70</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-102.03</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>14386844246.4</v>
+        <v>13831910429.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13675683609.2</t>
+          <t>13509805904.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>14618581897.64</v>
+        <v>14413977761.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>711160637</t>
+          <t>322104525</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-83739087.18903175</t>
+          <t>-85354428.47894374</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>306359263.681345</t>
+          <t>-94238805.57345963</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>136.24</t>
+          <t>140.74</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,17 +2061,17 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>904.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>909.0</t>
+          <t>926.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>899.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.29</t>
+          <t>5.2</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,17 +2304,17 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
@@ -2324,53 +2324,53 @@
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>971.8</v>
+        <v>962.95</v>
       </c>
       <c r="AN5" t="n">
-        <v>941.9</v>
+        <v>944.08</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13146559354.4</v>
+        <v>14386844246.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>14614553602.28</v>
+        <v>14618581897.64</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2501,7 +2501,7 @@
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>-0.95</t>
+          <t>4.99</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>977.55</v>
+        <v>971.8</v>
       </c>
       <c r="AN6" t="n">
-        <v>938.52</v>
+        <v>941.9</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13620510362.4</v>
+        <v>13146559354.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>14466055493.78</v>
+        <v>14614553602.28</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2926,12 +2926,12 @@
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>5.4</t>
+          <t>-1.27</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>980.85</v>
+        <v>977.55</v>
       </c>
       <c r="AN7" t="n">
-        <v>933.96</v>
+        <v>938.52</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>12590700418.8</v>
+        <v>13620510362.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>14368721493.28</v>
+        <v>14466055493.78</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3351,17 +3351,17 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>5.1</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,12 +3594,12 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>987.15</v>
+        <v>980.85</v>
       </c>
       <c r="AN8" t="n">
-        <v>929.9</v>
+        <v>933.96</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13187701378.4</v>
+        <v>12590700418.8</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>14292572173.18</v>
+        <v>14368721493.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3781,17 +3781,17 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>3.07</t>
+          <t>4.67</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>993</v>
+        <v>987.15</v>
       </c>
       <c r="AN9" t="n">
-        <v>925.54</v>
+        <v>929.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>12964522972</v>
+        <v>13187701378.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>14209168625.62</v>
+        <v>14292572173.18</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-273240924.15588</t>
+          <t>-303325579.8395176</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,17 +4211,17 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.43</t>
+          <t>2.76</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4469,58 +4469,58 @@
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>997.15</v>
+        <v>993</v>
       </c>
       <c r="AN10" t="n">
-        <v>920.92</v>
+        <v>925.54</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13091194606.6</v>
+        <v>12964522972</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>14155319682.02</v>
+        <v>14209168625.62</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-44367517.38797188</t>
+          <t>-273240924.15588</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,7 +4651,7 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>2.12</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>1002.3</v>
+        <v>997.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>916.24</v>
+        <v>920.92</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>11321413068.4</v>
+        <v>13091194606.6</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>13994353884.38</v>
+        <v>14155319682.02</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-516496615.2771072</t>
+          <t>-44367517.38797188</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,7 +5081,7 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.52</t>
+          <t>-0.93</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>14451.354</t>
+          <t>11148.197</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-2.33</t>
+          <t>-1.7</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.02</t>
+          <t>0.64</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-26.86</t>
+          <t>-19.33</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.62</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>50.00</t>
+          <t>38.57</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-0.09</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,73 +5314,73 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>455</t>
+          <t>367</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>11427</t>
+          <t>8820</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
         <is>
-          <t>6.67</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>13.37</t>
+          <t>7.41</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-0.60</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.22</t>
+          <t>-3.34</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>10.3</t>
+          <t>9.39</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>14.12</t>
+          <t>13.94</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>972.8</t>
+          <t>968.8</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>1005.15</v>
+        <v>1002.3</v>
       </c>
       <c r="AN12" t="n">
-        <v>911.3</v>
+        <v>916.24</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>798.52</t>
+          <t>804.14</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-50.05</t>
+          <t>-55.86</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>13.93</t>
+          <t>10.80</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>27.88</t>
+          <t>24.46</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-56.98</t>
+          <t>-62.25</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,24 +5400,24 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6454308304.944206</t>
+          <t>6462997726.791428</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>11246965605.2</v>
+        <v>11321413068.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>15377407355.7</t>
+          <t>14033372540.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>13940555876.02</v>
+        <v>13994353884.38</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
@@ -5426,17 +5426,17 @@
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-73989858.81012851</t>
+          <t>-142067821.3435099</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-374411751.6445465</t>
+          <t>-516496615.2771072</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>13958553198.0</t>
+          <t>10733728288.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>155.82</t>
+          <t>153.44</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.31</t>
+          <t>1.33</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,7 +5511,7 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>10.43</t>
+          <t>10.34</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>49.14</t>
+          <t>48.99</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>33.62</t>
+          <t>34.43</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2454678</t>
+          <t>2446886</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5571,17 +5571,17 @@
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>981.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>967.0</t>
+          <t>958.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>30647.12</t>
+          <t>17538.055</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>103.07</v>
+        <v>101.68</v>
       </c>
       <c r="AN13" t="n">
-        <v>103.31</v>
+        <v>103.29</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-80.19</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-121.07</t>
+          <t>-126.36</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>2683545818.0</t>
+          <t>1543850905.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>5000685349.4</v>
+        <v>4691522022.2</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4727097624.7</t>
+          <t>4375018215.4</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>6863428946.3</v>
+        <v>6753332147.84</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>273587724</t>
+          <t>316503806</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-299537059.7680103</t>
+          <t>-299279231.5113254</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-78239912.41163445</t>
+          <t>-297861176.0995588</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>2683545818.0</t>
+          <t>1543850905.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>60.22</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6033,7 +6033,7 @@
     <row r="14">
       <c r="A14" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B14" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>52066.846</t>
+          <t>30647.12</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>1.58</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-14.90</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,12 +6174,12 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
@@ -6194,53 +6194,53 @@
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>104.44</v>
+        <v>103.07</v>
       </c>
       <c r="AN14" t="n">
-        <v>103.43</v>
+        <v>103.31</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-161.95</t>
+          <t>-113.22</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-115.11</t>
+          <t>-121.07</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>4682266073.0</t>
+          <t>2683545818.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>5019578044.4</v>
+        <v>5000685349.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4597307742.4</t>
+          <t>4727097624.7</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>7180754379.14</v>
+        <v>6863428946.3</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>422270302</t>
+          <t>273587724</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-339772904.7418968</t>
+          <t>-299537059.7680103</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>116188863.3358154</t>
+          <t>-78239912.41163445</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>4682266073.0</t>
+          <t>2683545818.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>124181.065</t>
+          <t>52066.846</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-6.54</t>
+          <t>0.11</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-14.90</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,73 +6604,73 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>93.56</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>105.81</v>
+        <v>104.44</v>
       </c>
       <c r="AN15" t="n">
-        <v>103.41</v>
+        <v>103.43</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-272.55</t>
+          <t>-161.95</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-108.99</t>
+          <t>-115.11</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>4696916791.4</v>
+        <v>5019578044.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4341077616.0</t>
+          <t>4597307742.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>7241408797.74</v>
+        <v>7180754379.14</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>355839175</t>
+          <t>422270302</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-422675044.3923899</t>
+          <t>-339772904.7418968</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>175646056.2487507</t>
+          <t>116188863.3358154</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,24 +6791,24 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
           <t>2.48</t>
         </is>
       </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>2.52</t>
-        </is>
-      </c>
       <c r="BU15" t="inlineStr">
         <is>
           <t>6.21</t>
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>32684.421</t>
+          <t>124181.065</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-5.5</t>
+          <t>-4.85</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.80</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.56</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>106.92</v>
+        <v>105.81</v>
       </c>
       <c r="AN16" t="n">
-        <v>103.14</v>
+        <v>103.41</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-939.09</t>
+          <t>-272.55</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>3191641823.4</v>
+        <v>4696916791.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>3527299622.7</t>
+          <t>4341077616.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>7285669264.58</v>
+        <v>7241408797.74</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>-335657799</t>
+          <t>355839175</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-531460699.0544155</t>
+          <t>-422675044.3923899</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-477849918.1702256</t>
+          <t>175646056.2487507</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>31967.753</t>
+          <t>32684.421</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-10.21</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,17 +7464,17 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
@@ -7484,53 +7484,53 @@
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.80</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>95.85999999999999</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>108.02</v>
+        <v>106.92</v>
       </c>
       <c r="AN17" t="n">
-        <v>102.75</v>
+        <v>103.14</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-712.58</t>
+          <t>-939.09</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>4058514408.6</v>
+        <v>3191641823.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3531039856.9</t>
+          <t>3527299622.7</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>7317342463.3</v>
+        <v>7285669264.58</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>527474551</t>
+          <t>-335657799</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-541208113.7606318</t>
+          <t>-531460699.0544155</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-485391942.3698263</t>
+          <t>-477849918.1702256</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>29839.894</t>
+          <t>31967.753</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-8.47</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,73 +7894,73 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>95.85999999999999</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>109.04</v>
+        <v>108.02</v>
       </c>
       <c r="AN18" t="n">
-        <v>102.19</v>
+        <v>102.75</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-283.53</t>
+          <t>-712.58</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>4453509900</v>
+        <v>4058514408.6</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3688316666.2</t>
+          <t>3531039856.9</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>7280178623.2</v>
+        <v>7317342463.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>765193233</t>
+          <t>527474551</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-551356508.5589601</t>
+          <t>-541208113.7606318</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-484991116.1774759</t>
+          <t>-485391942.3698263</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>32132.941</t>
+          <t>29839.894</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.57</t>
+          <t>-4.97</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,12 +8324,12 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
@@ -8344,53 +8344,53 @@
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>98.74</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>110.06</v>
+        <v>109.04</v>
       </c>
       <c r="AN19" t="n">
-        <v>101.66</v>
+        <v>102.19</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>85.35</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-161.08</t>
+          <t>-283.53</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-81.65</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>4175037440.4</v>
+        <v>4453509900</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3901577638.9</t>
+          <t>3688316666.2</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>7265450343.64</v>
+        <v>7280178623.2</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>273459801</t>
+          <t>765193233</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-563422943.5374118</t>
+          <t>-551356508.5589601</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-433705440.8963513</t>
+          <t>-484991116.1774759</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.49</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-10.78</t>
+          <t>-5.87</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8769,58 +8769,58 @@
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>111.34</v>
+        <v>110.06</v>
       </c>
       <c r="AN20" t="n">
-        <v>101.12</v>
+        <v>101.66</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3985238440.6</v>
+        <v>4175037440.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>7220968787.64</v>
+        <v>7265450343.64</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-376123979.9270172</t>
+          <t>-433705440.8963513</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價跌量-</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-14.45</t>
+          <t>-9.03</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>111.96</v>
+        <v>111.34</v>
       </c>
       <c r="AN21" t="n">
-        <v>100.52</v>
+        <v>101.12</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3862957422</v>
+        <v>3985238440.6</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>7171595467.56</v>
+        <v>7220968787.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-379050437.0805759</t>
+          <t>-376123979.9270172</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-26.72</t>
+          <t>-12.64</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,17 +9614,17 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
@@ -9634,53 +9634,53 @@
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>112.52</v>
+        <v>111.96</v>
       </c>
       <c r="AN22" t="n">
-        <v>99.87</v>
+        <v>100.52</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3003565305.2</v>
+        <v>3862957422</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>7070679471.22</v>
+        <v>7171595467.56</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-731529321.5827818</t>
+          <t>-379050437.0805759</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>4.23</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>13178.714</t>
+          <t>45995.106</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-21.56</t>
+          <t>-24.72</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-4.94</t>
+          <t>-3.26</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-29.70</t>
+          <t>-26.89</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>1.92</t>
+          <t>6.25</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-12</t>
+          <t>2025-11-13</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>3.98</t>
+          <t>13.89</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.42</t>
+          <t>2.02</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,73 +10044,73 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>345</t>
+          <t>170</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>30647</t>
+          <t>17538</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>12.5</t>
+          <t>54.55</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
         <is>
-          <t>4.17</t>
+          <t>22.35</t>
         </is>
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>-1.49</t>
+          <t>3.08</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.27</t>
+          <t>-4.73</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>13.52</t>
+          <t>12.68</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>19.71</t>
+          <t>19.60</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>107.6</t>
+          <t>107.2</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>112.4</v>
+        <v>112.52</v>
       </c>
       <c r="AN23" t="n">
-        <v>99.02</v>
+        <v>99.87</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>82.71</t>
+          <t>83.5</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-54.62</t>
+          <t>-51.21</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.94</t>
+          <t>1.85</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>4.28</t>
+          <t>3.79</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-56.85</t>
+          <t>-61.75</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1903961767.22063</t>
+          <t>1904550915.418455</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>2923123432.4</v>
+        <v>3003565305.2</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>4157974302.6</t>
+          <t>4108066698.5</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>7004676232.68</v>
+        <v>7070679471.22</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1234850870</t>
+          <t>-1104501393</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-658969216.3510649</t>
+          <t>-670132309.4636368</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-962313517.7436905</t>
+          <t>-731529321.5827818</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>1385646995.0</t>
+          <t>5064644998.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>91.68</t>
+          <t>99.82</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10211,7 +10211,7 @@
       </c>
       <c r="BM23" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BN23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.83</t>
+          <t>2.95</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.52</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>37.91</t>
+          <t>38.52</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.32</t>
+          <t>41.2</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>207226</t>
+          <t>210553</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>104.5</t>
+          <t>106.5</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>113.5</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>103.5</t>
+          <t>105.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>106.0</t>
+          <t>110.5</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8820.259</t>
+          <t>8363.698</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-10.38</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-7.19</t>
+          <t>-8.18</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>80.33</t>
+          <t>63.93</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>63.91</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>917.0</t>
+          <t>924.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>945.55</v>
+        <v>942.4</v>
       </c>
       <c r="AN2" t="n">
-        <v>949.92</v>
+        <v>951.84</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>852.31</t>
+          <t>856.55</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-56.69</t>
+          <t>-33.12</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-109.92</t>
+          <t>-110.82</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,43 +1100,43 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12272712875.4</v>
+        <v>10674153029.2</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12946611618.9</t>
+          <t>11910356191.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13990667425.04</v>
+        <v>13939434751.06</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-673898743</t>
+          <t>-1236203162</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-189740222.8992386</t>
+          <t>-288377732.4823858</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-592350847.1632462</t>
+          <t>-830884035.1896954</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>149.21</t>
+          <t>146.56</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>955.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>959.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>11426.896</t>
+          <t>8820.259</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>-0.32</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1413,7 +1413,7 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>39.54</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>85.25</t>
+          <t>80.33</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>63.91</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>919.4</t>
+          <t>917.0</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>948.95</v>
+        <v>945.55</v>
       </c>
       <c r="AN3" t="n">
-        <v>947.8200000000001</v>
+        <v>949.92</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>847.89</t>
+          <t>852.31</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-56.69</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-108.52</t>
+          <t>-109.92</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>13777681330.2</v>
+        <v>12272712875.4</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>13184190874.5</t>
+          <t>12946611618.9</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>14165986897.28</v>
+        <v>13990667425.04</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>593490455</t>
+          <t>-673898743</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-116538291.2148735</t>
+          <t>-189740222.8992386</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-288049536.2624874</t>
+          <t>-592350847.1632462</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>149.21</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>955.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>950.0</t>
+          <t>959.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>10504.174</t>
+          <t>11426.896</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.4</t>
+          <t>-1.39</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>39.54</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>909.2</t>
+          <t>919.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>954.7</v>
+        <v>948.95</v>
       </c>
       <c r="AN4" t="n">
-        <v>945.54</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>843.16</t>
+          <t>847.89</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-265.70</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-108.52</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>13831910429.6</v>
+        <v>13777681330.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13509805904.0</t>
+          <t>13184190874.5</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>14413977761.06</v>
+        <v>14165986897.28</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>322104525</t>
+          <t>593490455</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-85354428.47894374</t>
+          <t>-116538291.2148735</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-94238805.57345963</t>
+          <t>-288049536.2624874</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>140.74</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>926.0</t>
+          <t>950.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>899.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>18856.003</t>
+          <t>10504.174</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>5.2</t>
+          <t>2.36</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>65.24</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>909.2</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>962.95</v>
+        <v>954.7</v>
       </c>
       <c r="AN5" t="n">
-        <v>944.08</v>
+        <v>945.54</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>838.41</t>
+          <t>843.16</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-940.86</t>
+          <t>-265.70</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-102.03</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>14386844246.4</v>
+        <v>13831910429.6</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13675683609.2</t>
+          <t>13509805904.0</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>14618581897.64</v>
+        <v>14413977761.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>711160637</t>
+          <t>322104525</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-83739087.18903175</t>
+          <t>-85354428.47894374</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>306359263.681345</t>
+          <t>-94238805.57345963</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>136.24</t>
+          <t>140.74</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>904.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>909.0</t>
+          <t>926.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>899.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.99</t>
+          <t>4.18</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,17 +2734,17 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
@@ -2754,53 +2754,53 @@
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>971.8</v>
+        <v>962.95</v>
       </c>
       <c r="AN6" t="n">
-        <v>941.9</v>
+        <v>944.08</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13146559354.4</v>
+        <v>14386844246.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>14614553602.28</v>
+        <v>14618581897.64</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2931,12 +2931,12 @@
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>3.97</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>977.55</v>
+        <v>971.8</v>
       </c>
       <c r="AN7" t="n">
-        <v>938.52</v>
+        <v>941.9</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13620510362.4</v>
+        <v>13146559354.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>14466055493.78</v>
+        <v>14614553602.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3356,17 +3356,17 @@
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>5.1</t>
+          <t>-2.36</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>980.85</v>
+        <v>977.55</v>
       </c>
       <c r="AN8" t="n">
-        <v>933.96</v>
+        <v>938.52</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>12590700418.8</v>
+        <v>13620510362.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>14368721493.28</v>
+        <v>14466055493.78</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.67</t>
+          <t>4.08</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,12 +4024,12 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>987.15</v>
+        <v>980.85</v>
       </c>
       <c r="AN9" t="n">
-        <v>929.9</v>
+        <v>933.96</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13187701378.4</v>
+        <v>12590700418.8</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>14292572173.18</v>
+        <v>14368721493.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>2.76</t>
+          <t>3.65</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>993</v>
+        <v>987.15</v>
       </c>
       <c r="AN10" t="n">
-        <v>925.54</v>
+        <v>929.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>12964522972</v>
+        <v>13187701378.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>14209168625.62</v>
+        <v>14292572173.18</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-273240924.15588</t>
+          <t>-303325579.8395176</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,7 +4641,7 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
@@ -4651,12 +4651,12 @@
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>2.12</t>
+          <t>1.72</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4899,58 +4899,58 @@
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>997.15</v>
+        <v>993</v>
       </c>
       <c r="AN11" t="n">
-        <v>920.92</v>
+        <v>925.54</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>13091194606.6</v>
+        <v>12964522972</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>14155319682.02</v>
+        <v>14209168625.62</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-44367517.38797188</t>
+          <t>-273240924.15588</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.93</t>
+          <t>-3.84</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11148.197</t>
+          <t>19610.238</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>-1.7</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>0.64</t>
+          <t>-0.03</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-19.33</t>
+          <t>-4.78</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-5.62</t>
+          <t>-9.16</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>38.57</t>
+          <t>67.85</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.49</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>367</t>
+          <t>458</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8820</t>
+          <t>8364</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>7.41</t>
+          <t>2.22</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-3.98</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.34</t>
+          <t>-3.71</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>9.39</t>
+          <t>8.28</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.94</t>
+          <t>13.80</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>968.8</t>
+          <t>960.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>1002.3</v>
+        <v>997.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>916.24</v>
+        <v>920.92</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>804.14</t>
+          <t>809.22</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-55.86</t>
+          <t>-74.06</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>10.80</t>
+          <t>5.36</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>24.46</t>
+          <t>20.64</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-62.25</t>
+          <t>-68.15</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6462997726.791428</t>
+          <t>6470511685.478602</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>11321413068.4</v>
+        <v>13091194606.6</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>14033372540.0</t>
+          <t>13748861147.6</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>13994353884.38</v>
+        <v>14155319682.02</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-2147483648</t>
+          <t>-657666541</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-142067821.3435099</t>
+          <t>-127037005.3503502</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-516496615.2771072</t>
+          <t>-44367517.38797188</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>10733728288.0</t>
+          <t>18182742782.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>153.44</t>
+          <t>143.92</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>10.34</t>
+          <t>9.95</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.74</t>
+          <t>0.75</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>48.99</t>
+          <t>48.47</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34.43</t>
+          <t>34.84</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2446886</t>
+          <t>2420910</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>958.0</t>
+          <t>922.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>17538.055</t>
+          <t>16281.325</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>89.84</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>101.68</v>
+        <v>100.24</v>
       </c>
       <c r="AN13" t="n">
-        <v>103.29</v>
+        <v>103.28</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-80.19</t>
+          <t>-60.15</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-126.36</t>
+          <t>-131.02</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1543850905.0</t>
+          <t>1429040476.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>4691522022.2</v>
+        <v>4370895798.6</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>4375018215.4</t>
+          <t>3781268811.0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>6753332147.84</v>
+        <v>6680203633.36</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>316503806</t>
+          <t>589626987</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-299279231.5113254</t>
+          <t>-322891705.6562934</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-297861176.0995588</t>
+          <t>-452760313.4536171</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1543850905.0</t>
+          <t>1429040476.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>60.22</t>
+          <t>58.59</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5931,22 +5931,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>30647.12</t>
+          <t>17538.055</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.58</t>
+          <t>-1.03</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>103.07</v>
+        <v>101.68</v>
       </c>
       <c r="AN14" t="n">
-        <v>103.31</v>
+        <v>103.29</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-80.19</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-121.07</t>
+          <t>-126.36</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>2683545818.0</t>
+          <t>1543850905.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>5000685349.4</v>
+        <v>4691522022.2</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>4727097624.7</t>
+          <t>4375018215.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>6863428946.3</v>
+        <v>6753332147.84</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>273587724</t>
+          <t>316503806</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-299537059.7680103</t>
+          <t>-299279231.5113254</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-78239912.41163445</t>
+          <t>-297861176.0995588</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>2683545818.0</t>
+          <t>1543850905.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>60.22</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6361,22 +6361,22 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6463,7 +6463,7 @@
     <row r="15">
       <c r="A15" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B15" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>52066.846</t>
+          <t>30647.12</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>0.11</t>
+          <t>0.57</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-14.90</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,12 +6604,12 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>104.44</v>
+        <v>103.07</v>
       </c>
       <c r="AN15" t="n">
-        <v>103.43</v>
+        <v>103.31</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-161.95</t>
+          <t>-113.22</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-115.11</t>
+          <t>-121.07</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>4682266073.0</t>
+          <t>2683545818.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>5019578044.4</v>
+        <v>5000685349.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>4597307742.4</t>
+          <t>4727097624.7</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>7180754379.14</v>
+        <v>6863428946.3</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>422270302</t>
+          <t>273587724</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-339772904.7418968</t>
+          <t>-299537059.7680103</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>116188863.3358154</t>
+          <t>-78239912.41163445</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>4682266073.0</t>
+          <t>2683545818.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>124181.065</t>
+          <t>52066.846</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-4.85</t>
+          <t>-0.91</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-14.90</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>93.56</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>105.81</v>
+        <v>104.44</v>
       </c>
       <c r="AN16" t="n">
-        <v>103.41</v>
+        <v>103.43</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-272.55</t>
+          <t>-161.95</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-108.99</t>
+          <t>-115.11</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>4696916791.4</v>
+        <v>5019578044.4</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4341077616.0</t>
+          <t>4597307742.4</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>7241408797.74</v>
+        <v>7180754379.14</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>355839175</t>
+          <t>422270302</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-422675044.3923899</t>
+          <t>-339772904.7418968</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>175646056.2487507</t>
+          <t>116188863.3358154</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>32684.421</t>
+          <t>124181.065</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-5.93</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-11.80</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.56</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>106.92</v>
+        <v>105.81</v>
       </c>
       <c r="AN17" t="n">
-        <v>103.14</v>
+        <v>103.41</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-939.09</t>
+          <t>-272.55</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>3191641823.4</v>
+        <v>4696916791.4</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>3527299622.7</t>
+          <t>4341077616.0</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>7285669264.58</v>
+        <v>7241408797.74</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>-335657799</t>
+          <t>355839175</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-531460699.0544155</t>
+          <t>-422675044.3923899</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-477849918.1702256</t>
+          <t>175646056.2487507</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>31967.753</t>
+          <t>32684.421</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-8.47</t>
+          <t>-4.9</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,17 +7894,17 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.80</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>95.85999999999999</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>108.02</v>
+        <v>106.92</v>
       </c>
       <c r="AN18" t="n">
-        <v>102.75</v>
+        <v>103.14</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-712.58</t>
+          <t>-939.09</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>4058514408.6</v>
+        <v>3191641823.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>3531039856.9</t>
+          <t>3527299622.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>7317342463.3</v>
+        <v>7285669264.58</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>527474551</t>
+          <t>-335657799</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-541208113.7606318</t>
+          <t>-531460699.0544155</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>-485391942.3698263</t>
+          <t>-477849918.1702256</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>29839.894</t>
+          <t>31967.753</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-4.97</t>
+          <t>-9.58</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>95.85999999999999</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>109.04</v>
+        <v>108.02</v>
       </c>
       <c r="AN19" t="n">
-        <v>102.19</v>
+        <v>102.75</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-283.53</t>
+          <t>-712.58</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>4453509900</v>
+        <v>4058514408.6</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>3688316666.2</t>
+          <t>3531039856.9</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>7280178623.2</v>
+        <v>7317342463.3</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>765193233</t>
+          <t>527474551</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-551356508.5589601</t>
+          <t>-541208113.7606318</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>-484991116.1774759</t>
+          <t>-485391942.3698263</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32132.941</t>
+          <t>29839.894</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-5.87</t>
+          <t>-6.04</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>7.01</t>
+          <t>20.75</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-9.81</t>
+          <t>-10.58</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>9.01</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-3.94</t>
+          <t>-0.42</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,12 +8754,12 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
@@ -8774,53 +8774,53 @@
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-7.44</t>
+          <t>-5.81</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-7.92</t>
+          <t>-9.44</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>8.26</t>
+          <t>6.7</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>19.11</t>
+          <t>18.92</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>101.34</t>
+          <t>98.74</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>110.06</v>
+        <v>109.04</v>
       </c>
       <c r="AN20" t="n">
-        <v>101.66</v>
+        <v>102.19</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>85.35</t>
+          <t>85.93</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-161.08</t>
+          <t>-283.53</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-1.11</t>
+          <t>-1.95</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>1.82</t>
+          <t>1.07</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-81.65</t>
+          <t>-89.26</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>4175037440.4</v>
+        <v>4453509900</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3901577638.9</t>
+          <t>3688316666.2</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>7265450343.64</v>
+        <v>7280178623.2</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>273459801</t>
+          <t>765193233</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-563422943.5374118</t>
+          <t>-551356508.5589601</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-433705440.8963513</t>
+          <t>-484991116.1774759</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>3068959808.0</t>
+          <t>2778009293.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>69.62</t>
+          <t>68.17</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8941,24 +8941,24 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價跌量-</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
           <t>2.51</t>
         </is>
       </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
       <c r="BU20" t="inlineStr">
         <is>
           <t>6.21</t>
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>96.0</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>97.5</t>
+          <t>94.4</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>93.0</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>-3.2</t>
+          <t>-2.92</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>40908.464</t>
+          <t>32132.941</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-9.03</t>
+          <t>-6.96</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>0.16</t>
+          <t>7.01</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.12</t>
+          <t>-9.81</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>12.36</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>-3.94</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,12 +9184,12 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
@@ -9199,58 +9199,58 @@
       </c>
       <c r="AG21" t="inlineStr">
         <is>
-          <t>18.18</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>-6.65</t>
+          <t>-7.44</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-7.06</t>
+          <t>-7.92</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>10.11</t>
+          <t>8.26</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>19.29</t>
+          <t>19.11</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>103.48</t>
+          <t>101.34</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>111.34</v>
+        <v>110.06</v>
       </c>
       <c r="AN21" t="n">
-        <v>101.12</v>
+        <v>101.66</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>84.77</t>
+          <t>85.35</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-103.95</t>
+          <t>-161.08</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-0.10</t>
+          <t>-1.11</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>2.55</t>
+          <t>1.82</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-74.26</t>
+          <t>-81.65</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>3985238440.6</v>
+        <v>4175037440.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3979054603.6</t>
+          <t>3901577638.9</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>7220968787.64</v>
+        <v>7265450343.64</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>6183837</t>
+          <t>273459801</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-587007944.0176046</t>
+          <t>-563422943.5374118</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-376123979.9270172</t>
+          <t>-433705440.8963513</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>3989400881.0</t>
+          <t>3068959808.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>74.68</t>
+          <t>69.62</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.58</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>100.0</t>
+          <t>96.0</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>101.0</t>
+          <t>97.5</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>96.2</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>96.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-10.29</t>
+          <t>-3.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>72776.258</t>
+          <t>40908.464</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-12.64</t>
+          <t>-10.15</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>-3.70</t>
+          <t>0.16</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-4.04</t>
+          <t>-7.12</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>21.99</t>
+          <t>12.36</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-4.91</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,12 +9614,12 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
@@ -9629,58 +9629,58 @@
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>22.35</t>
+          <t>18.18</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.28</t>
+          <t>-6.65</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-5.90</t>
+          <t>-7.06</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>11.39</t>
+          <t>10.11</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>19.46</t>
+          <t>19.29</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>105.36</t>
+          <t>103.48</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>111.96</v>
+        <v>111.34</v>
       </c>
       <c r="AN22" t="n">
-        <v>100.52</v>
+        <v>101.12</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>84.14</t>
+          <t>84.77</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-71.84</t>
+          <t>-103.95</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>0.91</t>
+          <t>-0.10</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>3.22</t>
+          <t>2.55</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-67.57</t>
+          <t>-74.26</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>3862957422</v>
+        <v>3985238440.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>4011436058.8</t>
+          <t>3979054603.6</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>7171595467.56</v>
+        <v>7220968787.64</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>-148478636</t>
+          <t>6183837</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-625350482.9431659</t>
+          <t>-587007944.0176046</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-379050437.0805759</t>
+          <t>-376123979.9270172</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>7366534520.0</t>
+          <t>3989400881.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>80.47</t>
+          <t>74.68</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.67</t>
+          <t>2.58</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>105.0</t>
+          <t>101.0</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>99.5</t>
+          <t>96.2</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>99.8</t>
+          <t>96.6</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>4.23</t>
+          <t>-10.29</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>45995.106</t>
+          <t>72776.258</t>
         </is>
       </c>
       <c r="E23" t="inlineStr">
@@ -9928,7 +9928,7 @@
       </c>
       <c r="F23" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="G23" t="inlineStr">
@@ -9938,17 +9938,17 @@
       </c>
       <c r="H23" t="inlineStr">
         <is>
-          <t>-24.72</t>
+          <t>-13.8</t>
         </is>
       </c>
       <c r="I23" t="inlineStr">
         <is>
-          <t>-3.26</t>
+          <t>-1.66</t>
         </is>
       </c>
       <c r="J23" t="inlineStr">
         <is>
-          <t>-26.89</t>
+          <t>-3.70</t>
         </is>
       </c>
       <c r="K23" t="inlineStr">
@@ -10013,7 +10013,7 @@
       </c>
       <c r="W23" t="inlineStr">
         <is>
-          <t>6.25</t>
+          <t>-4.04</t>
         </is>
       </c>
       <c r="X23" t="inlineStr">
@@ -10023,17 +10023,17 @@
       </c>
       <c r="Y23" t="inlineStr">
         <is>
-          <t>2025-11-13</t>
+          <t>2025-11-14</t>
         </is>
       </c>
       <c r="Z23" t="inlineStr">
         <is>
-          <t>13.89</t>
+          <t>21.99</t>
         </is>
       </c>
       <c r="AA23" t="inlineStr">
         <is>
-          <t>2.02</t>
+          <t>-4.91</t>
         </is>
       </c>
       <c r="AB23" t="inlineStr">
@@ -10044,17 +10044,17 @@
       <c r="AC23" t="inlineStr"/>
       <c r="AD23" t="inlineStr">
         <is>
-          <t>170</t>
+          <t>209</t>
         </is>
       </c>
       <c r="AE23" t="inlineStr">
         <is>
-          <t>17538</t>
+          <t>16281</t>
         </is>
       </c>
       <c r="AF23" t="inlineStr">
         <is>
-          <t>54.55</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG23" t="inlineStr">
@@ -10064,53 +10064,53 @@
       </c>
       <c r="AH23" t="inlineStr">
         <is>
-          <t>3.08</t>
+          <t>-5.28</t>
         </is>
       </c>
       <c r="AI23" t="inlineStr">
         <is>
-          <t>-4.73</t>
+          <t>-5.90</t>
         </is>
       </c>
       <c r="AJ23" t="inlineStr">
         <is>
-          <t>12.68</t>
+          <t>11.39</t>
         </is>
       </c>
       <c r="AK23" t="inlineStr">
         <is>
-          <t>19.60</t>
+          <t>19.46</t>
         </is>
       </c>
       <c r="AL23" t="inlineStr">
         <is>
-          <t>107.2</t>
+          <t>105.36</t>
         </is>
       </c>
       <c r="AM23" t="n">
-        <v>112.52</v>
+        <v>111.96</v>
       </c>
       <c r="AN23" t="n">
-        <v>99.87</v>
+        <v>100.52</v>
       </c>
       <c r="AO23" t="inlineStr">
         <is>
-          <t>83.5</t>
+          <t>84.14</t>
         </is>
       </c>
       <c r="AP23" t="inlineStr">
         <is>
-          <t>-51.21</t>
+          <t>-71.84</t>
         </is>
       </c>
       <c r="AQ23" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.91</t>
         </is>
       </c>
       <c r="AR23" t="inlineStr">
         <is>
-          <t>3.79</t>
+          <t>3.22</t>
         </is>
       </c>
       <c r="AS23" t="inlineStr">
@@ -10120,7 +10120,7 @@
       </c>
       <c r="AT23" t="inlineStr">
         <is>
-          <t>-61.75</t>
+          <t>-67.57</t>
         </is>
       </c>
       <c r="AU23" t="inlineStr">
@@ -10130,43 +10130,43 @@
       </c>
       <c r="AV23" t="inlineStr">
         <is>
-          <t>1904550915.418455</t>
+          <t>1904892357.987857</t>
         </is>
       </c>
       <c r="AW23" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="AX23" t="n">
-        <v>3003565305.2</v>
+        <v>3862957422</v>
       </c>
       <c r="AY23" t="inlineStr">
         <is>
-          <t>4108066698.5</t>
+          <t>4011436058.8</t>
         </is>
       </c>
       <c r="AZ23" t="n">
-        <v>7070679471.22</v>
+        <v>7171595467.56</v>
       </c>
       <c r="BA23" t="inlineStr">
         <is>
-          <t>-1104501393</t>
+          <t>-148478636</t>
         </is>
       </c>
       <c r="BB23" t="inlineStr">
         <is>
-          <t>-670132309.4636368</t>
+          <t>-625350482.9431659</t>
         </is>
       </c>
       <c r="BC23" t="inlineStr">
         <is>
-          <t>-731529321.5827818</t>
+          <t>-379050437.0805759</t>
         </is>
       </c>
       <c r="BD23" t="inlineStr">
         <is>
-          <t>5064644998.0</t>
+          <t>7366534520.0</t>
         </is>
       </c>
       <c r="BE23" t="inlineStr">
@@ -10186,7 +10186,7 @@
       </c>
       <c r="BH23" t="inlineStr">
         <is>
-          <t>99.82</t>
+          <t>80.47</t>
         </is>
       </c>
       <c r="BI23" t="inlineStr">
@@ -10231,7 +10231,7 @@
       </c>
       <c r="BQ23" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR23" t="inlineStr">
@@ -10241,12 +10241,12 @@
       </c>
       <c r="BS23" t="inlineStr">
         <is>
-          <t>2.95</t>
+          <t>2.67</t>
         </is>
       </c>
       <c r="BT23" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.51</t>
         </is>
       </c>
       <c r="BU23" t="inlineStr">
@@ -10256,7 +10256,7 @@
       </c>
       <c r="BV23" t="inlineStr">
         <is>
-          <t>38.52</t>
+          <t>38.13</t>
         </is>
       </c>
       <c r="BW23" t="inlineStr">
@@ -10271,12 +10271,12 @@
       </c>
       <c r="BY23" t="inlineStr">
         <is>
-          <t>41.2</t>
+          <t>41.28</t>
         </is>
       </c>
       <c r="BZ23" t="inlineStr">
         <is>
-          <t>210553</t>
+          <t>208414</t>
         </is>
       </c>
       <c r="CA23" t="inlineStr">
@@ -10296,22 +10296,22 @@
       </c>
       <c r="CD23" t="inlineStr">
         <is>
-          <t>106.5</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="CE23" t="inlineStr">
         <is>
-          <t>113.5</t>
+          <t>105.0</t>
         </is>
       </c>
       <c r="CF23" t="inlineStr">
         <is>
-          <t>105.5</t>
+          <t>99.5</t>
         </is>
       </c>
       <c r="CG23" t="inlineStr">
         <is>
-          <t>110.5</t>
+          <t>99.8</t>
         </is>
       </c>
       <c r="CH23" t="inlineStr">

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ23"/>
+  <dimension ref="A1:CJ13"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>8363.698</t>
+          <t>17532.398</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,12 +913,12 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-10.38</t>
+          <t>-14.86</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
@@ -983,7 +983,7 @@
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>-4.14</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,73 +1014,73 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
         <is>
-          <t>63.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.42</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>924.4</t>
+          <t>940.4</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>942.4</v>
+        <v>941.9</v>
       </c>
       <c r="AN2" t="n">
-        <v>951.84</v>
+        <v>954.48</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>856.55</t>
+          <t>860.81</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>-33.12</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-6.69</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,53 +1090,53 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.82</t>
+          <t>-110.32</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>7820188511.0</t>
+          <t>16856373921.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>10674153029.2</v>
+        <v>10663188933.6</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>11910356191.8</t>
+          <t>12525016590.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>13939434751.06</v>
+        <v>14016406079.92</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1236203162</t>
+          <t>-1861827656</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-288377732.4823858</t>
+          <t>-290069044.435629</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-830884035.1896954</t>
+          <t>-299371260.1784668</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>7820188511.0</t>
+          <t>16856373921.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>146.56</t>
+          <t>157.41</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1181,7 +1181,7 @@
       </c>
       <c r="BM2" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN2" t="inlineStr">
@@ -1201,22 +1201,22 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>936.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1296,7 +1296,7 @@
       </c>
       <c r="CJ2" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8820.259</t>
+          <t>8363.698</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,102 +1338,102 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
+          <t>4.21</t>
+        </is>
+      </c>
+      <c r="I3" t="inlineStr">
+        <is>
+          <t>2.35</t>
+        </is>
+      </c>
+      <c r="J3" t="inlineStr">
+        <is>
+          <t>-10.38</t>
+        </is>
+      </c>
+      <c r="K3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L3" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M3" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P3" t="inlineStr">
+        <is>
+          <t>2025-09-26 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q3" t="inlineStr">
+        <is>
+          <t>987.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>1015.0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
+          <t>784.0</t>
+        </is>
+      </c>
+      <c r="U3" t="inlineStr">
+        <is>
+          <t>848.0</t>
+        </is>
+      </c>
+      <c r="V3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W3" t="inlineStr">
+        <is>
+          <t>-8.18</t>
+        </is>
+      </c>
+      <c r="X3" t="inlineStr">
+        <is>
+          <t>16.39</t>
+        </is>
+      </c>
+      <c r="Y3" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z3" t="inlineStr">
+        <is>
+          <t>28.94</t>
+        </is>
+      </c>
+      <c r="AA3" t="inlineStr">
+        <is>
           <t>-1.07</t>
-        </is>
-      </c>
-      <c r="I3" t="inlineStr">
-        <is>
-          <t>-0.03</t>
-        </is>
-      </c>
-      <c r="J3" t="inlineStr">
-        <is>
-          <t>-5.21</t>
-        </is>
-      </c>
-      <c r="K3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L3" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M3" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="N3" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q3" t="inlineStr">
-        <is>
-          <t>987.0</t>
-        </is>
-      </c>
-      <c r="R3" t="inlineStr">
-        <is>
-          <t>1015.0</t>
-        </is>
-      </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
-      <c r="V3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W3" t="inlineStr">
-        <is>
-          <t>-7.19</t>
-        </is>
-      </c>
-      <c r="X3" t="inlineStr">
-        <is>
-          <t>16.39</t>
-        </is>
-      </c>
-      <c r="Y3" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z3" t="inlineStr">
-        <is>
-          <t>30.52</t>
-        </is>
-      </c>
-      <c r="AA3" t="inlineStr">
-        <is>
-          <t>-1.38</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>80.33</t>
+          <t>63.93</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>63.91</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>917.0</t>
+          <t>924.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>945.55</v>
+        <v>942.4</v>
       </c>
       <c r="AN3" t="n">
-        <v>949.92</v>
+        <v>951.84</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>852.31</t>
+          <t>856.55</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-56.69</t>
+          <t>-33.12</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,53 +1520,53 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-109.92</t>
+          <t>-110.82</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>12272712875.4</v>
+        <v>10674153029.2</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12946611618.9</t>
+          <t>11910356191.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13990667425.04</v>
+        <v>13939434751.06</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-673898743</t>
+          <t>-1236203162</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-189740222.8992386</t>
+          <t>-288377732.4823858</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-592350847.1632462</t>
+          <t>-830884035.1896954</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>149.21</t>
+          <t>146.56</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1611,7 +1611,7 @@
       </c>
       <c r="BM3" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>955.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>959.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1726,14 +1726,14 @@
       </c>
       <c r="CJ3" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>11426.896</t>
+          <t>8820.259</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>-1.39</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1843,7 +1843,7 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>-7.19</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>39.54</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>85.25</t>
+          <t>80.33</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>63.91</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>919.4</t>
+          <t>917.0</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>948.95</v>
+        <v>945.55</v>
       </c>
       <c r="AN4" t="n">
-        <v>947.8200000000001</v>
+        <v>949.92</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>847.89</t>
+          <t>852.31</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-56.69</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,53 +1950,53 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-108.52</t>
+          <t>-109.92</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>13777681330.2</v>
+        <v>12272712875.4</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>13184190874.5</t>
+          <t>12946611618.9</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>14165986897.28</v>
+        <v>13990667425.04</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>593490455</t>
+          <t>-673898743</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-116538291.2148735</t>
+          <t>-189740222.8992386</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-288049536.2624874</t>
+          <t>-592350847.1632462</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>149.21</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2041,7 +2041,7 @@
       </c>
       <c r="BM4" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>955.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>950.0</t>
+          <t>959.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2156,7 +2156,7 @@
       </c>
       <c r="CJ4" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>10504.174</t>
+          <t>11426.896</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.36</t>
+          <t>2.88</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2273,7 +2273,7 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>-6.90</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>39.54</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>909.2</t>
+          <t>919.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>954.7</v>
+        <v>948.95</v>
       </c>
       <c r="AN5" t="n">
-        <v>945.54</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>843.16</t>
+          <t>847.89</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-265.70</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,53 +2380,53 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-108.52</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13831910429.6</v>
+        <v>13777681330.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13509805904.0</t>
+          <t>13184190874.5</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>14413977761.06</v>
+        <v>14165986897.28</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>322104525</t>
+          <t>593490455</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-85354428.47894374</t>
+          <t>-116538291.2148735</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-94238805.57345963</t>
+          <t>-288049536.2624874</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>140.74</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2471,7 +2471,7 @@
       </c>
       <c r="BM5" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>926.0</t>
+          <t>950.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>899.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2586,7 +2586,7 @@
       </c>
       <c r="CJ5" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>18856.003</t>
+          <t>10504.174</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.18</t>
+          <t>6.47</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2703,7 +2703,7 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>-10.34</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>65.24</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>909.2</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>962.95</v>
+        <v>954.7</v>
       </c>
       <c r="AN6" t="n">
-        <v>944.08</v>
+        <v>945.54</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>838.41</t>
+          <t>843.16</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-940.86</t>
+          <t>-265.70</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,53 +2810,53 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-102.03</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>14386844246.4</v>
+        <v>13831910429.6</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13675683609.2</t>
+          <t>13509805904.0</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>14618581897.64</v>
+        <v>14413977761.06</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>711160637</t>
+          <t>322104525</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-83739087.18903175</t>
+          <t>-85354428.47894374</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>306359263.681345</t>
+          <t>-94238805.57345963</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>136.24</t>
+          <t>140.74</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2901,7 +2901,7 @@
       </c>
       <c r="BM6" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>904.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>909.0</t>
+          <t>926.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>899.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3016,7 +3016,7 @@
       </c>
       <c r="CJ6" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>3.97</t>
+          <t>8.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3133,7 +3133,7 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>-12.02</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,17 +3164,17 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
@@ -3184,53 +3184,53 @@
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>971.8</v>
+        <v>962.95</v>
       </c>
       <c r="AN7" t="n">
-        <v>941.9</v>
+        <v>944.08</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,53 +3240,53 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13146559354.4</v>
+        <v>14386844246.4</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>14614553602.28</v>
+        <v>14618581897.64</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3331,7 +3331,7 @@
       </c>
       <c r="BM7" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN7" t="inlineStr">
@@ -3361,12 +3361,12 @@
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3446,7 +3446,7 @@
       </c>
       <c r="CJ7" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>-2.36</t>
+          <t>8.02</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3563,7 +3563,7 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>-11.82</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>977.55</v>
+        <v>971.8</v>
       </c>
       <c r="AN8" t="n">
-        <v>938.52</v>
+        <v>941.9</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,53 +3670,53 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13620510362.4</v>
+        <v>13146559354.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>14466055493.78</v>
+        <v>14614553602.28</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3761,7 +3761,7 @@
       </c>
       <c r="BM8" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN8" t="inlineStr">
@@ -3786,17 +3786,17 @@
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3876,7 +3876,7 @@
       </c>
       <c r="CJ8" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>4.08</t>
+          <t>1.95</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3993,7 +3993,7 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>-6.01</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>980.85</v>
+        <v>977.55</v>
       </c>
       <c r="AN9" t="n">
-        <v>933.96</v>
+        <v>938.52</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,53 +4100,53 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>12590700418.8</v>
+        <v>13620510362.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>14368721493.28</v>
+        <v>14466055493.78</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4191,7 +4191,7 @@
       </c>
       <c r="BM9" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN9" t="inlineStr">
@@ -4211,22 +4211,22 @@
       </c>
       <c r="BQ9" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4306,7 +4306,7 @@
       </c>
       <c r="CJ9" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.65</t>
+          <t>8.12</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4423,7 +4423,7 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>-11.92</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,12 +4454,12 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
@@ -4474,53 +4474,53 @@
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>987.15</v>
+        <v>980.85</v>
       </c>
       <c r="AN10" t="n">
-        <v>929.9</v>
+        <v>933.96</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,53 +4530,53 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13187701378.4</v>
+        <v>12590700418.8</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>14292572173.18</v>
+        <v>14368721493.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4621,7 +4621,7 @@
       </c>
       <c r="BM10" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4736,7 +4736,7 @@
       </c>
       <c r="CJ10" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>1.72</t>
+          <t>7.71</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4853,7 +4853,7 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>-11.53</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>993</v>
+        <v>987.15</v>
       </c>
       <c r="AN11" t="n">
-        <v>925.54</v>
+        <v>929.9</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,53 +4960,53 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>12964522972</v>
+        <v>13187701378.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>14209168625.62</v>
+        <v>14292572173.18</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-273240924.15588</t>
+          <t>-303325579.8395176</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5051,7 +5051,7 @@
       </c>
       <c r="BM11" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5166,7 +5166,7 @@
       </c>
       <c r="CJ11" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-3.84</t>
+          <t>-0.64</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>19610.238</t>
+          <t>11523.207</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>5.86</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>-0.03</t>
+          <t>2.35</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-4.78</t>
+          <t>-1.67</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5283,7 +5283,7 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.16</t>
+          <t>-9.75</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-14</t>
+          <t>2025-11-17</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>67.85</t>
+          <t>39.87</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-2.49</t>
+          <t>-3.28</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>458</t>
+          <t>784</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>8364</t>
+          <t>17532</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5329,58 +5329,58 @@
       </c>
       <c r="AG12" t="inlineStr">
         <is>
-          <t>2.22</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.98</t>
+          <t>-3.27</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-3.71</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>8.28</t>
+          <t>7.29</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.80</t>
+          <t>13.67</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>960.2</t>
+          <t>947.0</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>997.15</v>
+        <v>993</v>
       </c>
       <c r="AN12" t="n">
-        <v>920.92</v>
+        <v>925.54</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>809.22</t>
+          <t>814.26</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-74.06</t>
+          <t>-96.69</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>5.36</t>
+          <t>0.55</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>20.64</t>
+          <t>16.62</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,53 +5390,53 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-68.15</t>
+          <t>-74.35</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
         <is>
-          <t>2025/10/07</t>
+          <t>2025/12/01</t>
         </is>
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6470511685.478602</t>
+          <t>6497312325.358974</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>13091194606.6</v>
+        <v>12964522972</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13748861147.6</t>
+          <t>13184192924.4</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>14155319682.02</v>
+        <v>14209168625.62</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-657666541</t>
+          <t>-219669952</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-127037005.3503502</t>
+          <t>-149529915.9358163</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-44367517.38797188</t>
+          <t>-273240924.15588</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>18182742782.0</t>
+          <t>10709769939.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>143.92</t>
+          <t>142.33</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5481,7 +5481,7 @@
       </c>
       <c r="BM12" t="inlineStr">
         <is>
-          <t>1.33</t>
+          <t>1.32</t>
         </is>
       </c>
       <c r="BN12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.95</t>
+          <t>9.88</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.72</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>48.47</t>
+          <t>50.6</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34.84</t>
+          <t>34.7</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2420910</t>
+          <t>2527409</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>931.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>922.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5596,16 +5596,12 @@
       </c>
       <c r="CJ12" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>True</t>
         </is>
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
+      <c r="A13" t="inlineStr"/>
       <c r="B13" t="inlineStr">
         <is>
           <t>1504</t>
@@ -5613,12 +5609,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>16281.325</t>
+          <t>0</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5624,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5638,17 +5634,17 @@
       </c>
       <c r="H13" t="inlineStr">
         <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="I13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="I13" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5658,37 +5654,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>99.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>2025-09-23 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>2025-10-14 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>2025-09-09 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>2025-09-19 00:00:00</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>104.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5698,12 +5694,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>79.6</t>
+          <t>0</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>80.8</t>
+          <t>0</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -5713,160 +5709,160 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>16.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>0</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>False</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>209</t>
+          <t>317</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>16281</t>
+          <t>16763</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>100.24</v>
+        <v>0</v>
       </c>
       <c r="AN13" t="n">
-        <v>103.28</v>
+        <v>0</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-60.15</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
         <is>
-          <t>9.92</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-131.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
         <is>
-          <t>2025/09/23</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1904892357.987857</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1429040476.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>4370895798.6</v>
+        <v>0</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3781268811.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>6680203633.36</v>
+        <v>0</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>589626987</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-322891705.6562934</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-452760313.4536171</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1429040476.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5876,17 +5872,17 @@
       </c>
       <c r="BF13" t="inlineStr">
         <is>
-          <t>55.3</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BG13" t="inlineStr">
         <is>
-          <t>2025/08/11</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>58.59</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5907,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.75</t>
+          <t>0.76</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,22 +5927,22 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>0</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.51</t>
+          <t>2.59</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5952,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>38.13</t>
+          <t>36.96</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5967,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>41.28</t>
+          <t>40.82</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>208414</t>
+          <t>201997</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5991,27 +5987,27 @@
       </c>
       <c r="CC13" t="inlineStr">
         <is>
-          <t>電機機械右上上市</t>
+          <t>電機機械右下上市</t>
         </is>
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>0</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6025,4306 +6021,6 @@
         </is>
       </c>
       <c r="CJ13" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="14">
-      <c r="A14" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B14" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C14" t="inlineStr">
-        <is>
-          <t>1.6</t>
-        </is>
-      </c>
-      <c r="D14" t="inlineStr">
-        <is>
-          <t>17538.055</t>
-        </is>
-      </c>
-      <c r="E14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F14" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
-      <c r="G14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H14" t="inlineStr">
-        <is>
-          <t>-1.03</t>
-        </is>
-      </c>
-      <c r="I14" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J14" t="inlineStr">
-        <is>
-          <t>7.23</t>
-        </is>
-      </c>
-      <c r="K14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L14" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M14" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N14" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O14" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P14" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q14" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R14" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T14" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U14" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W14" t="inlineStr">
-        <is>
-          <t>-14.81</t>
-        </is>
-      </c>
-      <c r="X14" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y14" t="inlineStr">
-        <is>
-          <t>2025-11-27</t>
-        </is>
-      </c>
-      <c r="Z14" t="inlineStr">
-        <is>
-          <t>5.30</t>
-        </is>
-      </c>
-      <c r="AA14" t="inlineStr">
-        <is>
-          <t>2.20</t>
-        </is>
-      </c>
-      <c r="AB14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC14" t="inlineStr"/>
-      <c r="AD14" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE14" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF14" t="inlineStr">
-        <is>
-          <t>14.89</t>
-        </is>
-      </c>
-      <c r="AG14" t="inlineStr">
-        <is>
-          <t>4.96</t>
-        </is>
-      </c>
-      <c r="AH14" t="inlineStr">
-        <is>
-          <t>-1.38</t>
-        </is>
-      </c>
-      <c r="AI14" t="inlineStr">
-        <is>
-          <t>-11.64</t>
-        </is>
-      </c>
-      <c r="AJ14" t="inlineStr">
-        <is>
-          <t>-1.57</t>
-        </is>
-      </c>
-      <c r="AK14" t="inlineStr">
-        <is>
-          <t>15.94</t>
-        </is>
-      </c>
-      <c r="AL14" t="inlineStr">
-        <is>
-          <t>89.84</t>
-        </is>
-      </c>
-      <c r="AM14" t="n">
-        <v>101.68</v>
-      </c>
-      <c r="AN14" t="n">
-        <v>103.29</v>
-      </c>
-      <c r="AO14" t="inlineStr">
-        <is>
-          <t>89.09</t>
-        </is>
-      </c>
-      <c r="AP14" t="inlineStr">
-        <is>
-          <t>-80.19</t>
-        </is>
-      </c>
-      <c r="AQ14" t="inlineStr">
-        <is>
-          <t>-4.71</t>
-        </is>
-      </c>
-      <c r="AR14" t="inlineStr">
-        <is>
-          <t>-2.61</t>
-        </is>
-      </c>
-      <c r="AS14" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT14" t="inlineStr">
-        <is>
-          <t>-126.36</t>
-        </is>
-      </c>
-      <c r="AU14" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV14" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW14" t="inlineStr">
-        <is>
-          <t>1543850905.0</t>
-        </is>
-      </c>
-      <c r="AX14" t="n">
-        <v>4691522022.2</v>
-      </c>
-      <c r="AY14" t="inlineStr">
-        <is>
-          <t>4375018215.4</t>
-        </is>
-      </c>
-      <c r="AZ14" t="n">
-        <v>6753332147.84</v>
-      </c>
-      <c r="BA14" t="inlineStr">
-        <is>
-          <t>316503806</t>
-        </is>
-      </c>
-      <c r="BB14" t="inlineStr">
-        <is>
-          <t>-299279231.5113254</t>
-        </is>
-      </c>
-      <c r="BC14" t="inlineStr">
-        <is>
-          <t>-297861176.0995588</t>
-        </is>
-      </c>
-      <c r="BD14" t="inlineStr">
-        <is>
-          <t>1543850905.0</t>
-        </is>
-      </c>
-      <c r="BE14" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF14" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG14" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH14" t="inlineStr">
-        <is>
-          <t>60.22</t>
-        </is>
-      </c>
-      <c r="BI14" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ14" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK14" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL14" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM14" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN14" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO14" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP14" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ14" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR14" t="inlineStr">
-        <is>
-          <t>價-量縮</t>
-        </is>
-      </c>
-      <c r="BS14" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="BT14" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU14" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV14" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW14" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX14" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY14" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ14" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA14" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB14" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC14" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD14" t="inlineStr">
-        <is>
-          <t>87.5</t>
-        </is>
-      </c>
-      <c r="CE14" t="inlineStr">
-        <is>
-          <t>88.7</t>
-        </is>
-      </c>
-      <c r="CF14" t="inlineStr">
-        <is>
-          <t>86.6</t>
-        </is>
-      </c>
-      <c r="CG14" t="inlineStr">
-        <is>
-          <t>88.6</t>
-        </is>
-      </c>
-      <c r="CH14" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI14" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ14" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="15">
-      <c r="A15" t="inlineStr">
-        <is>
-          <t>【e】</t>
-        </is>
-      </c>
-      <c r="B15" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C15" t="inlineStr">
-        <is>
-          <t>-1.46</t>
-        </is>
-      </c>
-      <c r="D15" t="inlineStr">
-        <is>
-          <t>30647.12</t>
-        </is>
-      </c>
-      <c r="E15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F15" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
-      </c>
-      <c r="G15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H15" t="inlineStr">
-        <is>
-          <t>0.57</t>
-        </is>
-      </c>
-      <c r="I15" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J15" t="inlineStr">
-        <is>
-          <t>5.79</t>
-        </is>
-      </c>
-      <c r="K15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L15" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M15" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N15" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O15" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P15" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q15" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R15" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T15" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U15" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W15" t="inlineStr">
-        <is>
-          <t>-16.15</t>
-        </is>
-      </c>
-      <c r="X15" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y15" t="inlineStr">
-        <is>
-          <t>2025-11-26</t>
-        </is>
-      </c>
-      <c r="Z15" t="inlineStr">
-        <is>
-          <t>9.26</t>
-        </is>
-      </c>
-      <c r="AA15" t="inlineStr">
-        <is>
-          <t>-1.72</t>
-        </is>
-      </c>
-      <c r="AB15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC15" t="inlineStr"/>
-      <c r="AD15" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE15" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF15" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG15" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="AH15" t="inlineStr">
-        <is>
-          <t>-4.53</t>
-        </is>
-      </c>
-      <c r="AI15" t="inlineStr">
-        <is>
-          <t>-11.38</t>
-        </is>
-      </c>
-      <c r="AJ15" t="inlineStr">
-        <is>
-          <t>-0.23</t>
-        </is>
-      </c>
-      <c r="AK15" t="inlineStr">
-        <is>
-          <t>16.49</t>
-        </is>
-      </c>
-      <c r="AL15" t="inlineStr">
-        <is>
-          <t>91.34</t>
-        </is>
-      </c>
-      <c r="AM15" t="n">
-        <v>103.07</v>
-      </c>
-      <c r="AN15" t="n">
-        <v>103.31</v>
-      </c>
-      <c r="AO15" t="inlineStr">
-        <is>
-          <t>88.68</t>
-        </is>
-      </c>
-      <c r="AP15" t="inlineStr">
-        <is>
-          <t>-113.22</t>
-        </is>
-      </c>
-      <c r="AQ15" t="inlineStr">
-        <is>
-          <t>-4.46</t>
-        </is>
-      </c>
-      <c r="AR15" t="inlineStr">
-        <is>
-          <t>-2.09</t>
-        </is>
-      </c>
-      <c r="AS15" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT15" t="inlineStr">
-        <is>
-          <t>-121.07</t>
-        </is>
-      </c>
-      <c r="AU15" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV15" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW15" t="inlineStr">
-        <is>
-          <t>2683545818.0</t>
-        </is>
-      </c>
-      <c r="AX15" t="n">
-        <v>5000685349.4</v>
-      </c>
-      <c r="AY15" t="inlineStr">
-        <is>
-          <t>4727097624.7</t>
-        </is>
-      </c>
-      <c r="AZ15" t="n">
-        <v>6863428946.3</v>
-      </c>
-      <c r="BA15" t="inlineStr">
-        <is>
-          <t>273587724</t>
-        </is>
-      </c>
-      <c r="BB15" t="inlineStr">
-        <is>
-          <t>-299537059.7680103</t>
-        </is>
-      </c>
-      <c r="BC15" t="inlineStr">
-        <is>
-          <t>-78239912.41163445</t>
-        </is>
-      </c>
-      <c r="BD15" t="inlineStr">
-        <is>
-          <t>2683545818.0</t>
-        </is>
-      </c>
-      <c r="BE15" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF15" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG15" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH15" t="inlineStr">
-        <is>
-          <t>57.69</t>
-        </is>
-      </c>
-      <c r="BI15" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ15" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK15" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL15" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM15" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN15" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO15" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP15" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ15" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR15" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS15" t="inlineStr">
-        <is>
-          <t>2.33</t>
-        </is>
-      </c>
-      <c r="BT15" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU15" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV15" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW15" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX15" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY15" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ15" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA15" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB15" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC15" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD15" t="inlineStr">
-        <is>
-          <t>88.9</t>
-        </is>
-      </c>
-      <c r="CE15" t="inlineStr">
-        <is>
-          <t>89.2</t>
-        </is>
-      </c>
-      <c r="CF15" t="inlineStr">
-        <is>
-          <t>86.7</t>
-        </is>
-      </c>
-      <c r="CG15" t="inlineStr">
-        <is>
-          <t>87.2</t>
-        </is>
-      </c>
-      <c r="CH15" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI15" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ15" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="16">
-      <c r="A16" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B16" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C16" t="inlineStr">
-        <is>
-          <t>-4.63</t>
-        </is>
-      </c>
-      <c r="D16" t="inlineStr">
-        <is>
-          <t>52066.846</t>
-        </is>
-      </c>
-      <c r="E16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F16" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="G16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H16" t="inlineStr">
-        <is>
-          <t>-0.91</t>
-        </is>
-      </c>
-      <c r="I16" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J16" t="inlineStr">
-        <is>
-          <t>9.19</t>
-        </is>
-      </c>
-      <c r="K16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L16" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M16" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N16" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O16" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P16" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q16" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R16" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T16" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U16" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W16" t="inlineStr">
-        <is>
-          <t>-14.90</t>
-        </is>
-      </c>
-      <c r="X16" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y16" t="inlineStr">
-        <is>
-          <t>2025-11-25</t>
-        </is>
-      </c>
-      <c r="Z16" t="inlineStr">
-        <is>
-          <t>15.73</t>
-        </is>
-      </c>
-      <c r="AA16" t="inlineStr">
-        <is>
-          <t>-6.32</t>
-        </is>
-      </c>
-      <c r="AB16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC16" t="inlineStr"/>
-      <c r="AD16" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE16" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF16" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG16" t="inlineStr">
-        <is>
-          <t>1.62</t>
-        </is>
-      </c>
-      <c r="AH16" t="inlineStr">
-        <is>
-          <t>-4.32</t>
-        </is>
-      </c>
-      <c r="AI16" t="inlineStr">
-        <is>
-          <t>-11.43</t>
-        </is>
-      </c>
-      <c r="AJ16" t="inlineStr">
-        <is>
-          <t>0.98</t>
-        </is>
-      </c>
-      <c r="AK16" t="inlineStr">
-        <is>
-          <t>17.22</t>
-        </is>
-      </c>
-      <c r="AL16" t="inlineStr">
-        <is>
-          <t>92.5</t>
-        </is>
-      </c>
-      <c r="AM16" t="n">
-        <v>104.44</v>
-      </c>
-      <c r="AN16" t="n">
-        <v>103.43</v>
-      </c>
-      <c r="AO16" t="inlineStr">
-        <is>
-          <t>88.23</t>
-        </is>
-      </c>
-      <c r="AP16" t="inlineStr">
-        <is>
-          <t>-161.95</t>
-        </is>
-      </c>
-      <c r="AQ16" t="inlineStr">
-        <is>
-          <t>-3.93</t>
-        </is>
-      </c>
-      <c r="AR16" t="inlineStr">
-        <is>
-          <t>-1.50</t>
-        </is>
-      </c>
-      <c r="AS16" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT16" t="inlineStr">
-        <is>
-          <t>-115.11</t>
-        </is>
-      </c>
-      <c r="AU16" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV16" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW16" t="inlineStr">
-        <is>
-          <t>4682266073.0</t>
-        </is>
-      </c>
-      <c r="AX16" t="n">
-        <v>5019578044.4</v>
-      </c>
-      <c r="AY16" t="inlineStr">
-        <is>
-          <t>4597307742.4</t>
-        </is>
-      </c>
-      <c r="AZ16" t="n">
-        <v>7180754379.14</v>
-      </c>
-      <c r="BA16" t="inlineStr">
-        <is>
-          <t>422270302</t>
-        </is>
-      </c>
-      <c r="BB16" t="inlineStr">
-        <is>
-          <t>-339772904.7418968</t>
-        </is>
-      </c>
-      <c r="BC16" t="inlineStr">
-        <is>
-          <t>116188863.3358154</t>
-        </is>
-      </c>
-      <c r="BD16" t="inlineStr">
-        <is>
-          <t>4682266073.0</t>
-        </is>
-      </c>
-      <c r="BE16" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF16" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG16" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH16" t="inlineStr">
-        <is>
-          <t>60.04</t>
-        </is>
-      </c>
-      <c r="BI16" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ16" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK16" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL16" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM16" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN16" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO16" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP16" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ16" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR16" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS16" t="inlineStr">
-        <is>
-          <t>2.37</t>
-        </is>
-      </c>
-      <c r="BT16" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU16" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV16" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW16" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX16" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY16" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ16" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA16" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB16" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC16" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD16" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="CE16" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="CF16" t="inlineStr">
-        <is>
-          <t>87.6</t>
-        </is>
-      </c>
-      <c r="CG16" t="inlineStr">
-        <is>
-          <t>88.5</t>
-        </is>
-      </c>
-      <c r="CH16" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI16" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ16" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="17">
-      <c r="A17" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B17" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C17" t="inlineStr">
-        <is>
-          <t>0.96</t>
-        </is>
-      </c>
-      <c r="D17" t="inlineStr">
-        <is>
-          <t>124181.065</t>
-        </is>
-      </c>
-      <c r="E17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F17" t="inlineStr">
-        <is>
-          <t>92.9</t>
-        </is>
-      </c>
-      <c r="G17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H17" t="inlineStr">
-        <is>
-          <t>-5.93</t>
-        </is>
-      </c>
-      <c r="I17" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J17" t="inlineStr">
-        <is>
-          <t>8.20</t>
-        </is>
-      </c>
-      <c r="K17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L17" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M17" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N17" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O17" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P17" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q17" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R17" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T17" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U17" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W17" t="inlineStr">
-        <is>
-          <t>-10.67</t>
-        </is>
-      </c>
-      <c r="X17" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y17" t="inlineStr">
-        <is>
-          <t>2025-11-24</t>
-        </is>
-      </c>
-      <c r="Z17" t="inlineStr">
-        <is>
-          <t>37.51</t>
-        </is>
-      </c>
-      <c r="AA17" t="inlineStr">
-        <is>
-          <t>0.90</t>
-        </is>
-      </c>
-      <c r="AB17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC17" t="inlineStr"/>
-      <c r="AD17" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE17" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF17" t="inlineStr">
-        <is>
-          <t>4.86</t>
-        </is>
-      </c>
-      <c r="AG17" t="inlineStr">
-        <is>
-          <t>7.53</t>
-        </is>
-      </c>
-      <c r="AH17" t="inlineStr">
-        <is>
-          <t>-0.71</t>
-        </is>
-      </c>
-      <c r="AI17" t="inlineStr">
-        <is>
-          <t>-11.58</t>
-        </is>
-      </c>
-      <c r="AJ17" t="inlineStr">
-        <is>
-          <t>2.32</t>
-        </is>
-      </c>
-      <c r="AK17" t="inlineStr">
-        <is>
-          <t>17.91</t>
-        </is>
-      </c>
-      <c r="AL17" t="inlineStr">
-        <is>
-          <t>93.56</t>
-        </is>
-      </c>
-      <c r="AM17" t="n">
-        <v>105.81</v>
-      </c>
-      <c r="AN17" t="n">
-        <v>103.41</v>
-      </c>
-      <c r="AO17" t="inlineStr">
-        <is>
-          <t>87.7</t>
-        </is>
-      </c>
-      <c r="AP17" t="inlineStr">
-        <is>
-          <t>-272.55</t>
-        </is>
-      </c>
-      <c r="AQ17" t="inlineStr">
-        <is>
-          <t>-3.32</t>
-        </is>
-      </c>
-      <c r="AR17" t="inlineStr">
-        <is>
-          <t>-0.89</t>
-        </is>
-      </c>
-      <c r="AS17" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT17" t="inlineStr">
-        <is>
-          <t>-108.99</t>
-        </is>
-      </c>
-      <c r="AU17" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV17" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW17" t="inlineStr">
-        <is>
-          <t>11515775721.0</t>
-        </is>
-      </c>
-      <c r="AX17" t="n">
-        <v>4696916791.4</v>
-      </c>
-      <c r="AY17" t="inlineStr">
-        <is>
-          <t>4341077616.0</t>
-        </is>
-      </c>
-      <c r="AZ17" t="n">
-        <v>7241408797.74</v>
-      </c>
-      <c r="BA17" t="inlineStr">
-        <is>
-          <t>355839175</t>
-        </is>
-      </c>
-      <c r="BB17" t="inlineStr">
-        <is>
-          <t>-422675044.3923899</t>
-        </is>
-      </c>
-      <c r="BC17" t="inlineStr">
-        <is>
-          <t>175646056.2487507</t>
-        </is>
-      </c>
-      <c r="BD17" t="inlineStr">
-        <is>
-          <t>11515775721.0</t>
-        </is>
-      </c>
-      <c r="BE17" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF17" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG17" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH17" t="inlineStr">
-        <is>
-          <t>67.99</t>
-        </is>
-      </c>
-      <c r="BI17" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ17" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK17" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL17" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM17" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN17" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO17" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP17" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ17" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR17" t="inlineStr">
-        <is>
-          <t>價-量增</t>
-        </is>
-      </c>
-      <c r="BS17" t="inlineStr">
-        <is>
-          <t>2.48</t>
-        </is>
-      </c>
-      <c r="BT17" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU17" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV17" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW17" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX17" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY17" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ17" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA17" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB17" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC17" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD17" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="CE17" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="CF17" t="inlineStr">
-        <is>
-          <t>91.0</t>
-        </is>
-      </c>
-      <c r="CG17" t="inlineStr">
-        <is>
-          <t>92.9</t>
-        </is>
-      </c>
-      <c r="CH17" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI17" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ17" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="18">
-      <c r="A18" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B18" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C18" t="inlineStr">
-        <is>
-          <t>-4.38</t>
-        </is>
-      </c>
-      <c r="D18" t="inlineStr">
-        <is>
-          <t>32684.421</t>
-        </is>
-      </c>
-      <c r="E18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F18" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="G18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H18" t="inlineStr">
-        <is>
-          <t>-4.9</t>
-        </is>
-      </c>
-      <c r="I18" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J18" t="inlineStr">
-        <is>
-          <t>-9.52</t>
-        </is>
-      </c>
-      <c r="K18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L18" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M18" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N18" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O18" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P18" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q18" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R18" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T18" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U18" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W18" t="inlineStr">
-        <is>
-          <t>-11.54</t>
-        </is>
-      </c>
-      <c r="X18" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y18" t="inlineStr">
-        <is>
-          <t>2025-11-21</t>
-        </is>
-      </c>
-      <c r="Z18" t="inlineStr">
-        <is>
-          <t>9.87</t>
-        </is>
-      </c>
-      <c r="AA18" t="inlineStr">
-        <is>
-          <t>-2.82</t>
-        </is>
-      </c>
-      <c r="AB18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC18" t="inlineStr"/>
-      <c r="AD18" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE18" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF18" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG18" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="AH18" t="inlineStr">
-        <is>
-          <t>-2.44</t>
-        </is>
-      </c>
-      <c r="AI18" t="inlineStr">
-        <is>
-          <t>-11.80</t>
-        </is>
-      </c>
-      <c r="AJ18" t="inlineStr">
-        <is>
-          <t>3.66</t>
-        </is>
-      </c>
-      <c r="AK18" t="inlineStr">
-        <is>
-          <t>18.39</t>
-        </is>
-      </c>
-      <c r="AL18" t="inlineStr">
-        <is>
-          <t>94.3</t>
-        </is>
-      </c>
-      <c r="AM18" t="n">
-        <v>106.92</v>
-      </c>
-      <c r="AN18" t="n">
-        <v>103.14</v>
-      </c>
-      <c r="AO18" t="inlineStr">
-        <is>
-          <t>87.12</t>
-        </is>
-      </c>
-      <c r="AP18" t="inlineStr">
-        <is>
-          <t>-939.09</t>
-        </is>
-      </c>
-      <c r="AQ18" t="inlineStr">
-        <is>
-          <t>-2.95</t>
-        </is>
-      </c>
-      <c r="AR18" t="inlineStr">
-        <is>
-          <t>-0.28</t>
-        </is>
-      </c>
-      <c r="AS18" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT18" t="inlineStr">
-        <is>
-          <t>-102.86</t>
-        </is>
-      </c>
-      <c r="AU18" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV18" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW18" t="inlineStr">
-        <is>
-          <t>3032171594.0</t>
-        </is>
-      </c>
-      <c r="AX18" t="n">
-        <v>3191641823.4</v>
-      </c>
-      <c r="AY18" t="inlineStr">
-        <is>
-          <t>3527299622.7</t>
-        </is>
-      </c>
-      <c r="AZ18" t="n">
-        <v>7285669264.58</v>
-      </c>
-      <c r="BA18" t="inlineStr">
-        <is>
-          <t>-335657799</t>
-        </is>
-      </c>
-      <c r="BB18" t="inlineStr">
-        <is>
-          <t>-531460699.0544155</t>
-        </is>
-      </c>
-      <c r="BC18" t="inlineStr">
-        <is>
-          <t>-477849918.1702256</t>
-        </is>
-      </c>
-      <c r="BD18" t="inlineStr">
-        <is>
-          <t>3032171594.0</t>
-        </is>
-      </c>
-      <c r="BE18" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF18" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG18" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH18" t="inlineStr">
-        <is>
-          <t>66.37</t>
-        </is>
-      </c>
-      <c r="BI18" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ18" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK18" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL18" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM18" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN18" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO18" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP18" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ18" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR18" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS18" t="inlineStr">
-        <is>
-          <t>2.46</t>
-        </is>
-      </c>
-      <c r="BT18" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU18" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV18" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW18" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX18" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY18" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ18" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA18" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB18" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC18" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD18" t="inlineStr">
-        <is>
-          <t>93.6</t>
-        </is>
-      </c>
-      <c r="CE18" t="inlineStr">
-        <is>
-          <t>95.0</t>
-        </is>
-      </c>
-      <c r="CF18" t="inlineStr">
-        <is>
-          <t>91.6</t>
-        </is>
-      </c>
-      <c r="CG18" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="CH18" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI18" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ18" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="19">
-      <c r="A19" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B19" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C19" t="inlineStr">
-        <is>
-          <t>3.2</t>
-        </is>
-      </c>
-      <c r="D19" t="inlineStr">
-        <is>
-          <t>31967.753</t>
-        </is>
-      </c>
-      <c r="E19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F19" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
-      <c r="G19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H19" t="inlineStr">
-        <is>
-          <t>-9.58</t>
-        </is>
-      </c>
-      <c r="I19" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J19" t="inlineStr">
-        <is>
-          <t>14.94</t>
-        </is>
-      </c>
-      <c r="K19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L19" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M19" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N19" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O19" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P19" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q19" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R19" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T19" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U19" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W19" t="inlineStr">
-        <is>
-          <t>-7.60</t>
-        </is>
-      </c>
-      <c r="X19" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y19" t="inlineStr">
-        <is>
-          <t>2025-11-20</t>
-        </is>
-      </c>
-      <c r="Z19" t="inlineStr">
-        <is>
-          <t>9.66</t>
-        </is>
-      </c>
-      <c r="AA19" t="inlineStr">
-        <is>
-          <t>-1.12</t>
-        </is>
-      </c>
-      <c r="AB19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC19" t="inlineStr"/>
-      <c r="AD19" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE19" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF19" t="inlineStr">
-        <is>
-          <t>17.71</t>
-        </is>
-      </c>
-      <c r="AG19" t="inlineStr">
-        <is>
-          <t>5.9</t>
-        </is>
-      </c>
-      <c r="AH19" t="inlineStr">
-        <is>
-          <t>0.25</t>
-        </is>
-      </c>
-      <c r="AI19" t="inlineStr">
-        <is>
-          <t>-11.25</t>
-        </is>
-      </c>
-      <c r="AJ19" t="inlineStr">
-        <is>
-          <t>5.13</t>
-        </is>
-      </c>
-      <c r="AK19" t="inlineStr">
-        <is>
-          <t>18.72</t>
-        </is>
-      </c>
-      <c r="AL19" t="inlineStr">
-        <is>
-          <t>95.85999999999999</t>
-        </is>
-      </c>
-      <c r="AM19" t="n">
-        <v>108.02</v>
-      </c>
-      <c r="AN19" t="n">
-        <v>102.75</v>
-      </c>
-      <c r="AO19" t="inlineStr">
-        <is>
-          <t>86.55</t>
-        </is>
-      </c>
-      <c r="AP19" t="inlineStr">
-        <is>
-          <t>-712.58</t>
-        </is>
-      </c>
-      <c r="AQ19" t="inlineStr">
-        <is>
-          <t>-2.35</t>
-        </is>
-      </c>
-      <c r="AR19" t="inlineStr">
-        <is>
-          <t>0.38</t>
-        </is>
-      </c>
-      <c r="AS19" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT19" t="inlineStr">
-        <is>
-          <t>-96.14</t>
-        </is>
-      </c>
-      <c r="AU19" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV19" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW19" t="inlineStr">
-        <is>
-          <t>3089667541.0</t>
-        </is>
-      </c>
-      <c r="AX19" t="n">
-        <v>4058514408.6</v>
-      </c>
-      <c r="AY19" t="inlineStr">
-        <is>
-          <t>3531039856.9</t>
-        </is>
-      </c>
-      <c r="AZ19" t="n">
-        <v>7317342463.3</v>
-      </c>
-      <c r="BA19" t="inlineStr">
-        <is>
-          <t>527474551</t>
-        </is>
-      </c>
-      <c r="BB19" t="inlineStr">
-        <is>
-          <t>-541208113.7606318</t>
-        </is>
-      </c>
-      <c r="BC19" t="inlineStr">
-        <is>
-          <t>-485391942.3698263</t>
-        </is>
-      </c>
-      <c r="BD19" t="inlineStr">
-        <is>
-          <t>3089667541.0</t>
-        </is>
-      </c>
-      <c r="BE19" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF19" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG19" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH19" t="inlineStr">
-        <is>
-          <t>73.78</t>
-        </is>
-      </c>
-      <c r="BI19" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ19" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK19" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL19" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM19" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN19" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO19" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP19" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ19" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR19" t="inlineStr">
-        <is>
-          <t>價漲量-</t>
-        </is>
-      </c>
-      <c r="BS19" t="inlineStr">
-        <is>
-          <t>2.57</t>
-        </is>
-      </c>
-      <c r="BT19" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU19" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV19" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW19" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX19" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY19" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ19" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA19" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB19" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC19" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD19" t="inlineStr">
-        <is>
-          <t>96.9</t>
-        </is>
-      </c>
-      <c r="CE19" t="inlineStr">
-        <is>
-          <t>98.8</t>
-        </is>
-      </c>
-      <c r="CF19" t="inlineStr">
-        <is>
-          <t>94.5</t>
-        </is>
-      </c>
-      <c r="CG19" t="inlineStr">
-        <is>
-          <t>96.1</t>
-        </is>
-      </c>
-      <c r="CH19" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI19" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ19" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="20">
-      <c r="A20" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B20" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C20" t="inlineStr">
-        <is>
-          <t>-0.85</t>
-        </is>
-      </c>
-      <c r="D20" t="inlineStr">
-        <is>
-          <t>29839.894</t>
-        </is>
-      </c>
-      <c r="E20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F20" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="G20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H20" t="inlineStr">
-        <is>
-          <t>-6.04</t>
-        </is>
-      </c>
-      <c r="I20" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J20" t="inlineStr">
-        <is>
-          <t>20.75</t>
-        </is>
-      </c>
-      <c r="K20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L20" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M20" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N20" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O20" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P20" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q20" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R20" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T20" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U20" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W20" t="inlineStr">
-        <is>
-          <t>-10.58</t>
-        </is>
-      </c>
-      <c r="X20" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y20" t="inlineStr">
-        <is>
-          <t>2025-11-19</t>
-        </is>
-      </c>
-      <c r="Z20" t="inlineStr">
-        <is>
-          <t>9.01</t>
-        </is>
-      </c>
-      <c r="AA20" t="inlineStr">
-        <is>
-          <t>-0.42</t>
-        </is>
-      </c>
-      <c r="AB20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC20" t="inlineStr"/>
-      <c r="AD20" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE20" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG20" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH20" t="inlineStr">
-        <is>
-          <t>-5.81</t>
-        </is>
-      </c>
-      <c r="AI20" t="inlineStr">
-        <is>
-          <t>-9.44</t>
-        </is>
-      </c>
-      <c r="AJ20" t="inlineStr">
-        <is>
-          <t>6.7</t>
-        </is>
-      </c>
-      <c r="AK20" t="inlineStr">
-        <is>
-          <t>18.92</t>
-        </is>
-      </c>
-      <c r="AL20" t="inlineStr">
-        <is>
-          <t>98.74</t>
-        </is>
-      </c>
-      <c r="AM20" t="n">
-        <v>109.04</v>
-      </c>
-      <c r="AN20" t="n">
-        <v>102.19</v>
-      </c>
-      <c r="AO20" t="inlineStr">
-        <is>
-          <t>85.93</t>
-        </is>
-      </c>
-      <c r="AP20" t="inlineStr">
-        <is>
-          <t>-283.53</t>
-        </is>
-      </c>
-      <c r="AQ20" t="inlineStr">
-        <is>
-          <t>-1.95</t>
-        </is>
-      </c>
-      <c r="AR20" t="inlineStr">
-        <is>
-          <t>1.07</t>
-        </is>
-      </c>
-      <c r="AS20" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT20" t="inlineStr">
-        <is>
-          <t>-89.26</t>
-        </is>
-      </c>
-      <c r="AU20" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV20" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW20" t="inlineStr">
-        <is>
-          <t>2778009293.0</t>
-        </is>
-      </c>
-      <c r="AX20" t="n">
-        <v>4453509900</v>
-      </c>
-      <c r="AY20" t="inlineStr">
-        <is>
-          <t>3688316666.2</t>
-        </is>
-      </c>
-      <c r="AZ20" t="n">
-        <v>7280178623.2</v>
-      </c>
-      <c r="BA20" t="inlineStr">
-        <is>
-          <t>765193233</t>
-        </is>
-      </c>
-      <c r="BB20" t="inlineStr">
-        <is>
-          <t>-551356508.5589601</t>
-        </is>
-      </c>
-      <c r="BC20" t="inlineStr">
-        <is>
-          <t>-484991116.1774759</t>
-        </is>
-      </c>
-      <c r="BD20" t="inlineStr">
-        <is>
-          <t>2778009293.0</t>
-        </is>
-      </c>
-      <c r="BE20" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF20" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG20" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH20" t="inlineStr">
-        <is>
-          <t>68.17</t>
-        </is>
-      </c>
-      <c r="BI20" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ20" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK20" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL20" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM20" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN20" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO20" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP20" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ20" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR20" t="inlineStr">
-        <is>
-          <t>價漲量縮</t>
-        </is>
-      </c>
-      <c r="BS20" t="inlineStr">
-        <is>
-          <t>2.49</t>
-        </is>
-      </c>
-      <c r="BT20" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU20" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV20" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW20" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX20" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY20" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ20" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA20" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB20" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC20" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD20" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="CE20" t="inlineStr">
-        <is>
-          <t>94.4</t>
-        </is>
-      </c>
-      <c r="CF20" t="inlineStr">
-        <is>
-          <t>92.0</t>
-        </is>
-      </c>
-      <c r="CG20" t="inlineStr">
-        <is>
-          <t>93.0</t>
-        </is>
-      </c>
-      <c r="CH20" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI20" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ20" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="21">
-      <c r="A21" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B21" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C21" t="inlineStr">
-        <is>
-          <t>-2.92</t>
-        </is>
-      </c>
-      <c r="D21" t="inlineStr">
-        <is>
-          <t>32132.941</t>
-        </is>
-      </c>
-      <c r="E21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F21" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="G21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H21" t="inlineStr">
-        <is>
-          <t>-6.96</t>
-        </is>
-      </c>
-      <c r="I21" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J21" t="inlineStr">
-        <is>
-          <t>7.01</t>
-        </is>
-      </c>
-      <c r="K21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L21" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M21" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N21" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O21" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P21" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q21" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R21" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T21" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U21" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W21" t="inlineStr">
-        <is>
-          <t>-9.81</t>
-        </is>
-      </c>
-      <c r="X21" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y21" t="inlineStr">
-        <is>
-          <t>2025-11-18</t>
-        </is>
-      </c>
-      <c r="Z21" t="inlineStr">
-        <is>
-          <t>9.71</t>
-        </is>
-      </c>
-      <c r="AA21" t="inlineStr">
-        <is>
-          <t>-3.94</t>
-        </is>
-      </c>
-      <c r="AB21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC21" t="inlineStr"/>
-      <c r="AD21" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE21" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG21" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AH21" t="inlineStr">
-        <is>
-          <t>-7.44</t>
-        </is>
-      </c>
-      <c r="AI21" t="inlineStr">
-        <is>
-          <t>-7.92</t>
-        </is>
-      </c>
-      <c r="AJ21" t="inlineStr">
-        <is>
-          <t>8.26</t>
-        </is>
-      </c>
-      <c r="AK21" t="inlineStr">
-        <is>
-          <t>19.11</t>
-        </is>
-      </c>
-      <c r="AL21" t="inlineStr">
-        <is>
-          <t>101.34</t>
-        </is>
-      </c>
-      <c r="AM21" t="n">
-        <v>110.06</v>
-      </c>
-      <c r="AN21" t="n">
-        <v>101.66</v>
-      </c>
-      <c r="AO21" t="inlineStr">
-        <is>
-          <t>85.35</t>
-        </is>
-      </c>
-      <c r="AP21" t="inlineStr">
-        <is>
-          <t>-161.08</t>
-        </is>
-      </c>
-      <c r="AQ21" t="inlineStr">
-        <is>
-          <t>-1.11</t>
-        </is>
-      </c>
-      <c r="AR21" t="inlineStr">
-        <is>
-          <t>1.82</t>
-        </is>
-      </c>
-      <c r="AS21" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT21" t="inlineStr">
-        <is>
-          <t>-81.65</t>
-        </is>
-      </c>
-      <c r="AU21" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV21" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW21" t="inlineStr">
-        <is>
-          <t>3068959808.0</t>
-        </is>
-      </c>
-      <c r="AX21" t="n">
-        <v>4175037440.4</v>
-      </c>
-      <c r="AY21" t="inlineStr">
-        <is>
-          <t>3901577638.9</t>
-        </is>
-      </c>
-      <c r="AZ21" t="n">
-        <v>7265450343.64</v>
-      </c>
-      <c r="BA21" t="inlineStr">
-        <is>
-          <t>273459801</t>
-        </is>
-      </c>
-      <c r="BB21" t="inlineStr">
-        <is>
-          <t>-563422943.5374118</t>
-        </is>
-      </c>
-      <c r="BC21" t="inlineStr">
-        <is>
-          <t>-433705440.8963513</t>
-        </is>
-      </c>
-      <c r="BD21" t="inlineStr">
-        <is>
-          <t>3068959808.0</t>
-        </is>
-      </c>
-      <c r="BE21" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF21" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG21" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH21" t="inlineStr">
-        <is>
-          <t>69.62</t>
-        </is>
-      </c>
-      <c r="BI21" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ21" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK21" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL21" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM21" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN21" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO21" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP21" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ21" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
-        </is>
-      </c>
-      <c r="BR21" t="inlineStr">
-        <is>
-          <t>價跌量增</t>
-        </is>
-      </c>
-      <c r="BS21" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BT21" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU21" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV21" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW21" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX21" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY21" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ21" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA21" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB21" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC21" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD21" t="inlineStr">
-        <is>
-          <t>96.0</t>
-        </is>
-      </c>
-      <c r="CE21" t="inlineStr">
-        <is>
-          <t>97.5</t>
-        </is>
-      </c>
-      <c r="CF21" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="CG21" t="inlineStr">
-        <is>
-          <t>93.8</t>
-        </is>
-      </c>
-      <c r="CH21" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI21" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ21" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="22">
-      <c r="A22" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B22" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C22" t="inlineStr">
-        <is>
-          <t>-3.2</t>
-        </is>
-      </c>
-      <c r="D22" t="inlineStr">
-        <is>
-          <t>40908.464</t>
-        </is>
-      </c>
-      <c r="E22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F22" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="G22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H22" t="inlineStr">
-        <is>
-          <t>-10.15</t>
-        </is>
-      </c>
-      <c r="I22" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J22" t="inlineStr">
-        <is>
-          <t>0.16</t>
-        </is>
-      </c>
-      <c r="K22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L22" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M22" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N22" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O22" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P22" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q22" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R22" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T22" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U22" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W22" t="inlineStr">
-        <is>
-          <t>-7.12</t>
-        </is>
-      </c>
-      <c r="X22" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y22" t="inlineStr">
-        <is>
-          <t>2025-11-17</t>
-        </is>
-      </c>
-      <c r="Z22" t="inlineStr">
-        <is>
-          <t>12.36</t>
-        </is>
-      </c>
-      <c r="AA22" t="inlineStr">
-        <is>
-          <t>-4.14</t>
-        </is>
-      </c>
-      <c r="AB22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC22" t="inlineStr"/>
-      <c r="AD22" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE22" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF22" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG22" t="inlineStr">
-        <is>
-          <t>18.18</t>
-        </is>
-      </c>
-      <c r="AH22" t="inlineStr">
-        <is>
-          <t>-6.65</t>
-        </is>
-      </c>
-      <c r="AI22" t="inlineStr">
-        <is>
-          <t>-7.06</t>
-        </is>
-      </c>
-      <c r="AJ22" t="inlineStr">
-        <is>
-          <t>10.11</t>
-        </is>
-      </c>
-      <c r="AK22" t="inlineStr">
-        <is>
-          <t>19.29</t>
-        </is>
-      </c>
-      <c r="AL22" t="inlineStr">
-        <is>
-          <t>103.48</t>
-        </is>
-      </c>
-      <c r="AM22" t="n">
-        <v>111.34</v>
-      </c>
-      <c r="AN22" t="n">
-        <v>101.12</v>
-      </c>
-      <c r="AO22" t="inlineStr">
-        <is>
-          <t>84.77</t>
-        </is>
-      </c>
-      <c r="AP22" t="inlineStr">
-        <is>
-          <t>-103.95</t>
-        </is>
-      </c>
-      <c r="AQ22" t="inlineStr">
-        <is>
-          <t>-0.10</t>
-        </is>
-      </c>
-      <c r="AR22" t="inlineStr">
-        <is>
-          <t>2.55</t>
-        </is>
-      </c>
-      <c r="AS22" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT22" t="inlineStr">
-        <is>
-          <t>-74.26</t>
-        </is>
-      </c>
-      <c r="AU22" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV22" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW22" t="inlineStr">
-        <is>
-          <t>3989400881.0</t>
-        </is>
-      </c>
-      <c r="AX22" t="n">
-        <v>3985238440.6</v>
-      </c>
-      <c r="AY22" t="inlineStr">
-        <is>
-          <t>3979054603.6</t>
-        </is>
-      </c>
-      <c r="AZ22" t="n">
-        <v>7220968787.64</v>
-      </c>
-      <c r="BA22" t="inlineStr">
-        <is>
-          <t>6183837</t>
-        </is>
-      </c>
-      <c r="BB22" t="inlineStr">
-        <is>
-          <t>-587007944.0176046</t>
-        </is>
-      </c>
-      <c r="BC22" t="inlineStr">
-        <is>
-          <t>-376123979.9270172</t>
-        </is>
-      </c>
-      <c r="BD22" t="inlineStr">
-        <is>
-          <t>3989400881.0</t>
-        </is>
-      </c>
-      <c r="BE22" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF22" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG22" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH22" t="inlineStr">
-        <is>
-          <t>74.68</t>
-        </is>
-      </c>
-      <c r="BI22" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ22" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK22" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL22" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM22" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN22" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO22" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP22" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ22" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR22" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS22" t="inlineStr">
-        <is>
-          <t>2.58</t>
-        </is>
-      </c>
-      <c r="BT22" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU22" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV22" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW22" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX22" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY22" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ22" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA22" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB22" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC22" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD22" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="CE22" t="inlineStr">
-        <is>
-          <t>101.0</t>
-        </is>
-      </c>
-      <c r="CF22" t="inlineStr">
-        <is>
-          <t>96.2</t>
-        </is>
-      </c>
-      <c r="CG22" t="inlineStr">
-        <is>
-          <t>96.6</t>
-        </is>
-      </c>
-      <c r="CH22" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI22" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ22" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-    </row>
-    <row r="23">
-      <c r="A23" t="inlineStr">
-        <is>
-          <t>【c】</t>
-        </is>
-      </c>
-      <c r="B23" t="inlineStr">
-        <is>
-          <t>1504</t>
-        </is>
-      </c>
-      <c r="C23" t="inlineStr">
-        <is>
-          <t>-10.29</t>
-        </is>
-      </c>
-      <c r="D23" t="inlineStr">
-        <is>
-          <t>72776.258</t>
-        </is>
-      </c>
-      <c r="E23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F23" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
-      <c r="G23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H23" t="inlineStr">
-        <is>
-          <t>-13.8</t>
-        </is>
-      </c>
-      <c r="I23" t="inlineStr">
-        <is>
-          <t>-1.66</t>
-        </is>
-      </c>
-      <c r="J23" t="inlineStr">
-        <is>
-          <t>-3.70</t>
-        </is>
-      </c>
-      <c r="K23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="L23" t="inlineStr">
-        <is>
-          <t>99.0</t>
-        </is>
-      </c>
-      <c r="M23" t="inlineStr">
-        <is>
-          <t>2025-09-23 00:00:00</t>
-        </is>
-      </c>
-      <c r="N23" t="inlineStr">
-        <is>
-          <t>2025-10-14 00:00:00</t>
-        </is>
-      </c>
-      <c r="O23" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P23" t="inlineStr">
-        <is>
-          <t>2025-09-19 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q23" t="inlineStr">
-        <is>
-          <t>94.0</t>
-        </is>
-      </c>
-      <c r="R23" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="S23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T23" t="inlineStr">
-        <is>
-          <t>79.6</t>
-        </is>
-      </c>
-      <c r="U23" t="inlineStr">
-        <is>
-          <t>80.8</t>
-        </is>
-      </c>
-      <c r="V23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="W23" t="inlineStr">
-        <is>
-          <t>-4.04</t>
-        </is>
-      </c>
-      <c r="X23" t="inlineStr">
-        <is>
-          <t>16.34</t>
-        </is>
-      </c>
-      <c r="Y23" t="inlineStr">
-        <is>
-          <t>2025-11-14</t>
-        </is>
-      </c>
-      <c r="Z23" t="inlineStr">
-        <is>
-          <t>21.99</t>
-        </is>
-      </c>
-      <c r="AA23" t="inlineStr">
-        <is>
-          <t>-4.91</t>
-        </is>
-      </c>
-      <c r="AB23" t="inlineStr">
-        <is>
-          <t>False</t>
-        </is>
-      </c>
-      <c r="AC23" t="inlineStr"/>
-      <c r="AD23" t="inlineStr">
-        <is>
-          <t>209</t>
-        </is>
-      </c>
-      <c r="AE23" t="inlineStr">
-        <is>
-          <t>16281</t>
-        </is>
-      </c>
-      <c r="AF23" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="AG23" t="inlineStr">
-        <is>
-          <t>22.35</t>
-        </is>
-      </c>
-      <c r="AH23" t="inlineStr">
-        <is>
-          <t>-5.28</t>
-        </is>
-      </c>
-      <c r="AI23" t="inlineStr">
-        <is>
-          <t>-5.90</t>
-        </is>
-      </c>
-      <c r="AJ23" t="inlineStr">
-        <is>
-          <t>11.39</t>
-        </is>
-      </c>
-      <c r="AK23" t="inlineStr">
-        <is>
-          <t>19.46</t>
-        </is>
-      </c>
-      <c r="AL23" t="inlineStr">
-        <is>
-          <t>105.36</t>
-        </is>
-      </c>
-      <c r="AM23" t="n">
-        <v>111.96</v>
-      </c>
-      <c r="AN23" t="n">
-        <v>100.52</v>
-      </c>
-      <c r="AO23" t="inlineStr">
-        <is>
-          <t>84.14</t>
-        </is>
-      </c>
-      <c r="AP23" t="inlineStr">
-        <is>
-          <t>-71.84</t>
-        </is>
-      </c>
-      <c r="AQ23" t="inlineStr">
-        <is>
-          <t>0.91</t>
-        </is>
-      </c>
-      <c r="AR23" t="inlineStr">
-        <is>
-          <t>3.22</t>
-        </is>
-      </c>
-      <c r="AS23" t="inlineStr">
-        <is>
-          <t>9.92</t>
-        </is>
-      </c>
-      <c r="AT23" t="inlineStr">
-        <is>
-          <t>-67.57</t>
-        </is>
-      </c>
-      <c r="AU23" t="inlineStr">
-        <is>
-          <t>2025/09/23</t>
-        </is>
-      </c>
-      <c r="AV23" t="inlineStr">
-        <is>
-          <t>1904892357.987857</t>
-        </is>
-      </c>
-      <c r="AW23" t="inlineStr">
-        <is>
-          <t>7366534520.0</t>
-        </is>
-      </c>
-      <c r="AX23" t="n">
-        <v>3862957422</v>
-      </c>
-      <c r="AY23" t="inlineStr">
-        <is>
-          <t>4011436058.8</t>
-        </is>
-      </c>
-      <c r="AZ23" t="n">
-        <v>7171595467.56</v>
-      </c>
-      <c r="BA23" t="inlineStr">
-        <is>
-          <t>-148478636</t>
-        </is>
-      </c>
-      <c r="BB23" t="inlineStr">
-        <is>
-          <t>-625350482.9431659</t>
-        </is>
-      </c>
-      <c r="BC23" t="inlineStr">
-        <is>
-          <t>-379050437.0805759</t>
-        </is>
-      </c>
-      <c r="BD23" t="inlineStr">
-        <is>
-          <t>7366534520.0</t>
-        </is>
-      </c>
-      <c r="BE23" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF23" t="inlineStr">
-        <is>
-          <t>55.3</t>
-        </is>
-      </c>
-      <c r="BG23" t="inlineStr">
-        <is>
-          <t>2025/08/11</t>
-        </is>
-      </c>
-      <c r="BH23" t="inlineStr">
-        <is>
-          <t>80.47</t>
-        </is>
-      </c>
-      <c r="BI23" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BJ23" t="inlineStr">
-        <is>
-          <t>東元</t>
-        </is>
-      </c>
-      <c r="BK23" t="inlineStr">
-        <is>
-          <t>電機機械</t>
-        </is>
-      </c>
-      <c r="BL23" t="inlineStr">
-        <is>
-          <t>上市</t>
-        </is>
-      </c>
-      <c r="BM23" t="inlineStr">
-        <is>
-          <t>0.75</t>
-        </is>
-      </c>
-      <c r="BN23" t="inlineStr">
-        <is>
-          <t>-4.506561377619261</t>
-        </is>
-      </c>
-      <c r="BO23" t="inlineStr">
-        <is>
-          <t>17.0797647787938</t>
-        </is>
-      </c>
-      <c r="BP23" t="inlineStr">
-        <is>
-          <t>5.983401519253764</t>
-        </is>
-      </c>
-      <c r="BQ23" t="inlineStr">
-        <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
-        </is>
-      </c>
-      <c r="BR23" t="inlineStr">
-        <is>
-          <t>價-量-</t>
-        </is>
-      </c>
-      <c r="BS23" t="inlineStr">
-        <is>
-          <t>2.67</t>
-        </is>
-      </c>
-      <c r="BT23" t="inlineStr">
-        <is>
-          <t>2.51</t>
-        </is>
-      </c>
-      <c r="BU23" t="inlineStr">
-        <is>
-          <t>6.21</t>
-        </is>
-      </c>
-      <c r="BV23" t="inlineStr">
-        <is>
-          <t>38.13</t>
-        </is>
-      </c>
-      <c r="BW23" t="inlineStr">
-        <is>
-          <t>24.44%</t>
-        </is>
-      </c>
-      <c r="BX23" t="inlineStr">
-        <is>
-          <t>11.24%</t>
-        </is>
-      </c>
-      <c r="BY23" t="inlineStr">
-        <is>
-          <t>41.28</t>
-        </is>
-      </c>
-      <c r="BZ23" t="inlineStr">
-        <is>
-          <t>208414</t>
-        </is>
-      </c>
-      <c r="CA23" t="inlineStr">
-        <is>
-          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
-        </is>
-      </c>
-      <c r="CB23" t="inlineStr">
-        <is>
-          <t>東元-電機機械-上市</t>
-        </is>
-      </c>
-      <c r="CC23" t="inlineStr">
-        <is>
-          <t>電機機械右上上市</t>
-        </is>
-      </c>
-      <c r="CD23" t="inlineStr">
-        <is>
-          <t>104.0</t>
-        </is>
-      </c>
-      <c r="CE23" t="inlineStr">
-        <is>
-          <t>105.0</t>
-        </is>
-      </c>
-      <c r="CF23" t="inlineStr">
-        <is>
-          <t>99.5</t>
-        </is>
-      </c>
-      <c r="CG23" t="inlineStr">
-        <is>
-          <t>99.8</t>
-        </is>
-      </c>
-      <c r="CH23" t="inlineStr">
-        <is>
-          <t>37.41</t>
-        </is>
-      </c>
-      <c r="CI23" t="inlineStr">
-        <is>
-          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
-        </is>
-      </c>
-      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -425,7 +425,7 @@
     <outlinePr summaryBelow="1" summaryRight="1"/>
     <pageSetUpPr/>
   </sheetPr>
-  <dimension ref="A1:CJ13"/>
+  <dimension ref="A1:CJ23"/>
   <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
   <sheetData>
     <row r="1">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>17532.398</t>
+          <t>20318.111</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,7 +898,7 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>989.0</t>
         </is>
       </c>
       <c r="G2" t="inlineStr">
@@ -913,17 +913,17 @@
       </c>
       <c r="I2" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J2" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="K2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="L2" t="inlineStr">
@@ -933,77 +933,77 @@
       </c>
       <c r="M2" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N2" t="inlineStr">
+      <c r="P2" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q2" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
+        <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="T2" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
+      <c r="U2" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T2" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U2" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
         <is>
-          <t>-4.14</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X2" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>81.42</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>940.4</t>
+          <t>956.2</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>941.9</v>
+        <v>942.6</v>
       </c>
       <c r="AN2" t="n">
-        <v>954.48</v>
+        <v>957.54</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>860.81</t>
+          <t>865.41</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>83.10</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-110.32</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>16856373921.0</t>
+          <t>20108685563.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>10663188933.6</v>
+        <v>12769117326</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>12525016590.0</t>
+          <t>13300513877.8</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>14016406079.92</v>
+        <v>14242798853.4</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-1861827656</t>
+          <t>-531396551</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-290069044.435629</t>
+          <t>-195582216.5249392</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>-299371260.1784668</t>
+          <t>324095336.9838543</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>16856373921.0</t>
+          <t>20108685563.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>157.41</t>
+          <t>161.64</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>936.0</t>
+          <t>988.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>974.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>989.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1303,7 +1303,7 @@
     <row r="3">
       <c r="A3" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B3" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>8363.698</t>
+          <t>17532.398</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,17 +1338,17 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>4.21</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-10.38</t>
+          <t>-14.86</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
@@ -1363,49 +1363,49 @@
       </c>
       <c r="M3" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N3" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O3" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N3" t="inlineStr">
+      <c r="P3" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O3" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P3" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q3" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S3" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T3" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R3" t="inlineStr">
+      <c r="U3" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S3" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T3" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U3" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V3" t="inlineStr">
         <is>
           <t>0</t>
@@ -1413,27 +1413,27 @@
       </c>
       <c r="W3" t="inlineStr">
         <is>
-          <t>-8.18</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X3" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,73 +1444,73 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
         <is>
-          <t>63.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.42</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>924.4</t>
+          <t>940.4</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>942.4</v>
+        <v>941.9</v>
       </c>
       <c r="AN3" t="n">
-        <v>951.84</v>
+        <v>954.48</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>856.55</t>
+          <t>860.81</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>-33.12</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-6.69</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.82</t>
+          <t>-110.32</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,43 +1530,43 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>7820188511.0</t>
+          <t>16856373921.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>10674153029.2</v>
+        <v>10663188933.6</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>11910356191.8</t>
+          <t>12525016590.0</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>13939434751.06</v>
+        <v>14016406079.92</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1236203162</t>
+          <t>-1861827656</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-288377732.4823858</t>
+          <t>-290069044.435629</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-830884035.1896954</t>
+          <t>-299371260.1784668</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>7820188511.0</t>
+          <t>16856373921.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>146.56</t>
+          <t>157.41</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,22 +1631,22 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>936.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8820.259</t>
+          <t>8363.698</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>3.19</t>
+          <t>5.76</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-10.38</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1793,49 +1793,49 @@
       </c>
       <c r="M4" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N4" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O4" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N4" t="inlineStr">
+      <c r="P4" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O4" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P4" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q4" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S4" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T4" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R4" t="inlineStr">
+      <c r="U4" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S4" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T4" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U4" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V4" t="inlineStr">
         <is>
           <t>0</t>
@@ -1843,27 +1843,27 @@
       </c>
       <c r="W4" t="inlineStr">
         <is>
-          <t>-7.19</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X4" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>80.33</t>
+          <t>63.93</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>63.91</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>917.0</t>
+          <t>924.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>945.55</v>
+        <v>942.4</v>
       </c>
       <c r="AN4" t="n">
-        <v>949.92</v>
+        <v>951.84</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>852.31</t>
+          <t>856.55</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-56.69</t>
+          <t>-33.12</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-109.92</t>
+          <t>-110.82</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>12272712875.4</v>
+        <v>10674153029.2</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>12946611618.9</t>
+          <t>11910356191.8</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13990667425.04</v>
+        <v>13939434751.06</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-673898743</t>
+          <t>-1236203162</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-189740222.8992386</t>
+          <t>-288377732.4823858</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-592350847.1632462</t>
+          <t>-830884035.1896954</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>149.21</t>
+          <t>146.56</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>955.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>959.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2163,7 +2163,7 @@
     <row r="5">
       <c r="A5" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B5" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>11426.896</t>
+          <t>8820.259</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>2.88</t>
+          <t>4.75</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2223,49 +2223,49 @@
       </c>
       <c r="M5" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N5" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O5" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N5" t="inlineStr">
+      <c r="P5" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O5" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P5" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q5" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S5" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T5" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R5" t="inlineStr">
+      <c r="U5" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S5" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T5" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U5" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V5" t="inlineStr">
         <is>
           <t>0</t>
@@ -2273,27 +2273,27 @@
       </c>
       <c r="W5" t="inlineStr">
         <is>
-          <t>-6.90</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X5" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>39.54</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>85.25</t>
+          <t>80.33</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>63.91</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>919.4</t>
+          <t>917.0</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>948.95</v>
+        <v>945.55</v>
       </c>
       <c r="AN5" t="n">
-        <v>947.8200000000001</v>
+        <v>949.92</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>847.89</t>
+          <t>852.31</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-56.69</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-108.52</t>
+          <t>-109.92</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>13777681330.2</v>
+        <v>12272712875.4</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>13184190874.5</t>
+          <t>12946611618.9</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>14165986897.28</v>
+        <v>13990667425.04</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>593490455</t>
+          <t>-673898743</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-116538291.2148735</t>
+          <t>-189740222.8992386</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-288049536.2624874</t>
+          <t>-592350847.1632462</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>149.21</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>955.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>950.0</t>
+          <t>959.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>10504.174</t>
+          <t>11426.896</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>6.47</t>
+          <t>4.45</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2653,49 +2653,49 @@
       </c>
       <c r="M6" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N6" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O6" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N6" t="inlineStr">
+      <c r="P6" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O6" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P6" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q6" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S6" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T6" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R6" t="inlineStr">
+      <c r="U6" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S6" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T6" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U6" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V6" t="inlineStr">
         <is>
           <t>0</t>
@@ -2703,27 +2703,27 @@
       </c>
       <c r="W6" t="inlineStr">
         <is>
-          <t>-10.34</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X6" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>39.54</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>909.2</t>
+          <t>919.4</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>954.7</v>
+        <v>948.95</v>
       </c>
       <c r="AN6" t="n">
-        <v>945.54</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>843.16</t>
+          <t>847.89</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-265.70</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-108.52</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13831910429.6</v>
+        <v>13777681330.2</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13509805904.0</t>
+          <t>13184190874.5</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>14413977761.06</v>
+        <v>14165986897.28</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>322104525</t>
+          <t>593490455</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-85354428.47894374</t>
+          <t>-116538291.2148735</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-94238805.57345963</t>
+          <t>-288049536.2624874</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>140.74</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>926.0</t>
+          <t>950.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>899.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>18856.003</t>
+          <t>10504.174</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>8.22</t>
+          <t>7.99</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3083,49 +3083,49 @@
       </c>
       <c r="M7" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N7" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O7" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N7" t="inlineStr">
+      <c r="P7" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O7" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P7" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q7" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S7" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T7" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R7" t="inlineStr">
+      <c r="U7" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S7" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T7" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U7" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V7" t="inlineStr">
         <is>
           <t>0</t>
@@ -3133,27 +3133,27 @@
       </c>
       <c r="W7" t="inlineStr">
         <is>
-          <t>-12.02</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X7" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>65.24</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>909.2</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>962.95</v>
+        <v>954.7</v>
       </c>
       <c r="AN7" t="n">
-        <v>944.08</v>
+        <v>945.54</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>838.41</t>
+          <t>843.16</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-940.86</t>
+          <t>-265.70</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-102.03</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>14386844246.4</v>
+        <v>13831910429.6</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13675683609.2</t>
+          <t>13509805904.0</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>14618581897.64</v>
+        <v>14413977761.06</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>711160637</t>
+          <t>322104525</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-83739087.18903175</t>
+          <t>-85354428.47894374</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>306359263.681345</t>
+          <t>-94238805.57345963</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>136.24</t>
+          <t>140.74</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>904.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>909.0</t>
+          <t>926.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>899.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>8.02</t>
+          <t>9.71</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3513,49 +3513,49 @@
       </c>
       <c r="M8" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N8" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O8" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N8" t="inlineStr">
+      <c r="P8" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O8" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P8" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q8" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S8" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T8" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R8" t="inlineStr">
+      <c r="U8" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S8" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T8" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U8" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V8" t="inlineStr">
         <is>
           <t>0</t>
@@ -3563,27 +3563,27 @@
       </c>
       <c r="W8" t="inlineStr">
         <is>
-          <t>-11.82</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X8" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,17 +3594,17 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
@@ -3614,53 +3614,53 @@
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>971.8</v>
+        <v>962.95</v>
       </c>
       <c r="AN8" t="n">
-        <v>941.9</v>
+        <v>944.08</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>13146559354.4</v>
+        <v>14386844246.4</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>14614553602.28</v>
+        <v>14618581897.64</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3791,12 +3791,12 @@
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>1.95</t>
+          <t>9.5</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3943,49 +3943,49 @@
       </c>
       <c r="M9" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N9" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O9" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N9" t="inlineStr">
+      <c r="P9" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O9" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P9" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q9" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S9" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T9" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R9" t="inlineStr">
+      <c r="U9" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S9" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T9" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U9" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V9" t="inlineStr">
         <is>
           <t>0</t>
@@ -3993,27 +3993,27 @@
       </c>
       <c r="W9" t="inlineStr">
         <is>
-          <t>-6.01</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X9" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,73 +4024,73 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>977.55</v>
+        <v>971.8</v>
       </c>
       <c r="AN9" t="n">
-        <v>938.52</v>
+        <v>941.9</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13620510362.4</v>
+        <v>13146559354.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>14466055493.78</v>
+        <v>14614553602.28</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4216,17 +4216,17 @@
       </c>
       <c r="BR9" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>8.12</t>
+          <t>3.54</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4373,49 +4373,49 @@
       </c>
       <c r="M10" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N10" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O10" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N10" t="inlineStr">
+      <c r="P10" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O10" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P10" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q10" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S10" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T10" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R10" t="inlineStr">
+      <c r="U10" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S10" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T10" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U10" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V10" t="inlineStr">
         <is>
           <t>0</t>
@@ -4423,27 +4423,27 @@
       </c>
       <c r="W10" t="inlineStr">
         <is>
-          <t>-11.92</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X10" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>980.85</v>
+        <v>977.55</v>
       </c>
       <c r="AN10" t="n">
-        <v>933.96</v>
+        <v>938.52</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>12590700418.8</v>
+        <v>13620510362.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>14368721493.28</v>
+        <v>14466055493.78</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4641,22 +4641,22 @@
       </c>
       <c r="BQ10" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價漲量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>7.71</t>
+          <t>9.61</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4803,49 +4803,49 @@
       </c>
       <c r="M11" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N11" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O11" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N11" t="inlineStr">
+      <c r="P11" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O11" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P11" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q11" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S11" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T11" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R11" t="inlineStr">
+      <c r="U11" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S11" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T11" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U11" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V11" t="inlineStr">
         <is>
           <t>0</t>
@@ -4853,27 +4853,27 @@
       </c>
       <c r="W11" t="inlineStr">
         <is>
-          <t>-11.53</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X11" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,12 +4884,12 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
@@ -4904,53 +4904,53 @@
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>987.15</v>
+        <v>980.85</v>
       </c>
       <c r="AN11" t="n">
-        <v>929.9</v>
+        <v>933.96</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>13187701378.4</v>
+        <v>12590700418.8</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>14292572173.18</v>
+        <v>14368721493.28</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-0.64</t>
+          <t>-1.99</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>11523.207</t>
+          <t>13615.098</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>5.86</t>
+          <t>9.2</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.35</t>
+          <t>2.04</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>-1.67</t>
+          <t>5.17</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5233,49 +5233,49 @@
       </c>
       <c r="M12" t="inlineStr">
         <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N12" t="inlineStr">
+        <is>
+          <t>2025-12-03 00:00:00</t>
+        </is>
+      </c>
+      <c r="O12" t="inlineStr">
+        <is>
           <t>2025-10-07 00:00:00</t>
         </is>
       </c>
-      <c r="N12" t="inlineStr">
+      <c r="P12" t="inlineStr">
         <is>
           <t>2025-10-20 00:00:00</t>
         </is>
       </c>
-      <c r="O12" t="inlineStr">
-        <is>
-          <t>2025-09-09 00:00:00</t>
-        </is>
-      </c>
-      <c r="P12" t="inlineStr">
-        <is>
-          <t>2025-09-26 00:00:00</t>
-        </is>
-      </c>
       <c r="Q12" t="inlineStr">
         <is>
+          <t>989.0</t>
+        </is>
+      </c>
+      <c r="R12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S12" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T12" t="inlineStr">
+        <is>
           <t>987.0</t>
         </is>
       </c>
-      <c r="R12" t="inlineStr">
+      <c r="U12" t="inlineStr">
         <is>
           <t>1015.0</t>
         </is>
       </c>
-      <c r="S12" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="T12" t="inlineStr">
-        <is>
-          <t>784.0</t>
-        </is>
-      </c>
-      <c r="U12" t="inlineStr">
-        <is>
-          <t>848.0</t>
-        </is>
-      </c>
       <c r="V12" t="inlineStr">
         <is>
           <t>0</t>
@@ -5283,27 +5283,27 @@
       </c>
       <c r="W12" t="inlineStr">
         <is>
-          <t>-9.75</t>
+          <t>0</t>
         </is>
       </c>
       <c r="X12" t="inlineStr">
         <is>
-          <t>16.39</t>
+          <t>-2.56</t>
         </is>
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-17</t>
+          <t>2025-11-18</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>39.87</t>
+          <t>47.11</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.28</t>
+          <t>-3.56</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>784</t>
+          <t>734</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>17532</t>
+          <t>20318</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.27</t>
+          <t>-3.67</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-5.57</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>7.29</t>
+          <t>6.16</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.67</t>
+          <t>13.54</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>947.0</t>
+          <t>932.2</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>993</v>
+        <v>987.15</v>
       </c>
       <c r="AN12" t="n">
-        <v>925.54</v>
+        <v>929.9</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>814.26</t>
+          <t>818.99</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-96.69</t>
+          <t>-137.65</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>0.55</t>
+          <t>-4.66</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>16.62</t>
+          <t>12.37</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-74.35</t>
+          <t>-80.92</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6497312325.358974</t>
+          <t>6530976217.278093</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>12964522972</v>
+        <v>13187701378.4</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>13184192924.4</t>
+          <t>12539817288.3</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>14209168625.62</v>
+        <v>14292572173.18</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>-219669952</t>
+          <t>647884090</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-149529915.9358163</t>
+          <t>-173190787.3056165</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-273240924.15588</t>
+          <t>-303325579.8395176</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>10709769939.0</t>
+          <t>12353712685.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>142.33</t>
+          <t>137.57</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.88</t>
+          <t>9.69</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.72</t>
+          <t>0.71</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>50.6</t>
+          <t>51.43</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34.7</t>
+          <t>34.53</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2527409</t>
+          <t>2568970</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>931.0</t>
+          <t>906.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>930.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>898.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5601,7 +5601,11 @@
       </c>
     </row>
     <row r="13">
-      <c r="A13" t="inlineStr"/>
+      <c r="A13" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
       <c r="B13" t="inlineStr">
         <is>
           <t>1504</t>
@@ -5609,42 +5613,42 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
+          <t>1.88</t>
+        </is>
+      </c>
+      <c r="D13" t="inlineStr">
+        <is>
+          <t>22425.724</t>
+        </is>
+      </c>
+      <c r="E13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F13" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="G13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H13" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="D13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="E13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="F13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="G13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H13" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>-2.68</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5654,37 +5658,37 @@
       </c>
       <c r="L13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>99.0</t>
         </is>
       </c>
       <c r="M13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-23 00:00:00</t>
         </is>
       </c>
       <c r="N13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-10-14 00:00:00</t>
         </is>
       </c>
       <c r="O13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-09 00:00:00</t>
         </is>
       </c>
       <c r="P13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-09-19 00:00:00</t>
         </is>
       </c>
       <c r="Q13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="R13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>104.0</t>
         </is>
       </c>
       <c r="S13" t="inlineStr">
@@ -5694,12 +5698,12 @@
       </c>
       <c r="T13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>79.6</t>
         </is>
       </c>
       <c r="U13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>80.8</t>
         </is>
       </c>
       <c r="V13" t="inlineStr">
@@ -5709,318 +5713,4618 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>16.34</t>
         </is>
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>False</t>
         </is>
       </c>
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>317</t>
+          <t>217</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>16763</t>
+          <t>22426</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
+          <t>14.41</t>
+        </is>
+      </c>
+      <c r="AG13" t="inlineStr">
+        <is>
+          <t>6.68</t>
+        </is>
+      </c>
+      <c r="AH13" t="inlineStr">
+        <is>
+          <t>-0.48</t>
+        </is>
+      </c>
+      <c r="AI13" t="inlineStr">
+        <is>
+          <t>-10.62</t>
+        </is>
+      </c>
+      <c r="AJ13" t="inlineStr">
+        <is>
+          <t>-5.69</t>
+        </is>
+      </c>
+      <c r="AK13" t="inlineStr">
+        <is>
+          <t>14.31</t>
+        </is>
+      </c>
+      <c r="AL13" t="inlineStr">
+        <is>
+          <t>87.02</t>
+        </is>
+      </c>
+      <c r="AM13" t="n">
+        <v>97.36</v>
+      </c>
+      <c r="AN13" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AO13" t="inlineStr">
+        <is>
+          <t>90.31</t>
+        </is>
+      </c>
+      <c r="AP13" t="inlineStr">
+        <is>
+          <t>-37.45</t>
+        </is>
+      </c>
+      <c r="AQ13" t="inlineStr">
+        <is>
+          <t>-5.33</t>
+        </is>
+      </c>
+      <c r="AR13" t="inlineStr">
+        <is>
+          <t>-3.88</t>
+        </is>
+      </c>
+      <c r="AS13" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT13" t="inlineStr">
+        <is>
+          <t>-139.07</t>
+        </is>
+      </c>
+      <c r="AU13" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV13" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW13" t="inlineStr">
+        <is>
+          <t>1953507738.0</t>
+        </is>
+      </c>
+      <c r="AX13" t="n">
+        <v>1808547588.4</v>
+      </c>
+      <c r="AY13" t="inlineStr">
+        <is>
+          <t>3414062816.4</t>
+        </is>
+      </c>
+      <c r="AZ13" t="n">
+        <v>6610661657.54</v>
+      </c>
+      <c r="BA13" t="inlineStr">
+        <is>
+          <t>-1605515228</t>
+        </is>
+      </c>
+      <c r="BB13" t="inlineStr">
+        <is>
+          <t>-389584858.462798</t>
+        </is>
+      </c>
+      <c r="BC13" t="inlineStr">
+        <is>
+          <t>-564576189.6084146</t>
+        </is>
+      </c>
+      <c r="BD13" t="inlineStr">
+        <is>
+          <t>1953507738.0</t>
+        </is>
+      </c>
+      <c r="BE13" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF13" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG13" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH13" t="inlineStr">
+        <is>
+          <t>56.60</t>
+        </is>
+      </c>
+      <c r="BI13" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ13" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK13" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL13" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM13" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN13" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO13" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP13" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ13" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR13" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS13" t="inlineStr">
+        <is>
+          <t>2.31</t>
+        </is>
+      </c>
+      <c r="BT13" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU13" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV13" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW13" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX13" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY13" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ13" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA13" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB13" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC13" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD13" t="inlineStr">
+        <is>
+          <t>85.2</t>
+        </is>
+      </c>
+      <c r="CE13" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="CF13" t="inlineStr">
+        <is>
+          <t>84.8</t>
+        </is>
+      </c>
+      <c r="CG13" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="CH13" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI13" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ13" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="14">
+      <c r="A14" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B14" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C14" t="inlineStr">
+        <is>
+          <t>-3.09</t>
+        </is>
+      </c>
+      <c r="D14" t="inlineStr">
+        <is>
+          <t>16762.955</t>
+        </is>
+      </c>
+      <c r="E14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F14" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="G14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H14" t="inlineStr">
+        <is>
+          <t>1.85</t>
+        </is>
+      </c>
+      <c r="I14" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J14" t="inlineStr">
+        <is>
+          <t>-33.22</t>
+        </is>
+      </c>
+      <c r="K14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L14" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M14" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N14" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O14" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P14" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q14" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R14" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T14" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U14" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W14" t="inlineStr">
+        <is>
+          <t>-18.27</t>
+        </is>
+      </c>
+      <c r="X14" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y14" t="inlineStr">
+        <is>
+          <t>2025-12-01</t>
+        </is>
+      </c>
+      <c r="Z14" t="inlineStr">
+        <is>
+          <t>5.06</t>
+        </is>
+      </c>
+      <c r="AA14" t="inlineStr">
+        <is>
+          <t>-2.59</t>
+        </is>
+      </c>
+      <c r="AB14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC14" t="inlineStr"/>
+      <c r="AD14" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE14" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF14" t="inlineStr">
+        <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AG13" t="inlineStr">
+      <c r="AG14" t="inlineStr">
+        <is>
+          <t>6.84</t>
+        </is>
+      </c>
+      <c r="AH14" t="inlineStr">
+        <is>
+          <t>-2.75</t>
+        </is>
+      </c>
+      <c r="AI14" t="inlineStr">
+        <is>
+          <t>-11.46</t>
+        </is>
+      </c>
+      <c r="AJ14" t="inlineStr">
+        <is>
+          <t>-4.39</t>
+        </is>
+      </c>
+      <c r="AK14" t="inlineStr">
+        <is>
+          <t>14.83</t>
+        </is>
+      </c>
+      <c r="AL14" t="inlineStr">
+        <is>
+          <t>87.4</t>
+        </is>
+      </c>
+      <c r="AM14" t="n">
+        <v>98.70999999999999</v>
+      </c>
+      <c r="AN14" t="n">
+        <v>103.24</v>
+      </c>
+      <c r="AO14" t="inlineStr">
+        <is>
+          <t>89.91</t>
+        </is>
+      </c>
+      <c r="AP14" t="inlineStr">
+        <is>
+          <t>-49.64</t>
+        </is>
+      </c>
+      <c r="AQ14" t="inlineStr">
+        <is>
+          <t>-5.26</t>
+        </is>
+      </c>
+      <c r="AR14" t="inlineStr">
+        <is>
+          <t>-3.51</t>
+        </is>
+      </c>
+      <c r="AS14" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT14" t="inlineStr">
+        <is>
+          <t>-135.42</t>
+        </is>
+      </c>
+      <c r="AU14" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV14" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW14" t="inlineStr">
+        <is>
+          <t>1432793005.0</t>
+        </is>
+      </c>
+      <c r="AX14" t="n">
+        <v>2354299255.4</v>
+      </c>
+      <c r="AY14" t="inlineStr">
+        <is>
+          <t>3525608023.4</t>
+        </is>
+      </c>
+      <c r="AZ14" t="n">
+        <v>6627710000.74</v>
+      </c>
+      <c r="BA14" t="inlineStr">
+        <is>
+          <t>-1171308768</t>
+        </is>
+      </c>
+      <c r="BB14" t="inlineStr">
+        <is>
+          <t>-357768252.7999586</t>
+        </is>
+      </c>
+      <c r="BC14" t="inlineStr">
+        <is>
+          <t>-549589262.0901175</t>
+        </is>
+      </c>
+      <c r="BD14" t="inlineStr">
+        <is>
+          <t>1432793005.0</t>
+        </is>
+      </c>
+      <c r="BE14" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF14" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG14" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH14" t="inlineStr">
+        <is>
+          <t>53.71</t>
+        </is>
+      </c>
+      <c r="BI14" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ14" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK14" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL14" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM14" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN14" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO14" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP14" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ14" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR14" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS14" t="inlineStr">
+        <is>
+          <t>2.27</t>
+        </is>
+      </c>
+      <c r="BT14" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU14" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV14" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW14" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX14" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY14" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ14" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA14" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB14" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC14" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD14" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CE14" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CF14" t="inlineStr">
+        <is>
+          <t>84.7</t>
+        </is>
+      </c>
+      <c r="CG14" t="inlineStr">
+        <is>
+          <t>85.0</t>
+        </is>
+      </c>
+      <c r="CH14" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI14" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ14" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="15">
+      <c r="A15" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B15" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C15" t="inlineStr">
+        <is>
+          <t>-1.01</t>
+        </is>
+      </c>
+      <c r="D15" t="inlineStr">
+        <is>
+          <t>16281.325</t>
+        </is>
+      </c>
+      <c r="E15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F15" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="G15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H15" t="inlineStr">
+        <is>
+          <t>-1.27</t>
+        </is>
+      </c>
+      <c r="I15" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J15" t="inlineStr">
+        <is>
+          <t>15.59</t>
+        </is>
+      </c>
+      <c r="K15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L15" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M15" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N15" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O15" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P15" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q15" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R15" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T15" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U15" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W15" t="inlineStr">
+        <is>
+          <t>-15.67</t>
+        </is>
+      </c>
+      <c r="X15" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y15" t="inlineStr">
+        <is>
+          <t>2025-11-28</t>
+        </is>
+      </c>
+      <c r="Z15" t="inlineStr">
+        <is>
+          <t>4.92</t>
+        </is>
+      </c>
+      <c r="AA15" t="inlineStr">
+        <is>
+          <t>-0.79</t>
+        </is>
+      </c>
+      <c r="AB15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC15" t="inlineStr"/>
+      <c r="AD15" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE15" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF15" t="inlineStr">
+        <is>
+          <t>5.62</t>
+        </is>
+      </c>
+      <c r="AG15" t="inlineStr">
+        <is>
+          <t>6.84</t>
+        </is>
+      </c>
+      <c r="AH15" t="inlineStr">
+        <is>
+          <t>-1.44</t>
+        </is>
+      </c>
+      <c r="AI15" t="inlineStr">
+        <is>
+          <t>-11.23</t>
+        </is>
+      </c>
+      <c r="AJ15" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="AK15" t="inlineStr">
+        <is>
+          <t>15.39</t>
+        </is>
+      </c>
+      <c r="AL15" t="inlineStr">
+        <is>
+          <t>88.98</t>
+        </is>
+      </c>
+      <c r="AM15" t="n">
+        <v>100.24</v>
+      </c>
+      <c r="AN15" t="n">
+        <v>103.28</v>
+      </c>
+      <c r="AO15" t="inlineStr">
+        <is>
+          <t>89.51</t>
+        </is>
+      </c>
+      <c r="AP15" t="inlineStr">
+        <is>
+          <t>-60.15</t>
+        </is>
+      </c>
+      <c r="AQ15" t="inlineStr">
+        <is>
+          <t>-4.93</t>
+        </is>
+      </c>
+      <c r="AR15" t="inlineStr">
+        <is>
+          <t>-3.08</t>
+        </is>
+      </c>
+      <c r="AS15" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT15" t="inlineStr">
+        <is>
+          <t>-131.02</t>
+        </is>
+      </c>
+      <c r="AU15" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV15" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW15" t="inlineStr">
+        <is>
+          <t>1429040476.0</t>
+        </is>
+      </c>
+      <c r="AX15" t="n">
+        <v>4370895798.6</v>
+      </c>
+      <c r="AY15" t="inlineStr">
+        <is>
+          <t>3781268811.0</t>
+        </is>
+      </c>
+      <c r="AZ15" t="n">
+        <v>6680203633.36</v>
+      </c>
+      <c r="BA15" t="inlineStr">
+        <is>
+          <t>589626987</t>
+        </is>
+      </c>
+      <c r="BB15" t="inlineStr">
+        <is>
+          <t>-322891705.6562934</t>
+        </is>
+      </c>
+      <c r="BC15" t="inlineStr">
+        <is>
+          <t>-452760313.4536171</t>
+        </is>
+      </c>
+      <c r="BD15" t="inlineStr">
+        <is>
+          <t>1429040476.0</t>
+        </is>
+      </c>
+      <c r="BE15" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF15" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG15" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH15" t="inlineStr">
+        <is>
+          <t>58.59</t>
+        </is>
+      </c>
+      <c r="BI15" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ15" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK15" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL15" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM15" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN15" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO15" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP15" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ15" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR15" t="inlineStr">
+        <is>
+          <t>價漲量縮</t>
+        </is>
+      </c>
+      <c r="BS15" t="inlineStr">
+        <is>
+          <t>2.34</t>
+        </is>
+      </c>
+      <c r="BT15" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU15" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV15" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW15" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX15" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY15" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ15" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA15" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB15" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC15" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD15" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="CE15" t="inlineStr">
+        <is>
+          <t>89.0</t>
+        </is>
+      </c>
+      <c r="CF15" t="inlineStr">
+        <is>
+          <t>87.1</t>
+        </is>
+      </c>
+      <c r="CG15" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="CH15" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI15" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ15" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="16">
+      <c r="A16" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B16" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C16" t="inlineStr">
+        <is>
+          <t>1.6</t>
+        </is>
+      </c>
+      <c r="D16" t="inlineStr">
+        <is>
+          <t>17538.055</t>
+        </is>
+      </c>
+      <c r="E16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F16" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="G16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H16" t="inlineStr">
+        <is>
+          <t>-2.31</t>
+        </is>
+      </c>
+      <c r="I16" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J16" t="inlineStr">
+        <is>
+          <t>7.23</t>
+        </is>
+      </c>
+      <c r="K16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L16" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M16" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N16" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O16" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P16" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q16" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R16" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T16" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U16" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W16" t="inlineStr">
+        <is>
+          <t>-14.81</t>
+        </is>
+      </c>
+      <c r="X16" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y16" t="inlineStr">
+        <is>
+          <t>2025-11-27</t>
+        </is>
+      </c>
+      <c r="Z16" t="inlineStr">
+        <is>
+          <t>5.30</t>
+        </is>
+      </c>
+      <c r="AA16" t="inlineStr">
+        <is>
+          <t>2.20</t>
+        </is>
+      </c>
+      <c r="AB16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC16" t="inlineStr"/>
+      <c r="AD16" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE16" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF16" t="inlineStr">
+        <is>
+          <t>14.89</t>
+        </is>
+      </c>
+      <c r="AG16" t="inlineStr">
+        <is>
+          <t>4.96</t>
+        </is>
+      </c>
+      <c r="AH16" t="inlineStr">
+        <is>
+          <t>-1.38</t>
+        </is>
+      </c>
+      <c r="AI16" t="inlineStr">
+        <is>
+          <t>-11.64</t>
+        </is>
+      </c>
+      <c r="AJ16" t="inlineStr">
+        <is>
+          <t>-1.57</t>
+        </is>
+      </c>
+      <c r="AK16" t="inlineStr">
+        <is>
+          <t>15.94</t>
+        </is>
+      </c>
+      <c r="AL16" t="inlineStr">
+        <is>
+          <t>89.84</t>
+        </is>
+      </c>
+      <c r="AM16" t="n">
+        <v>101.68</v>
+      </c>
+      <c r="AN16" t="n">
+        <v>103.29</v>
+      </c>
+      <c r="AO16" t="inlineStr">
+        <is>
+          <t>89.09</t>
+        </is>
+      </c>
+      <c r="AP16" t="inlineStr">
+        <is>
+          <t>-80.19</t>
+        </is>
+      </c>
+      <c r="AQ16" t="inlineStr">
+        <is>
+          <t>-4.71</t>
+        </is>
+      </c>
+      <c r="AR16" t="inlineStr">
+        <is>
+          <t>-2.61</t>
+        </is>
+      </c>
+      <c r="AS16" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT16" t="inlineStr">
+        <is>
+          <t>-126.36</t>
+        </is>
+      </c>
+      <c r="AU16" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV16" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW16" t="inlineStr">
+        <is>
+          <t>1543850905.0</t>
+        </is>
+      </c>
+      <c r="AX16" t="n">
+        <v>4691522022.2</v>
+      </c>
+      <c r="AY16" t="inlineStr">
+        <is>
+          <t>4375018215.4</t>
+        </is>
+      </c>
+      <c r="AZ16" t="n">
+        <v>6753332147.84</v>
+      </c>
+      <c r="BA16" t="inlineStr">
+        <is>
+          <t>316503806</t>
+        </is>
+      </c>
+      <c r="BB16" t="inlineStr">
+        <is>
+          <t>-299279231.5113254</t>
+        </is>
+      </c>
+      <c r="BC16" t="inlineStr">
+        <is>
+          <t>-297861176.0995588</t>
+        </is>
+      </c>
+      <c r="BD16" t="inlineStr">
+        <is>
+          <t>1543850905.0</t>
+        </is>
+      </c>
+      <c r="BE16" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF16" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG16" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH16" t="inlineStr">
+        <is>
+          <t>60.22</t>
+        </is>
+      </c>
+      <c r="BI16" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ16" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK16" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL16" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM16" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN16" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO16" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP16" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ16" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR16" t="inlineStr">
+        <is>
+          <t>價-量縮</t>
+        </is>
+      </c>
+      <c r="BS16" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="BT16" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU16" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV16" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW16" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX16" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY16" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ16" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA16" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB16" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC16" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD16" t="inlineStr">
+        <is>
+          <t>87.5</t>
+        </is>
+      </c>
+      <c r="CE16" t="inlineStr">
+        <is>
+          <t>88.7</t>
+        </is>
+      </c>
+      <c r="CF16" t="inlineStr">
+        <is>
+          <t>86.6</t>
+        </is>
+      </c>
+      <c r="CG16" t="inlineStr">
+        <is>
+          <t>88.6</t>
+        </is>
+      </c>
+      <c r="CH16" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI16" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ16" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="17">
+      <c r="A17" t="inlineStr">
+        <is>
+          <t>【e】</t>
+        </is>
+      </c>
+      <c r="B17" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C17" t="inlineStr">
+        <is>
+          <t>-1.46</t>
+        </is>
+      </c>
+      <c r="D17" t="inlineStr">
+        <is>
+          <t>30647.12</t>
+        </is>
+      </c>
+      <c r="E17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F17" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="G17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H17" t="inlineStr">
+        <is>
+          <t>-0.69</t>
+        </is>
+      </c>
+      <c r="I17" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J17" t="inlineStr">
+        <is>
+          <t>5.79</t>
+        </is>
+      </c>
+      <c r="K17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L17" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M17" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N17" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O17" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P17" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q17" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R17" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T17" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U17" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W17" t="inlineStr">
+        <is>
+          <t>-16.15</t>
+        </is>
+      </c>
+      <c r="X17" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y17" t="inlineStr">
+        <is>
+          <t>2025-11-26</t>
+        </is>
+      </c>
+      <c r="Z17" t="inlineStr">
+        <is>
+          <t>9.26</t>
+        </is>
+      </c>
+      <c r="AA17" t="inlineStr">
+        <is>
+          <t>-1.72</t>
+        </is>
+      </c>
+      <c r="AB17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC17" t="inlineStr"/>
+      <c r="AD17" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE17" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF17" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AH13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AI13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AJ13" t="inlineStr">
+      <c r="AG17" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="AH17" t="inlineStr">
+        <is>
+          <t>-4.53</t>
+        </is>
+      </c>
+      <c r="AI17" t="inlineStr">
+        <is>
+          <t>-11.38</t>
+        </is>
+      </c>
+      <c r="AJ17" t="inlineStr">
+        <is>
+          <t>-0.23</t>
+        </is>
+      </c>
+      <c r="AK17" t="inlineStr">
+        <is>
+          <t>16.49</t>
+        </is>
+      </c>
+      <c r="AL17" t="inlineStr">
+        <is>
+          <t>91.34</t>
+        </is>
+      </c>
+      <c r="AM17" t="n">
+        <v>103.07</v>
+      </c>
+      <c r="AN17" t="n">
+        <v>103.31</v>
+      </c>
+      <c r="AO17" t="inlineStr">
+        <is>
+          <t>88.68</t>
+        </is>
+      </c>
+      <c r="AP17" t="inlineStr">
+        <is>
+          <t>-113.22</t>
+        </is>
+      </c>
+      <c r="AQ17" t="inlineStr">
+        <is>
+          <t>-4.46</t>
+        </is>
+      </c>
+      <c r="AR17" t="inlineStr">
+        <is>
+          <t>-2.09</t>
+        </is>
+      </c>
+      <c r="AS17" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT17" t="inlineStr">
+        <is>
+          <t>-121.07</t>
+        </is>
+      </c>
+      <c r="AU17" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV17" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW17" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
+      </c>
+      <c r="AX17" t="n">
+        <v>5000685349.4</v>
+      </c>
+      <c r="AY17" t="inlineStr">
+        <is>
+          <t>4727097624.7</t>
+        </is>
+      </c>
+      <c r="AZ17" t="n">
+        <v>6863428946.3</v>
+      </c>
+      <c r="BA17" t="inlineStr">
+        <is>
+          <t>273587724</t>
+        </is>
+      </c>
+      <c r="BB17" t="inlineStr">
+        <is>
+          <t>-299537059.7680103</t>
+        </is>
+      </c>
+      <c r="BC17" t="inlineStr">
+        <is>
+          <t>-78239912.41163445</t>
+        </is>
+      </c>
+      <c r="BD17" t="inlineStr">
+        <is>
+          <t>2683545818.0</t>
+        </is>
+      </c>
+      <c r="BE17" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF17" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG17" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH17" t="inlineStr">
+        <is>
+          <t>57.69</t>
+        </is>
+      </c>
+      <c r="BI17" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ17" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK17" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL17" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM17" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN17" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO17" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP17" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ17" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR17" t="inlineStr">
+        <is>
+          <t>價漲量-</t>
+        </is>
+      </c>
+      <c r="BS17" t="inlineStr">
+        <is>
+          <t>2.33</t>
+        </is>
+      </c>
+      <c r="BT17" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU17" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV17" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW17" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX17" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY17" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ17" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA17" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB17" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC17" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD17" t="inlineStr">
+        <is>
+          <t>88.9</t>
+        </is>
+      </c>
+      <c r="CE17" t="inlineStr">
+        <is>
+          <t>89.2</t>
+        </is>
+      </c>
+      <c r="CF17" t="inlineStr">
+        <is>
+          <t>86.7</t>
+        </is>
+      </c>
+      <c r="CG17" t="inlineStr">
+        <is>
+          <t>87.2</t>
+        </is>
+      </c>
+      <c r="CH17" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI17" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ17" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="18">
+      <c r="A18" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B18" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C18" t="inlineStr">
+        <is>
+          <t>-4.63</t>
+        </is>
+      </c>
+      <c r="D18" t="inlineStr">
+        <is>
+          <t>52066.846</t>
+        </is>
+      </c>
+      <c r="E18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F18" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="G18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H18" t="inlineStr">
+        <is>
+          <t>-2.19</t>
+        </is>
+      </c>
+      <c r="I18" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J18" t="inlineStr">
+        <is>
+          <t>9.19</t>
+        </is>
+      </c>
+      <c r="K18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L18" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M18" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N18" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O18" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P18" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q18" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R18" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T18" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U18" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W18" t="inlineStr">
+        <is>
+          <t>-14.90</t>
+        </is>
+      </c>
+      <c r="X18" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y18" t="inlineStr">
+        <is>
+          <t>2025-11-25</t>
+        </is>
+      </c>
+      <c r="Z18" t="inlineStr">
+        <is>
+          <t>15.73</t>
+        </is>
+      </c>
+      <c r="AA18" t="inlineStr">
+        <is>
+          <t>-6.32</t>
+        </is>
+      </c>
+      <c r="AB18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC18" t="inlineStr"/>
+      <c r="AD18" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE18" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF18" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AK13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AL13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AM13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AN13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AO13" t="inlineStr">
+      <c r="AG18" t="inlineStr">
+        <is>
+          <t>1.62</t>
+        </is>
+      </c>
+      <c r="AH18" t="inlineStr">
+        <is>
+          <t>-4.32</t>
+        </is>
+      </c>
+      <c r="AI18" t="inlineStr">
+        <is>
+          <t>-11.43</t>
+        </is>
+      </c>
+      <c r="AJ18" t="inlineStr">
+        <is>
+          <t>0.98</t>
+        </is>
+      </c>
+      <c r="AK18" t="inlineStr">
+        <is>
+          <t>17.22</t>
+        </is>
+      </c>
+      <c r="AL18" t="inlineStr">
+        <is>
+          <t>92.5</t>
+        </is>
+      </c>
+      <c r="AM18" t="n">
+        <v>104.44</v>
+      </c>
+      <c r="AN18" t="n">
+        <v>103.43</v>
+      </c>
+      <c r="AO18" t="inlineStr">
+        <is>
+          <t>88.23</t>
+        </is>
+      </c>
+      <c r="AP18" t="inlineStr">
+        <is>
+          <t>-161.95</t>
+        </is>
+      </c>
+      <c r="AQ18" t="inlineStr">
+        <is>
+          <t>-3.93</t>
+        </is>
+      </c>
+      <c r="AR18" t="inlineStr">
+        <is>
+          <t>-1.50</t>
+        </is>
+      </c>
+      <c r="AS18" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT18" t="inlineStr">
+        <is>
+          <t>-115.11</t>
+        </is>
+      </c>
+      <c r="AU18" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV18" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW18" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
+      </c>
+      <c r="AX18" t="n">
+        <v>5019578044.4</v>
+      </c>
+      <c r="AY18" t="inlineStr">
+        <is>
+          <t>4597307742.4</t>
+        </is>
+      </c>
+      <c r="AZ18" t="n">
+        <v>7180754379.14</v>
+      </c>
+      <c r="BA18" t="inlineStr">
+        <is>
+          <t>422270302</t>
+        </is>
+      </c>
+      <c r="BB18" t="inlineStr">
+        <is>
+          <t>-339772904.7418968</t>
+        </is>
+      </c>
+      <c r="BC18" t="inlineStr">
+        <is>
+          <t>116188863.3358154</t>
+        </is>
+      </c>
+      <c r="BD18" t="inlineStr">
+        <is>
+          <t>4682266073.0</t>
+        </is>
+      </c>
+      <c r="BE18" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF18" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG18" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH18" t="inlineStr">
+        <is>
+          <t>60.04</t>
+        </is>
+      </c>
+      <c r="BI18" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ18" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK18" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL18" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM18" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN18" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO18" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP18" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ18" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR18" t="inlineStr">
+        <is>
+          <t>價跌量增</t>
+        </is>
+      </c>
+      <c r="BS18" t="inlineStr">
+        <is>
+          <t>2.37</t>
+        </is>
+      </c>
+      <c r="BT18" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU18" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV18" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW18" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX18" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY18" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ18" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA18" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB18" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC18" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD18" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="CE18" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="CF18" t="inlineStr">
+        <is>
+          <t>87.6</t>
+        </is>
+      </c>
+      <c r="CG18" t="inlineStr">
+        <is>
+          <t>88.5</t>
+        </is>
+      </c>
+      <c r="CH18" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI18" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ18" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="19">
+      <c r="A19" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B19" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C19" t="inlineStr">
+        <is>
+          <t>0.96</t>
+        </is>
+      </c>
+      <c r="D19" t="inlineStr">
+        <is>
+          <t>124181.065</t>
+        </is>
+      </c>
+      <c r="E19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F19" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="G19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H19" t="inlineStr">
+        <is>
+          <t>-7.27</t>
+        </is>
+      </c>
+      <c r="I19" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J19" t="inlineStr">
+        <is>
+          <t>8.20</t>
+        </is>
+      </c>
+      <c r="K19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L19" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M19" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N19" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O19" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P19" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q19" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R19" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T19" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U19" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W19" t="inlineStr">
+        <is>
+          <t>-10.67</t>
+        </is>
+      </c>
+      <c r="X19" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y19" t="inlineStr">
+        <is>
+          <t>2025-11-24</t>
+        </is>
+      </c>
+      <c r="Z19" t="inlineStr">
+        <is>
+          <t>37.51</t>
+        </is>
+      </c>
+      <c r="AA19" t="inlineStr">
+        <is>
+          <t>0.90</t>
+        </is>
+      </c>
+      <c r="AB19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC19" t="inlineStr"/>
+      <c r="AD19" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE19" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF19" t="inlineStr">
+        <is>
+          <t>4.86</t>
+        </is>
+      </c>
+      <c r="AG19" t="inlineStr">
+        <is>
+          <t>7.53</t>
+        </is>
+      </c>
+      <c r="AH19" t="inlineStr">
+        <is>
+          <t>-0.71</t>
+        </is>
+      </c>
+      <c r="AI19" t="inlineStr">
+        <is>
+          <t>-11.58</t>
+        </is>
+      </c>
+      <c r="AJ19" t="inlineStr">
+        <is>
+          <t>2.32</t>
+        </is>
+      </c>
+      <c r="AK19" t="inlineStr">
+        <is>
+          <t>17.91</t>
+        </is>
+      </c>
+      <c r="AL19" t="inlineStr">
+        <is>
+          <t>93.56</t>
+        </is>
+      </c>
+      <c r="AM19" t="n">
+        <v>105.81</v>
+      </c>
+      <c r="AN19" t="n">
+        <v>103.41</v>
+      </c>
+      <c r="AO19" t="inlineStr">
+        <is>
+          <t>87.7</t>
+        </is>
+      </c>
+      <c r="AP19" t="inlineStr">
+        <is>
+          <t>-272.55</t>
+        </is>
+      </c>
+      <c r="AQ19" t="inlineStr">
+        <is>
+          <t>-3.32</t>
+        </is>
+      </c>
+      <c r="AR19" t="inlineStr">
+        <is>
+          <t>-0.89</t>
+        </is>
+      </c>
+      <c r="AS19" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT19" t="inlineStr">
+        <is>
+          <t>-108.99</t>
+        </is>
+      </c>
+      <c r="AU19" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV19" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW19" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
+      </c>
+      <c r="AX19" t="n">
+        <v>4696916791.4</v>
+      </c>
+      <c r="AY19" t="inlineStr">
+        <is>
+          <t>4341077616.0</t>
+        </is>
+      </c>
+      <c r="AZ19" t="n">
+        <v>7241408797.74</v>
+      </c>
+      <c r="BA19" t="inlineStr">
+        <is>
+          <t>355839175</t>
+        </is>
+      </c>
+      <c r="BB19" t="inlineStr">
+        <is>
+          <t>-422675044.3923899</t>
+        </is>
+      </c>
+      <c r="BC19" t="inlineStr">
+        <is>
+          <t>175646056.2487507</t>
+        </is>
+      </c>
+      <c r="BD19" t="inlineStr">
+        <is>
+          <t>11515775721.0</t>
+        </is>
+      </c>
+      <c r="BE19" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF19" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG19" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH19" t="inlineStr">
+        <is>
+          <t>67.99</t>
+        </is>
+      </c>
+      <c r="BI19" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ19" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK19" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL19" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM19" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN19" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO19" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP19" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ19" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR19" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS19" t="inlineStr">
+        <is>
+          <t>2.48</t>
+        </is>
+      </c>
+      <c r="BT19" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU19" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV19" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW19" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX19" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY19" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ19" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA19" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB19" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC19" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD19" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="CE19" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="CF19" t="inlineStr">
+        <is>
+          <t>91.0</t>
+        </is>
+      </c>
+      <c r="CG19" t="inlineStr">
+        <is>
+          <t>92.9</t>
+        </is>
+      </c>
+      <c r="CH19" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI19" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ19" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="20">
+      <c r="A20" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B20" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C20" t="inlineStr">
+        <is>
+          <t>-4.38</t>
+        </is>
+      </c>
+      <c r="D20" t="inlineStr">
+        <is>
+          <t>32684.421</t>
+        </is>
+      </c>
+      <c r="E20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F20" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="G20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H20" t="inlineStr">
+        <is>
+          <t>-6.24</t>
+        </is>
+      </c>
+      <c r="I20" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J20" t="inlineStr">
+        <is>
+          <t>-9.52</t>
+        </is>
+      </c>
+      <c r="K20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L20" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M20" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N20" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O20" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P20" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q20" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R20" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T20" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U20" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W20" t="inlineStr">
+        <is>
+          <t>-11.54</t>
+        </is>
+      </c>
+      <c r="X20" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y20" t="inlineStr">
+        <is>
+          <t>2025-11-21</t>
+        </is>
+      </c>
+      <c r="Z20" t="inlineStr">
+        <is>
+          <t>9.87</t>
+        </is>
+      </c>
+      <c r="AA20" t="inlineStr">
+        <is>
+          <t>-2.82</t>
+        </is>
+      </c>
+      <c r="AB20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC20" t="inlineStr"/>
+      <c r="AD20" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE20" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF20" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AP13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AR13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AS13" t="inlineStr">
+      <c r="AG20" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AH20" t="inlineStr">
+        <is>
+          <t>-2.44</t>
+        </is>
+      </c>
+      <c r="AI20" t="inlineStr">
+        <is>
+          <t>-11.80</t>
+        </is>
+      </c>
+      <c r="AJ20" t="inlineStr">
+        <is>
+          <t>3.66</t>
+        </is>
+      </c>
+      <c r="AK20" t="inlineStr">
+        <is>
+          <t>18.39</t>
+        </is>
+      </c>
+      <c r="AL20" t="inlineStr">
+        <is>
+          <t>94.3</t>
+        </is>
+      </c>
+      <c r="AM20" t="n">
+        <v>106.92</v>
+      </c>
+      <c r="AN20" t="n">
+        <v>103.14</v>
+      </c>
+      <c r="AO20" t="inlineStr">
+        <is>
+          <t>87.12</t>
+        </is>
+      </c>
+      <c r="AP20" t="inlineStr">
+        <is>
+          <t>-939.09</t>
+        </is>
+      </c>
+      <c r="AQ20" t="inlineStr">
+        <is>
+          <t>-2.95</t>
+        </is>
+      </c>
+      <c r="AR20" t="inlineStr">
+        <is>
+          <t>-0.28</t>
+        </is>
+      </c>
+      <c r="AS20" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT20" t="inlineStr">
+        <is>
+          <t>-102.86</t>
+        </is>
+      </c>
+      <c r="AU20" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV20" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW20" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
+      </c>
+      <c r="AX20" t="n">
+        <v>3191641823.4</v>
+      </c>
+      <c r="AY20" t="inlineStr">
+        <is>
+          <t>3527299622.7</t>
+        </is>
+      </c>
+      <c r="AZ20" t="n">
+        <v>7285669264.58</v>
+      </c>
+      <c r="BA20" t="inlineStr">
+        <is>
+          <t>-335657799</t>
+        </is>
+      </c>
+      <c r="BB20" t="inlineStr">
+        <is>
+          <t>-531460699.0544155</t>
+        </is>
+      </c>
+      <c r="BC20" t="inlineStr">
+        <is>
+          <t>-477849918.1702256</t>
+        </is>
+      </c>
+      <c r="BD20" t="inlineStr">
+        <is>
+          <t>3032171594.0</t>
+        </is>
+      </c>
+      <c r="BE20" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF20" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG20" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH20" t="inlineStr">
+        <is>
+          <t>66.37</t>
+        </is>
+      </c>
+      <c r="BI20" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ20" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK20" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL20" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM20" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN20" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO20" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP20" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ20" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR20" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS20" t="inlineStr">
+        <is>
+          <t>2.46</t>
+        </is>
+      </c>
+      <c r="BT20" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU20" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV20" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW20" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX20" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY20" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ20" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA20" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB20" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC20" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD20" t="inlineStr">
+        <is>
+          <t>93.6</t>
+        </is>
+      </c>
+      <c r="CE20" t="inlineStr">
+        <is>
+          <t>95.0</t>
+        </is>
+      </c>
+      <c r="CF20" t="inlineStr">
+        <is>
+          <t>91.6</t>
+        </is>
+      </c>
+      <c r="CG20" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="CH20" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI20" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ20" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="21">
+      <c r="A21" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B21" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C21" t="inlineStr">
+        <is>
+          <t>3.2</t>
+        </is>
+      </c>
+      <c r="D21" t="inlineStr">
+        <is>
+          <t>31967.753</t>
+        </is>
+      </c>
+      <c r="E21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F21" t="inlineStr">
+        <is>
+          <t>96.1</t>
+        </is>
+      </c>
+      <c r="G21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H21" t="inlineStr">
+        <is>
+          <t>-10.97</t>
+        </is>
+      </c>
+      <c r="I21" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J21" t="inlineStr">
+        <is>
+          <t>14.94</t>
+        </is>
+      </c>
+      <c r="K21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L21" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M21" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N21" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O21" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P21" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q21" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R21" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T21" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U21" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W21" t="inlineStr">
+        <is>
+          <t>-7.60</t>
+        </is>
+      </c>
+      <c r="X21" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y21" t="inlineStr">
+        <is>
+          <t>2025-11-20</t>
+        </is>
+      </c>
+      <c r="Z21" t="inlineStr">
+        <is>
+          <t>9.66</t>
+        </is>
+      </c>
+      <c r="AA21" t="inlineStr">
+        <is>
+          <t>-1.12</t>
+        </is>
+      </c>
+      <c r="AB21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC21" t="inlineStr"/>
+      <c r="AD21" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE21" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF21" t="inlineStr">
+        <is>
+          <t>17.71</t>
+        </is>
+      </c>
+      <c r="AG21" t="inlineStr">
+        <is>
+          <t>5.9</t>
+        </is>
+      </c>
+      <c r="AH21" t="inlineStr">
+        <is>
+          <t>0.25</t>
+        </is>
+      </c>
+      <c r="AI21" t="inlineStr">
+        <is>
+          <t>-11.25</t>
+        </is>
+      </c>
+      <c r="AJ21" t="inlineStr">
+        <is>
+          <t>5.13</t>
+        </is>
+      </c>
+      <c r="AK21" t="inlineStr">
+        <is>
+          <t>18.72</t>
+        </is>
+      </c>
+      <c r="AL21" t="inlineStr">
+        <is>
+          <t>95.85999999999999</t>
+        </is>
+      </c>
+      <c r="AM21" t="n">
+        <v>108.02</v>
+      </c>
+      <c r="AN21" t="n">
+        <v>102.75</v>
+      </c>
+      <c r="AO21" t="inlineStr">
+        <is>
+          <t>86.55</t>
+        </is>
+      </c>
+      <c r="AP21" t="inlineStr">
+        <is>
+          <t>-712.58</t>
+        </is>
+      </c>
+      <c r="AQ21" t="inlineStr">
+        <is>
+          <t>-2.35</t>
+        </is>
+      </c>
+      <c r="AR21" t="inlineStr">
+        <is>
+          <t>0.38</t>
+        </is>
+      </c>
+      <c r="AS21" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT21" t="inlineStr">
+        <is>
+          <t>-96.14</t>
+        </is>
+      </c>
+      <c r="AU21" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV21" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW21" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
+      </c>
+      <c r="AX21" t="n">
+        <v>4058514408.6</v>
+      </c>
+      <c r="AY21" t="inlineStr">
+        <is>
+          <t>3531039856.9</t>
+        </is>
+      </c>
+      <c r="AZ21" t="n">
+        <v>7317342463.3</v>
+      </c>
+      <c r="BA21" t="inlineStr">
+        <is>
+          <t>527474551</t>
+        </is>
+      </c>
+      <c r="BB21" t="inlineStr">
+        <is>
+          <t>-541208113.7606318</t>
+        </is>
+      </c>
+      <c r="BC21" t="inlineStr">
+        <is>
+          <t>-485391942.3698263</t>
+        </is>
+      </c>
+      <c r="BD21" t="inlineStr">
+        <is>
+          <t>3089667541.0</t>
+        </is>
+      </c>
+      <c r="BE21" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF21" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG21" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH21" t="inlineStr">
+        <is>
+          <t>73.78</t>
+        </is>
+      </c>
+      <c r="BI21" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ21" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK21" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL21" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM21" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN21" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO21" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP21" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ21" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+        </is>
+      </c>
+      <c r="BR21" t="inlineStr">
+        <is>
+          <t>價-量增</t>
+        </is>
+      </c>
+      <c r="BS21" t="inlineStr">
+        <is>
+          <t>2.57</t>
+        </is>
+      </c>
+      <c r="BT21" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU21" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV21" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW21" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX21" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY21" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ21" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA21" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB21" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC21" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD21" t="inlineStr">
+        <is>
+          <t>96.9</t>
+        </is>
+      </c>
+      <c r="CE21" t="inlineStr">
+        <is>
+          <t>98.8</t>
+        </is>
+      </c>
+      <c r="CF21" t="inlineStr">
+        <is>
+          <t>94.5</t>
+        </is>
+      </c>
+      <c r="CG21" t="inlineStr">
+        <is>
+          <t>96.1</t>
+        </is>
+      </c>
+      <c r="CH21" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI21" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ21" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="22">
+      <c r="A22" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B22" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C22" t="inlineStr">
+        <is>
+          <t>-0.85</t>
+        </is>
+      </c>
+      <c r="D22" t="inlineStr">
+        <is>
+          <t>29839.894</t>
+        </is>
+      </c>
+      <c r="E22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F22" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="G22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H22" t="inlineStr">
+        <is>
+          <t>-7.39</t>
+        </is>
+      </c>
+      <c r="I22" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J22" t="inlineStr">
+        <is>
+          <t>20.75</t>
+        </is>
+      </c>
+      <c r="K22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L22" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M22" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N22" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O22" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P22" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q22" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R22" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T22" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U22" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W22" t="inlineStr">
+        <is>
+          <t>-10.58</t>
+        </is>
+      </c>
+      <c r="X22" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y22" t="inlineStr">
+        <is>
+          <t>2025-11-19</t>
+        </is>
+      </c>
+      <c r="Z22" t="inlineStr">
+        <is>
+          <t>9.01</t>
+        </is>
+      </c>
+      <c r="AA22" t="inlineStr">
+        <is>
+          <t>-0.42</t>
+        </is>
+      </c>
+      <c r="AB22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC22" t="inlineStr"/>
+      <c r="AD22" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE22" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF22" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="AT13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AU13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AV13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AW13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AX13" t="n">
-        <v>0</v>
-      </c>
-      <c r="AY13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="AZ13" t="n">
-        <v>0</v>
-      </c>
-      <c r="BA13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BB13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BC13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BE13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BF13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BG13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BH13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BI13" t="inlineStr">
+      <c r="AG22" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="AH22" t="inlineStr">
+        <is>
+          <t>-5.81</t>
+        </is>
+      </c>
+      <c r="AI22" t="inlineStr">
+        <is>
+          <t>-9.44</t>
+        </is>
+      </c>
+      <c r="AJ22" t="inlineStr">
+        <is>
+          <t>6.7</t>
+        </is>
+      </c>
+      <c r="AK22" t="inlineStr">
+        <is>
+          <t>18.92</t>
+        </is>
+      </c>
+      <c r="AL22" t="inlineStr">
+        <is>
+          <t>98.74</t>
+        </is>
+      </c>
+      <c r="AM22" t="n">
+        <v>109.04</v>
+      </c>
+      <c r="AN22" t="n">
+        <v>102.19</v>
+      </c>
+      <c r="AO22" t="inlineStr">
+        <is>
+          <t>85.93</t>
+        </is>
+      </c>
+      <c r="AP22" t="inlineStr">
+        <is>
+          <t>-283.53</t>
+        </is>
+      </c>
+      <c r="AQ22" t="inlineStr">
+        <is>
+          <t>-1.95</t>
+        </is>
+      </c>
+      <c r="AR22" t="inlineStr">
+        <is>
+          <t>1.07</t>
+        </is>
+      </c>
+      <c r="AS22" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT22" t="inlineStr">
+        <is>
+          <t>-89.26</t>
+        </is>
+      </c>
+      <c r="AU22" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV22" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW22" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
+      </c>
+      <c r="AX22" t="n">
+        <v>4453509900</v>
+      </c>
+      <c r="AY22" t="inlineStr">
+        <is>
+          <t>3688316666.2</t>
+        </is>
+      </c>
+      <c r="AZ22" t="n">
+        <v>7280178623.2</v>
+      </c>
+      <c r="BA22" t="inlineStr">
+        <is>
+          <t>765193233</t>
+        </is>
+      </c>
+      <c r="BB22" t="inlineStr">
+        <is>
+          <t>-551356508.5589601</t>
+        </is>
+      </c>
+      <c r="BC22" t="inlineStr">
+        <is>
+          <t>-484991116.1774759</t>
+        </is>
+      </c>
+      <c r="BD22" t="inlineStr">
+        <is>
+          <t>2778009293.0</t>
+        </is>
+      </c>
+      <c r="BE22" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF22" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG22" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH22" t="inlineStr">
+        <is>
+          <t>68.17</t>
+        </is>
+      </c>
+      <c r="BI22" t="inlineStr">
         <is>
           <t>東元</t>
         </is>
       </c>
-      <c r="BJ13" t="inlineStr">
+      <c r="BJ22" t="inlineStr">
         <is>
           <t>東元</t>
         </is>
       </c>
-      <c r="BK13" t="inlineStr">
+      <c r="BK22" t="inlineStr">
         <is>
           <t>電機機械</t>
         </is>
       </c>
-      <c r="BL13" t="inlineStr">
+      <c r="BL22" t="inlineStr">
         <is>
           <t>上市</t>
         </is>
       </c>
-      <c r="BM13" t="inlineStr">
+      <c r="BM22" t="inlineStr">
         <is>
           <t>0.76</t>
         </is>
       </c>
-      <c r="BN13" t="inlineStr">
+      <c r="BN22" t="inlineStr">
         <is>
           <t>-4.506561377619261</t>
         </is>
       </c>
-      <c r="BO13" t="inlineStr">
+      <c r="BO22" t="inlineStr">
         <is>
           <t>17.0797647787938</t>
         </is>
       </c>
-      <c r="BP13" t="inlineStr">
+      <c r="BP22" t="inlineStr">
         <is>
           <t>5.983401519253764</t>
         </is>
       </c>
-      <c r="BQ13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="BR13" t="inlineStr">
+      <c r="BQ22" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR22" t="inlineStr">
         <is>
           <t>價-量-</t>
         </is>
       </c>
-      <c r="BS13" t="inlineStr">
-        <is>
-          <t>0.00</t>
-        </is>
-      </c>
-      <c r="BT13" t="inlineStr">
-        <is>
-          <t>2.59</t>
-        </is>
-      </c>
-      <c r="BU13" t="inlineStr">
+      <c r="BS22" t="inlineStr">
+        <is>
+          <t>2.49</t>
+        </is>
+      </c>
+      <c r="BT22" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU22" t="inlineStr">
         <is>
           <t>6.21</t>
         </is>
       </c>
-      <c r="BV13" t="inlineStr">
-        <is>
-          <t>36.96</t>
-        </is>
-      </c>
-      <c r="BW13" t="inlineStr">
+      <c r="BV22" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW22" t="inlineStr">
         <is>
           <t>24.44%</t>
         </is>
       </c>
-      <c r="BX13" t="inlineStr">
+      <c r="BX22" t="inlineStr">
         <is>
           <t>11.24%</t>
         </is>
       </c>
-      <c r="BY13" t="inlineStr">
-        <is>
-          <t>40.82</t>
-        </is>
-      </c>
-      <c r="BZ13" t="inlineStr">
-        <is>
-          <t>201997</t>
-        </is>
-      </c>
-      <c r="CA13" t="inlineStr">
+      <c r="BY22" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ22" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA22" t="inlineStr">
         <is>
           <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
         </is>
       </c>
-      <c r="CB13" t="inlineStr">
+      <c r="CB22" t="inlineStr">
         <is>
           <t>東元-電機機械-上市</t>
         </is>
       </c>
-      <c r="CC13" t="inlineStr">
-        <is>
-          <t>電機機械右下上市</t>
-        </is>
-      </c>
-      <c r="CD13" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="CE13" t="inlineStr">
+      <c r="CC22" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD22" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="CE22" t="inlineStr">
+        <is>
+          <t>94.4</t>
+        </is>
+      </c>
+      <c r="CF22" t="inlineStr">
+        <is>
+          <t>92.0</t>
+        </is>
+      </c>
+      <c r="CG22" t="inlineStr">
+        <is>
+          <t>93.0</t>
+        </is>
+      </c>
+      <c r="CH22" t="inlineStr">
+        <is>
+          <t>37.41</t>
+        </is>
+      </c>
+      <c r="CI22" t="inlineStr">
+        <is>
+          <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
+        </is>
+      </c>
+      <c r="CJ22" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+    </row>
+    <row r="23">
+      <c r="A23" t="inlineStr">
+        <is>
+          <t>【c】</t>
+        </is>
+      </c>
+      <c r="B23" t="inlineStr">
+        <is>
+          <t>1504</t>
+        </is>
+      </c>
+      <c r="C23" t="inlineStr">
+        <is>
+          <t>-2.92</t>
+        </is>
+      </c>
+      <c r="D23" t="inlineStr">
+        <is>
+          <t>32132.941</t>
+        </is>
+      </c>
+      <c r="E23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="F23" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="G23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H23" t="inlineStr">
+        <is>
+          <t>-8.31</t>
+        </is>
+      </c>
+      <c r="I23" t="inlineStr">
+        <is>
+          <t>-2.68</t>
+        </is>
+      </c>
+      <c r="J23" t="inlineStr">
+        <is>
+          <t>7.01</t>
+        </is>
+      </c>
+      <c r="K23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="L23" t="inlineStr">
+        <is>
+          <t>99.0</t>
+        </is>
+      </c>
+      <c r="M23" t="inlineStr">
+        <is>
+          <t>2025-09-23 00:00:00</t>
+        </is>
+      </c>
+      <c r="N23" t="inlineStr">
+        <is>
+          <t>2025-10-14 00:00:00</t>
+        </is>
+      </c>
+      <c r="O23" t="inlineStr">
+        <is>
+          <t>2025-09-09 00:00:00</t>
+        </is>
+      </c>
+      <c r="P23" t="inlineStr">
+        <is>
+          <t>2025-09-19 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q23" t="inlineStr">
+        <is>
+          <t>94.0</t>
+        </is>
+      </c>
+      <c r="R23" t="inlineStr">
+        <is>
+          <t>104.0</t>
+        </is>
+      </c>
+      <c r="S23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="T23" t="inlineStr">
+        <is>
+          <t>79.6</t>
+        </is>
+      </c>
+      <c r="U23" t="inlineStr">
+        <is>
+          <t>80.8</t>
+        </is>
+      </c>
+      <c r="V23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="W23" t="inlineStr">
+        <is>
+          <t>-9.81</t>
+        </is>
+      </c>
+      <c r="X23" t="inlineStr">
+        <is>
+          <t>16.34</t>
+        </is>
+      </c>
+      <c r="Y23" t="inlineStr">
+        <is>
+          <t>2025-11-18</t>
+        </is>
+      </c>
+      <c r="Z23" t="inlineStr">
+        <is>
+          <t>9.71</t>
+        </is>
+      </c>
+      <c r="AA23" t="inlineStr">
+        <is>
+          <t>-3.94</t>
+        </is>
+      </c>
+      <c r="AB23" t="inlineStr">
+        <is>
+          <t>False</t>
+        </is>
+      </c>
+      <c r="AC23" t="inlineStr"/>
+      <c r="AD23" t="inlineStr">
+        <is>
+          <t>217</t>
+        </is>
+      </c>
+      <c r="AE23" t="inlineStr">
+        <is>
+          <t>22426</t>
+        </is>
+      </c>
+      <c r="AF23" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CF13" t="inlineStr">
+      <c r="AG23" t="inlineStr">
         <is>
           <t>0.0</t>
         </is>
       </c>
-      <c r="CG13" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="CH13" t="inlineStr">
+      <c r="AH23" t="inlineStr">
+        <is>
+          <t>-7.44</t>
+        </is>
+      </c>
+      <c r="AI23" t="inlineStr">
+        <is>
+          <t>-7.92</t>
+        </is>
+      </c>
+      <c r="AJ23" t="inlineStr">
+        <is>
+          <t>8.26</t>
+        </is>
+      </c>
+      <c r="AK23" t="inlineStr">
+        <is>
+          <t>19.11</t>
+        </is>
+      </c>
+      <c r="AL23" t="inlineStr">
+        <is>
+          <t>101.34</t>
+        </is>
+      </c>
+      <c r="AM23" t="n">
+        <v>110.06</v>
+      </c>
+      <c r="AN23" t="n">
+        <v>101.66</v>
+      </c>
+      <c r="AO23" t="inlineStr">
+        <is>
+          <t>85.35</t>
+        </is>
+      </c>
+      <c r="AP23" t="inlineStr">
+        <is>
+          <t>-161.08</t>
+        </is>
+      </c>
+      <c r="AQ23" t="inlineStr">
+        <is>
+          <t>-1.11</t>
+        </is>
+      </c>
+      <c r="AR23" t="inlineStr">
+        <is>
+          <t>1.82</t>
+        </is>
+      </c>
+      <c r="AS23" t="inlineStr">
+        <is>
+          <t>9.92</t>
+        </is>
+      </c>
+      <c r="AT23" t="inlineStr">
+        <is>
+          <t>-81.65</t>
+        </is>
+      </c>
+      <c r="AU23" t="inlineStr">
+        <is>
+          <t>2025/09/23</t>
+        </is>
+      </c>
+      <c r="AV23" t="inlineStr">
+        <is>
+          <t>1906700999.581197</t>
+        </is>
+      </c>
+      <c r="AW23" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
+      </c>
+      <c r="AX23" t="n">
+        <v>4175037440.4</v>
+      </c>
+      <c r="AY23" t="inlineStr">
+        <is>
+          <t>3901577638.9</t>
+        </is>
+      </c>
+      <c r="AZ23" t="n">
+        <v>7265450343.64</v>
+      </c>
+      <c r="BA23" t="inlineStr">
+        <is>
+          <t>273459801</t>
+        </is>
+      </c>
+      <c r="BB23" t="inlineStr">
+        <is>
+          <t>-563422943.5374118</t>
+        </is>
+      </c>
+      <c r="BC23" t="inlineStr">
+        <is>
+          <t>-433705440.8963513</t>
+        </is>
+      </c>
+      <c r="BD23" t="inlineStr">
+        <is>
+          <t>3068959808.0</t>
+        </is>
+      </c>
+      <c r="BE23" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="BF23" t="inlineStr">
+        <is>
+          <t>55.3</t>
+        </is>
+      </c>
+      <c r="BG23" t="inlineStr">
+        <is>
+          <t>2025/08/11</t>
+        </is>
+      </c>
+      <c r="BH23" t="inlineStr">
+        <is>
+          <t>69.62</t>
+        </is>
+      </c>
+      <c r="BI23" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BJ23" t="inlineStr">
+        <is>
+          <t>東元</t>
+        </is>
+      </c>
+      <c r="BK23" t="inlineStr">
+        <is>
+          <t>電機機械</t>
+        </is>
+      </c>
+      <c r="BL23" t="inlineStr">
+        <is>
+          <t>上市</t>
+        </is>
+      </c>
+      <c r="BM23" t="inlineStr">
+        <is>
+          <t>0.76</t>
+        </is>
+      </c>
+      <c r="BN23" t="inlineStr">
+        <is>
+          <t>-4.506561377619261</t>
+        </is>
+      </c>
+      <c r="BO23" t="inlineStr">
+        <is>
+          <t>17.0797647787938</t>
+        </is>
+      </c>
+      <c r="BP23" t="inlineStr">
+        <is>
+          <t>5.983401519253764</t>
+        </is>
+      </c>
+      <c r="BQ23" t="inlineStr">
+        <is>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+        </is>
+      </c>
+      <c r="BR23" t="inlineStr">
+        <is>
+          <t>價-量-</t>
+        </is>
+      </c>
+      <c r="BS23" t="inlineStr">
+        <is>
+          <t>2.51</t>
+        </is>
+      </c>
+      <c r="BT23" t="inlineStr">
+        <is>
+          <t>2.54</t>
+        </is>
+      </c>
+      <c r="BU23" t="inlineStr">
+        <is>
+          <t>6.21</t>
+        </is>
+      </c>
+      <c r="BV23" t="inlineStr">
+        <is>
+          <t>37.65</t>
+        </is>
+      </c>
+      <c r="BW23" t="inlineStr">
+        <is>
+          <t>24.44%</t>
+        </is>
+      </c>
+      <c r="BX23" t="inlineStr">
+        <is>
+          <t>11.24%</t>
+        </is>
+      </c>
+      <c r="BY23" t="inlineStr">
+        <is>
+          <t>40.94</t>
+        </is>
+      </c>
+      <c r="BZ23" t="inlineStr">
+        <is>
+          <t>205800</t>
+        </is>
+      </c>
+      <c r="CA23" t="inlineStr">
+        <is>
+          <t>機電系統暨自動化產品52.37%、機電工程與電力設備21.39%、空調暨家電產品19.08%、其他7.16% (2024年)</t>
+        </is>
+      </c>
+      <c r="CB23" t="inlineStr">
+        <is>
+          <t>東元-電機機械-上市</t>
+        </is>
+      </c>
+      <c r="CC23" t="inlineStr">
+        <is>
+          <t>電機機械右上上市</t>
+        </is>
+      </c>
+      <c r="CD23" t="inlineStr">
+        <is>
+          <t>96.0</t>
+        </is>
+      </c>
+      <c r="CE23" t="inlineStr">
+        <is>
+          <t>97.5</t>
+        </is>
+      </c>
+      <c r="CF23" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="CG23" t="inlineStr">
+        <is>
+          <t>93.8</t>
+        </is>
+      </c>
+      <c r="CH23" t="inlineStr">
         <is>
           <t>37.41</t>
         </is>
       </c>
-      <c r="CI13" t="inlineStr">
+      <c r="CI23" t="inlineStr">
         <is>
           <t>** 電機機械 - 傳動元件、電控元件、冷凍空調設備及零件、機電系統工程** 建材營造 - 機電工程** 人工智慧 - 移動控制** 電動車輛產業 - 大功率鋰電池芯/模組、電池管理系統、動力馬達等零組件** 風力發電 - 監控系統、電力系統</t>
         </is>
       </c>
-      <c r="CJ13" t="inlineStr">
+      <c r="CJ23" t="inlineStr">
         <is>
           <t>False</t>
         </is>

--- a/Result/checksun_type/監控系統.xlsx
+++ b/Result/checksun_type/監控系統.xlsx
@@ -873,7 +873,7 @@
     <row r="2">
       <c r="A2" t="inlineStr">
         <is>
-          <t>【d】</t>
+          <t>【d】;【x】看好</t>
         </is>
       </c>
       <c r="B2" t="inlineStr">
@@ -883,12 +883,12 @@
       </c>
       <c r="C2" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="D2" t="inlineStr">
         <is>
-          <t>20318.111</t>
+          <t>12779.073</t>
         </is>
       </c>
       <c r="E2" t="inlineStr">
@@ -898,74 +898,74 @@
       </c>
       <c r="F2" t="inlineStr">
         <is>
+          <t>997.0</t>
+        </is>
+      </c>
+      <c r="G2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="H2" t="inlineStr">
+        <is>
+          <t>0.0</t>
+        </is>
+      </c>
+      <c r="I2" t="inlineStr">
+        <is>
+          <t>1.78</t>
+        </is>
+      </c>
+      <c r="J2" t="inlineStr">
+        <is>
+          <t>-2.27</t>
+        </is>
+      </c>
+      <c r="K2" t="inlineStr">
+        <is>
+          <t>2025-12-02</t>
+        </is>
+      </c>
+      <c r="L2" t="inlineStr">
+        <is>
+          <t>100.0</t>
+        </is>
+      </c>
+      <c r="M2" t="inlineStr">
+        <is>
+          <t>2025-12-02 00:00:00</t>
+        </is>
+      </c>
+      <c r="N2" t="inlineStr">
+        <is>
+          <t>2025-12-04 00:00:00</t>
+        </is>
+      </c>
+      <c r="O2" t="inlineStr">
+        <is>
+          <t>2025-10-07 00:00:00</t>
+        </is>
+      </c>
+      <c r="P2" t="inlineStr">
+        <is>
+          <t>2025-10-20 00:00:00</t>
+        </is>
+      </c>
+      <c r="Q2" t="inlineStr">
+        <is>
           <t>989.0</t>
         </is>
       </c>
-      <c r="G2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="H2" t="inlineStr">
-        <is>
-          <t>0.0</t>
-        </is>
-      </c>
-      <c r="I2" t="inlineStr">
-        <is>
-          <t>2.04</t>
-        </is>
-      </c>
-      <c r="J2" t="inlineStr">
-        <is>
-          <t>-4.00</t>
-        </is>
-      </c>
-      <c r="K2" t="inlineStr">
-        <is>
-          <t>2025-12-02</t>
-        </is>
-      </c>
-      <c r="L2" t="inlineStr">
-        <is>
-          <t>100.0</t>
-        </is>
-      </c>
-      <c r="M2" t="inlineStr">
-        <is>
-          <t>2025-12-02 00:00:00</t>
-        </is>
-      </c>
-      <c r="N2" t="inlineStr">
-        <is>
-          <t>2025-12-03 00:00:00</t>
-        </is>
-      </c>
-      <c r="O2" t="inlineStr">
-        <is>
-          <t>2025-10-07 00:00:00</t>
-        </is>
-      </c>
-      <c r="P2" t="inlineStr">
-        <is>
-          <t>2025-10-20 00:00:00</t>
-        </is>
-      </c>
-      <c r="Q2" t="inlineStr">
+      <c r="R2" t="inlineStr">
+        <is>
+          <t>0</t>
+        </is>
+      </c>
+      <c r="S2" t="inlineStr">
         <is>
           <t>989.0</t>
         </is>
       </c>
-      <c r="R2" t="inlineStr">
-        <is>
-          <t>0</t>
-        </is>
-      </c>
-      <c r="S2" t="inlineStr">
-        <is>
-          <t>989.0</t>
-        </is>
-      </c>
       <c r="T2" t="inlineStr">
         <is>
           <t>987.0</t>
@@ -978,7 +978,7 @@
       </c>
       <c r="V2" t="inlineStr">
         <is>
-          <t>0.00</t>
+          <t>0.81</t>
         </is>
       </c>
       <c r="W2" t="inlineStr">
@@ -993,17 +993,17 @@
       </c>
       <c r="Y2" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z2" t="inlineStr">
         <is>
-          <t>70.30</t>
+          <t>44.21</t>
         </is>
       </c>
       <c r="AA2" t="inlineStr">
         <is>
-          <t>0.63</t>
+          <t>0.52</t>
         </is>
       </c>
       <c r="AB2" t="inlineStr">
@@ -1014,12 +1014,12 @@
       <c r="AC2" t="inlineStr"/>
       <c r="AD2" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE2" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF2" t="inlineStr">
@@ -1029,58 +1029,58 @@
       </c>
       <c r="AG2" t="inlineStr">
         <is>
-          <t>87.98</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AH2" t="inlineStr">
         <is>
-          <t>3.43</t>
+          <t>3.15</t>
         </is>
       </c>
       <c r="AI2" t="inlineStr">
         <is>
-          <t>1.44</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="AJ2" t="inlineStr">
         <is>
-          <t>-1.56</t>
+          <t>-1.62</t>
         </is>
       </c>
       <c r="AK2" t="inlineStr">
         <is>
-          <t>10.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="AL2" t="inlineStr">
         <is>
-          <t>956.2</t>
+          <t>966.6</t>
         </is>
       </c>
       <c r="AM2" t="n">
-        <v>942.6</v>
+        <v>944.1</v>
       </c>
       <c r="AN2" t="n">
-        <v>957.54</v>
+        <v>959.64</v>
       </c>
       <c r="AO2" t="inlineStr">
         <is>
-          <t>865.41</t>
+          <t>870.09</t>
         </is>
       </c>
       <c r="AP2" t="inlineStr">
         <is>
-          <t>83.10</t>
+          <t>184.23</t>
         </is>
       </c>
       <c r="AQ2" t="inlineStr">
         <is>
-          <t>-0.94</t>
+          <t>3.19</t>
         </is>
       </c>
       <c r="AR2" t="inlineStr">
         <is>
-          <t>-5.54</t>
+          <t>-3.79</t>
         </is>
       </c>
       <c r="AS2" t="inlineStr">
@@ -1090,7 +1090,7 @@
       </c>
       <c r="AT2" t="inlineStr">
         <is>
-          <t>-108.54</t>
+          <t>-105.85</t>
         </is>
       </c>
       <c r="AU2" t="inlineStr">
@@ -1100,48 +1100,48 @@
       </c>
       <c r="AV2" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW2" t="inlineStr">
         <is>
-          <t>20108685563.0</t>
+          <t>12687615192.0</t>
         </is>
       </c>
       <c r="AX2" t="n">
-        <v>12769117326</v>
+        <v>13166159783.8</v>
       </c>
       <c r="AY2" t="inlineStr">
         <is>
-          <t>13300513877.8</t>
+          <t>13471920557.0</t>
         </is>
       </c>
       <c r="AZ2" t="n">
-        <v>14242798853.4</v>
+        <v>14103294472.94</v>
       </c>
       <c r="BA2" t="inlineStr">
         <is>
-          <t>-531396551</t>
+          <t>-305760773</t>
         </is>
       </c>
       <c r="BB2" t="inlineStr">
         <is>
-          <t>-195582216.5249392</t>
+          <t>-135363522.6368131</t>
         </is>
       </c>
       <c r="BC2" t="inlineStr">
         <is>
-          <t>324095336.9838543</t>
+          <t>195839293.7478809</t>
         </is>
       </c>
       <c r="BD2" t="inlineStr">
         <is>
-          <t>20108685563.0</t>
+          <t>12687615192.0</t>
         </is>
       </c>
       <c r="BE2" t="inlineStr">
         <is>
-          <t>2025-12-03</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF2" t="inlineStr">
@@ -1156,7 +1156,7 @@
       </c>
       <c r="BH2" t="inlineStr">
         <is>
-          <t>161.64</t>
+          <t>163.76</t>
         </is>
       </c>
       <c r="BI2" t="inlineStr">
@@ -1201,7 +1201,7 @@
       </c>
       <c r="BQ2" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR2" t="inlineStr">
@@ -1211,12 +1211,12 @@
       </c>
       <c r="BS2" t="inlineStr">
         <is>
-          <t>10.67</t>
+          <t>10.76</t>
         </is>
       </c>
       <c r="BT2" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU2" t="inlineStr">
@@ -1226,7 +1226,7 @@
       </c>
       <c r="BV2" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW2" t="inlineStr">
@@ -1241,12 +1241,12 @@
       </c>
       <c r="BY2" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ2" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA2" t="inlineStr">
@@ -1266,22 +1266,22 @@
       </c>
       <c r="CD2" t="inlineStr">
         <is>
-          <t>988.0</t>
+          <t>997.0</t>
         </is>
       </c>
       <c r="CE2" t="inlineStr">
         <is>
-          <t>998.0</t>
+          <t>1005.0</t>
         </is>
       </c>
       <c r="CF2" t="inlineStr">
         <is>
-          <t>974.0</t>
+          <t>984.0</t>
         </is>
       </c>
       <c r="CG2" t="inlineStr">
         <is>
-          <t>989.0</t>
+          <t>997.0</t>
         </is>
       </c>
       <c r="CH2" t="inlineStr">
@@ -1313,12 +1313,12 @@
       </c>
       <c r="C3" t="inlineStr">
         <is>
-          <t>4.38</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="D3" t="inlineStr">
         <is>
-          <t>17532.398</t>
+          <t>20318.111</t>
         </is>
       </c>
       <c r="E3" t="inlineStr">
@@ -1328,7 +1328,7 @@
       </c>
       <c r="F3" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>989.0</t>
         </is>
       </c>
       <c r="G3" t="inlineStr">
@@ -1338,22 +1338,22 @@
       </c>
       <c r="H3" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>0.8</t>
         </is>
       </c>
       <c r="I3" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J3" t="inlineStr">
         <is>
-          <t>-14.86</t>
+          <t>-4.00</t>
         </is>
       </c>
       <c r="K3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="L3" t="inlineStr">
@@ -1368,7 +1368,7 @@
       </c>
       <c r="N3" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O3" t="inlineStr">
@@ -1393,7 +1393,7 @@
       </c>
       <c r="S3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>989.0</t>
         </is>
       </c>
       <c r="T3" t="inlineStr">
@@ -1408,7 +1408,7 @@
       </c>
       <c r="V3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>0.00</t>
         </is>
       </c>
       <c r="W3" t="inlineStr">
@@ -1423,17 +1423,17 @@
       </c>
       <c r="Y3" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z3" t="inlineStr">
         <is>
-          <t>60.66</t>
+          <t>70.30</t>
         </is>
       </c>
       <c r="AA3" t="inlineStr">
         <is>
-          <t>3.89</t>
+          <t>0.63</t>
         </is>
       </c>
       <c r="AB3" t="inlineStr">
@@ -1444,12 +1444,12 @@
       <c r="AC3" t="inlineStr"/>
       <c r="AD3" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE3" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF3" t="inlineStr">
@@ -1459,58 +1459,58 @@
       </c>
       <c r="AG3" t="inlineStr">
         <is>
-          <t>81.42</t>
+          <t>87.98</t>
         </is>
       </c>
       <c r="AH3" t="inlineStr">
         <is>
-          <t>3.47</t>
+          <t>3.43</t>
         </is>
       </c>
       <c r="AI3" t="inlineStr">
         <is>
-          <t>-0.16</t>
+          <t>1.44</t>
         </is>
       </c>
       <c r="AJ3" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-1.56</t>
         </is>
       </c>
       <c r="AK3" t="inlineStr">
         <is>
-          <t>10.88</t>
+          <t>10.65</t>
         </is>
       </c>
       <c r="AL3" t="inlineStr">
         <is>
-          <t>940.4</t>
+          <t>956.2</t>
         </is>
       </c>
       <c r="AM3" t="n">
-        <v>941.9</v>
+        <v>942.6</v>
       </c>
       <c r="AN3" t="n">
-        <v>954.48</v>
+        <v>957.54</v>
       </c>
       <c r="AO3" t="inlineStr">
         <is>
-          <t>860.81</t>
+          <t>865.41</t>
         </is>
       </c>
       <c r="AP3" t="inlineStr">
         <is>
-          <t>19.59</t>
+          <t>83.10</t>
         </is>
       </c>
       <c r="AQ3" t="inlineStr">
         <is>
-          <t>-5.38</t>
+          <t>-0.94</t>
         </is>
       </c>
       <c r="AR3" t="inlineStr">
         <is>
-          <t>-6.69</t>
+          <t>-5.54</t>
         </is>
       </c>
       <c r="AS3" t="inlineStr">
@@ -1520,7 +1520,7 @@
       </c>
       <c r="AT3" t="inlineStr">
         <is>
-          <t>-110.32</t>
+          <t>-108.54</t>
         </is>
       </c>
       <c r="AU3" t="inlineStr">
@@ -1530,48 +1530,48 @@
       </c>
       <c r="AV3" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW3" t="inlineStr">
         <is>
-          <t>16856373921.0</t>
+          <t>20108685563.0</t>
         </is>
       </c>
       <c r="AX3" t="n">
-        <v>10663188933.6</v>
+        <v>12769117326</v>
       </c>
       <c r="AY3" t="inlineStr">
         <is>
-          <t>12525016590.0</t>
+          <t>13300513877.8</t>
         </is>
       </c>
       <c r="AZ3" t="n">
-        <v>14016406079.92</v>
+        <v>14242798853.4</v>
       </c>
       <c r="BA3" t="inlineStr">
         <is>
-          <t>-1861827656</t>
+          <t>-531396551</t>
         </is>
       </c>
       <c r="BB3" t="inlineStr">
         <is>
-          <t>-290069044.435629</t>
+          <t>-195582216.5249392</t>
         </is>
       </c>
       <c r="BC3" t="inlineStr">
         <is>
-          <t>-299371260.1784668</t>
+          <t>324095336.9838543</t>
         </is>
       </c>
       <c r="BD3" t="inlineStr">
         <is>
-          <t>16856373921.0</t>
+          <t>20108685563.0</t>
         </is>
       </c>
       <c r="BE3" t="inlineStr">
         <is>
-          <t>0</t>
+          <t>2025-12-04</t>
         </is>
       </c>
       <c r="BF3" t="inlineStr">
@@ -1586,7 +1586,7 @@
       </c>
       <c r="BH3" t="inlineStr">
         <is>
-          <t>157.41</t>
+          <t>161.64</t>
         </is>
       </c>
       <c r="BI3" t="inlineStr">
@@ -1631,7 +1631,7 @@
       </c>
       <c r="BQ3" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR3" t="inlineStr">
@@ -1641,12 +1641,12 @@
       </c>
       <c r="BS3" t="inlineStr">
         <is>
-          <t>10.50</t>
+          <t>10.67</t>
         </is>
       </c>
       <c r="BT3" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU3" t="inlineStr">
@@ -1656,7 +1656,7 @@
       </c>
       <c r="BV3" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW3" t="inlineStr">
@@ -1671,12 +1671,12 @@
       </c>
       <c r="BY3" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ3" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA3" t="inlineStr">
@@ -1696,22 +1696,22 @@
       </c>
       <c r="CD3" t="inlineStr">
         <is>
-          <t>936.0</t>
+          <t>988.0</t>
         </is>
       </c>
       <c r="CE3" t="inlineStr">
         <is>
-          <t>978.0</t>
+          <t>998.0</t>
         </is>
       </c>
       <c r="CF3" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>974.0</t>
         </is>
       </c>
       <c r="CG3" t="inlineStr">
         <is>
-          <t>973.0</t>
+          <t>989.0</t>
         </is>
       </c>
       <c r="CH3" t="inlineStr">
@@ -1733,7 +1733,7 @@
     <row r="4">
       <c r="A4" t="inlineStr">
         <is>
-          <t>【e】</t>
+          <t>【d】</t>
         </is>
       </c>
       <c r="B4" t="inlineStr">
@@ -1743,12 +1743,12 @@
       </c>
       <c r="C4" t="inlineStr">
         <is>
-          <t>-1.06</t>
+          <t>4.38</t>
         </is>
       </c>
       <c r="D4" t="inlineStr">
         <is>
-          <t>8363.698</t>
+          <t>17532.398</t>
         </is>
       </c>
       <c r="E4" t="inlineStr">
@@ -1758,7 +1758,7 @@
       </c>
       <c r="F4" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="G4" t="inlineStr">
@@ -1768,17 +1768,17 @@
       </c>
       <c r="H4" t="inlineStr">
         <is>
-          <t>5.76</t>
+          <t>2.41</t>
         </is>
       </c>
       <c r="I4" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J4" t="inlineStr">
         <is>
-          <t>-10.38</t>
+          <t>-14.86</t>
         </is>
       </c>
       <c r="K4" t="inlineStr">
@@ -1798,7 +1798,7 @@
       </c>
       <c r="N4" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O4" t="inlineStr">
@@ -1853,17 +1853,17 @@
       </c>
       <c r="Y4" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z4" t="inlineStr">
         <is>
-          <t>28.94</t>
+          <t>60.66</t>
         </is>
       </c>
       <c r="AA4" t="inlineStr">
         <is>
-          <t>-1.07</t>
+          <t>3.89</t>
         </is>
       </c>
       <c r="AB4" t="inlineStr">
@@ -1874,73 +1874,73 @@
       <c r="AC4" t="inlineStr"/>
       <c r="AD4" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE4" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF4" t="inlineStr">
         <is>
-          <t>63.93</t>
+          <t>100.0</t>
         </is>
       </c>
       <c r="AG4" t="inlineStr">
         <is>
-          <t>76.5</t>
+          <t>81.42</t>
         </is>
       </c>
       <c r="AH4" t="inlineStr">
         <is>
-          <t>0.82</t>
+          <t>3.47</t>
         </is>
       </c>
       <c r="AI4" t="inlineStr">
         <is>
-          <t>-1.91</t>
+          <t>-0.16</t>
         </is>
       </c>
       <c r="AJ4" t="inlineStr">
         <is>
-          <t>-0.99</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AK4" t="inlineStr">
         <is>
-          <t>11.12</t>
+          <t>10.88</t>
         </is>
       </c>
       <c r="AL4" t="inlineStr">
         <is>
-          <t>924.4</t>
+          <t>940.4</t>
         </is>
       </c>
       <c r="AM4" t="n">
-        <v>942.4</v>
+        <v>941.9</v>
       </c>
       <c r="AN4" t="n">
-        <v>951.84</v>
+        <v>954.48</v>
       </c>
       <c r="AO4" t="inlineStr">
         <is>
-          <t>856.55</t>
+          <t>860.81</t>
         </is>
       </c>
       <c r="AP4" t="inlineStr">
         <is>
-          <t>-33.12</t>
+          <t>19.59</t>
         </is>
       </c>
       <c r="AQ4" t="inlineStr">
         <is>
-          <t>-9.34</t>
+          <t>-5.38</t>
         </is>
       </c>
       <c r="AR4" t="inlineStr">
         <is>
-          <t>-7.01</t>
+          <t>-6.69</t>
         </is>
       </c>
       <c r="AS4" t="inlineStr">
@@ -1950,7 +1950,7 @@
       </c>
       <c r="AT4" t="inlineStr">
         <is>
-          <t>-110.82</t>
+          <t>-110.32</t>
         </is>
       </c>
       <c r="AU4" t="inlineStr">
@@ -1960,43 +1960,43 @@
       </c>
       <c r="AV4" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW4" t="inlineStr">
         <is>
-          <t>7820188511.0</t>
+          <t>16856373921.0</t>
         </is>
       </c>
       <c r="AX4" t="n">
-        <v>10674153029.2</v>
+        <v>10663188933.6</v>
       </c>
       <c r="AY4" t="inlineStr">
         <is>
-          <t>11910356191.8</t>
+          <t>12525016590.0</t>
         </is>
       </c>
       <c r="AZ4" t="n">
-        <v>13939434751.06</v>
+        <v>14016406079.92</v>
       </c>
       <c r="BA4" t="inlineStr">
         <is>
-          <t>-1236203162</t>
+          <t>-1861827656</t>
         </is>
       </c>
       <c r="BB4" t="inlineStr">
         <is>
-          <t>-288377732.4823858</t>
+          <t>-290069044.435629</t>
         </is>
       </c>
       <c r="BC4" t="inlineStr">
         <is>
-          <t>-830884035.1896954</t>
+          <t>-299371260.1784668</t>
         </is>
       </c>
       <c r="BD4" t="inlineStr">
         <is>
-          <t>7820188511.0</t>
+          <t>16856373921.0</t>
         </is>
       </c>
       <c r="BE4" t="inlineStr">
@@ -2016,7 +2016,7 @@
       </c>
       <c r="BH4" t="inlineStr">
         <is>
-          <t>146.56</t>
+          <t>157.41</t>
         </is>
       </c>
       <c r="BI4" t="inlineStr">
@@ -2061,22 +2061,22 @@
       </c>
       <c r="BQ4" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR4" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS4" t="inlineStr">
         <is>
-          <t>10.06</t>
+          <t>10.50</t>
         </is>
       </c>
       <c r="BT4" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU4" t="inlineStr">
@@ -2086,7 +2086,7 @@
       </c>
       <c r="BV4" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW4" t="inlineStr">
@@ -2101,12 +2101,12 @@
       </c>
       <c r="BY4" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ4" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA4" t="inlineStr">
@@ -2126,22 +2126,22 @@
       </c>
       <c r="CD4" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>936.0</t>
         </is>
       </c>
       <c r="CE4" t="inlineStr">
         <is>
-          <t>946.0</t>
+          <t>978.0</t>
         </is>
       </c>
       <c r="CF4" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="CG4" t="inlineStr">
         <is>
-          <t>932.0</t>
+          <t>973.0</t>
         </is>
       </c>
       <c r="CH4" t="inlineStr">
@@ -2173,12 +2173,12 @@
       </c>
       <c r="C5" t="inlineStr">
         <is>
-          <t>-0.31</t>
+          <t>-1.06</t>
         </is>
       </c>
       <c r="D5" t="inlineStr">
         <is>
-          <t>8820.259</t>
+          <t>8363.698</t>
         </is>
       </c>
       <c r="E5" t="inlineStr">
@@ -2188,7 +2188,7 @@
       </c>
       <c r="F5" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="G5" t="inlineStr">
@@ -2198,17 +2198,17 @@
       </c>
       <c r="H5" t="inlineStr">
         <is>
-          <t>4.75</t>
+          <t>6.52</t>
         </is>
       </c>
       <c r="I5" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J5" t="inlineStr">
         <is>
-          <t>-5.21</t>
+          <t>-10.38</t>
         </is>
       </c>
       <c r="K5" t="inlineStr">
@@ -2228,7 +2228,7 @@
       </c>
       <c r="N5" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O5" t="inlineStr">
@@ -2283,17 +2283,17 @@
       </c>
       <c r="Y5" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z5" t="inlineStr">
         <is>
-          <t>30.52</t>
+          <t>28.94</t>
         </is>
       </c>
       <c r="AA5" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.07</t>
         </is>
       </c>
       <c r="AB5" t="inlineStr">
@@ -2304,73 +2304,73 @@
       <c r="AC5" t="inlineStr"/>
       <c r="AD5" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE5" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF5" t="inlineStr">
         <is>
-          <t>80.33</t>
+          <t>63.93</t>
         </is>
       </c>
       <c r="AG5" t="inlineStr">
         <is>
-          <t>63.91</t>
+          <t>76.5</t>
         </is>
       </c>
       <c r="AH5" t="inlineStr">
         <is>
-          <t>2.73</t>
+          <t>0.82</t>
         </is>
       </c>
       <c r="AI5" t="inlineStr">
         <is>
-          <t>-3.02</t>
+          <t>-1.91</t>
         </is>
       </c>
       <c r="AJ5" t="inlineStr">
         <is>
-          <t>-0.46</t>
+          <t>-0.99</t>
         </is>
       </c>
       <c r="AK5" t="inlineStr">
         <is>
-          <t>11.45</t>
+          <t>11.12</t>
         </is>
       </c>
       <c r="AL5" t="inlineStr">
         <is>
-          <t>917.0</t>
+          <t>924.4</t>
         </is>
       </c>
       <c r="AM5" t="n">
-        <v>945.55</v>
+        <v>942.4</v>
       </c>
       <c r="AN5" t="n">
-        <v>949.92</v>
+        <v>951.84</v>
       </c>
       <c r="AO5" t="inlineStr">
         <is>
-          <t>852.31</t>
+          <t>856.55</t>
         </is>
       </c>
       <c r="AP5" t="inlineStr">
         <is>
-          <t>-56.69</t>
+          <t>-33.12</t>
         </is>
       </c>
       <c r="AQ5" t="inlineStr">
         <is>
-          <t>-10.08</t>
+          <t>-9.34</t>
         </is>
       </c>
       <c r="AR5" t="inlineStr">
         <is>
-          <t>-6.43</t>
+          <t>-7.01</t>
         </is>
       </c>
       <c r="AS5" t="inlineStr">
@@ -2380,7 +2380,7 @@
       </c>
       <c r="AT5" t="inlineStr">
         <is>
-          <t>-109.92</t>
+          <t>-110.82</t>
         </is>
       </c>
       <c r="AU5" t="inlineStr">
@@ -2390,43 +2390,43 @@
       </c>
       <c r="AV5" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW5" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="AX5" t="n">
-        <v>12272712875.4</v>
+        <v>10674153029.2</v>
       </c>
       <c r="AY5" t="inlineStr">
         <is>
-          <t>12946611618.9</t>
+          <t>11910356191.8</t>
         </is>
       </c>
       <c r="AZ5" t="n">
-        <v>13990667425.04</v>
+        <v>13939434751.06</v>
       </c>
       <c r="BA5" t="inlineStr">
         <is>
-          <t>-673898743</t>
+          <t>-1236203162</t>
         </is>
       </c>
       <c r="BB5" t="inlineStr">
         <is>
-          <t>-189740222.8992386</t>
+          <t>-288377732.4823858</t>
         </is>
       </c>
       <c r="BC5" t="inlineStr">
         <is>
-          <t>-592350847.1632462</t>
+          <t>-830884035.1896954</t>
         </is>
       </c>
       <c r="BD5" t="inlineStr">
         <is>
-          <t>8357935732.0</t>
+          <t>7820188511.0</t>
         </is>
       </c>
       <c r="BE5" t="inlineStr">
@@ -2446,7 +2446,7 @@
       </c>
       <c r="BH5" t="inlineStr">
         <is>
-          <t>149.21</t>
+          <t>146.56</t>
         </is>
       </c>
       <c r="BI5" t="inlineStr">
@@ -2491,22 +2491,22 @@
       </c>
       <c r="BQ5" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR5" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS5" t="inlineStr">
         <is>
-          <t>10.16</t>
+          <t>10.06</t>
         </is>
       </c>
       <c r="BT5" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU5" t="inlineStr">
@@ -2516,7 +2516,7 @@
       </c>
       <c r="BV5" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW5" t="inlineStr">
@@ -2531,12 +2531,12 @@
       </c>
       <c r="BY5" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ5" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA5" t="inlineStr">
@@ -2556,22 +2556,22 @@
       </c>
       <c r="CD5" t="inlineStr">
         <is>
-          <t>955.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CE5" t="inlineStr">
         <is>
-          <t>959.0</t>
+          <t>946.0</t>
         </is>
       </c>
       <c r="CF5" t="inlineStr">
         <is>
-          <t>938.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CG5" t="inlineStr">
         <is>
-          <t>942.0</t>
+          <t>932.0</t>
         </is>
       </c>
       <c r="CH5" t="inlineStr">
@@ -2593,7 +2593,7 @@
     <row r="6">
       <c r="A6" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B6" t="inlineStr">
@@ -2603,12 +2603,12 @@
       </c>
       <c r="C6" t="inlineStr">
         <is>
-          <t>3.77</t>
+          <t>-0.31</t>
         </is>
       </c>
       <c r="D6" t="inlineStr">
         <is>
-          <t>11426.896</t>
+          <t>8820.259</t>
         </is>
       </c>
       <c r="E6" t="inlineStr">
@@ -2618,7 +2618,7 @@
       </c>
       <c r="F6" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="G6" t="inlineStr">
@@ -2628,17 +2628,17 @@
       </c>
       <c r="H6" t="inlineStr">
         <is>
-          <t>4.45</t>
+          <t>5.52</t>
         </is>
       </c>
       <c r="I6" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J6" t="inlineStr">
         <is>
-          <t>4.50</t>
+          <t>-5.21</t>
         </is>
       </c>
       <c r="K6" t="inlineStr">
@@ -2658,7 +2658,7 @@
       </c>
       <c r="N6" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O6" t="inlineStr">
@@ -2713,17 +2713,17 @@
       </c>
       <c r="Y6" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z6" t="inlineStr">
         <is>
-          <t>39.54</t>
+          <t>30.52</t>
         </is>
       </c>
       <c r="AA6" t="inlineStr">
         <is>
-          <t>2.64</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AB6" t="inlineStr">
@@ -2734,73 +2734,73 @@
       <c r="AC6" t="inlineStr"/>
       <c r="AD6" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE6" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF6" t="inlineStr">
         <is>
-          <t>85.25</t>
+          <t>80.33</t>
         </is>
       </c>
       <c r="AG6" t="inlineStr">
         <is>
-          <t>37.13</t>
+          <t>63.91</t>
         </is>
       </c>
       <c r="AH6" t="inlineStr">
         <is>
-          <t>2.78</t>
+          <t>2.73</t>
         </is>
       </c>
       <c r="AI6" t="inlineStr">
         <is>
-          <t>-3.11</t>
+          <t>-3.02</t>
         </is>
       </c>
       <c r="AJ6" t="inlineStr">
         <is>
-          <t>0.12</t>
+          <t>-0.46</t>
         </is>
       </c>
       <c r="AK6" t="inlineStr">
         <is>
-          <t>11.79</t>
+          <t>11.45</t>
         </is>
       </c>
       <c r="AL6" t="inlineStr">
         <is>
-          <t>919.4</t>
+          <t>917.0</t>
         </is>
       </c>
       <c r="AM6" t="n">
-        <v>948.95</v>
+        <v>945.55</v>
       </c>
       <c r="AN6" t="n">
-        <v>947.8200000000001</v>
+        <v>949.92</v>
       </c>
       <c r="AO6" t="inlineStr">
         <is>
-          <t>847.89</t>
+          <t>852.31</t>
         </is>
       </c>
       <c r="AP6" t="inlineStr">
         <is>
-          <t>-115.56</t>
+          <t>-56.69</t>
         </is>
       </c>
       <c r="AQ6" t="inlineStr">
         <is>
-          <t>-11.90</t>
+          <t>-10.08</t>
         </is>
       </c>
       <c r="AR6" t="inlineStr">
         <is>
-          <t>-5.52</t>
+          <t>-6.43</t>
         </is>
       </c>
       <c r="AS6" t="inlineStr">
@@ -2810,7 +2810,7 @@
       </c>
       <c r="AT6" t="inlineStr">
         <is>
-          <t>-108.52</t>
+          <t>-109.92</t>
         </is>
       </c>
       <c r="AU6" t="inlineStr">
@@ -2820,43 +2820,43 @@
       </c>
       <c r="AV6" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW6" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="AX6" t="n">
-        <v>13777681330.2</v>
+        <v>12272712875.4</v>
       </c>
       <c r="AY6" t="inlineStr">
         <is>
-          <t>13184190874.5</t>
+          <t>12946611618.9</t>
         </is>
       </c>
       <c r="AZ6" t="n">
-        <v>14165986897.28</v>
+        <v>13990667425.04</v>
       </c>
       <c r="BA6" t="inlineStr">
         <is>
-          <t>593490455</t>
+          <t>-673898743</t>
         </is>
       </c>
       <c r="BB6" t="inlineStr">
         <is>
-          <t>-116538291.2148735</t>
+          <t>-189740222.8992386</t>
         </is>
       </c>
       <c r="BC6" t="inlineStr">
         <is>
-          <t>-288049536.2624874</t>
+          <t>-592350847.1632462</t>
         </is>
       </c>
       <c r="BD6" t="inlineStr">
         <is>
-          <t>10702402903.0</t>
+          <t>8357935732.0</t>
         </is>
       </c>
       <c r="BE6" t="inlineStr">
@@ -2876,7 +2876,7 @@
       </c>
       <c r="BH6" t="inlineStr">
         <is>
-          <t>150.00</t>
+          <t>149.21</t>
         </is>
       </c>
       <c r="BI6" t="inlineStr">
@@ -2921,22 +2921,22 @@
       </c>
       <c r="BQ6" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;盤整震盪,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;觀望為宜&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;1&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR6" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS6" t="inlineStr">
         <is>
-          <t>10.20</t>
+          <t>10.16</t>
         </is>
       </c>
       <c r="BT6" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU6" t="inlineStr">
@@ -2946,7 +2946,7 @@
       </c>
       <c r="BV6" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW6" t="inlineStr">
@@ -2961,12 +2961,12 @@
       </c>
       <c r="BY6" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ6" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA6" t="inlineStr">
@@ -2986,22 +2986,22 @@
       </c>
       <c r="CD6" t="inlineStr">
         <is>
-          <t>928.0</t>
+          <t>955.0</t>
         </is>
       </c>
       <c r="CE6" t="inlineStr">
         <is>
-          <t>950.0</t>
+          <t>959.0</t>
         </is>
       </c>
       <c r="CF6" t="inlineStr">
         <is>
-          <t>916.0</t>
+          <t>938.0</t>
         </is>
       </c>
       <c r="CG6" t="inlineStr">
         <is>
-          <t>945.0</t>
+          <t>942.0</t>
         </is>
       </c>
       <c r="CH6" t="inlineStr">
@@ -3033,12 +3033,12 @@
       </c>
       <c r="C7" t="inlineStr">
         <is>
-          <t>1.86</t>
+          <t>3.77</t>
         </is>
       </c>
       <c r="D7" t="inlineStr">
         <is>
-          <t>10504.174</t>
+          <t>11426.896</t>
         </is>
       </c>
       <c r="E7" t="inlineStr">
@@ -3048,7 +3048,7 @@
       </c>
       <c r="F7" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="G7" t="inlineStr">
@@ -3058,17 +3058,17 @@
       </c>
       <c r="H7" t="inlineStr">
         <is>
-          <t>7.99</t>
+          <t>5.22</t>
         </is>
       </c>
       <c r="I7" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J7" t="inlineStr">
         <is>
-          <t>2.38</t>
+          <t>4.50</t>
         </is>
       </c>
       <c r="K7" t="inlineStr">
@@ -3088,7 +3088,7 @@
       </c>
       <c r="N7" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O7" t="inlineStr">
@@ -3143,17 +3143,17 @@
       </c>
       <c r="Y7" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z7" t="inlineStr">
         <is>
-          <t>36.34</t>
+          <t>39.54</t>
         </is>
       </c>
       <c r="AA7" t="inlineStr">
         <is>
-          <t>-0.53</t>
+          <t>2.64</t>
         </is>
       </c>
       <c r="AB7" t="inlineStr">
@@ -3164,73 +3164,73 @@
       <c r="AC7" t="inlineStr"/>
       <c r="AD7" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE7" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF7" t="inlineStr">
         <is>
-          <t>26.15</t>
+          <t>85.25</t>
         </is>
       </c>
       <c r="AG7" t="inlineStr">
         <is>
-          <t>9.15</t>
+          <t>37.13</t>
         </is>
       </c>
       <c r="AH7" t="inlineStr">
         <is>
-          <t>0.09</t>
+          <t>2.78</t>
         </is>
       </c>
       <c r="AI7" t="inlineStr">
         <is>
-          <t>-4.77</t>
+          <t>-3.11</t>
         </is>
       </c>
       <c r="AJ7" t="inlineStr">
         <is>
-          <t>0.97</t>
+          <t>0.12</t>
         </is>
       </c>
       <c r="AK7" t="inlineStr">
         <is>
-          <t>12.14</t>
+          <t>11.79</t>
         </is>
       </c>
       <c r="AL7" t="inlineStr">
         <is>
-          <t>909.2</t>
+          <t>919.4</t>
         </is>
       </c>
       <c r="AM7" t="n">
-        <v>954.7</v>
+        <v>948.95</v>
       </c>
       <c r="AN7" t="n">
-        <v>945.54</v>
+        <v>947.8200000000001</v>
       </c>
       <c r="AO7" t="inlineStr">
         <is>
-          <t>843.16</t>
+          <t>847.89</t>
         </is>
       </c>
       <c r="AP7" t="inlineStr">
         <is>
-          <t>-265.70</t>
+          <t>-115.56</t>
         </is>
       </c>
       <c r="AQ7" t="inlineStr">
         <is>
-          <t>-14.36</t>
+          <t>-11.90</t>
         </is>
       </c>
       <c r="AR7" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-5.52</t>
         </is>
       </c>
       <c r="AS7" t="inlineStr">
@@ -3240,7 +3240,7 @@
       </c>
       <c r="AT7" t="inlineStr">
         <is>
-          <t>-106.06</t>
+          <t>-108.52</t>
         </is>
       </c>
       <c r="AU7" t="inlineStr">
@@ -3250,43 +3250,43 @@
       </c>
       <c r="AV7" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW7" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="AX7" t="n">
-        <v>13831910429.6</v>
+        <v>13777681330.2</v>
       </c>
       <c r="AY7" t="inlineStr">
         <is>
-          <t>13509805904.0</t>
+          <t>13184190874.5</t>
         </is>
       </c>
       <c r="AZ7" t="n">
-        <v>14413977761.06</v>
+        <v>14165986897.28</v>
       </c>
       <c r="BA7" t="inlineStr">
         <is>
-          <t>322104525</t>
+          <t>593490455</t>
         </is>
       </c>
       <c r="BB7" t="inlineStr">
         <is>
-          <t>-85354428.47894374</t>
+          <t>-116538291.2148735</t>
         </is>
       </c>
       <c r="BC7" t="inlineStr">
         <is>
-          <t>-94238805.57345963</t>
+          <t>-288049536.2624874</t>
         </is>
       </c>
       <c r="BD7" t="inlineStr">
         <is>
-          <t>9579043601.0</t>
+          <t>10702402903.0</t>
         </is>
       </c>
       <c r="BE7" t="inlineStr">
@@ -3306,7 +3306,7 @@
       </c>
       <c r="BH7" t="inlineStr">
         <is>
-          <t>140.74</t>
+          <t>150.00</t>
         </is>
       </c>
       <c r="BI7" t="inlineStr">
@@ -3351,22 +3351,22 @@
       </c>
       <c r="BQ7" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR7" t="inlineStr">
         <is>
-          <t>價跌量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS7" t="inlineStr">
         <is>
-          <t>9.82</t>
+          <t>10.20</t>
         </is>
       </c>
       <c r="BT7" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU7" t="inlineStr">
@@ -3376,7 +3376,7 @@
       </c>
       <c r="BV7" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW7" t="inlineStr">
@@ -3391,12 +3391,12 @@
       </c>
       <c r="BY7" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ7" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA7" t="inlineStr">
@@ -3416,22 +3416,22 @@
       </c>
       <c r="CD7" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>928.0</t>
         </is>
       </c>
       <c r="CE7" t="inlineStr">
         <is>
-          <t>926.0</t>
+          <t>950.0</t>
         </is>
       </c>
       <c r="CF7" t="inlineStr">
         <is>
-          <t>899.0</t>
+          <t>916.0</t>
         </is>
       </c>
       <c r="CG7" t="inlineStr">
         <is>
-          <t>910.0</t>
+          <t>945.0</t>
         </is>
       </c>
       <c r="CH7" t="inlineStr">
@@ -3463,12 +3463,12 @@
       </c>
       <c r="C8" t="inlineStr">
         <is>
-          <t>-0.22</t>
+          <t>1.86</t>
         </is>
       </c>
       <c r="D8" t="inlineStr">
         <is>
-          <t>18856.003</t>
+          <t>10504.174</t>
         </is>
       </c>
       <c r="E8" t="inlineStr">
@@ -3478,7 +3478,7 @@
       </c>
       <c r="F8" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="G8" t="inlineStr">
@@ -3488,17 +3488,17 @@
       </c>
       <c r="H8" t="inlineStr">
         <is>
-          <t>9.71</t>
+          <t>8.73</t>
         </is>
       </c>
       <c r="I8" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J8" t="inlineStr">
         <is>
-          <t>5.20</t>
+          <t>2.38</t>
         </is>
       </c>
       <c r="K8" t="inlineStr">
@@ -3518,7 +3518,7 @@
       </c>
       <c r="N8" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O8" t="inlineStr">
@@ -3573,17 +3573,17 @@
       </c>
       <c r="Y8" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z8" t="inlineStr">
         <is>
-          <t>65.24</t>
+          <t>36.34</t>
         </is>
       </c>
       <c r="AA8" t="inlineStr">
         <is>
-          <t>-1.79</t>
+          <t>-0.53</t>
         </is>
       </c>
       <c r="AB8" t="inlineStr">
@@ -3594,73 +3594,73 @@
       <c r="AC8" t="inlineStr"/>
       <c r="AD8" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE8" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF8" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>26.15</t>
         </is>
       </c>
       <c r="AG8" t="inlineStr">
         <is>
-          <t>23.15</t>
+          <t>9.15</t>
         </is>
       </c>
       <c r="AH8" t="inlineStr">
         <is>
-          <t>-1.52</t>
+          <t>0.09</t>
         </is>
       </c>
       <c r="AI8" t="inlineStr">
         <is>
-          <t>-5.83</t>
+          <t>-4.77</t>
         </is>
       </c>
       <c r="AJ8" t="inlineStr">
         <is>
-          <t>2.0</t>
+          <t>0.97</t>
         </is>
       </c>
       <c r="AK8" t="inlineStr">
         <is>
-          <t>12.60</t>
+          <t>12.14</t>
         </is>
       </c>
       <c r="AL8" t="inlineStr">
         <is>
-          <t>906.8</t>
+          <t>909.2</t>
         </is>
       </c>
       <c r="AM8" t="n">
-        <v>962.95</v>
+        <v>954.7</v>
       </c>
       <c r="AN8" t="n">
-        <v>944.08</v>
+        <v>945.54</v>
       </c>
       <c r="AO8" t="inlineStr">
         <is>
-          <t>838.41</t>
+          <t>843.16</t>
         </is>
       </c>
       <c r="AP8" t="inlineStr">
         <is>
-          <t>-940.86</t>
+          <t>-265.70</t>
         </is>
       </c>
       <c r="AQ8" t="inlineStr">
         <is>
-          <t>-13.72</t>
+          <t>-14.36</t>
         </is>
       </c>
       <c r="AR8" t="inlineStr">
         <is>
-          <t>-1.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AS8" t="inlineStr">
@@ -3670,7 +3670,7 @@
       </c>
       <c r="AT8" t="inlineStr">
         <is>
-          <t>-102.03</t>
+          <t>-106.06</t>
         </is>
       </c>
       <c r="AU8" t="inlineStr">
@@ -3680,43 +3680,43 @@
       </c>
       <c r="AV8" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW8" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="AX8" t="n">
-        <v>14386844246.4</v>
+        <v>13831910429.6</v>
       </c>
       <c r="AY8" t="inlineStr">
         <is>
-          <t>13675683609.2</t>
+          <t>13509805904.0</t>
         </is>
       </c>
       <c r="AZ8" t="n">
-        <v>14618581897.64</v>
+        <v>14413977761.06</v>
       </c>
       <c r="BA8" t="inlineStr">
         <is>
-          <t>711160637</t>
+          <t>322104525</t>
         </is>
       </c>
       <c r="BB8" t="inlineStr">
         <is>
-          <t>-83739087.18903175</t>
+          <t>-85354428.47894374</t>
         </is>
       </c>
       <c r="BC8" t="inlineStr">
         <is>
-          <t>306359263.681345</t>
+          <t>-94238805.57345963</t>
         </is>
       </c>
       <c r="BD8" t="inlineStr">
         <is>
-          <t>16911194399.0</t>
+          <t>9579043601.0</t>
         </is>
       </c>
       <c r="BE8" t="inlineStr">
@@ -3736,7 +3736,7 @@
       </c>
       <c r="BH8" t="inlineStr">
         <is>
-          <t>136.24</t>
+          <t>140.74</t>
         </is>
       </c>
       <c r="BI8" t="inlineStr">
@@ -3781,22 +3781,22 @@
       </c>
       <c r="BQ8" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR8" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量縮</t>
         </is>
       </c>
       <c r="BS8" t="inlineStr">
         <is>
-          <t>9.64</t>
+          <t>9.82</t>
         </is>
       </c>
       <c r="BT8" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU8" t="inlineStr">
@@ -3806,7 +3806,7 @@
       </c>
       <c r="BV8" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW8" t="inlineStr">
@@ -3821,12 +3821,12 @@
       </c>
       <c r="BY8" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ8" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA8" t="inlineStr">
@@ -3846,22 +3846,22 @@
       </c>
       <c r="CD8" t="inlineStr">
         <is>
-          <t>904.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CE8" t="inlineStr">
         <is>
-          <t>909.0</t>
+          <t>926.0</t>
         </is>
       </c>
       <c r="CF8" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>899.0</t>
         </is>
       </c>
       <c r="CG8" t="inlineStr">
         <is>
-          <t>893.0</t>
+          <t>910.0</t>
         </is>
       </c>
       <c r="CH8" t="inlineStr">
@@ -3893,12 +3893,12 @@
       </c>
       <c r="C9" t="inlineStr">
         <is>
-          <t>-6.5</t>
+          <t>-0.22</t>
         </is>
       </c>
       <c r="D9" t="inlineStr">
         <is>
-          <t>17544.293</t>
+          <t>18856.003</t>
         </is>
       </c>
       <c r="E9" t="inlineStr">
@@ -3908,7 +3908,7 @@
       </c>
       <c r="F9" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="G9" t="inlineStr">
@@ -3918,17 +3918,17 @@
       </c>
       <c r="H9" t="inlineStr">
         <is>
-          <t>9.5</t>
+          <t>10.43</t>
         </is>
       </c>
       <c r="I9" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J9" t="inlineStr">
         <is>
-          <t>0.21</t>
+          <t>5.20</t>
         </is>
       </c>
       <c r="K9" t="inlineStr">
@@ -3948,7 +3948,7 @@
       </c>
       <c r="N9" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O9" t="inlineStr">
@@ -4003,17 +4003,17 @@
       </c>
       <c r="Y9" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z9" t="inlineStr">
         <is>
-          <t>60.70</t>
+          <t>65.24</t>
         </is>
       </c>
       <c r="AA9" t="inlineStr">
         <is>
-          <t>-2.01</t>
+          <t>-1.79</t>
         </is>
       </c>
       <c r="AB9" t="inlineStr">
@@ -4024,17 +4024,17 @@
       <c r="AC9" t="inlineStr"/>
       <c r="AD9" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE9" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF9" t="inlineStr">
         <is>
-          <t>1.28</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG9" t="inlineStr">
@@ -4044,53 +4044,53 @@
       </c>
       <c r="AH9" t="inlineStr">
         <is>
-          <t>-1.80</t>
+          <t>-1.52</t>
         </is>
       </c>
       <c r="AI9" t="inlineStr">
         <is>
-          <t>-6.22</t>
+          <t>-5.83</t>
         </is>
       </c>
       <c r="AJ9" t="inlineStr">
         <is>
-          <t>3.17</t>
+          <t>2.0</t>
         </is>
       </c>
       <c r="AK9" t="inlineStr">
         <is>
-          <t>12.96</t>
+          <t>12.60</t>
         </is>
       </c>
       <c r="AL9" t="inlineStr">
         <is>
-          <t>911.4</t>
+          <t>906.8</t>
         </is>
       </c>
       <c r="AM9" t="n">
-        <v>971.8</v>
+        <v>962.95</v>
       </c>
       <c r="AN9" t="n">
-        <v>941.9</v>
+        <v>944.08</v>
       </c>
       <c r="AO9" t="inlineStr">
         <is>
-          <t>833.81</t>
+          <t>838.41</t>
         </is>
       </c>
       <c r="AP9" t="inlineStr">
         <is>
-          <t>-715.83</t>
+          <t>-940.86</t>
         </is>
       </c>
       <c r="AQ9" t="inlineStr">
         <is>
-          <t>-10.98</t>
+          <t>-13.72</t>
         </is>
       </c>
       <c r="AR9" t="inlineStr">
         <is>
-          <t>1.78</t>
+          <t>-1.32</t>
         </is>
       </c>
       <c r="AS9" t="inlineStr">
@@ -4100,7 +4100,7 @@
       </c>
       <c r="AT9" t="inlineStr">
         <is>
-          <t>-97.25</t>
+          <t>-102.03</t>
         </is>
       </c>
       <c r="AU9" t="inlineStr">
@@ -4110,43 +4110,43 @@
       </c>
       <c r="AV9" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW9" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="AX9" t="n">
-        <v>13146559354.4</v>
+        <v>14386844246.4</v>
       </c>
       <c r="AY9" t="inlineStr">
         <is>
-          <t>13118876980.5</t>
+          <t>13675683609.2</t>
         </is>
       </c>
       <c r="AZ9" t="n">
-        <v>14614553602.28</v>
+        <v>14618581897.64</v>
       </c>
       <c r="BA9" t="inlineStr">
         <is>
-          <t>27682373</t>
+          <t>711160637</t>
         </is>
       </c>
       <c r="BB9" t="inlineStr">
         <is>
-          <t>-154666060.0745548</t>
+          <t>-83739087.18903175</t>
         </is>
       </c>
       <c r="BC9" t="inlineStr">
         <is>
-          <t>82113231.98530579</t>
+          <t>306359263.681345</t>
         </is>
       </c>
       <c r="BD9" t="inlineStr">
         <is>
-          <t>15812987742.0</t>
+          <t>16911194399.0</t>
         </is>
       </c>
       <c r="BE9" t="inlineStr">
@@ -4166,7 +4166,7 @@
       </c>
       <c r="BH9" t="inlineStr">
         <is>
-          <t>136.77</t>
+          <t>136.24</t>
         </is>
       </c>
       <c r="BI9" t="inlineStr">
@@ -4221,12 +4221,12 @@
       </c>
       <c r="BS9" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.64</t>
         </is>
       </c>
       <c r="BT9" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU9" t="inlineStr">
@@ -4236,7 +4236,7 @@
       </c>
       <c r="BV9" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW9" t="inlineStr">
@@ -4251,12 +4251,12 @@
       </c>
       <c r="BY9" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ9" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA9" t="inlineStr">
@@ -4276,22 +4276,22 @@
       </c>
       <c r="CD9" t="inlineStr">
         <is>
-          <t>907.0</t>
+          <t>904.0</t>
         </is>
       </c>
       <c r="CE9" t="inlineStr">
         <is>
-          <t>913.0</t>
+          <t>909.0</t>
         </is>
       </c>
       <c r="CF9" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CG9" t="inlineStr">
         <is>
-          <t>895.0</t>
+          <t>893.0</t>
         </is>
       </c>
       <c r="CH9" t="inlineStr">
@@ -4323,12 +4323,12 @@
       </c>
       <c r="C10" t="inlineStr">
         <is>
-          <t>6.39</t>
+          <t>-6.5</t>
         </is>
       </c>
       <c r="D10" t="inlineStr">
         <is>
-          <t>16670.416</t>
+          <t>17544.293</t>
         </is>
       </c>
       <c r="E10" t="inlineStr">
@@ -4338,7 +4338,7 @@
       </c>
       <c r="F10" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="G10" t="inlineStr">
@@ -4348,17 +4348,17 @@
       </c>
       <c r="H10" t="inlineStr">
         <is>
-          <t>3.54</t>
+          <t>10.23</t>
         </is>
       </c>
       <c r="I10" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J10" t="inlineStr">
         <is>
-          <t>9.22</t>
+          <t>0.21</t>
         </is>
       </c>
       <c r="K10" t="inlineStr">
@@ -4378,7 +4378,7 @@
       </c>
       <c r="N10" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O10" t="inlineStr">
@@ -4433,17 +4433,17 @@
       </c>
       <c r="Y10" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z10" t="inlineStr">
         <is>
-          <t>57.68</t>
+          <t>60.70</t>
         </is>
       </c>
       <c r="AA10" t="inlineStr">
         <is>
-          <t>0.99</t>
+          <t>-2.01</t>
         </is>
       </c>
       <c r="AB10" t="inlineStr">
@@ -4454,73 +4454,73 @@
       <c r="AC10" t="inlineStr"/>
       <c r="AD10" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE10" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF10" t="inlineStr">
         <is>
-          <t>68.18</t>
+          <t>1.28</t>
         </is>
       </c>
       <c r="AG10" t="inlineStr">
         <is>
-          <t>22.73</t>
+          <t>23.15</t>
         </is>
       </c>
       <c r="AH10" t="inlineStr">
         <is>
-          <t>4.06</t>
+          <t>-1.80</t>
         </is>
       </c>
       <c r="AI10" t="inlineStr">
         <is>
-          <t>-6.21</t>
+          <t>-6.22</t>
         </is>
       </c>
       <c r="AJ10" t="inlineStr">
         <is>
-          <t>4.16</t>
+          <t>3.17</t>
         </is>
       </c>
       <c r="AK10" t="inlineStr">
         <is>
-          <t>13.19</t>
+          <t>12.96</t>
         </is>
       </c>
       <c r="AL10" t="inlineStr">
         <is>
-          <t>916.8</t>
+          <t>911.4</t>
         </is>
       </c>
       <c r="AM10" t="n">
-        <v>977.55</v>
+        <v>971.8</v>
       </c>
       <c r="AN10" t="n">
-        <v>938.52</v>
+        <v>941.9</v>
       </c>
       <c r="AO10" t="inlineStr">
         <is>
-          <t>829.15</t>
+          <t>833.81</t>
         </is>
       </c>
       <c r="AP10" t="inlineStr">
         <is>
-          <t>-251.21</t>
+          <t>-715.83</t>
         </is>
       </c>
       <c r="AQ10" t="inlineStr">
         <is>
-          <t>-7.52</t>
+          <t>-10.98</t>
         </is>
       </c>
       <c r="AR10" t="inlineStr">
         <is>
-          <t>4.97</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="AS10" t="inlineStr">
@@ -4530,7 +4530,7 @@
       </c>
       <c r="AT10" t="inlineStr">
         <is>
-          <t>-92.33</t>
+          <t>-97.25</t>
         </is>
       </c>
       <c r="AU10" t="inlineStr">
@@ -4540,43 +4540,43 @@
       </c>
       <c r="AV10" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW10" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="AX10" t="n">
-        <v>13620510362.4</v>
+        <v>13146559354.4</v>
       </c>
       <c r="AY10" t="inlineStr">
         <is>
-          <t>12470961715.4</t>
+          <t>13118876980.5</t>
         </is>
       </c>
       <c r="AZ10" t="n">
-        <v>14466055493.78</v>
+        <v>14614553602.28</v>
       </c>
       <c r="BA10" t="inlineStr">
         <is>
-          <t>1149548647</t>
+          <t>27682373</t>
         </is>
       </c>
       <c r="BB10" t="inlineStr">
         <is>
-          <t>-197716840.4490749</t>
+          <t>-154666060.0745548</t>
         </is>
       </c>
       <c r="BC10" t="inlineStr">
         <is>
-          <t>-123505858.3299389</t>
+          <t>82113231.98530579</t>
         </is>
       </c>
       <c r="BD10" t="inlineStr">
         <is>
-          <t>15882778006.0</t>
+          <t>15812987742.0</t>
         </is>
       </c>
       <c r="BE10" t="inlineStr">
@@ -4596,7 +4596,7 @@
       </c>
       <c r="BH10" t="inlineStr">
         <is>
-          <t>152.38</t>
+          <t>136.77</t>
         </is>
       </c>
       <c r="BI10" t="inlineStr">
@@ -4646,17 +4646,17 @@
       </c>
       <c r="BR10" t="inlineStr">
         <is>
-          <t>價漲量增</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS10" t="inlineStr">
         <is>
-          <t>10.29</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="BT10" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU10" t="inlineStr">
@@ -4666,7 +4666,7 @@
       </c>
       <c r="BV10" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW10" t="inlineStr">
@@ -4681,12 +4681,12 @@
       </c>
       <c r="BY10" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ10" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA10" t="inlineStr">
@@ -4706,22 +4706,22 @@
       </c>
       <c r="CD10" t="inlineStr">
         <is>
-          <t>939.0</t>
+          <t>907.0</t>
         </is>
       </c>
       <c r="CE10" t="inlineStr">
         <is>
-          <t>965.0</t>
+          <t>913.0</t>
         </is>
       </c>
       <c r="CF10" t="inlineStr">
         <is>
-          <t>934.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CG10" t="inlineStr">
         <is>
-          <t>954.0</t>
+          <t>895.0</t>
         </is>
       </c>
       <c r="CH10" t="inlineStr">
@@ -4753,12 +4753,12 @@
       </c>
       <c r="C11" t="inlineStr">
         <is>
-          <t>-0.45</t>
+          <t>6.39</t>
         </is>
       </c>
       <c r="D11" t="inlineStr">
         <is>
-          <t>12208.506</t>
+          <t>16670.416</t>
         </is>
       </c>
       <c r="E11" t="inlineStr">
@@ -4768,7 +4768,7 @@
       </c>
       <c r="F11" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="G11" t="inlineStr">
@@ -4778,17 +4778,17 @@
       </c>
       <c r="H11" t="inlineStr">
         <is>
-          <t>9.61</t>
+          <t>4.31</t>
         </is>
       </c>
       <c r="I11" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J11" t="inlineStr">
         <is>
-          <t>5.64</t>
+          <t>9.22</t>
         </is>
       </c>
       <c r="K11" t="inlineStr">
@@ -4808,7 +4808,7 @@
       </c>
       <c r="N11" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O11" t="inlineStr">
@@ -4863,17 +4863,17 @@
       </c>
       <c r="Y11" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z11" t="inlineStr">
         <is>
-          <t>42.24</t>
+          <t>57.68</t>
         </is>
       </c>
       <c r="AA11" t="inlineStr">
         <is>
-          <t>-1.34</t>
+          <t>0.99</t>
         </is>
       </c>
       <c r="AB11" t="inlineStr">
@@ -4884,73 +4884,73 @@
       <c r="AC11" t="inlineStr"/>
       <c r="AD11" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE11" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>68.18</t>
         </is>
       </c>
       <c r="AG11" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>22.73</t>
         </is>
       </c>
       <c r="AH11" t="inlineStr">
         <is>
-          <t>-2.57</t>
+          <t>4.06</t>
         </is>
       </c>
       <c r="AI11" t="inlineStr">
         <is>
-          <t>-6.45</t>
+          <t>-6.21</t>
         </is>
       </c>
       <c r="AJ11" t="inlineStr">
         <is>
-          <t>5.02</t>
+          <t>4.16</t>
         </is>
       </c>
       <c r="AK11" t="inlineStr">
         <is>
-          <t>13.39</t>
+          <t>13.19</t>
         </is>
       </c>
       <c r="AL11" t="inlineStr">
         <is>
-          <t>917.6</t>
+          <t>916.8</t>
         </is>
       </c>
       <c r="AM11" t="n">
-        <v>980.85</v>
+        <v>977.55</v>
       </c>
       <c r="AN11" t="n">
-        <v>933.96</v>
+        <v>938.52</v>
       </c>
       <c r="AO11" t="inlineStr">
         <is>
-          <t>823.69</t>
+          <t>829.15</t>
         </is>
       </c>
       <c r="AP11" t="inlineStr">
         <is>
-          <t>-211.22</t>
+          <t>-251.21</t>
         </is>
       </c>
       <c r="AQ11" t="inlineStr">
         <is>
-          <t>-9.00</t>
+          <t>-7.52</t>
         </is>
       </c>
       <c r="AR11" t="inlineStr">
         <is>
-          <t>8.09</t>
+          <t>4.97</t>
         </is>
       </c>
       <c r="AS11" t="inlineStr">
@@ -4960,7 +4960,7 @@
       </c>
       <c r="AT11" t="inlineStr">
         <is>
-          <t>-87.51</t>
+          <t>-92.33</t>
         </is>
       </c>
       <c r="AU11" t="inlineStr">
@@ -4970,43 +4970,43 @@
       </c>
       <c r="AV11" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW11" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="AX11" t="n">
-        <v>12590700418.8</v>
+        <v>13620510362.4</v>
       </c>
       <c r="AY11" t="inlineStr">
         <is>
-          <t>11918833012.0</t>
+          <t>12470961715.4</t>
         </is>
       </c>
       <c r="AZ11" t="n">
-        <v>14368721493.28</v>
+        <v>14466055493.78</v>
       </c>
       <c r="BA11" t="inlineStr">
         <is>
-          <t>671867406</t>
+          <t>1149548647</t>
         </is>
       </c>
       <c r="BB11" t="inlineStr">
         <is>
-          <t>-211209746.2889178</t>
+          <t>-197716840.4490749</t>
         </is>
       </c>
       <c r="BC11" t="inlineStr">
         <is>
-          <t>-420314020.6970749</t>
+          <t>-123505858.3299389</t>
         </is>
       </c>
       <c r="BD11" t="inlineStr">
         <is>
-          <t>10973548400.0</t>
+          <t>15882778006.0</t>
         </is>
       </c>
       <c r="BE11" t="inlineStr">
@@ -5026,7 +5026,7 @@
       </c>
       <c r="BH11" t="inlineStr">
         <is>
-          <t>136.51</t>
+          <t>152.38</t>
         </is>
       </c>
       <c r="BI11" t="inlineStr">
@@ -5071,7 +5071,7 @@
       </c>
       <c r="BQ11" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR11" t="inlineStr">
@@ -5081,12 +5081,12 @@
       </c>
       <c r="BS11" t="inlineStr">
         <is>
-          <t>9.65</t>
+          <t>10.29</t>
         </is>
       </c>
       <c r="BT11" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU11" t="inlineStr">
@@ -5096,7 +5096,7 @@
       </c>
       <c r="BV11" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW11" t="inlineStr">
@@ -5111,12 +5111,12 @@
       </c>
       <c r="BY11" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ11" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA11" t="inlineStr">
@@ -5136,22 +5136,22 @@
       </c>
       <c r="CD11" t="inlineStr">
         <is>
-          <t>890.0</t>
+          <t>939.0</t>
         </is>
       </c>
       <c r="CE11" t="inlineStr">
         <is>
-          <t>911.0</t>
+          <t>965.0</t>
         </is>
       </c>
       <c r="CF11" t="inlineStr">
         <is>
-          <t>889.0</t>
+          <t>934.0</t>
         </is>
       </c>
       <c r="CG11" t="inlineStr">
         <is>
-          <t>894.0</t>
+          <t>954.0</t>
         </is>
       </c>
       <c r="CH11" t="inlineStr">
@@ -5183,12 +5183,12 @@
       </c>
       <c r="C12" t="inlineStr">
         <is>
-          <t>-1.99</t>
+          <t>-0.45</t>
         </is>
       </c>
       <c r="D12" t="inlineStr">
         <is>
-          <t>13615.098</t>
+          <t>12208.506</t>
         </is>
       </c>
       <c r="E12" t="inlineStr">
@@ -5198,7 +5198,7 @@
       </c>
       <c r="F12" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="G12" t="inlineStr">
@@ -5208,17 +5208,17 @@
       </c>
       <c r="H12" t="inlineStr">
         <is>
-          <t>9.2</t>
+          <t>10.33</t>
         </is>
       </c>
       <c r="I12" t="inlineStr">
         <is>
-          <t>2.04</t>
+          <t>1.78</t>
         </is>
       </c>
       <c r="J12" t="inlineStr">
         <is>
-          <t>5.17</t>
+          <t>5.64</t>
         </is>
       </c>
       <c r="K12" t="inlineStr">
@@ -5238,7 +5238,7 @@
       </c>
       <c r="N12" t="inlineStr">
         <is>
-          <t>2025-12-03 00:00:00</t>
+          <t>2025-12-04 00:00:00</t>
         </is>
       </c>
       <c r="O12" t="inlineStr">
@@ -5293,17 +5293,17 @@
       </c>
       <c r="Y12" t="inlineStr">
         <is>
-          <t>2025-11-18</t>
+          <t>2025-11-19</t>
         </is>
       </c>
       <c r="Z12" t="inlineStr">
         <is>
-          <t>47.11</t>
+          <t>42.24</t>
         </is>
       </c>
       <c r="AA12" t="inlineStr">
         <is>
-          <t>-3.56</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="AB12" t="inlineStr">
@@ -5314,12 +5314,12 @@
       <c r="AC12" t="inlineStr"/>
       <c r="AD12" t="inlineStr">
         <is>
-          <t>734</t>
+          <t>406</t>
         </is>
       </c>
       <c r="AE12" t="inlineStr">
         <is>
-          <t>20318</t>
+          <t>12779</t>
         </is>
       </c>
       <c r="AF12" t="inlineStr">
@@ -5334,53 +5334,53 @@
       </c>
       <c r="AH12" t="inlineStr">
         <is>
-          <t>-3.67</t>
+          <t>-2.57</t>
         </is>
       </c>
       <c r="AI12" t="inlineStr">
         <is>
-          <t>-5.57</t>
+          <t>-6.45</t>
         </is>
       </c>
       <c r="AJ12" t="inlineStr">
         <is>
-          <t>6.16</t>
+          <t>5.02</t>
         </is>
       </c>
       <c r="AK12" t="inlineStr">
         <is>
-          <t>13.54</t>
+          <t>13.39</t>
         </is>
       </c>
       <c r="AL12" t="inlineStr">
         <is>
-          <t>932.2</t>
+          <t>917.6</t>
         </is>
       </c>
       <c r="AM12" t="n">
-        <v>987.15</v>
+        <v>980.85</v>
       </c>
       <c r="AN12" t="n">
-        <v>929.9</v>
+        <v>933.96</v>
       </c>
       <c r="AO12" t="inlineStr">
         <is>
-          <t>818.99</t>
+          <t>823.69</t>
         </is>
       </c>
       <c r="AP12" t="inlineStr">
         <is>
-          <t>-137.65</t>
+          <t>-211.22</t>
         </is>
       </c>
       <c r="AQ12" t="inlineStr">
         <is>
-          <t>-4.66</t>
+          <t>-9.00</t>
         </is>
       </c>
       <c r="AR12" t="inlineStr">
         <is>
-          <t>12.37</t>
+          <t>8.09</t>
         </is>
       </c>
       <c r="AS12" t="inlineStr">
@@ -5390,7 +5390,7 @@
       </c>
       <c r="AT12" t="inlineStr">
         <is>
-          <t>-80.92</t>
+          <t>-87.51</t>
         </is>
       </c>
       <c r="AU12" t="inlineStr">
@@ -5400,43 +5400,43 @@
       </c>
       <c r="AV12" t="inlineStr">
         <is>
-          <t>6530976217.278093</t>
+          <t>6548732533.429688</t>
         </is>
       </c>
       <c r="AW12" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="AX12" t="n">
-        <v>13187701378.4</v>
+        <v>12590700418.8</v>
       </c>
       <c r="AY12" t="inlineStr">
         <is>
-          <t>12539817288.3</t>
+          <t>11918833012.0</t>
         </is>
       </c>
       <c r="AZ12" t="n">
-        <v>14292572173.18</v>
+        <v>14368721493.28</v>
       </c>
       <c r="BA12" t="inlineStr">
         <is>
-          <t>647884090</t>
+          <t>671867406</t>
         </is>
       </c>
       <c r="BB12" t="inlineStr">
         <is>
-          <t>-173190787.3056165</t>
+          <t>-211209746.2889178</t>
         </is>
       </c>
       <c r="BC12" t="inlineStr">
         <is>
-          <t>-303325579.8395176</t>
+          <t>-420314020.6970749</t>
         </is>
       </c>
       <c r="BD12" t="inlineStr">
         <is>
-          <t>12353712685.0</t>
+          <t>10973548400.0</t>
         </is>
       </c>
       <c r="BE12" t="inlineStr">
@@ -5456,7 +5456,7 @@
       </c>
       <c r="BH12" t="inlineStr">
         <is>
-          <t>137.57</t>
+          <t>136.51</t>
         </is>
       </c>
       <c r="BI12" t="inlineStr">
@@ -5501,7 +5501,7 @@
       </c>
       <c r="BQ12" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR12" t="inlineStr">
@@ -5511,12 +5511,12 @@
       </c>
       <c r="BS12" t="inlineStr">
         <is>
-          <t>9.69</t>
+          <t>9.65</t>
         </is>
       </c>
       <c r="BT12" t="inlineStr">
         <is>
-          <t>0.71</t>
+          <t>0.7</t>
         </is>
       </c>
       <c r="BU12" t="inlineStr">
@@ -5526,7 +5526,7 @@
       </c>
       <c r="BV12" t="inlineStr">
         <is>
-          <t>51.43</t>
+          <t>51.85</t>
         </is>
       </c>
       <c r="BW12" t="inlineStr">
@@ -5541,12 +5541,12 @@
       </c>
       <c r="BY12" t="inlineStr">
         <is>
-          <t>34.53</t>
+          <t>34.97</t>
         </is>
       </c>
       <c r="BZ12" t="inlineStr">
         <is>
-          <t>2568970</t>
+          <t>2589750</t>
         </is>
       </c>
       <c r="CA12" t="inlineStr">
@@ -5566,22 +5566,22 @@
       </c>
       <c r="CD12" t="inlineStr">
         <is>
-          <t>906.0</t>
+          <t>890.0</t>
         </is>
       </c>
       <c r="CE12" t="inlineStr">
         <is>
-          <t>930.0</t>
+          <t>911.0</t>
         </is>
       </c>
       <c r="CF12" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>889.0</t>
         </is>
       </c>
       <c r="CG12" t="inlineStr">
         <is>
-          <t>898.0</t>
+          <t>894.0</t>
         </is>
       </c>
       <c r="CH12" t="inlineStr">
@@ -5613,12 +5613,12 @@
       </c>
       <c r="C13" t="inlineStr">
         <is>
-          <t>1.88</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="D13" t="inlineStr">
         <is>
-          <t>22425.724</t>
+          <t>13251.743</t>
         </is>
       </c>
       <c r="E13" t="inlineStr">
@@ -5628,7 +5628,7 @@
       </c>
       <c r="F13" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="G13" t="inlineStr">
@@ -5643,12 +5643,12 @@
       </c>
       <c r="I13" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J13" t="inlineStr">
         <is>
-          <t>-47.03</t>
+          <t>-53.77</t>
         </is>
       </c>
       <c r="K13" t="inlineStr">
@@ -5713,7 +5713,7 @@
       </c>
       <c r="W13" t="inlineStr">
         <is>
-          <t>-16.73</t>
+          <t>-16.35</t>
         </is>
       </c>
       <c r="X13" t="inlineStr">
@@ -5723,17 +5723,17 @@
       </c>
       <c r="Y13" t="inlineStr">
         <is>
-          <t>2025-12-02</t>
+          <t>2025-12-03</t>
         </is>
       </c>
       <c r="Z13" t="inlineStr">
         <is>
-          <t>6.77</t>
+          <t>4.00</t>
         </is>
       </c>
       <c r="AA13" t="inlineStr">
         <is>
-          <t>-0.07</t>
+          <t>-1.37</t>
         </is>
       </c>
       <c r="AB13" t="inlineStr">
@@ -5744,73 +5744,73 @@
       <c r="AC13" t="inlineStr"/>
       <c r="AD13" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE13" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF13" t="inlineStr">
         <is>
-          <t>14.41</t>
+          <t>25.32</t>
         </is>
       </c>
       <c r="AG13" t="inlineStr">
         <is>
-          <t>6.68</t>
+          <t>13.24</t>
         </is>
       </c>
       <c r="AH13" t="inlineStr">
         <is>
-          <t>-0.48</t>
+          <t>0.02</t>
         </is>
       </c>
       <c r="AI13" t="inlineStr">
         <is>
-          <t>-10.62</t>
+          <t>-9.55</t>
         </is>
       </c>
       <c r="AJ13" t="inlineStr">
         <is>
-          <t>-5.69</t>
+          <t>-6.92</t>
         </is>
       </c>
       <c r="AK13" t="inlineStr">
         <is>
-          <t>14.31</t>
+          <t>13.91</t>
         </is>
       </c>
       <c r="AL13" t="inlineStr">
         <is>
-          <t>87.02</t>
+          <t>86.97999999999999</t>
         </is>
       </c>
       <c r="AM13" t="n">
-        <v>97.36</v>
+        <v>96.16</v>
       </c>
       <c r="AN13" t="n">
-        <v>103.24</v>
+        <v>103.31</v>
       </c>
       <c r="AO13" t="inlineStr">
         <is>
-          <t>90.31</t>
+          <t>90.7</t>
         </is>
       </c>
       <c r="AP13" t="inlineStr">
         <is>
-          <t>-37.45</t>
+          <t>-27.20</t>
         </is>
       </c>
       <c r="AQ13" t="inlineStr">
         <is>
-          <t>-5.33</t>
+          <t>-5.29</t>
         </is>
       </c>
       <c r="AR13" t="inlineStr">
         <is>
-          <t>-3.88</t>
+          <t>-4.16</t>
         </is>
       </c>
       <c r="AS13" t="inlineStr">
@@ -5820,7 +5820,7 @@
       </c>
       <c r="AT13" t="inlineStr">
         <is>
-          <t>-139.07</t>
+          <t>-141.92</t>
         </is>
       </c>
       <c r="AU13" t="inlineStr">
@@ -5830,43 +5830,43 @@
       </c>
       <c r="AV13" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW13" t="inlineStr">
         <is>
-          <t>1953507738.0</t>
+          <t>1157608498.0</t>
         </is>
       </c>
       <c r="AX13" t="n">
-        <v>1808547588.4</v>
+        <v>1503360124.4</v>
       </c>
       <c r="AY13" t="inlineStr">
         <is>
-          <t>3414062816.4</t>
+          <t>3252022736.9</t>
         </is>
       </c>
       <c r="AZ13" t="n">
-        <v>6610661657.54</v>
+        <v>6558031030.34</v>
       </c>
       <c r="BA13" t="inlineStr">
         <is>
-          <t>-1605515228</t>
+          <t>-1748662612</t>
         </is>
       </c>
       <c r="BB13" t="inlineStr">
         <is>
-          <t>-389584858.462798</t>
+          <t>-425132584.4117541</t>
         </is>
       </c>
       <c r="BC13" t="inlineStr">
         <is>
-          <t>-564576189.6084146</t>
+          <t>-620645077.1310129</t>
         </is>
       </c>
       <c r="BD13" t="inlineStr">
         <is>
-          <t>1953507738.0</t>
+          <t>1157608498.0</t>
         </is>
       </c>
       <c r="BE13" t="inlineStr">
@@ -5886,7 +5886,7 @@
       </c>
       <c r="BH13" t="inlineStr">
         <is>
-          <t>56.60</t>
+          <t>57.32</t>
         </is>
       </c>
       <c r="BI13" t="inlineStr">
@@ -5911,7 +5911,7 @@
       </c>
       <c r="BM13" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN13" t="inlineStr">
@@ -5931,7 +5931,7 @@
       </c>
       <c r="BQ13" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;觀望&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR13" t="inlineStr">
@@ -5941,12 +5941,12 @@
       </c>
       <c r="BS13" t="inlineStr">
         <is>
-          <t>2.31</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT13" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU13" t="inlineStr">
@@ -5956,7 +5956,7 @@
       </c>
       <c r="BV13" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW13" t="inlineStr">
@@ -5971,12 +5971,12 @@
       </c>
       <c r="BY13" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ13" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA13" t="inlineStr">
@@ -5996,22 +5996,22 @@
       </c>
       <c r="CD13" t="inlineStr">
         <is>
-          <t>85.2</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CE13" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>88.8</t>
         </is>
       </c>
       <c r="CF13" t="inlineStr">
         <is>
-          <t>84.8</t>
+          <t>86.4</t>
         </is>
       </c>
       <c r="CG13" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.0</t>
         </is>
       </c>
       <c r="CH13" t="inlineStr">
@@ -6043,12 +6043,12 @@
       </c>
       <c r="C14" t="inlineStr">
         <is>
-          <t>-3.09</t>
+          <t>1.88</t>
         </is>
       </c>
       <c r="D14" t="inlineStr">
         <is>
-          <t>16762.955</t>
+          <t>22425.724</t>
         </is>
       </c>
       <c r="E14" t="inlineStr">
@@ -6058,7 +6058,7 @@
       </c>
       <c r="F14" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="G14" t="inlineStr">
@@ -6068,17 +6068,17 @@
       </c>
       <c r="H14" t="inlineStr">
         <is>
-          <t>1.85</t>
+          <t>0.46</t>
         </is>
       </c>
       <c r="I14" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J14" t="inlineStr">
         <is>
-          <t>-33.22</t>
+          <t>-47.03</t>
         </is>
       </c>
       <c r="K14" t="inlineStr">
@@ -6143,7 +6143,7 @@
       </c>
       <c r="W14" t="inlineStr">
         <is>
-          <t>-18.27</t>
+          <t>-16.73</t>
         </is>
       </c>
       <c r="X14" t="inlineStr">
@@ -6153,17 +6153,17 @@
       </c>
       <c r="Y14" t="inlineStr">
         <is>
-          <t>2025-12-01</t>
+          <t>2025-12-02</t>
         </is>
       </c>
       <c r="Z14" t="inlineStr">
         <is>
-          <t>5.06</t>
+          <t>6.77</t>
         </is>
       </c>
       <c r="AA14" t="inlineStr">
         <is>
-          <t>-2.59</t>
+          <t>-0.07</t>
         </is>
       </c>
       <c r="AB14" t="inlineStr">
@@ -6174,73 +6174,73 @@
       <c r="AC14" t="inlineStr"/>
       <c r="AD14" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE14" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF14" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.41</t>
         </is>
       </c>
       <c r="AG14" t="inlineStr">
         <is>
-          <t>6.84</t>
+          <t>6.68</t>
         </is>
       </c>
       <c r="AH14" t="inlineStr">
         <is>
-          <t>-2.75</t>
+          <t>-0.48</t>
         </is>
       </c>
       <c r="AI14" t="inlineStr">
         <is>
-          <t>-11.46</t>
+          <t>-10.62</t>
         </is>
       </c>
       <c r="AJ14" t="inlineStr">
         <is>
-          <t>-4.39</t>
+          <t>-5.69</t>
         </is>
       </c>
       <c r="AK14" t="inlineStr">
         <is>
-          <t>14.83</t>
+          <t>14.31</t>
         </is>
       </c>
       <c r="AL14" t="inlineStr">
         <is>
-          <t>87.4</t>
+          <t>87.02</t>
         </is>
       </c>
       <c r="AM14" t="n">
-        <v>98.70999999999999</v>
+        <v>97.36</v>
       </c>
       <c r="AN14" t="n">
         <v>103.24</v>
       </c>
       <c r="AO14" t="inlineStr">
         <is>
-          <t>89.91</t>
+          <t>90.31</t>
         </is>
       </c>
       <c r="AP14" t="inlineStr">
         <is>
-          <t>-49.64</t>
+          <t>-37.45</t>
         </is>
       </c>
       <c r="AQ14" t="inlineStr">
         <is>
-          <t>-5.26</t>
+          <t>-5.33</t>
         </is>
       </c>
       <c r="AR14" t="inlineStr">
         <is>
-          <t>-3.51</t>
+          <t>-3.88</t>
         </is>
       </c>
       <c r="AS14" t="inlineStr">
@@ -6250,7 +6250,7 @@
       </c>
       <c r="AT14" t="inlineStr">
         <is>
-          <t>-135.42</t>
+          <t>-139.07</t>
         </is>
       </c>
       <c r="AU14" t="inlineStr">
@@ -6260,43 +6260,43 @@
       </c>
       <c r="AV14" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW14" t="inlineStr">
         <is>
-          <t>1432793005.0</t>
+          <t>1953507738.0</t>
         </is>
       </c>
       <c r="AX14" t="n">
-        <v>2354299255.4</v>
+        <v>1808547588.4</v>
       </c>
       <c r="AY14" t="inlineStr">
         <is>
-          <t>3525608023.4</t>
+          <t>3414062816.4</t>
         </is>
       </c>
       <c r="AZ14" t="n">
-        <v>6627710000.74</v>
+        <v>6610661657.54</v>
       </c>
       <c r="BA14" t="inlineStr">
         <is>
-          <t>-1171308768</t>
+          <t>-1605515228</t>
         </is>
       </c>
       <c r="BB14" t="inlineStr">
         <is>
-          <t>-357768252.7999586</t>
+          <t>-389584858.462798</t>
         </is>
       </c>
       <c r="BC14" t="inlineStr">
         <is>
-          <t>-549589262.0901175</t>
+          <t>-564576189.6084146</t>
         </is>
       </c>
       <c r="BD14" t="inlineStr">
         <is>
-          <t>1432793005.0</t>
+          <t>1953507738.0</t>
         </is>
       </c>
       <c r="BE14" t="inlineStr">
@@ -6316,7 +6316,7 @@
       </c>
       <c r="BH14" t="inlineStr">
         <is>
-          <t>53.71</t>
+          <t>56.60</t>
         </is>
       </c>
       <c r="BI14" t="inlineStr">
@@ -6341,7 +6341,7 @@
       </c>
       <c r="BM14" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN14" t="inlineStr">
@@ -6361,7 +6361,7 @@
       </c>
       <c r="BQ14" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR14" t="inlineStr">
@@ -6371,12 +6371,12 @@
       </c>
       <c r="BS14" t="inlineStr">
         <is>
-          <t>2.27</t>
+          <t>2.31</t>
         </is>
       </c>
       <c r="BT14" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU14" t="inlineStr">
@@ -6386,7 +6386,7 @@
       </c>
       <c r="BV14" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW14" t="inlineStr">
@@ -6401,12 +6401,12 @@
       </c>
       <c r="BY14" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ14" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA14" t="inlineStr">
@@ -6426,22 +6426,22 @@
       </c>
       <c r="CD14" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>85.2</t>
         </is>
       </c>
       <c r="CE14" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CF14" t="inlineStr">
         <is>
-          <t>84.7</t>
+          <t>84.8</t>
         </is>
       </c>
       <c r="CG14" t="inlineStr">
         <is>
-          <t>85.0</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CH14" t="inlineStr">
@@ -6473,12 +6473,12 @@
       </c>
       <c r="C15" t="inlineStr">
         <is>
-          <t>-1.01</t>
+          <t>-3.09</t>
         </is>
       </c>
       <c r="D15" t="inlineStr">
         <is>
-          <t>16281.325</t>
+          <t>16762.955</t>
         </is>
       </c>
       <c r="E15" t="inlineStr">
@@ -6488,7 +6488,7 @@
       </c>
       <c r="F15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="G15" t="inlineStr">
@@ -6498,17 +6498,17 @@
       </c>
       <c r="H15" t="inlineStr">
         <is>
-          <t>-1.27</t>
+          <t>2.3</t>
         </is>
       </c>
       <c r="I15" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J15" t="inlineStr">
         <is>
-          <t>15.59</t>
+          <t>-33.22</t>
         </is>
       </c>
       <c r="K15" t="inlineStr">
@@ -6573,7 +6573,7 @@
       </c>
       <c r="W15" t="inlineStr">
         <is>
-          <t>-15.67</t>
+          <t>-18.27</t>
         </is>
       </c>
       <c r="X15" t="inlineStr">
@@ -6583,17 +6583,17 @@
       </c>
       <c r="Y15" t="inlineStr">
         <is>
-          <t>2025-11-28</t>
+          <t>2025-12-01</t>
         </is>
       </c>
       <c r="Z15" t="inlineStr">
         <is>
-          <t>4.92</t>
+          <t>5.06</t>
         </is>
       </c>
       <c r="AA15" t="inlineStr">
         <is>
-          <t>-0.79</t>
+          <t>-2.59</t>
         </is>
       </c>
       <c r="AB15" t="inlineStr">
@@ -6604,17 +6604,17 @@
       <c r="AC15" t="inlineStr"/>
       <c r="AD15" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE15" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF15" t="inlineStr">
         <is>
-          <t>5.62</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG15" t="inlineStr">
@@ -6624,53 +6624,53 @@
       </c>
       <c r="AH15" t="inlineStr">
         <is>
-          <t>-1.44</t>
+          <t>-2.75</t>
         </is>
       </c>
       <c r="AI15" t="inlineStr">
         <is>
-          <t>-11.23</t>
+          <t>-11.46</t>
         </is>
       </c>
       <c r="AJ15" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-4.39</t>
         </is>
       </c>
       <c r="AK15" t="inlineStr">
         <is>
-          <t>15.39</t>
+          <t>14.83</t>
         </is>
       </c>
       <c r="AL15" t="inlineStr">
         <is>
-          <t>88.98</t>
+          <t>87.4</t>
         </is>
       </c>
       <c r="AM15" t="n">
-        <v>100.24</v>
+        <v>98.70999999999999</v>
       </c>
       <c r="AN15" t="n">
-        <v>103.28</v>
+        <v>103.24</v>
       </c>
       <c r="AO15" t="inlineStr">
         <is>
-          <t>89.51</t>
+          <t>89.91</t>
         </is>
       </c>
       <c r="AP15" t="inlineStr">
         <is>
-          <t>-60.15</t>
+          <t>-49.64</t>
         </is>
       </c>
       <c r="AQ15" t="inlineStr">
         <is>
-          <t>-4.93</t>
+          <t>-5.26</t>
         </is>
       </c>
       <c r="AR15" t="inlineStr">
         <is>
-          <t>-3.08</t>
+          <t>-3.51</t>
         </is>
       </c>
       <c r="AS15" t="inlineStr">
@@ -6680,7 +6680,7 @@
       </c>
       <c r="AT15" t="inlineStr">
         <is>
-          <t>-131.02</t>
+          <t>-135.42</t>
         </is>
       </c>
       <c r="AU15" t="inlineStr">
@@ -6690,43 +6690,43 @@
       </c>
       <c r="AV15" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW15" t="inlineStr">
         <is>
-          <t>1429040476.0</t>
+          <t>1432793005.0</t>
         </is>
       </c>
       <c r="AX15" t="n">
-        <v>4370895798.6</v>
+        <v>2354299255.4</v>
       </c>
       <c r="AY15" t="inlineStr">
         <is>
-          <t>3781268811.0</t>
+          <t>3525608023.4</t>
         </is>
       </c>
       <c r="AZ15" t="n">
-        <v>6680203633.36</v>
+        <v>6627710000.74</v>
       </c>
       <c r="BA15" t="inlineStr">
         <is>
-          <t>589626987</t>
+          <t>-1171308768</t>
         </is>
       </c>
       <c r="BB15" t="inlineStr">
         <is>
-          <t>-322891705.6562934</t>
+          <t>-357768252.7999586</t>
         </is>
       </c>
       <c r="BC15" t="inlineStr">
         <is>
-          <t>-452760313.4536171</t>
+          <t>-549589262.0901175</t>
         </is>
       </c>
       <c r="BD15" t="inlineStr">
         <is>
-          <t>1429040476.0</t>
+          <t>1432793005.0</t>
         </is>
       </c>
       <c r="BE15" t="inlineStr">
@@ -6746,7 +6746,7 @@
       </c>
       <c r="BH15" t="inlineStr">
         <is>
-          <t>58.59</t>
+          <t>53.71</t>
         </is>
       </c>
       <c r="BI15" t="inlineStr">
@@ -6771,7 +6771,7 @@
       </c>
       <c r="BM15" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN15" t="inlineStr">
@@ -6791,22 +6791,22 @@
       </c>
       <c r="BQ15" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR15" t="inlineStr">
         <is>
-          <t>價漲量縮</t>
+          <t>價-量-</t>
         </is>
       </c>
       <c r="BS15" t="inlineStr">
         <is>
-          <t>2.34</t>
+          <t>2.27</t>
         </is>
       </c>
       <c r="BT15" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU15" t="inlineStr">
@@ -6816,7 +6816,7 @@
       </c>
       <c r="BV15" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW15" t="inlineStr">
@@ -6831,12 +6831,12 @@
       </c>
       <c r="BY15" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ15" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA15" t="inlineStr">
@@ -6856,22 +6856,22 @@
       </c>
       <c r="CD15" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CE15" t="inlineStr">
         <is>
-          <t>89.0</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CF15" t="inlineStr">
         <is>
-          <t>87.1</t>
+          <t>84.7</t>
         </is>
       </c>
       <c r="CG15" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>85.0</t>
         </is>
       </c>
       <c r="CH15" t="inlineStr">
@@ -6903,12 +6903,12 @@
       </c>
       <c r="C16" t="inlineStr">
         <is>
-          <t>1.6</t>
+          <t>-1.01</t>
         </is>
       </c>
       <c r="D16" t="inlineStr">
         <is>
-          <t>17538.055</t>
+          <t>16281.325</t>
         </is>
       </c>
       <c r="E16" t="inlineStr">
@@ -6918,7 +6918,7 @@
       </c>
       <c r="F16" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="G16" t="inlineStr">
@@ -6928,17 +6928,17 @@
       </c>
       <c r="H16" t="inlineStr">
         <is>
-          <t>-2.31</t>
+          <t>-0.8</t>
         </is>
       </c>
       <c r="I16" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J16" t="inlineStr">
         <is>
-          <t>7.23</t>
+          <t>15.59</t>
         </is>
       </c>
       <c r="K16" t="inlineStr">
@@ -7003,7 +7003,7 @@
       </c>
       <c r="W16" t="inlineStr">
         <is>
-          <t>-14.81</t>
+          <t>-15.67</t>
         </is>
       </c>
       <c r="X16" t="inlineStr">
@@ -7013,17 +7013,17 @@
       </c>
       <c r="Y16" t="inlineStr">
         <is>
-          <t>2025-11-27</t>
+          <t>2025-11-28</t>
         </is>
       </c>
       <c r="Z16" t="inlineStr">
         <is>
-          <t>5.30</t>
+          <t>4.92</t>
         </is>
       </c>
       <c r="AA16" t="inlineStr">
         <is>
-          <t>2.20</t>
+          <t>-0.79</t>
         </is>
       </c>
       <c r="AB16" t="inlineStr">
@@ -7034,73 +7034,73 @@
       <c r="AC16" t="inlineStr"/>
       <c r="AD16" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE16" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF16" t="inlineStr">
         <is>
-          <t>14.89</t>
+          <t>5.62</t>
         </is>
       </c>
       <c r="AG16" t="inlineStr">
         <is>
-          <t>4.96</t>
+          <t>6.84</t>
         </is>
       </c>
       <c r="AH16" t="inlineStr">
         <is>
-          <t>-1.38</t>
+          <t>-1.44</t>
         </is>
       </c>
       <c r="AI16" t="inlineStr">
         <is>
-          <t>-11.64</t>
+          <t>-11.23</t>
         </is>
       </c>
       <c r="AJ16" t="inlineStr">
         <is>
-          <t>-1.57</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AK16" t="inlineStr">
         <is>
-          <t>15.94</t>
+          <t>15.39</t>
         </is>
       </c>
       <c r="AL16" t="inlineStr">
         <is>
-          <t>89.84</t>
+          <t>88.98</t>
         </is>
       </c>
       <c r="AM16" t="n">
-        <v>101.68</v>
+        <v>100.24</v>
       </c>
       <c r="AN16" t="n">
-        <v>103.29</v>
+        <v>103.28</v>
       </c>
       <c r="AO16" t="inlineStr">
         <is>
-          <t>89.09</t>
+          <t>89.51</t>
         </is>
       </c>
       <c r="AP16" t="inlineStr">
         <is>
-          <t>-80.19</t>
+          <t>-60.15</t>
         </is>
       </c>
       <c r="AQ16" t="inlineStr">
         <is>
-          <t>-4.71</t>
+          <t>-4.93</t>
         </is>
       </c>
       <c r="AR16" t="inlineStr">
         <is>
-          <t>-2.61</t>
+          <t>-3.08</t>
         </is>
       </c>
       <c r="AS16" t="inlineStr">
@@ -7110,7 +7110,7 @@
       </c>
       <c r="AT16" t="inlineStr">
         <is>
-          <t>-126.36</t>
+          <t>-131.02</t>
         </is>
       </c>
       <c r="AU16" t="inlineStr">
@@ -7120,43 +7120,43 @@
       </c>
       <c r="AV16" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW16" t="inlineStr">
         <is>
-          <t>1543850905.0</t>
+          <t>1429040476.0</t>
         </is>
       </c>
       <c r="AX16" t="n">
-        <v>4691522022.2</v>
+        <v>4370895798.6</v>
       </c>
       <c r="AY16" t="inlineStr">
         <is>
-          <t>4375018215.4</t>
+          <t>3781268811.0</t>
         </is>
       </c>
       <c r="AZ16" t="n">
-        <v>6753332147.84</v>
+        <v>6680203633.36</v>
       </c>
       <c r="BA16" t="inlineStr">
         <is>
-          <t>316503806</t>
+          <t>589626987</t>
         </is>
       </c>
       <c r="BB16" t="inlineStr">
         <is>
-          <t>-299279231.5113254</t>
+          <t>-322891705.6562934</t>
         </is>
       </c>
       <c r="BC16" t="inlineStr">
         <is>
-          <t>-297861176.0995588</t>
+          <t>-452760313.4536171</t>
         </is>
       </c>
       <c r="BD16" t="inlineStr">
         <is>
-          <t>1543850905.0</t>
+          <t>1429040476.0</t>
         </is>
       </c>
       <c r="BE16" t="inlineStr">
@@ -7176,7 +7176,7 @@
       </c>
       <c r="BH16" t="inlineStr">
         <is>
-          <t>60.22</t>
+          <t>58.59</t>
         </is>
       </c>
       <c r="BI16" t="inlineStr">
@@ -7201,7 +7201,7 @@
       </c>
       <c r="BM16" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN16" t="inlineStr">
@@ -7221,22 +7221,22 @@
       </c>
       <c r="BQ16" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR16" t="inlineStr">
         <is>
-          <t>價-量縮</t>
+          <t>價漲量縮</t>
         </is>
       </c>
       <c r="BS16" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.34</t>
         </is>
       </c>
       <c r="BT16" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU16" t="inlineStr">
@@ -7246,7 +7246,7 @@
       </c>
       <c r="BV16" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW16" t="inlineStr">
@@ -7261,12 +7261,12 @@
       </c>
       <c r="BY16" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ16" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA16" t="inlineStr">
@@ -7286,22 +7286,22 @@
       </c>
       <c r="CD16" t="inlineStr">
         <is>
-          <t>87.5</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CE16" t="inlineStr">
         <is>
-          <t>88.7</t>
+          <t>89.0</t>
         </is>
       </c>
       <c r="CF16" t="inlineStr">
         <is>
-          <t>86.6</t>
+          <t>87.1</t>
         </is>
       </c>
       <c r="CG16" t="inlineStr">
         <is>
-          <t>88.6</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="CH16" t="inlineStr">
@@ -7333,12 +7333,12 @@
       </c>
       <c r="C17" t="inlineStr">
         <is>
-          <t>-1.46</t>
+          <t>1.6</t>
         </is>
       </c>
       <c r="D17" t="inlineStr">
         <is>
-          <t>30647.12</t>
+          <t>17538.055</t>
         </is>
       </c>
       <c r="E17" t="inlineStr">
@@ -7348,7 +7348,7 @@
       </c>
       <c r="F17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="G17" t="inlineStr">
@@ -7358,17 +7358,17 @@
       </c>
       <c r="H17" t="inlineStr">
         <is>
-          <t>-0.69</t>
+          <t>-1.84</t>
         </is>
       </c>
       <c r="I17" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J17" t="inlineStr">
         <is>
-          <t>5.79</t>
+          <t>7.23</t>
         </is>
       </c>
       <c r="K17" t="inlineStr">
@@ -7433,7 +7433,7 @@
       </c>
       <c r="W17" t="inlineStr">
         <is>
-          <t>-16.15</t>
+          <t>-14.81</t>
         </is>
       </c>
       <c r="X17" t="inlineStr">
@@ -7443,17 +7443,17 @@
       </c>
       <c r="Y17" t="inlineStr">
         <is>
-          <t>2025-11-26</t>
+          <t>2025-11-27</t>
         </is>
       </c>
       <c r="Z17" t="inlineStr">
         <is>
-          <t>9.26</t>
+          <t>5.30</t>
         </is>
       </c>
       <c r="AA17" t="inlineStr">
         <is>
-          <t>-1.72</t>
+          <t>2.20</t>
         </is>
       </c>
       <c r="AB17" t="inlineStr">
@@ -7464,73 +7464,73 @@
       <c r="AC17" t="inlineStr"/>
       <c r="AD17" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE17" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF17" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>14.89</t>
         </is>
       </c>
       <c r="AG17" t="inlineStr">
         <is>
-          <t>1.62</t>
+          <t>4.96</t>
         </is>
       </c>
       <c r="AH17" t="inlineStr">
         <is>
-          <t>-4.53</t>
+          <t>-1.38</t>
         </is>
       </c>
       <c r="AI17" t="inlineStr">
         <is>
-          <t>-11.38</t>
+          <t>-11.64</t>
         </is>
       </c>
       <c r="AJ17" t="inlineStr">
         <is>
-          <t>-0.23</t>
+          <t>-1.57</t>
         </is>
       </c>
       <c r="AK17" t="inlineStr">
         <is>
-          <t>16.49</t>
+          <t>15.94</t>
         </is>
       </c>
       <c r="AL17" t="inlineStr">
         <is>
-          <t>91.34</t>
+          <t>89.84</t>
         </is>
       </c>
       <c r="AM17" t="n">
-        <v>103.07</v>
+        <v>101.68</v>
       </c>
       <c r="AN17" t="n">
-        <v>103.31</v>
+        <v>103.29</v>
       </c>
       <c r="AO17" t="inlineStr">
         <is>
-          <t>88.68</t>
+          <t>89.09</t>
         </is>
       </c>
       <c r="AP17" t="inlineStr">
         <is>
-          <t>-113.22</t>
+          <t>-80.19</t>
         </is>
       </c>
       <c r="AQ17" t="inlineStr">
         <is>
-          <t>-4.46</t>
+          <t>-4.71</t>
         </is>
       </c>
       <c r="AR17" t="inlineStr">
         <is>
-          <t>-2.09</t>
+          <t>-2.61</t>
         </is>
       </c>
       <c r="AS17" t="inlineStr">
@@ -7540,7 +7540,7 @@
       </c>
       <c r="AT17" t="inlineStr">
         <is>
-          <t>-121.07</t>
+          <t>-126.36</t>
         </is>
       </c>
       <c r="AU17" t="inlineStr">
@@ -7550,43 +7550,43 @@
       </c>
       <c r="AV17" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW17" t="inlineStr">
         <is>
-          <t>2683545818.0</t>
+          <t>1543850905.0</t>
         </is>
       </c>
       <c r="AX17" t="n">
-        <v>5000685349.4</v>
+        <v>4691522022.2</v>
       </c>
       <c r="AY17" t="inlineStr">
         <is>
-          <t>4727097624.7</t>
+          <t>4375018215.4</t>
         </is>
       </c>
       <c r="AZ17" t="n">
-        <v>6863428946.3</v>
+        <v>6753332147.84</v>
       </c>
       <c r="BA17" t="inlineStr">
         <is>
-          <t>273587724</t>
+          <t>316503806</t>
         </is>
       </c>
       <c r="BB17" t="inlineStr">
         <is>
-          <t>-299537059.7680103</t>
+          <t>-299279231.5113254</t>
         </is>
       </c>
       <c r="BC17" t="inlineStr">
         <is>
-          <t>-78239912.41163445</t>
+          <t>-297861176.0995588</t>
         </is>
       </c>
       <c r="BD17" t="inlineStr">
         <is>
-          <t>2683545818.0</t>
+          <t>1543850905.0</t>
         </is>
       </c>
       <c r="BE17" t="inlineStr">
@@ -7606,7 +7606,7 @@
       </c>
       <c r="BH17" t="inlineStr">
         <is>
-          <t>57.69</t>
+          <t>60.22</t>
         </is>
       </c>
       <c r="BI17" t="inlineStr">
@@ -7631,7 +7631,7 @@
       </c>
       <c r="BM17" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN17" t="inlineStr">
@@ -7651,22 +7651,22 @@
       </c>
       <c r="BQ17" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR17" t="inlineStr">
         <is>
-          <t>價漲量-</t>
+          <t>價-量縮</t>
         </is>
       </c>
       <c r="BS17" t="inlineStr">
         <is>
-          <t>2.33</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT17" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU17" t="inlineStr">
@@ -7676,7 +7676,7 @@
       </c>
       <c r="BV17" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW17" t="inlineStr">
@@ -7691,12 +7691,12 @@
       </c>
       <c r="BY17" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ17" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA17" t="inlineStr">
@@ -7716,22 +7716,22 @@
       </c>
       <c r="CD17" t="inlineStr">
         <is>
-          <t>88.9</t>
+          <t>87.5</t>
         </is>
       </c>
       <c r="CE17" t="inlineStr">
         <is>
-          <t>89.2</t>
+          <t>88.7</t>
         </is>
       </c>
       <c r="CF17" t="inlineStr">
         <is>
-          <t>86.7</t>
+          <t>86.6</t>
         </is>
       </c>
       <c r="CG17" t="inlineStr">
         <is>
-          <t>87.2</t>
+          <t>88.6</t>
         </is>
       </c>
       <c r="CH17" t="inlineStr">
@@ -7753,7 +7753,7 @@
     <row r="18">
       <c r="A18" t="inlineStr">
         <is>
-          <t>【c】</t>
+          <t>【e】</t>
         </is>
       </c>
       <c r="B18" t="inlineStr">
@@ -7763,12 +7763,12 @@
       </c>
       <c r="C18" t="inlineStr">
         <is>
-          <t>-4.63</t>
+          <t>-1.46</t>
         </is>
       </c>
       <c r="D18" t="inlineStr">
         <is>
-          <t>52066.846</t>
+          <t>30647.12</t>
         </is>
       </c>
       <c r="E18" t="inlineStr">
@@ -7778,7 +7778,7 @@
       </c>
       <c r="F18" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="G18" t="inlineStr">
@@ -7788,17 +7788,17 @@
       </c>
       <c r="H18" t="inlineStr">
         <is>
-          <t>-2.19</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="I18" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J18" t="inlineStr">
         <is>
-          <t>9.19</t>
+          <t>5.79</t>
         </is>
       </c>
       <c r="K18" t="inlineStr">
@@ -7863,7 +7863,7 @@
       </c>
       <c r="W18" t="inlineStr">
         <is>
-          <t>-14.90</t>
+          <t>-16.15</t>
         </is>
       </c>
       <c r="X18" t="inlineStr">
@@ -7873,17 +7873,17 @@
       </c>
       <c r="Y18" t="inlineStr">
         <is>
-          <t>2025-11-25</t>
+          <t>2025-11-26</t>
         </is>
       </c>
       <c r="Z18" t="inlineStr">
         <is>
-          <t>15.73</t>
+          <t>9.26</t>
         </is>
       </c>
       <c r="AA18" t="inlineStr">
         <is>
-          <t>-6.32</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="AB18" t="inlineStr">
@@ -7894,12 +7894,12 @@
       <c r="AC18" t="inlineStr"/>
       <c r="AD18" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE18" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF18" t="inlineStr">
@@ -7914,53 +7914,53 @@
       </c>
       <c r="AH18" t="inlineStr">
         <is>
-          <t>-4.32</t>
+          <t>-4.53</t>
         </is>
       </c>
       <c r="AI18" t="inlineStr">
         <is>
-          <t>-11.43</t>
+          <t>-11.38</t>
         </is>
       </c>
       <c r="AJ18" t="inlineStr">
         <is>
-          <t>0.98</t>
+          <t>-0.23</t>
         </is>
       </c>
       <c r="AK18" t="inlineStr">
         <is>
-          <t>17.22</t>
+          <t>16.49</t>
         </is>
       </c>
       <c r="AL18" t="inlineStr">
         <is>
-          <t>92.5</t>
+          <t>91.34</t>
         </is>
       </c>
       <c r="AM18" t="n">
-        <v>104.44</v>
+        <v>103.07</v>
       </c>
       <c r="AN18" t="n">
-        <v>103.43</v>
+        <v>103.31</v>
       </c>
       <c r="AO18" t="inlineStr">
         <is>
-          <t>88.23</t>
+          <t>88.68</t>
         </is>
       </c>
       <c r="AP18" t="inlineStr">
         <is>
-          <t>-161.95</t>
+          <t>-113.22</t>
         </is>
       </c>
       <c r="AQ18" t="inlineStr">
         <is>
-          <t>-3.93</t>
+          <t>-4.46</t>
         </is>
       </c>
       <c r="AR18" t="inlineStr">
         <is>
-          <t>-1.50</t>
+          <t>-2.09</t>
         </is>
       </c>
       <c r="AS18" t="inlineStr">
@@ -7970,7 +7970,7 @@
       </c>
       <c r="AT18" t="inlineStr">
         <is>
-          <t>-115.11</t>
+          <t>-121.07</t>
         </is>
       </c>
       <c r="AU18" t="inlineStr">
@@ -7980,43 +7980,43 @@
       </c>
       <c r="AV18" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW18" t="inlineStr">
         <is>
-          <t>4682266073.0</t>
+          <t>2683545818.0</t>
         </is>
       </c>
       <c r="AX18" t="n">
-        <v>5019578044.4</v>
+        <v>5000685349.4</v>
       </c>
       <c r="AY18" t="inlineStr">
         <is>
-          <t>4597307742.4</t>
+          <t>4727097624.7</t>
         </is>
       </c>
       <c r="AZ18" t="n">
-        <v>7180754379.14</v>
+        <v>6863428946.3</v>
       </c>
       <c r="BA18" t="inlineStr">
         <is>
-          <t>422270302</t>
+          <t>273587724</t>
         </is>
       </c>
       <c r="BB18" t="inlineStr">
         <is>
-          <t>-339772904.7418968</t>
+          <t>-299537059.7680103</t>
         </is>
       </c>
       <c r="BC18" t="inlineStr">
         <is>
-          <t>116188863.3358154</t>
+          <t>-78239912.41163445</t>
         </is>
       </c>
       <c r="BD18" t="inlineStr">
         <is>
-          <t>4682266073.0</t>
+          <t>2683545818.0</t>
         </is>
       </c>
       <c r="BE18" t="inlineStr">
@@ -8036,7 +8036,7 @@
       </c>
       <c r="BH18" t="inlineStr">
         <is>
-          <t>60.04</t>
+          <t>57.69</t>
         </is>
       </c>
       <c r="BI18" t="inlineStr">
@@ -8061,7 +8061,7 @@
       </c>
       <c r="BM18" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN18" t="inlineStr">
@@ -8081,22 +8081,22 @@
       </c>
       <c r="BQ18" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;空頭排列&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
         </is>
       </c>
       <c r="BR18" t="inlineStr">
         <is>
-          <t>價跌量增</t>
+          <t>價漲量-</t>
         </is>
       </c>
       <c r="BS18" t="inlineStr">
         <is>
-          <t>2.37</t>
+          <t>2.33</t>
         </is>
       </c>
       <c r="BT18" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU18" t="inlineStr">
@@ -8106,7 +8106,7 @@
       </c>
       <c r="BV18" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW18" t="inlineStr">
@@ -8121,12 +8121,12 @@
       </c>
       <c r="BY18" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ18" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA18" t="inlineStr">
@@ -8146,22 +8146,22 @@
       </c>
       <c r="CD18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>88.9</t>
         </is>
       </c>
       <c r="CE18" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>89.2</t>
         </is>
       </c>
       <c r="CF18" t="inlineStr">
         <is>
-          <t>87.6</t>
+          <t>86.7</t>
         </is>
       </c>
       <c r="CG18" t="inlineStr">
         <is>
-          <t>88.5</t>
+          <t>87.2</t>
         </is>
       </c>
       <c r="CH18" t="inlineStr">
@@ -8193,12 +8193,12 @@
       </c>
       <c r="C19" t="inlineStr">
         <is>
-          <t>0.96</t>
+          <t>-4.63</t>
         </is>
       </c>
       <c r="D19" t="inlineStr">
         <is>
-          <t>124181.065</t>
+          <t>52066.846</t>
         </is>
       </c>
       <c r="E19" t="inlineStr">
@@ -8208,7 +8208,7 @@
       </c>
       <c r="F19" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="G19" t="inlineStr">
@@ -8218,17 +8218,17 @@
       </c>
       <c r="H19" t="inlineStr">
         <is>
-          <t>-7.27</t>
+          <t>-1.72</t>
         </is>
       </c>
       <c r="I19" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J19" t="inlineStr">
         <is>
-          <t>8.20</t>
+          <t>9.19</t>
         </is>
       </c>
       <c r="K19" t="inlineStr">
@@ -8293,7 +8293,7 @@
       </c>
       <c r="W19" t="inlineStr">
         <is>
-          <t>-10.67</t>
+          <t>-14.90</t>
         </is>
       </c>
       <c r="X19" t="inlineStr">
@@ -8303,17 +8303,17 @@
       </c>
       <c r="Y19" t="inlineStr">
         <is>
-          <t>2025-11-24</t>
+          <t>2025-11-25</t>
         </is>
       </c>
       <c r="Z19" t="inlineStr">
         <is>
-          <t>37.51</t>
+          <t>15.73</t>
         </is>
       </c>
       <c r="AA19" t="inlineStr">
         <is>
-          <t>0.90</t>
+          <t>-6.32</t>
         </is>
       </c>
       <c r="AB19" t="inlineStr">
@@ -8324,73 +8324,73 @@
       <c r="AC19" t="inlineStr"/>
       <c r="AD19" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE19" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF19" t="inlineStr">
         <is>
-          <t>4.86</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG19" t="inlineStr">
         <is>
-          <t>7.53</t>
+          <t>1.62</t>
         </is>
       </c>
       <c r="AH19" t="inlineStr">
         <is>
-          <t>-0.71</t>
+          <t>-4.32</t>
         </is>
       </c>
       <c r="AI19" t="inlineStr">
         <is>
-          <t>-11.58</t>
+          <t>-11.43</t>
         </is>
       </c>
       <c r="AJ19" t="inlineStr">
         <is>
-          <t>2.32</t>
+          <t>0.98</t>
         </is>
       </c>
       <c r="AK19" t="inlineStr">
         <is>
-          <t>17.91</t>
+          <t>17.22</t>
         </is>
       </c>
       <c r="AL19" t="inlineStr">
         <is>
-          <t>93.56</t>
+          <t>92.5</t>
         </is>
       </c>
       <c r="AM19" t="n">
-        <v>105.81</v>
+        <v>104.44</v>
       </c>
       <c r="AN19" t="n">
-        <v>103.41</v>
+        <v>103.43</v>
       </c>
       <c r="AO19" t="inlineStr">
         <is>
-          <t>87.7</t>
+          <t>88.23</t>
         </is>
       </c>
       <c r="AP19" t="inlineStr">
         <is>
-          <t>-272.55</t>
+          <t>-161.95</t>
         </is>
       </c>
       <c r="AQ19" t="inlineStr">
         <is>
-          <t>-3.32</t>
+          <t>-3.93</t>
         </is>
       </c>
       <c r="AR19" t="inlineStr">
         <is>
-          <t>-0.89</t>
+          <t>-1.50</t>
         </is>
       </c>
       <c r="AS19" t="inlineStr">
@@ -8400,7 +8400,7 @@
       </c>
       <c r="AT19" t="inlineStr">
         <is>
-          <t>-108.99</t>
+          <t>-115.11</t>
         </is>
       </c>
       <c r="AU19" t="inlineStr">
@@ -8410,43 +8410,43 @@
       </c>
       <c r="AV19" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW19" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="AX19" t="n">
-        <v>4696916791.4</v>
+        <v>5019578044.4</v>
       </c>
       <c r="AY19" t="inlineStr">
         <is>
-          <t>4341077616.0</t>
+          <t>4597307742.4</t>
         </is>
       </c>
       <c r="AZ19" t="n">
-        <v>7241408797.74</v>
+        <v>7180754379.14</v>
       </c>
       <c r="BA19" t="inlineStr">
         <is>
-          <t>355839175</t>
+          <t>422270302</t>
         </is>
       </c>
       <c r="BB19" t="inlineStr">
         <is>
-          <t>-422675044.3923899</t>
+          <t>-339772904.7418968</t>
         </is>
       </c>
       <c r="BC19" t="inlineStr">
         <is>
-          <t>175646056.2487507</t>
+          <t>116188863.3358154</t>
         </is>
       </c>
       <c r="BD19" t="inlineStr">
         <is>
-          <t>11515775721.0</t>
+          <t>4682266073.0</t>
         </is>
       </c>
       <c r="BE19" t="inlineStr">
@@ -8466,7 +8466,7 @@
       </c>
       <c r="BH19" t="inlineStr">
         <is>
-          <t>67.99</t>
+          <t>60.04</t>
         </is>
       </c>
       <c r="BI19" t="inlineStr">
@@ -8491,7 +8491,7 @@
       </c>
       <c r="BM19" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN19" t="inlineStr">
@@ -8511,22 +8511,22 @@
       </c>
       <c r="BQ19" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR19" t="inlineStr">
         <is>
-          <t>價-量增</t>
+          <t>價跌量增</t>
         </is>
       </c>
       <c r="BS19" t="inlineStr">
         <is>
-          <t>2.48</t>
+          <t>2.37</t>
         </is>
       </c>
       <c r="BT19" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU19" t="inlineStr">
@@ -8536,7 +8536,7 @@
       </c>
       <c r="BV19" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW19" t="inlineStr">
@@ -8551,12 +8551,12 @@
       </c>
       <c r="BY19" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ19" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA19" t="inlineStr">
@@ -8576,22 +8576,22 @@
       </c>
       <c r="CD19" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CE19" t="inlineStr">
         <is>
-          <t>94.0</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF19" t="inlineStr">
         <is>
-          <t>91.0</t>
+          <t>87.6</t>
         </is>
       </c>
       <c r="CG19" t="inlineStr">
         <is>
-          <t>92.9</t>
+          <t>88.5</t>
         </is>
       </c>
       <c r="CH19" t="inlineStr">
@@ -8623,12 +8623,12 @@
       </c>
       <c r="C20" t="inlineStr">
         <is>
-          <t>-4.38</t>
+          <t>0.96</t>
         </is>
       </c>
       <c r="D20" t="inlineStr">
         <is>
-          <t>32684.421</t>
+          <t>124181.065</t>
         </is>
       </c>
       <c r="E20" t="inlineStr">
@@ -8638,7 +8638,7 @@
       </c>
       <c r="F20" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="G20" t="inlineStr">
@@ -8648,17 +8648,17 @@
       </c>
       <c r="H20" t="inlineStr">
         <is>
-          <t>-6.24</t>
+          <t>-6.78</t>
         </is>
       </c>
       <c r="I20" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J20" t="inlineStr">
         <is>
-          <t>-9.52</t>
+          <t>8.20</t>
         </is>
       </c>
       <c r="K20" t="inlineStr">
@@ -8723,7 +8723,7 @@
       </c>
       <c r="W20" t="inlineStr">
         <is>
-          <t>-11.54</t>
+          <t>-10.67</t>
         </is>
       </c>
       <c r="X20" t="inlineStr">
@@ -8733,17 +8733,17 @@
       </c>
       <c r="Y20" t="inlineStr">
         <is>
-          <t>2025-11-21</t>
+          <t>2025-11-24</t>
         </is>
       </c>
       <c r="Z20" t="inlineStr">
         <is>
-          <t>9.87</t>
+          <t>37.51</t>
         </is>
       </c>
       <c r="AA20" t="inlineStr">
         <is>
-          <t>-2.82</t>
+          <t>0.90</t>
         </is>
       </c>
       <c r="AB20" t="inlineStr">
@@ -8754,73 +8754,73 @@
       <c r="AC20" t="inlineStr"/>
       <c r="AD20" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE20" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF20" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>4.86</t>
         </is>
       </c>
       <c r="AG20" t="inlineStr">
         <is>
-          <t>5.9</t>
+          <t>7.53</t>
         </is>
       </c>
       <c r="AH20" t="inlineStr">
         <is>
-          <t>-2.44</t>
+          <t>-0.71</t>
         </is>
       </c>
       <c r="AI20" t="inlineStr">
         <is>
-          <t>-11.80</t>
+          <t>-11.58</t>
         </is>
       </c>
       <c r="AJ20" t="inlineStr">
         <is>
-          <t>3.66</t>
+          <t>2.32</t>
         </is>
       </c>
       <c r="AK20" t="inlineStr">
         <is>
-          <t>18.39</t>
+          <t>17.91</t>
         </is>
       </c>
       <c r="AL20" t="inlineStr">
         <is>
-          <t>94.3</t>
+          <t>93.56</t>
         </is>
       </c>
       <c r="AM20" t="n">
-        <v>106.92</v>
+        <v>105.81</v>
       </c>
       <c r="AN20" t="n">
-        <v>103.14</v>
+        <v>103.41</v>
       </c>
       <c r="AO20" t="inlineStr">
         <is>
-          <t>87.12</t>
+          <t>87.7</t>
         </is>
       </c>
       <c r="AP20" t="inlineStr">
         <is>
-          <t>-939.09</t>
+          <t>-272.55</t>
         </is>
       </c>
       <c r="AQ20" t="inlineStr">
         <is>
-          <t>-2.95</t>
+          <t>-3.32</t>
         </is>
       </c>
       <c r="AR20" t="inlineStr">
         <is>
-          <t>-0.28</t>
+          <t>-0.89</t>
         </is>
       </c>
       <c r="AS20" t="inlineStr">
@@ -8830,7 +8830,7 @@
       </c>
       <c r="AT20" t="inlineStr">
         <is>
-          <t>-102.86</t>
+          <t>-108.99</t>
         </is>
       </c>
       <c r="AU20" t="inlineStr">
@@ -8840,43 +8840,43 @@
       </c>
       <c r="AV20" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW20" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="AX20" t="n">
-        <v>3191641823.4</v>
+        <v>4696916791.4</v>
       </c>
       <c r="AY20" t="inlineStr">
         <is>
-          <t>3527299622.7</t>
+          <t>4341077616.0</t>
         </is>
       </c>
       <c r="AZ20" t="n">
-        <v>7285669264.58</v>
+        <v>7241408797.74</v>
       </c>
       <c r="BA20" t="inlineStr">
         <is>
-          <t>-335657799</t>
+          <t>355839175</t>
         </is>
       </c>
       <c r="BB20" t="inlineStr">
         <is>
-          <t>-531460699.0544155</t>
+          <t>-422675044.3923899</t>
         </is>
       </c>
       <c r="BC20" t="inlineStr">
         <is>
-          <t>-477849918.1702256</t>
+          <t>175646056.2487507</t>
         </is>
       </c>
       <c r="BD20" t="inlineStr">
         <is>
-          <t>3032171594.0</t>
+          <t>11515775721.0</t>
         </is>
       </c>
       <c r="BE20" t="inlineStr">
@@ -8896,7 +8896,7 @@
       </c>
       <c r="BH20" t="inlineStr">
         <is>
-          <t>66.37</t>
+          <t>67.99</t>
         </is>
       </c>
       <c r="BI20" t="inlineStr">
@@ -8921,7 +8921,7 @@
       </c>
       <c r="BM20" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN20" t="inlineStr">
@@ -8941,22 +8941,22 @@
       </c>
       <c r="BQ20" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚,爆量上攻&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;下影大於實體兩倍&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR20" t="inlineStr">
         <is>
-          <t>價-量-</t>
+          <t>價-量增</t>
         </is>
       </c>
       <c r="BS20" t="inlineStr">
         <is>
-          <t>2.46</t>
+          <t>2.48</t>
         </is>
       </c>
       <c r="BT20" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU20" t="inlineStr">
@@ -8966,7 +8966,7 @@
       </c>
       <c r="BV20" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW20" t="inlineStr">
@@ -8981,12 +8981,12 @@
       </c>
       <c r="BY20" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ20" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA20" t="inlineStr">
@@ -9006,22 +9006,22 @@
       </c>
       <c r="CD20" t="inlineStr">
         <is>
-          <t>93.6</t>
+          <t>93.8</t>
         </is>
       </c>
       <c r="CE20" t="inlineStr">
         <is>
-          <t>95.0</t>
+          <t>94.0</t>
         </is>
       </c>
       <c r="CF20" t="inlineStr">
         <is>
-          <t>91.6</t>
+          <t>91.0</t>
         </is>
       </c>
       <c r="CG20" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>92.9</t>
         </is>
       </c>
       <c r="CH20" t="inlineStr">
@@ -9053,12 +9053,12 @@
       </c>
       <c r="C21" t="inlineStr">
         <is>
-          <t>3.2</t>
+          <t>-4.38</t>
         </is>
       </c>
       <c r="D21" t="inlineStr">
         <is>
-          <t>31967.753</t>
+          <t>32684.421</t>
         </is>
       </c>
       <c r="E21" t="inlineStr">
@@ -9068,7 +9068,7 @@
       </c>
       <c r="F21" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="G21" t="inlineStr">
@@ -9078,17 +9078,17 @@
       </c>
       <c r="H21" t="inlineStr">
         <is>
-          <t>-10.97</t>
+          <t>-5.75</t>
         </is>
       </c>
       <c r="I21" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J21" t="inlineStr">
         <is>
-          <t>14.94</t>
+          <t>-9.52</t>
         </is>
       </c>
       <c r="K21" t="inlineStr">
@@ -9153,7 +9153,7 @@
       </c>
       <c r="W21" t="inlineStr">
         <is>
-          <t>-7.60</t>
+          <t>-11.54</t>
         </is>
       </c>
       <c r="X21" t="inlineStr">
@@ -9163,17 +9163,17 @@
       </c>
       <c r="Y21" t="inlineStr">
         <is>
-          <t>2025-11-20</t>
+          <t>2025-11-21</t>
         </is>
       </c>
       <c r="Z21" t="inlineStr">
         <is>
-          <t>9.66</t>
+          <t>9.87</t>
         </is>
       </c>
       <c r="AA21" t="inlineStr">
         <is>
-          <t>-1.12</t>
+          <t>-2.82</t>
         </is>
       </c>
       <c r="AB21" t="inlineStr">
@@ -9184,17 +9184,17 @@
       <c r="AC21" t="inlineStr"/>
       <c r="AD21" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE21" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF21" t="inlineStr">
         <is>
-          <t>17.71</t>
+          <t>0.0</t>
         </is>
       </c>
       <c r="AG21" t="inlineStr">
@@ -9204,53 +9204,53 @@
       </c>
       <c r="AH21" t="inlineStr">
         <is>
-          <t>0.25</t>
+          <t>-2.44</t>
         </is>
       </c>
       <c r="AI21" t="inlineStr">
         <is>
-          <t>-11.25</t>
+          <t>-11.80</t>
         </is>
       </c>
       <c r="AJ21" t="inlineStr">
         <is>
-          <t>5.13</t>
+          <t>3.66</t>
         </is>
       </c>
       <c r="AK21" t="inlineStr">
         <is>
-          <t>18.72</t>
+          <t>18.39</t>
         </is>
       </c>
       <c r="AL21" t="inlineStr">
         <is>
-          <t>95.85999999999999</t>
+          <t>94.3</t>
         </is>
       </c>
       <c r="AM21" t="n">
-        <v>108.02</v>
+        <v>106.92</v>
       </c>
       <c r="AN21" t="n">
-        <v>102.75</v>
+        <v>103.14</v>
       </c>
       <c r="AO21" t="inlineStr">
         <is>
-          <t>86.55</t>
+          <t>87.12</t>
         </is>
       </c>
       <c r="AP21" t="inlineStr">
         <is>
-          <t>-712.58</t>
+          <t>-939.09</t>
         </is>
       </c>
       <c r="AQ21" t="inlineStr">
         <is>
-          <t>-2.35</t>
+          <t>-2.95</t>
         </is>
       </c>
       <c r="AR21" t="inlineStr">
         <is>
-          <t>0.38</t>
+          <t>-0.28</t>
         </is>
       </c>
       <c r="AS21" t="inlineStr">
@@ -9260,7 +9260,7 @@
       </c>
       <c r="AT21" t="inlineStr">
         <is>
-          <t>-96.14</t>
+          <t>-102.86</t>
         </is>
       </c>
       <c r="AU21" t="inlineStr">
@@ -9270,43 +9270,43 @@
       </c>
       <c r="AV21" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW21" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="AX21" t="n">
-        <v>4058514408.6</v>
+        <v>3191641823.4</v>
       </c>
       <c r="AY21" t="inlineStr">
         <is>
-          <t>3531039856.9</t>
+          <t>3527299622.7</t>
         </is>
       </c>
       <c r="AZ21" t="n">
-        <v>7317342463.3</v>
+        <v>7285669264.58</v>
       </c>
       <c r="BA21" t="inlineStr">
         <is>
-          <t>527474551</t>
+          <t>-335657799</t>
         </is>
       </c>
       <c r="BB21" t="inlineStr">
         <is>
-          <t>-541208113.7606318</t>
+          <t>-531460699.0544155</t>
         </is>
       </c>
       <c r="BC21" t="inlineStr">
         <is>
-          <t>-485391942.3698263</t>
+          <t>-477849918.1702256</t>
         </is>
       </c>
       <c r="BD21" t="inlineStr">
         <is>
-          <t>3089667541.0</t>
+          <t>3032171594.0</t>
         </is>
       </c>
       <c r="BE21" t="inlineStr">
@@ -9326,7 +9326,7 @@
       </c>
       <c r="BH21" t="inlineStr">
         <is>
-          <t>73.78</t>
+          <t>66.37</t>
         </is>
       </c>
       <c r="BI21" t="inlineStr">
@@ -9351,7 +9351,7 @@
       </c>
       <c r="BM21" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN21" t="inlineStr">
@@ -9371,7 +9371,7 @@
       </c>
       <c r="BQ21" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;中性&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR21" t="inlineStr">
@@ -9381,12 +9381,12 @@
       </c>
       <c r="BS21" t="inlineStr">
         <is>
-          <t>2.57</t>
+          <t>2.46</t>
         </is>
       </c>
       <c r="BT21" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU21" t="inlineStr">
@@ -9396,7 +9396,7 @@
       </c>
       <c r="BV21" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW21" t="inlineStr">
@@ -9411,12 +9411,12 @@
       </c>
       <c r="BY21" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ21" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA21" t="inlineStr">
@@ -9436,22 +9436,22 @@
       </c>
       <c r="CD21" t="inlineStr">
         <is>
-          <t>96.9</t>
+          <t>93.6</t>
         </is>
       </c>
       <c r="CE21" t="inlineStr">
         <is>
-          <t>98.8</t>
+          <t>95.0</t>
         </is>
       </c>
       <c r="CF21" t="inlineStr">
         <is>
-          <t>94.5</t>
+          <t>91.6</t>
         </is>
       </c>
       <c r="CG21" t="inlineStr">
         <is>
-          <t>96.1</t>
+          <t>92.0</t>
         </is>
       </c>
       <c r="CH21" t="inlineStr">
@@ -9483,12 +9483,12 @@
       </c>
       <c r="C22" t="inlineStr">
         <is>
-          <t>-0.85</t>
+          <t>3.2</t>
         </is>
       </c>
       <c r="D22" t="inlineStr">
         <is>
-          <t>29839.894</t>
+          <t>31967.753</t>
         </is>
       </c>
       <c r="E22" t="inlineStr">
@@ -9498,7 +9498,7 @@
       </c>
       <c r="F22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="G22" t="inlineStr">
@@ -9508,17 +9508,17 @@
       </c>
       <c r="H22" t="inlineStr">
         <is>
-          <t>-7.39</t>
+          <t>-10.46</t>
         </is>
       </c>
       <c r="I22" t="inlineStr">
         <is>
-          <t>-2.68</t>
+          <t>-1.34</t>
         </is>
       </c>
       <c r="J22" t="inlineStr">
         <is>
-          <t>20.75</t>
+          <t>14.94</t>
         </is>
       </c>
       <c r="K22" t="inlineStr">
@@ -9583,7 +9583,7 @@
       </c>
       <c r="W22" t="inlineStr">
         <is>
-          <t>-10.58</t>
+          <t>-7.60</t>
         </is>
       </c>
       <c r="X22" t="inlineStr">
@@ -9593,17 +9593,17 @@
       </c>
       <c r="Y22" t="inlineStr">
         <is>
-          <t>2025-11-19</t>
+          <t>2025-11-20</t>
         </is>
       </c>
       <c r="Z22" t="inlineStr">
         <is>
-          <t>9.01</t>
+          <t>9.66</t>
         </is>
       </c>
       <c r="AA22" t="inlineStr">
         <is>
-          <t>-0.42</t>
+          <t>-1.12</t>
         </is>
       </c>
       <c r="AB22" t="inlineStr">
@@ -9614,73 +9614,73 @@
       <c r="AC22" t="inlineStr"/>
       <c r="AD22" t="inlineStr">
         <is>
-          <t>217</t>
+          <t>194</t>
         </is>
       </c>
       <c r="AE22" t="inlineStr">
         <is>
-          <t>22426</t>
+          <t>13252</t>
         </is>
       </c>
       <c r="AF22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>17.71</t>
         </is>
       </c>
       <c r="AG22" t="inlineStr">
         <is>
-          <t>0.0</t>
+          <t>5.9</t>
         </is>
       </c>
       <c r="AH22" t="inlineStr">
         <is>
-          <t>-5.81</t>
+          <t>0.25</t>
         </is>
       </c>
       <c r="AI22" t="inlineStr">
         <is>
-          <t>-9.44</t>
+          <t>-11.25</t>
         </is>
       </c>
       <c r="AJ22" t="inlineStr">
         <is>
-          <t>6.7</t>
+          <t>5.13</t>
         </is>
       </c>
       <c r="AK22" t="inlineStr">
         <is>
-          <t>18.92</t>
+          <t>18.72</t>
         </is>
       </c>
       <c r="AL22" t="inlineStr">
         <is>
-          <t>98.74</t>
+          <t>95.85999999999999</t>
         </is>
       </c>
       <c r="AM22" t="n">
-        <v>109.04</v>
+        <v>108.02</v>
       </c>
       <c r="AN22" t="n">
-        <v>102.19</v>
+        <v>102.75</v>
       </c>
       <c r="AO22" t="inlineStr">
         <is>
-          <t>85.93</t>
+          <t>86.55</t>
         </is>
       </c>
       <c r="AP22" t="inlineStr">
         <is>
-          <t>-283.53</t>
+          <t>-712.58</t>
         </is>
       </c>
       <c r="AQ22" t="inlineStr">
         <is>
-          <t>-1.95</t>
+          <t>-2.35</t>
         </is>
       </c>
       <c r="AR22" t="inlineStr">
         <is>
-          <t>1.07</t>
+          <t>0.38</t>
         </is>
       </c>
       <c r="AS22" t="inlineStr">
@@ -9690,7 +9690,7 @@
       </c>
       <c r="AT22" t="inlineStr">
         <is>
-          <t>-89.26</t>
+          <t>-96.14</t>
         </is>
       </c>
       <c r="AU22" t="inlineStr">
@@ -9700,43 +9700,43 @@
       </c>
       <c r="AV22" t="inlineStr">
         <is>
-          <t>1906700999.581197</t>
+          <t>1906458768.780939</t>
         </is>
       </c>
       <c r="AW22" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="AX22" t="n">
-        <v>4453509900</v>
+        <v>4058514408.6</v>
       </c>
       <c r="AY22" t="inlineStr">
         <is>
-          <t>3688316666.2</t>
+          <t>3531039856.9</t>
         </is>
       </c>
       <c r="AZ22" t="n">
-        <v>7280178623.2</v>
+        <v>7317342463.3</v>
       </c>
       <c r="BA22" t="inlineStr">
         <is>
-          <t>765193233</t>
+          <t>527474551</t>
         </is>
       </c>
       <c r="BB22" t="inlineStr">
         <is>
-          <t>-551356508.5589601</t>
+          <t>-541208113.7606318</t>
         </is>
       </c>
       <c r="BC22" t="inlineStr">
         <is>
-          <t>-484991116.1774759</t>
+          <t>-485391942.3698263</t>
         </is>
       </c>
       <c r="BD22" t="inlineStr">
         <is>
-          <t>2778009293.0</t>
+          <t>3089667541.0</t>
         </is>
       </c>
       <c r="BE22" t="inlineStr">
@@ -9756,7 +9756,7 @@
       </c>
       <c r="BH22" t="inlineStr">
         <is>
-          <t>68.17</t>
+          <t>73.78</t>
         </is>
       </c>
       <c r="BI22" t="inlineStr">
@@ -9781,7 +9781,7 @@
       </c>
       <c r="BM22" t="inlineStr">
         <is>
-          <t>0.76</t>
+          <t>0.77</t>
         </is>
       </c>
       <c r="BN22" t="inlineStr">
@@ -9801,7 +9801,7 @@
       </c>
       <c r="BQ22" t="inlineStr">
         <is>
-          <t>&lt;b&gt;分類：&lt;/b&gt;&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;正向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;|三隻烏鴉</t>
+          <t>&lt;b&gt;分類：&lt;/b&gt;低檔翻揚&lt;br&gt;&lt;b&gt;建議：&lt;/b&gt;&lt;br&gt;&lt;b&gt;評分：&lt;/b&gt;0&lt;br&gt;&lt;b&gt;K棒方向：&lt;/b&gt;負向&lt;br&gt;&lt;b&gt;多日K棒方向：&lt;/b&gt;&lt;br&gt;&lt;b&gt;K棒續強：&lt;/b&gt;&lt;br&gt;&lt;b&gt;多日K棒型態：&lt;/b&gt;</t>
         </is>
       </c>
       <c r="BR22" t="inlineStr">
@@ -9811,12 +9811,12 @@
       </c>
       <c r="BS22" t="inlineStr">
         <is>
-          <t>2.49</t>
+          <t>2.57</t>
         </is>
       </c>
       <c r="BT22" t="inlineStr">
         <is>
-          <t>2.54</t>
+          <t>2.53</t>
         </is>
       </c>
       <c r="BU22" t="inlineStr">
@@ -9826,7 +9826,7 @@
       </c>
       <c r="BV22" t="inlineStr">
         <is>
-          <t>37.65</t>
+          <t>37.83</t>
         </is>
       </c>
       <c r="BW22" t="inlineStr">
@@ -9841,12 +9841,12 @@
       </c>
       <c r="BY22" t="inlineStr">
         <is>
-          <t>40.94</t>
+          <t>41.31</t>
         </is>
       </c>
       <c r="BZ22" t="inlineStr">
         <is>
-          <t>205800</t>
+          <t>206750</t>
         </is>
       </c>
       <c r="CA22" t="inlineStr">
@@ -9866,22 +9866,22 @@
       </c>
       <c r="CD22" t="inlineStr">
         <is>
-          <t>93.8</t>
+          <t>96.9</t>
         </is>
       </c>
       <c r="CE22" t="inlineStr">
         <is>
-          <t>94.4</t>
+          <t>98.8</t>
         </is>
       </c>
       <c r="CF22" t="inlineStr">
         <is>
-          <t>92.0</t>
+          <t>94.5</t>
         </is>
       </c>
       <c r="CG22" t="inlineStr">
         <is>
-          <t>93.0</t>
+          <t>96.1</t>
         </is>
       </c>
       <c r="CH22" t="inlineStr">
@@ -9913,12 +9913,12 @@
       </c>
       <c r="C23" t="inlineStr">
         <is>
-          <t>-2.92</t>
+          <t>-0.85</t>
         </is>
       </c>
       <c r="D23" t="inlineStr">
         <is>
-          <t>32132.941</t>
+      